--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="108">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,90 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Costa Rican Primera Division</t>
+  </si>
+  <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
+    <t>Icelandic Urvalsdeild</t>
+  </si>
+  <si>
+    <t>2026-08-04</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>02:00:00</t>
+  </si>
+  <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>LDU</t>
+  </si>
+  <si>
+    <t>Central Cordoba (SdE)</t>
+  </si>
+  <si>
+    <t>CA Huracan</t>
+  </si>
+  <si>
+    <t>Atletico Bucaramanga</t>
+  </si>
+  <si>
+    <t>Municipal Perez Zeledon</t>
+  </si>
+  <si>
+    <t>Politehnica Timisoara</t>
+  </si>
+  <si>
+    <t>Thor</t>
+  </si>
+  <si>
+    <t>Delfin</t>
+  </si>
+  <si>
+    <t>San Lorenzo</t>
+  </si>
+  <si>
+    <t>Atl Tucuman</t>
+  </si>
+  <si>
+    <t>Cucuta Deportivo</t>
+  </si>
+  <si>
+    <t>Cs Cartagines</t>
+  </si>
+  <si>
+    <t>Chindia Targoviste</t>
+  </si>
+  <si>
+    <t>Breidablik</t>
+  </si>
+  <si>
+    <t>2026-08-02 00:38:45</t>
   </si>
 </sst>
 </file>
@@ -585,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +912,1700 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>1.29</v>
+      </c>
+      <c r="G2">
+        <v>1.36</v>
+      </c>
+      <c r="H2">
+        <v>14.5</v>
+      </c>
+      <c r="I2">
+        <v>19.5</v>
+      </c>
+      <c r="J2">
+        <v>5.2</v>
+      </c>
+      <c r="K2">
+        <v>5.9</v>
+      </c>
+      <c r="L2">
+        <v>1.31</v>
+      </c>
+      <c r="M2">
+        <v>1.06</v>
+      </c>
+      <c r="N2">
+        <v>3.6</v>
+      </c>
+      <c r="O2">
+        <v>1.31</v>
+      </c>
+      <c r="P2">
+        <v>1.9</v>
+      </c>
+      <c r="Q2">
+        <v>1.92</v>
+      </c>
+      <c r="R2">
+        <v>1.34</v>
+      </c>
+      <c r="S2">
+        <v>3.3</v>
+      </c>
+      <c r="T2">
+        <v>2.54</v>
+      </c>
+      <c r="U2">
+        <v>1.52</v>
+      </c>
+      <c r="V2">
+        <v>1.05</v>
+      </c>
+      <c r="W2">
+        <v>3.8</v>
+      </c>
+      <c r="X2">
+        <v>16</v>
+      </c>
+      <c r="Y2">
+        <v>42</v>
+      </c>
+      <c r="Z2">
+        <v>200</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>7</v>
+      </c>
+      <c r="AC2">
+        <v>13.5</v>
+      </c>
+      <c r="AD2">
+        <v>75</v>
+      </c>
+      <c r="AE2">
+        <v>510</v>
+      </c>
+      <c r="AF2">
+        <v>7</v>
+      </c>
+      <c r="AG2">
+        <v>12.5</v>
+      </c>
+      <c r="AH2">
+        <v>48</v>
+      </c>
+      <c r="AI2">
+        <v>380</v>
+      </c>
+      <c r="AJ2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK2">
+        <v>18.5</v>
+      </c>
+      <c r="AL2">
+        <v>75</v>
+      </c>
+      <c r="AM2">
+        <v>430</v>
+      </c>
+      <c r="AN2">
+        <v>7.8</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>13</v>
+      </c>
+      <c r="AQ2">
+        <v>25</v>
+      </c>
+      <c r="AR2">
+        <v>7.8</v>
+      </c>
+      <c r="AS2">
+        <v>8</v>
+      </c>
+      <c r="AT2">
+        <v>5.9</v>
+      </c>
+      <c r="AU2">
+        <v>10.5</v>
+      </c>
+      <c r="AV2">
+        <v>38</v>
+      </c>
+      <c r="AW2">
+        <v>8</v>
+      </c>
+      <c r="AX2">
+        <v>5.8</v>
+      </c>
+      <c r="AY2">
+        <v>10</v>
+      </c>
+      <c r="AZ2">
+        <v>29</v>
+      </c>
+      <c r="BA2">
+        <v>7.8</v>
+      </c>
+      <c r="BB2">
+        <v>8</v>
+      </c>
+      <c r="BC2">
+        <v>14.5</v>
+      </c>
+      <c r="BD2">
+        <v>40</v>
+      </c>
+      <c r="BE2">
+        <v>8</v>
+      </c>
+      <c r="BF2">
+        <v>5.6</v>
+      </c>
+      <c r="BG2">
+        <v>8</v>
+      </c>
+      <c r="BH2">
+        <v>3.7</v>
+      </c>
+      <c r="BI2">
+        <v>3.15</v>
+      </c>
+      <c r="BJ2">
+        <v>16</v>
+      </c>
+      <c r="BK2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>10.5</v>
+      </c>
+      <c r="BN2">
+        <v>3.5</v>
+      </c>
+      <c r="BO2">
+        <v>3</v>
+      </c>
+      <c r="BP2">
+        <v>7.8</v>
+      </c>
+      <c r="BQ2">
+        <v>4.8</v>
+      </c>
+      <c r="BR2">
+        <v>34</v>
+      </c>
+      <c r="BS2">
+        <v>8.4</v>
+      </c>
+      <c r="BT2">
+        <v>18</v>
+      </c>
+      <c r="BU2">
+        <v>6.8</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>10.5</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>10.5</v>
+      </c>
+      <c r="BZ2">
+        <v>15.5</v>
+      </c>
+      <c r="CA2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3">
+        <v>3.15</v>
+      </c>
+      <c r="G3">
+        <v>3.45</v>
+      </c>
+      <c r="H3">
+        <v>2.62</v>
+      </c>
+      <c r="I3">
+        <v>2.94</v>
+      </c>
+      <c r="J3">
+        <v>2.88</v>
+      </c>
+      <c r="K3">
+        <v>3.05</v>
+      </c>
+      <c r="L3">
+        <v>1.51</v>
+      </c>
+      <c r="M3">
+        <v>1.14</v>
+      </c>
+      <c r="N3">
+        <v>2.42</v>
+      </c>
+      <c r="O3">
+        <v>1.61</v>
+      </c>
+      <c r="P3">
+        <v>1.47</v>
+      </c>
+      <c r="Q3">
+        <v>2.86</v>
+      </c>
+      <c r="R3">
+        <v>1.15</v>
+      </c>
+      <c r="S3">
+        <v>6</v>
+      </c>
+      <c r="T3">
+        <v>2.2</v>
+      </c>
+      <c r="U3">
+        <v>1.71</v>
+      </c>
+      <c r="V3">
+        <v>1.53</v>
+      </c>
+      <c r="W3">
+        <v>1.4</v>
+      </c>
+      <c r="X3">
+        <v>8</v>
+      </c>
+      <c r="Y3">
+        <v>8</v>
+      </c>
+      <c r="Z3">
+        <v>17</v>
+      </c>
+      <c r="AA3">
+        <v>60</v>
+      </c>
+      <c r="AB3">
+        <v>9</v>
+      </c>
+      <c r="AC3">
+        <v>7.4</v>
+      </c>
+      <c r="AD3">
+        <v>14.5</v>
+      </c>
+      <c r="AE3">
+        <v>50</v>
+      </c>
+      <c r="AF3">
+        <v>22</v>
+      </c>
+      <c r="AG3">
+        <v>16</v>
+      </c>
+      <c r="AH3">
+        <v>30</v>
+      </c>
+      <c r="AI3">
+        <v>90</v>
+      </c>
+      <c r="AJ3">
+        <v>80</v>
+      </c>
+      <c r="AK3">
+        <v>65</v>
+      </c>
+      <c r="AL3">
+        <v>110</v>
+      </c>
+      <c r="AM3">
+        <v>270</v>
+      </c>
+      <c r="AN3">
+        <v>95</v>
+      </c>
+      <c r="AO3">
+        <v>65</v>
+      </c>
+      <c r="AP3">
+        <v>6.8</v>
+      </c>
+      <c r="AQ3">
+        <v>6.6</v>
+      </c>
+      <c r="AR3">
+        <v>13.5</v>
+      </c>
+      <c r="AS3">
+        <v>8</v>
+      </c>
+      <c r="AT3">
+        <v>7.4</v>
+      </c>
+      <c r="AU3">
+        <v>6</v>
+      </c>
+      <c r="AV3">
+        <v>11.5</v>
+      </c>
+      <c r="AW3">
+        <v>36</v>
+      </c>
+      <c r="AX3">
+        <v>17.5</v>
+      </c>
+      <c r="AY3">
+        <v>13</v>
+      </c>
+      <c r="AZ3">
+        <v>21</v>
+      </c>
+      <c r="BA3">
+        <v>8.6</v>
+      </c>
+      <c r="BB3">
+        <v>8.6</v>
+      </c>
+      <c r="BC3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE3">
+        <v>9.4</v>
+      </c>
+      <c r="BF3">
+        <v>8.6</v>
+      </c>
+      <c r="BG3">
+        <v>38</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.04</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.04</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.04</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.04</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.04</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.04</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.04</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.04</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.04</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.04</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4">
+        <v>2.08</v>
+      </c>
+      <c r="G4">
+        <v>2.2</v>
+      </c>
+      <c r="H4">
+        <v>4.5</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>3.05</v>
+      </c>
+      <c r="K4">
+        <v>3.25</v>
+      </c>
+      <c r="L4">
+        <v>1.62</v>
+      </c>
+      <c r="M4">
+        <v>1.13</v>
+      </c>
+      <c r="N4">
+        <v>2.44</v>
+      </c>
+      <c r="O4">
+        <v>1.59</v>
+      </c>
+      <c r="P4">
+        <v>1.49</v>
+      </c>
+      <c r="Q4">
+        <v>2.84</v>
+      </c>
+      <c r="R4">
+        <v>1.16</v>
+      </c>
+      <c r="S4">
+        <v>6</v>
+      </c>
+      <c r="T4">
+        <v>2.26</v>
+      </c>
+      <c r="U4">
+        <v>1.65</v>
+      </c>
+      <c r="V4">
+        <v>1.25</v>
+      </c>
+      <c r="W4">
+        <v>1.84</v>
+      </c>
+      <c r="X4">
+        <v>9.4</v>
+      </c>
+      <c r="Y4">
+        <v>11.5</v>
+      </c>
+      <c r="Z4">
+        <v>42</v>
+      </c>
+      <c r="AA4">
+        <v>170</v>
+      </c>
+      <c r="AB4">
+        <v>6.6</v>
+      </c>
+      <c r="AC4">
+        <v>7.8</v>
+      </c>
+      <c r="AD4">
+        <v>22</v>
+      </c>
+      <c r="AE4">
+        <v>120</v>
+      </c>
+      <c r="AF4">
+        <v>12</v>
+      </c>
+      <c r="AG4">
+        <v>12.5</v>
+      </c>
+      <c r="AH4">
+        <v>29</v>
+      </c>
+      <c r="AI4">
+        <v>150</v>
+      </c>
+      <c r="AJ4">
+        <v>36</v>
+      </c>
+      <c r="AK4">
+        <v>40</v>
+      </c>
+      <c r="AL4">
+        <v>85</v>
+      </c>
+      <c r="AM4">
+        <v>300</v>
+      </c>
+      <c r="AN4">
+        <v>40</v>
+      </c>
+      <c r="AO4">
+        <v>200</v>
+      </c>
+      <c r="AP4">
+        <v>7</v>
+      </c>
+      <c r="AQ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR4">
+        <v>6</v>
+      </c>
+      <c r="AS4">
+        <v>6.8</v>
+      </c>
+      <c r="AT4">
+        <v>5.6</v>
+      </c>
+      <c r="AU4">
+        <v>6.4</v>
+      </c>
+      <c r="AV4">
+        <v>17.5</v>
+      </c>
+      <c r="AW4">
+        <v>6.6</v>
+      </c>
+      <c r="AX4">
+        <v>9.6</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>5.6</v>
+      </c>
+      <c r="BA4">
+        <v>6.8</v>
+      </c>
+      <c r="BB4">
+        <v>5.9</v>
+      </c>
+      <c r="BC4">
+        <v>6</v>
+      </c>
+      <c r="BD4">
+        <v>6.4</v>
+      </c>
+      <c r="BE4">
+        <v>6.8</v>
+      </c>
+      <c r="BF4">
+        <v>6</v>
+      </c>
+      <c r="BG4">
+        <v>6.8</v>
+      </c>
+      <c r="BH4">
+        <v>2.66</v>
+      </c>
+      <c r="BI4">
+        <v>2.16</v>
+      </c>
+      <c r="BJ4">
+        <v>13</v>
+      </c>
+      <c r="BK4">
+        <v>7.6</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>11</v>
+      </c>
+      <c r="BN4">
+        <v>4.7</v>
+      </c>
+      <c r="BO4">
+        <v>3.95</v>
+      </c>
+      <c r="BP4">
+        <v>19</v>
+      </c>
+      <c r="BQ4">
+        <v>7</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU4">
+        <v>4.9</v>
+      </c>
+      <c r="BV4">
+        <v>75</v>
+      </c>
+      <c r="BW4">
+        <v>9.4</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>10</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>9.4</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5">
+        <v>1.58</v>
+      </c>
+      <c r="G5">
+        <v>1.74</v>
+      </c>
+      <c r="H5">
+        <v>5.7</v>
+      </c>
+      <c r="I5">
+        <v>8.6</v>
+      </c>
+      <c r="J5">
+        <v>3.7</v>
+      </c>
+      <c r="K5">
+        <v>5.3</v>
+      </c>
+      <c r="L5">
+        <v>1.01</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>3</v>
+      </c>
+      <c r="O5">
+        <v>1.36</v>
+      </c>
+      <c r="P5">
+        <v>1.71</v>
+      </c>
+      <c r="Q5">
+        <v>2.08</v>
+      </c>
+      <c r="R5">
+        <v>1.26</v>
+      </c>
+      <c r="S5">
+        <v>3.6</v>
+      </c>
+      <c r="T5">
+        <v>1.11</v>
+      </c>
+      <c r="U5">
+        <v>1.11</v>
+      </c>
+      <c r="V5">
+        <v>1.13</v>
+      </c>
+      <c r="W5">
+        <v>2.34</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.01</v>
+      </c>
+      <c r="AQ5">
+        <v>1.01</v>
+      </c>
+      <c r="AR5">
+        <v>1.01</v>
+      </c>
+      <c r="AS5">
+        <v>1.01</v>
+      </c>
+      <c r="AT5">
+        <v>1.01</v>
+      </c>
+      <c r="AU5">
+        <v>1.01</v>
+      </c>
+      <c r="AV5">
+        <v>1.01</v>
+      </c>
+      <c r="AW5">
+        <v>1.01</v>
+      </c>
+      <c r="AX5">
+        <v>1.01</v>
+      </c>
+      <c r="AY5">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5">
+        <v>1.01</v>
+      </c>
+      <c r="BA5">
+        <v>1.01</v>
+      </c>
+      <c r="BB5">
+        <v>1.01</v>
+      </c>
+      <c r="BC5">
+        <v>1.01</v>
+      </c>
+      <c r="BD5">
+        <v>1.01</v>
+      </c>
+      <c r="BE5">
+        <v>1.01</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.04</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.04</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.04</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.04</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.04</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.04</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.04</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.04</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.04</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.04</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6">
+        <v>3.6</v>
+      </c>
+      <c r="G6">
+        <v>4.8</v>
+      </c>
+      <c r="H6">
+        <v>2.02</v>
+      </c>
+      <c r="I6">
+        <v>2.28</v>
+      </c>
+      <c r="J6">
+        <v>2.96</v>
+      </c>
+      <c r="K6">
+        <v>3.75</v>
+      </c>
+      <c r="L6">
+        <v>1.45</v>
+      </c>
+      <c r="M6">
+        <v>1.09</v>
+      </c>
+      <c r="N6">
+        <v>3.1</v>
+      </c>
+      <c r="O6">
+        <v>1.38</v>
+      </c>
+      <c r="P6">
+        <v>1.74</v>
+      </c>
+      <c r="Q6">
+        <v>2.12</v>
+      </c>
+      <c r="R6">
+        <v>1.27</v>
+      </c>
+      <c r="S6">
+        <v>3.7</v>
+      </c>
+      <c r="T6">
+        <v>1.89</v>
+      </c>
+      <c r="U6">
+        <v>1.93</v>
+      </c>
+      <c r="V6">
+        <v>1.78</v>
+      </c>
+      <c r="W6">
+        <v>1.26</v>
+      </c>
+      <c r="X6">
+        <v>13.5</v>
+      </c>
+      <c r="Y6">
+        <v>9.6</v>
+      </c>
+      <c r="Z6">
+        <v>15</v>
+      </c>
+      <c r="AA6">
+        <v>32</v>
+      </c>
+      <c r="AB6">
+        <v>15</v>
+      </c>
+      <c r="AC6">
+        <v>9</v>
+      </c>
+      <c r="AD6">
+        <v>12.5</v>
+      </c>
+      <c r="AE6">
+        <v>29</v>
+      </c>
+      <c r="AF6">
+        <v>34</v>
+      </c>
+      <c r="AG6">
+        <v>19.5</v>
+      </c>
+      <c r="AH6">
+        <v>23</v>
+      </c>
+      <c r="AI6">
+        <v>55</v>
+      </c>
+      <c r="AJ6">
+        <v>110</v>
+      </c>
+      <c r="AK6">
+        <v>70</v>
+      </c>
+      <c r="AL6">
+        <v>80</v>
+      </c>
+      <c r="AM6">
+        <v>150</v>
+      </c>
+      <c r="AN6">
+        <v>85</v>
+      </c>
+      <c r="AO6">
+        <v>24</v>
+      </c>
+      <c r="AP6">
+        <v>3.7</v>
+      </c>
+      <c r="AQ6">
+        <v>3.35</v>
+      </c>
+      <c r="AR6">
+        <v>3.8</v>
+      </c>
+      <c r="AS6">
+        <v>4.4</v>
+      </c>
+      <c r="AT6">
+        <v>3.8</v>
+      </c>
+      <c r="AU6">
+        <v>3.25</v>
+      </c>
+      <c r="AV6">
+        <v>3.65</v>
+      </c>
+      <c r="AW6">
+        <v>4.3</v>
+      </c>
+      <c r="AX6">
+        <v>4.4</v>
+      </c>
+      <c r="AY6">
+        <v>4</v>
+      </c>
+      <c r="AZ6">
+        <v>4.2</v>
+      </c>
+      <c r="BA6">
+        <v>4.7</v>
+      </c>
+      <c r="BB6">
+        <v>4.9</v>
+      </c>
+      <c r="BC6">
+        <v>4.8</v>
+      </c>
+      <c r="BD6">
+        <v>4.8</v>
+      </c>
+      <c r="BE6">
+        <v>5</v>
+      </c>
+      <c r="BF6">
+        <v>4.8</v>
+      </c>
+      <c r="BG6">
+        <v>4.2</v>
+      </c>
+      <c r="BH6">
+        <v>3.2</v>
+      </c>
+      <c r="BI6">
+        <v>2.6</v>
+      </c>
+      <c r="BJ6">
+        <v>11</v>
+      </c>
+      <c r="BK6">
+        <v>5.2</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>2.4</v>
+      </c>
+      <c r="BN6">
+        <v>7.6</v>
+      </c>
+      <c r="BO6">
+        <v>4.3</v>
+      </c>
+      <c r="BP6">
+        <v>38</v>
+      </c>
+      <c r="BQ6">
+        <v>8</v>
+      </c>
+      <c r="BR6">
+        <v>55</v>
+      </c>
+      <c r="BS6">
+        <v>8.4</v>
+      </c>
+      <c r="BT6">
+        <v>5</v>
+      </c>
+      <c r="BU6">
+        <v>3.35</v>
+      </c>
+      <c r="BV6">
+        <v>17</v>
+      </c>
+      <c r="BW6">
+        <v>6.2</v>
+      </c>
+      <c r="BX6">
+        <v>36</v>
+      </c>
+      <c r="BY6">
+        <v>7.8</v>
+      </c>
+      <c r="BZ6">
+        <v>34</v>
+      </c>
+      <c r="CA6">
+        <v>7.8</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7">
+        <v>1.04</v>
+      </c>
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>1.04</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>1.01</v>
+      </c>
+      <c r="K7">
+        <v>950</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.24</v>
+      </c>
+      <c r="Q8">
+        <v>1.01</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 00:38:45</t>
+    <t>2026-08-02 02:52:46</t>
   </si>
 </sst>
 </file>
@@ -931,19 +931,19 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G2">
         <v>1.36</v>
       </c>
       <c r="H2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="I2">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K2">
         <v>5.9</v>
@@ -973,16 +973,16 @@
         <v>3.3</v>
       </c>
       <c r="T2">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="U2">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V2">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="X2">
         <v>16</v>
@@ -991,7 +991,7 @@
         <v>42</v>
       </c>
       <c r="Z2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1003,10 +1003,10 @@
         <v>13.5</v>
       </c>
       <c r="AD2">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AE2">
-        <v>510</v>
+        <v>460</v>
       </c>
       <c r="AF2">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>48</v>
       </c>
       <c r="AI2">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AJ2">
         <v>9.800000000000001</v>
@@ -1030,7 +1030,7 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AN2">
         <v>7.8</v>
@@ -1045,10 +1045,10 @@
         <v>25</v>
       </c>
       <c r="AR2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2">
         <v>5.9</v>
@@ -1057,10 +1057,10 @@
         <v>10.5</v>
       </c>
       <c r="AV2">
-        <v>38</v>
+        <v>7.2</v>
       </c>
       <c r="AW2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2">
         <v>5.8</v>
@@ -1072,7 +1072,7 @@
         <v>29</v>
       </c>
       <c r="BA2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB2">
         <v>8</v>
@@ -1090,7 +1090,7 @@
         <v>5.6</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2">
         <v>3.7</v>
@@ -1120,7 +1120,7 @@
         <v>7.8</v>
       </c>
       <c r="BQ2">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BR2">
         <v>34</v>
@@ -1150,7 +1150,7 @@
         <v>15.5</v>
       </c>
       <c r="CA2">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="CB2" t="s">
         <v>107</v>
@@ -1182,7 +1182,7 @@
         <v>2.62</v>
       </c>
       <c r="I3">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="J3">
         <v>2.88</v>
@@ -1221,10 +1221,10 @@
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X3">
         <v>8</v>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K4">
         <v>3.25</v>
@@ -1439,13 +1439,13 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O4">
         <v>1.59</v>
       </c>
       <c r="P4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
         <v>2.84</v>
@@ -1529,7 +1529,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AS4">
         <v>6.8</v>
@@ -1604,25 +1604,25 @@
         <v>19</v>
       </c>
       <c r="BQ4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU4">
         <v>4.9</v>
       </c>
       <c r="BV4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
         <v>1000</v>
@@ -1634,7 +1634,7 @@
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>107</v>
@@ -1660,19 +1660,19 @@
         <v>1.58</v>
       </c>
       <c r="G5">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="H5">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1708,7 +1708,7 @@
         <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1902,7 +1902,7 @@
         <v>3.6</v>
       </c>
       <c r="G6">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H6">
         <v>2.02</v>
@@ -1941,10 +1941,10 @@
         <v>3.7</v>
       </c>
       <c r="T6">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
         <v>1.78</v>
@@ -2064,7 +2064,7 @@
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6">
         <v>11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 02:52:46</t>
+    <t>2026-08-02 05:07:19</t>
   </si>
 </sst>
 </file>
@@ -1179,10 +1179,10 @@
         <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="I3">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J3">
         <v>2.88</v>
@@ -1221,10 +1221,10 @@
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
         <v>8</v>
@@ -1427,7 +1427,7 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
         <v>3.25</v>
@@ -1439,7 +1439,7 @@
         <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O4">
         <v>1.59</v>
@@ -1475,7 +1475,7 @@
         <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA4">
         <v>170</v>
@@ -1544,7 +1544,7 @@
         <v>17.5</v>
       </c>
       <c r="AW4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX4">
         <v>9.6</v>
@@ -1553,22 +1553,22 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA4">
         <v>6.8</v>
       </c>
       <c r="BB4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC4">
         <v>6</v>
       </c>
       <c r="BD4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF4">
         <v>6</v>
@@ -1660,7 +1660,7 @@
         <v>1.58</v>
       </c>
       <c r="G5">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="H5">
         <v>6.6</v>
@@ -1708,7 +1708,7 @@
         <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -1938,19 +1938,19 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.7</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
         <v>1.78</v>
       </c>
       <c r="W6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X6">
         <v>13.5</v>
@@ -2064,7 +2064,7 @@
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6">
         <v>11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 05:07:19</t>
+    <t>2026-08-02 07:21:43</t>
   </si>
 </sst>
 </file>
@@ -934,7 +934,7 @@
         <v>1.3</v>
       </c>
       <c r="G2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H2">
         <v>13.5</v>
@@ -973,7 +973,7 @@
         <v>3.3</v>
       </c>
       <c r="T2">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
         <v>1.54</v>
@@ -982,7 +982,7 @@
         <v>1.06</v>
       </c>
       <c r="W2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X2">
         <v>16</v>
@@ -1081,7 +1081,7 @@
         <v>14.5</v>
       </c>
       <c r="BD2">
-        <v>40</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
         <v>8</v>
@@ -1173,7 +1173,7 @@
         <v>101</v>
       </c>
       <c r="F3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G3">
         <v>3.45</v>
@@ -1182,7 +1182,7 @@
         <v>2.68</v>
       </c>
       <c r="I3">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>2.88</v>
@@ -1221,10 +1221,10 @@
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X3">
         <v>8</v>
@@ -1233,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="Z3">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA3">
         <v>60</v>
@@ -1257,7 +1257,7 @@
         <v>16</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI3">
         <v>90</v>
@@ -1287,10 +1287,10 @@
         <v>6.6</v>
       </c>
       <c r="AR3">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AS3">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AT3">
         <v>7.4</v>
@@ -1302,10 +1302,10 @@
         <v>11.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="AX3">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AY3">
         <v>13</v>
@@ -1314,22 +1314,22 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BC3">
+        <v>7.8</v>
+      </c>
+      <c r="BD3">
+        <v>8.4</v>
+      </c>
+      <c r="BE3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF3">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BD3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE3">
-        <v>9.4</v>
-      </c>
-      <c r="BF3">
-        <v>8.6</v>
       </c>
       <c r="BG3">
         <v>38</v>
@@ -1415,10 +1415,10 @@
         <v>102</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
         <v>4.5</v>
@@ -1427,16 +1427,16 @@
         <v>5</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L4">
         <v>1.62</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N4">
         <v>2.44</v>
@@ -1445,7 +1445,7 @@
         <v>1.59</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q4">
         <v>2.84</v>
@@ -1466,10 +1466,10 @@
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X4">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4">
         <v>11.5</v>
@@ -1478,7 +1478,7 @@
         <v>40</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB4">
         <v>6.6</v>
@@ -1532,7 +1532,7 @@
         <v>28</v>
       </c>
       <c r="AS4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT4">
         <v>5.6</v>
@@ -1544,7 +1544,7 @@
         <v>17.5</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX4">
         <v>9.6</v>
@@ -1553,28 +1553,28 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC4">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD4">
+        <v>7.4</v>
+      </c>
+      <c r="BE4">
+        <v>7.8</v>
+      </c>
+      <c r="BF4">
         <v>6.6</v>
       </c>
-      <c r="BE4">
-        <v>7</v>
-      </c>
-      <c r="BF4">
-        <v>6</v>
-      </c>
       <c r="BG4">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
         <v>2.66</v>
@@ -1938,7 +1938,7 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>1.05</v>
+        <v>3.7</v>
       </c>
       <c r="T6">
         <v>1.89</v>
@@ -1950,7 +1950,7 @@
         <v>1.78</v>
       </c>
       <c r="W6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X6">
         <v>13.5</v>
@@ -2064,7 +2064,7 @@
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6">
         <v>11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 07:21:43</t>
+    <t>2026-08-02 09:44:41</t>
   </si>
 </sst>
 </file>
@@ -943,7 +943,7 @@
         <v>18</v>
       </c>
       <c r="J2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K2">
         <v>5.9</v>
@@ -1173,19 +1173,19 @@
         <v>101</v>
       </c>
       <c r="F3">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G3">
         <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="J3">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1194,55 +1194,55 @@
         <v>1.51</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P3">
         <v>1.47</v>
       </c>
       <c r="Q3">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="R3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>6</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U3">
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W3">
         <v>1.41</v>
       </c>
       <c r="X3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3">
         <v>14.5</v>
@@ -1251,7 +1251,7 @@
         <v>50</v>
       </c>
       <c r="AF3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG3">
         <v>16</v>
@@ -1260,79 +1260,79 @@
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK3">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AL3">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
         <v>270</v>
       </c>
       <c r="AN3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
         <v>65</v>
       </c>
       <c r="AP3">
+        <v>7</v>
+      </c>
+      <c r="AQ3">
         <v>6.8</v>
       </c>
-      <c r="AQ3">
-        <v>6.6</v>
-      </c>
       <c r="AR3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS3">
         <v>34</v>
       </c>
       <c r="AT3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AX3">
         <v>15</v>
       </c>
       <c r="AY3">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA3">
-        <v>8.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BC3">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BD3">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BE3">
-        <v>8.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BF3">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BG3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1415,7 +1415,7 @@
         <v>102</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G4">
         <v>2.22</v>
@@ -1424,7 +1424,7 @@
         <v>4.5</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -1445,7 +1445,7 @@
         <v>1.59</v>
       </c>
       <c r="P4">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
         <v>2.84</v>
@@ -1902,7 +1902,7 @@
         <v>3.6</v>
       </c>
       <c r="G6">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="H6">
         <v>2.02</v>
@@ -1938,19 +1938,19 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.7</v>
+        <v>1.05</v>
       </c>
       <c r="T6">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
         <v>1.78</v>
       </c>
       <c r="W6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X6">
         <v>13.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 09:44:41</t>
+    <t>2026-08-02 12:09:59</t>
   </si>
 </sst>
 </file>
@@ -943,40 +943,40 @@
         <v>18</v>
       </c>
       <c r="J2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K2">
         <v>5.9</v>
       </c>
       <c r="L2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M2">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R2">
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U2">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="V2">
         <v>1.06</v>
@@ -985,7 +985,7 @@
         <v>3.85</v>
       </c>
       <c r="X2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
         <v>42</v>
@@ -1000,7 +1000,7 @@
         <v>7</v>
       </c>
       <c r="AC2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD2">
         <v>950</v>
@@ -1009,31 +1009,31 @@
         <v>460</v>
       </c>
       <c r="AF2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>48</v>
+        <v>950</v>
       </c>
       <c r="AI2">
         <v>350</v>
       </c>
       <c r="AJ2">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AK2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM2">
         <v>400</v>
       </c>
       <c r="AN2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1045,10 +1045,10 @@
         <v>25</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
         <v>5.9</v>
@@ -1057,22 +1057,22 @@
         <v>10.5</v>
       </c>
       <c r="AV2">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="AY2">
         <v>10</v>
       </c>
       <c r="AZ2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BA2">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BB2">
         <v>8</v>
@@ -1081,28 +1081,28 @@
         <v>14.5</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BF2">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BK2">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1111,19 +1111,19 @@
         <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BO2">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BP2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BQ2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
         <v>8.4</v>
@@ -1138,19 +1138,19 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ2">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="CA2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="CB2" t="s">
         <v>107</v>
@@ -1173,19 +1173,19 @@
         <v>101</v>
       </c>
       <c r="F3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H3">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K3">
         <v>3.05</v>
@@ -1200,7 +1200,7 @@
         <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="P3">
         <v>1.47</v>
@@ -1212,16 +1212,16 @@
         <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T3">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
         <v>1.41</v>
@@ -1230,7 +1230,7 @@
         <v>7.8</v>
       </c>
       <c r="Y3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z3">
         <v>16.5</v>
@@ -1239,7 +1239,7 @@
         <v>55</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
@@ -1251,7 +1251,7 @@
         <v>50</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG3">
         <v>16</v>
@@ -1263,22 +1263,22 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>75</v>
+        <v>730</v>
       </c>
       <c r="AK3">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="AL3">
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AP3">
         <v>7</v>
@@ -1287,7 +1287,7 @@
         <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AS3">
         <v>34</v>
@@ -1299,40 +1299,40 @@
         <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC3">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="BD3">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BE3">
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG3">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1418,7 +1418,7 @@
         <v>2.08</v>
       </c>
       <c r="G4">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H4">
         <v>4.5</v>
@@ -1427,7 +1427,7 @@
         <v>4.9</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K4">
         <v>3.2</v>
@@ -1451,7 +1451,7 @@
         <v>2.84</v>
       </c>
       <c r="R4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -1466,7 +1466,7 @@
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X4">
         <v>8.199999999999999</v>
@@ -1666,7 +1666,7 @@
         <v>6.6</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>3.75</v>
@@ -1678,145 +1678,145 @@
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q5">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S5">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
         <v>2.52</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1899,13 +1899,13 @@
         <v>104</v>
       </c>
       <c r="F6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="G6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H6">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I6">
         <v>2.28</v>
@@ -1914,7 +1914,7 @@
         <v>2.96</v>
       </c>
       <c r="K6">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
         <v>1.45</v>
@@ -1929,7 +1929,7 @@
         <v>1.38</v>
       </c>
       <c r="P6">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q6">
         <v>2.12</v>
@@ -1938,25 +1938,25 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>1.05</v>
+        <v>3.95</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
         <v>1.78</v>
       </c>
       <c r="W6">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X6">
         <v>13.5</v>
       </c>
       <c r="Y6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>15</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
         <v>12.5</v>
@@ -2007,97 +2007,97 @@
         <v>24</v>
       </c>
       <c r="AP6">
-        <v>3.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="AR6">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT6">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="AU6">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AV6">
-        <v>3.65</v>
+        <v>8.4</v>
       </c>
       <c r="AW6">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="AX6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AZ6">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB6">
+        <v>5</v>
+      </c>
+      <c r="BC6">
         <v>4.9</v>
       </c>
-      <c r="BC6">
-        <v>4.8</v>
-      </c>
       <c r="BD6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG6">
-        <v>4.2</v>
+        <v>17</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="BJ6">
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BN6">
         <v>7.6</v>
       </c>
       <c r="BO6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP6">
         <v>38</v>
       </c>
       <c r="BQ6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BU6">
         <v>3.35</v>
@@ -2106,19 +2106,19 @@
         <v>17</v>
       </c>
       <c r="BW6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX6">
         <v>36</v>
       </c>
       <c r="BY6">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB6" t="s">
         <v>107</v>
@@ -2159,16 +2159,16 @@
         <v>950</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P7">
         <v>1.24</v>
@@ -2177,184 +2177,184 @@
         <v>1.01</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 12:09:59</t>
+    <t>2026-08-02 14:21:57</t>
   </si>
 </sst>
 </file>
@@ -943,13 +943,13 @@
         <v>18</v>
       </c>
       <c r="J2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -961,22 +961,22 @@
         <v>1.32</v>
       </c>
       <c r="P2">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U2">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="V2">
         <v>1.06</v>
@@ -985,7 +985,7 @@
         <v>3.85</v>
       </c>
       <c r="X2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y2">
         <v>42</v>
@@ -1009,19 +1009,19 @@
         <v>460</v>
       </c>
       <c r="AF2">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>950</v>
+        <v>65</v>
       </c>
       <c r="AI2">
         <v>350</v>
       </c>
       <c r="AJ2">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK2">
         <v>18</v>
@@ -1033,22 +1033,22 @@
         <v>400</v>
       </c>
       <c r="AN2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ2">
         <v>25</v>
       </c>
       <c r="AR2">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AT2">
         <v>5.9</v>
@@ -1057,13 +1057,13 @@
         <v>10.5</v>
       </c>
       <c r="AV2">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="AX2">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY2">
         <v>10</v>
@@ -1072,25 +1072,25 @@
         <v>34</v>
       </c>
       <c r="BA2">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC2">
         <v>14.5</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE2">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF2">
         <v>5.9</v>
       </c>
       <c r="BG2">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BH2">
         <v>3.6</v>
@@ -1099,7 +1099,7 @@
         <v>3.05</v>
       </c>
       <c r="BJ2">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BK2">
         <v>6.4</v>
@@ -1111,10 +1111,10 @@
         <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BO2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BP2">
         <v>8</v>
@@ -1123,13 +1123,13 @@
         <v>5.7</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS2">
         <v>8.4</v>
       </c>
       <c r="BT2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BU2">
         <v>6.8</v>
@@ -1138,13 +1138,13 @@
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>17</v>
@@ -1179,10 +1179,10 @@
         <v>3.5</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="I3">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="J3">
         <v>2.94</v>
@@ -1197,7 +1197,7 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O3">
         <v>1.64</v>
@@ -1215,16 +1215,16 @@
         <v>6.2</v>
       </c>
       <c r="T3">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
         <v>7.8</v>
@@ -1233,25 +1233,25 @@
         <v>7.6</v>
       </c>
       <c r="Z3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA3">
         <v>55</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3">
         <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
         <v>50</v>
       </c>
       <c r="AF3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG3">
         <v>16</v>
@@ -1263,10 +1263,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>730</v>
+        <v>760</v>
       </c>
       <c r="AK3">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1284,7 +1284,7 @@
         <v>7</v>
       </c>
       <c r="AQ3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR3">
         <v>13.5</v>
@@ -1293,7 +1293,7 @@
         <v>34</v>
       </c>
       <c r="AT3">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
@@ -1308,10 +1308,10 @@
         <v>17</v>
       </c>
       <c r="AY3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ3">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
         <v>36</v>
@@ -1332,7 +1332,7 @@
         <v>34</v>
       </c>
       <c r="BG3">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1424,13 +1424,13 @@
         <v>4.5</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L4">
         <v>1.62</v>
@@ -1577,7 +1577,7 @@
         <v>7.8</v>
       </c>
       <c r="BH4">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="BI4">
         <v>2.16</v>
@@ -1592,7 +1592,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1604,13 +1604,13 @@
         <v>19</v>
       </c>
       <c r="BQ4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT4">
         <v>8</v>
@@ -1622,19 +1622,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
+        <v>10.5</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
         <v>10</v>
-      </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
-        <v>9.800000000000001</v>
       </c>
       <c r="CB4" t="s">
         <v>107</v>
@@ -1684,7 +1684,7 @@
         <v>3.15</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
         <v>1.73</v>
@@ -1902,10 +1902,10 @@
         <v>3.8</v>
       </c>
       <c r="G6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H6">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I6">
         <v>2.28</v>
@@ -1938,19 +1938,19 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V6">
         <v>1.78</v>
       </c>
       <c r="W6">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X6">
         <v>13.5</v>
@@ -2001,55 +2001,55 @@
         <v>150</v>
       </c>
       <c r="AN6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO6">
         <v>24</v>
       </c>
       <c r="AP6">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ6">
         <v>6.4</v>
       </c>
       <c r="AR6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU6">
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA6">
         <v>4.8</v>
       </c>
       <c r="BB6">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC6">
         <v>4.9</v>
       </c>
       <c r="BD6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE6">
         <v>5.1</v>
@@ -2058,7 +2058,7 @@
         <v>4.9</v>
       </c>
       <c r="BG6">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
@@ -2153,7 +2153,7 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2165,28 +2165,28 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R7">
+        <v>1.15</v>
+      </c>
+      <c r="S7">
         <v>1.05</v>
       </c>
-      <c r="S7">
-        <v>1.01</v>
-      </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2306,55 +2306,55 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 14:21:57</t>
+    <t>2026-08-02 16:32:47</t>
   </si>
 </sst>
 </file>
@@ -934,7 +934,7 @@
         <v>1.3</v>
       </c>
       <c r="G2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H2">
         <v>13.5</v>
@@ -958,7 +958,7 @@
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
         <v>1.86</v>
@@ -982,7 +982,7 @@
         <v>1.06</v>
       </c>
       <c r="W2">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -1033,7 +1033,7 @@
         <v>400</v>
       </c>
       <c r="AN2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1045,10 +1045,10 @@
         <v>25</v>
       </c>
       <c r="AR2">
+        <v>10</v>
+      </c>
+      <c r="AS2">
         <v>10.5</v>
-      </c>
-      <c r="AS2">
-        <v>11</v>
       </c>
       <c r="AT2">
         <v>5.9</v>
@@ -1057,10 +1057,10 @@
         <v>10.5</v>
       </c>
       <c r="AV2">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX2">
         <v>5.6</v>
@@ -1072,7 +1072,7 @@
         <v>34</v>
       </c>
       <c r="BA2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BB2">
         <v>8.199999999999999</v>
@@ -1081,16 +1081,16 @@
         <v>14.5</v>
       </c>
       <c r="BD2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF2">
         <v>5.9</v>
       </c>
       <c r="BG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH2">
         <v>3.6</v>
@@ -1120,10 +1120,10 @@
         <v>8</v>
       </c>
       <c r="BQ2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BR2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
         <v>8.4</v>
@@ -1150,7 +1150,7 @@
         <v>17</v>
       </c>
       <c r="CA2">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="CB2" t="s">
         <v>107</v>
@@ -1173,10 +1173,10 @@
         <v>101</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G3">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H3">
         <v>2.6</v>
@@ -1188,7 +1188,7 @@
         <v>2.94</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
         <v>1.51</v>
@@ -1212,7 +1212,7 @@
         <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
         <v>2.3</v>
@@ -1233,7 +1233,7 @@
         <v>7.6</v>
       </c>
       <c r="Z3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA3">
         <v>55</v>
@@ -1415,22 +1415,22 @@
         <v>102</v>
       </c>
       <c r="F4">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G4">
         <v>2.2</v>
       </c>
       <c r="H4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L4">
         <v>1.62</v>
@@ -1439,13 +1439,13 @@
         <v>1.14</v>
       </c>
       <c r="N4">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="O4">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q4">
         <v>2.84</v>
@@ -1457,13 +1457,13 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V4">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
         <v>1.84</v>
@@ -1475,106 +1475,106 @@
         <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
         <v>6.6</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
         <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AI4">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
+        <v>30</v>
+      </c>
+      <c r="AK4">
         <v>36</v>
       </c>
-      <c r="AK4">
-        <v>40</v>
-      </c>
       <c r="AL4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
         <v>300</v>
       </c>
       <c r="AN4">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AO4">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR4">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="AT4">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW4">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="AX4">
         <v>9.6</v>
       </c>
       <c r="AY4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ4">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="BA4">
-        <v>7.6</v>
+        <v>42</v>
       </c>
       <c r="BB4">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BC4">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BE4">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>6.6</v>
+        <v>19.5</v>
       </c>
       <c r="BG4">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BH4">
         <v>2.64</v>
@@ -1598,7 +1598,7 @@
         <v>4.7</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP4">
         <v>19</v>
@@ -1899,22 +1899,22 @@
         <v>104</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G6">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="H6">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I6">
         <v>2.28</v>
       </c>
       <c r="J6">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="K6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L6">
         <v>1.45</v>
@@ -1923,7 +1923,7 @@
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
         <v>1.38</v>
@@ -1938,19 +1938,19 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T6">
         <v>1.87</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
         <v>1.78</v>
       </c>
       <c r="W6">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X6">
         <v>13.5</v>
@@ -2013,34 +2013,34 @@
         <v>6.4</v>
       </c>
       <c r="AR6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS6">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AT6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
         <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX6">
         <v>4.6</v>
       </c>
       <c r="AY6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ6">
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="BB6">
         <v>5.1</v>
@@ -2064,7 +2064,7 @@
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6">
         <v>11</v>
@@ -2082,13 +2082,13 @@
         <v>7.6</v>
       </c>
       <c r="BO6">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BP6">
         <v>38</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="BR6">
         <v>55</v>
@@ -2100,7 +2100,7 @@
         <v>4.9</v>
       </c>
       <c r="BU6">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BV6">
         <v>17</v>
@@ -2144,7 +2144,7 @@
         <v>1.04</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H7">
         <v>1.04</v>
@@ -2153,7 +2153,7 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2165,7 +2165,7 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O7">
         <v>1.33</v>
@@ -2180,7 +2180,7 @@
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2401,208 +2401,208 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>107</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 16:32:47</t>
+    <t>2026-08-02 18:42:52</t>
   </si>
 </sst>
 </file>
@@ -946,7 +946,7 @@
         <v>5.1</v>
       </c>
       <c r="K2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L2">
         <v>1.33</v>
@@ -1176,7 +1176,7 @@
         <v>3.35</v>
       </c>
       <c r="G3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H3">
         <v>2.6</v>
@@ -1197,7 +1197,7 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O3">
         <v>1.64</v>
@@ -1209,7 +1209,7 @@
         <v>2.9</v>
       </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
         <v>6.4</v>
@@ -1415,7 +1415,7 @@
         <v>102</v>
       </c>
       <c r="F4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G4">
         <v>2.2</v>
@@ -1424,7 +1424,7 @@
         <v>4.4</v>
       </c>
       <c r="I4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J4">
         <v>3.1</v>
@@ -1442,19 +1442,19 @@
         <v>2.52</v>
       </c>
       <c r="O4">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="R4">
         <v>1.17</v>
       </c>
       <c r="S4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T4">
         <v>2.32</v>
@@ -1466,16 +1466,16 @@
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AA4">
         <v>1000</v>
@@ -1508,13 +1508,13 @@
         <v>30</v>
       </c>
       <c r="AK4">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AL4">
         <v>1000</v>
       </c>
       <c r="AM4">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>34</v>
@@ -1541,7 +1541,7 @@
         <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AW4">
         <v>34</v>
@@ -1607,7 +1607,7 @@
         <v>7.4</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS4">
         <v>9.800000000000001</v>
@@ -1619,7 +1619,7 @@
         <v>4.9</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW4">
         <v>10</v>
@@ -1657,7 +1657,7 @@
         <v>103</v>
       </c>
       <c r="F5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G5">
         <v>1.65</v>
@@ -1666,7 +1666,7 @@
         <v>6.6</v>
       </c>
       <c r="I5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>3.75</v>
@@ -1714,25 +1714,25 @@
         <v>14</v>
       </c>
       <c r="Y5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z5">
         <v>70</v>
       </c>
       <c r="AA5">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AB5">
         <v>7.2</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>30</v>
       </c>
       <c r="AE5">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF5">
         <v>9.199999999999999</v>
@@ -1744,7 +1744,7 @@
         <v>28</v>
       </c>
       <c r="AI5">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ5">
         <v>16.5</v>
@@ -1756,13 +1756,13 @@
         <v>55</v>
       </c>
       <c r="AM5">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN5">
         <v>14</v>
       </c>
       <c r="AO5">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1771,10 +1771,10 @@
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT5">
         <v>5.8</v>
@@ -1783,10 +1783,10 @@
         <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX5">
         <v>7.4</v>
@@ -1795,10 +1795,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -1807,16 +1807,16 @@
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
         <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1905,10 +1905,10 @@
         <v>4.5</v>
       </c>
       <c r="H6">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="I6">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J6">
         <v>3.15</v>
@@ -1926,7 +1926,7 @@
         <v>3.15</v>
       </c>
       <c r="O6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
         <v>1.73</v>
@@ -1938,16 +1938,16 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V6">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="W6">
         <v>1.28</v>
@@ -1995,13 +1995,13 @@
         <v>70</v>
       </c>
       <c r="AL6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM6">
         <v>150</v>
       </c>
       <c r="AN6">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AO6">
         <v>24</v>
@@ -2013,22 +2013,22 @@
         <v>6.4</v>
       </c>
       <c r="AR6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS6">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AT6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX6">
         <v>4.6</v>
@@ -2040,22 +2040,22 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>4.8</v>
       </c>
       <c r="BB6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BC6">
         <v>4.9</v>
       </c>
       <c r="BD6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BE6">
         <v>5.1</v>
       </c>
       <c r="BF6">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG6">
         <v>15.5</v>
@@ -2150,10 +2150,10 @@
         <v>1.04</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2404,7 +2404,7 @@
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
         <v>1.26</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 18:42:52</t>
+    <t>2026-08-02 20:52:13</t>
   </si>
 </sst>
 </file>
@@ -946,10 +946,10 @@
         <v>5.1</v>
       </c>
       <c r="K2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L2">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
         <v>1.07</v>
@@ -1173,22 +1173,22 @@
         <v>101</v>
       </c>
       <c r="F3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G3">
         <v>3.5</v>
       </c>
       <c r="H3">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J3">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="L3">
         <v>1.51</v>
@@ -1197,7 +1197,7 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O3">
         <v>1.64</v>
@@ -1206,10 +1206,10 @@
         <v>1.47</v>
       </c>
       <c r="Q3">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>6.4</v>
@@ -1221,7 +1221,7 @@
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W3">
         <v>1.4</v>
@@ -1445,7 +1445,7 @@
         <v>1.6</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q4">
         <v>2.88</v>
@@ -1553,7 +1553,7 @@
         <v>11</v>
       </c>
       <c r="AZ4">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA4">
         <v>42</v>
@@ -1926,7 +1926,7 @@
         <v>3.15</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P6">
         <v>1.73</v>
@@ -1938,10 +1938,10 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="T6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U6">
         <v>1.93</v>
@@ -2013,19 +2013,19 @@
         <v>6.4</v>
       </c>
       <c r="AR6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="AT6">
         <v>10</v>
       </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV6">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
         <v>19</v>
@@ -2034,7 +2034,7 @@
         <v>4.6</v>
       </c>
       <c r="AY6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ6">
         <v>15</v>
@@ -2058,13 +2058,13 @@
         <v>5</v>
       </c>
       <c r="BG6">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="BJ6">
         <v>11</v>
@@ -2153,7 +2153,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2425,10 +2425,10 @@
         <v>1.08</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
         <v>1.01</v>
@@ -2491,52 +2491,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2548,61 +2548,61 @@
         <v>1000</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
         <v>1000</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
         <v>1000</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
         <v>1000</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
         <v>107</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -337,7 +337,7 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 20:52:13</t>
+    <t>2026-08-02 23:00:04</t>
   </si>
 </sst>
 </file>
@@ -964,7 +964,7 @@
         <v>1.86</v>
       </c>
       <c r="Q2">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R2">
         <v>1.32</v>
@@ -973,10 +973,10 @@
         <v>3.5</v>
       </c>
       <c r="T2">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V2">
         <v>1.06</v>
@@ -1173,7 +1173,7 @@
         <v>101</v>
       </c>
       <c r="F3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G3">
         <v>3.5</v>
@@ -1188,7 +1188,7 @@
         <v>2.96</v>
       </c>
       <c r="K3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L3">
         <v>1.51</v>
@@ -1197,7 +1197,7 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O3">
         <v>1.64</v>
@@ -1263,10 +1263,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>760</v>
+        <v>860</v>
       </c>
       <c r="AK3">
-        <v>360</v>
+        <v>390</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1293,7 +1293,7 @@
         <v>34</v>
       </c>
       <c r="AT3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU3">
         <v>6.2</v>
@@ -1418,19 +1418,19 @@
         <v>2.1</v>
       </c>
       <c r="G4">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="H4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J4">
         <v>3.1</v>
       </c>
       <c r="K4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
         <v>1.62</v>
@@ -1442,7 +1442,7 @@
         <v>2.52</v>
       </c>
       <c r="O4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P4">
         <v>1.49</v>
@@ -1460,28 +1460,28 @@
         <v>2.32</v>
       </c>
       <c r="U4">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W4">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y4">
         <v>11.5</v>
       </c>
       <c r="Z4">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -1490,25 +1490,25 @@
         <v>21</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="AL4">
         <v>1000</v>
@@ -1517,61 +1517,61 @@
         <v>1000</v>
       </c>
       <c r="AN4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP4">
         <v>7.2</v>
       </c>
       <c r="AQ4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS4">
         <v>38</v>
       </c>
       <c r="AT4">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AW4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY4">
         <v>11</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BA4">
         <v>42</v>
       </c>
       <c r="BB4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BD4">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BE4">
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="BG4">
         <v>42</v>
@@ -1672,7 +1672,7 @@
         <v>3.75</v>
       </c>
       <c r="K5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -1681,13 +1681,13 @@
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
         <v>2.14</v>
@@ -1911,7 +1911,7 @@
         <v>2.24</v>
       </c>
       <c r="J6">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K6">
         <v>3.6</v>
@@ -1938,7 +1938,7 @@
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="T6">
         <v>1.9</v>
@@ -1956,7 +1956,7 @@
         <v>13.5</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>15</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6">
         <v>12.5</v>
@@ -1995,7 +1995,7 @@
         <v>70</v>
       </c>
       <c r="AL6">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM6">
         <v>150</v>
@@ -2010,13 +2010,13 @@
         <v>9</v>
       </c>
       <c r="AQ6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR6">
         <v>9.800000000000001</v>
       </c>
       <c r="AS6">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AT6">
         <v>10</v>
@@ -2025,13 +2025,13 @@
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AW6">
         <v>19</v>
       </c>
       <c r="AX6">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AY6">
         <v>13</v>
@@ -2040,25 +2040,25 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>4.8</v>
+        <v>32</v>
       </c>
       <c r="BB6">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BC6">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD6">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE6">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF6">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
@@ -2141,19 +2141,19 @@
         <v>105</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2165,13 +2165,13 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="O7">
         <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q7">
         <v>1.33</v>
@@ -2180,7 +2180,7 @@
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
         <v>1.11</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
   <si>
     <t>League</t>
   </si>
@@ -295,6 +295,12 @@
     <t>18:30:00</t>
   </si>
   <si>
+    <t>21:10:00</t>
+  </si>
+  <si>
+    <t>23:15:00</t>
+  </si>
+  <si>
     <t>LDU</t>
   </si>
   <si>
@@ -316,6 +322,12 @@
     <t>Thor</t>
   </si>
   <si>
+    <t>Llaneros FC</t>
+  </si>
+  <si>
+    <t>Tolima</t>
+  </si>
+  <si>
     <t>Delfin</t>
   </si>
   <si>
@@ -337,7 +349,13 @@
     <t>Breidablik</t>
   </si>
   <si>
-    <t>2026-08-02 23:00:04</t>
+    <t>Fortaleza FC</t>
+  </si>
+  <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
+    <t>2026-08-03 01:08:30</t>
   </si>
 </sst>
 </file>
@@ -669,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -925,79 +943,79 @@
         <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F2">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G2">
         <v>1.36</v>
       </c>
       <c r="H2">
+        <v>11.5</v>
+      </c>
+      <c r="I2">
         <v>13.5</v>
       </c>
-      <c r="I2">
-        <v>18</v>
-      </c>
       <c r="J2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K2">
         <v>5.8</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
         <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="Q2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="U2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V2">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="X2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Y2">
         <v>42</v>
       </c>
       <c r="Z2">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AC2">
         <v>13</v>
@@ -1006,7 +1024,7 @@
         <v>950</v>
       </c>
       <c r="AE2">
-        <v>460</v>
+        <v>380</v>
       </c>
       <c r="AF2">
         <v>6.6</v>
@@ -1015,10 +1033,10 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AI2">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="AJ2">
         <v>9.800000000000001</v>
@@ -1027,13 +1045,13 @@
         <v>18</v>
       </c>
       <c r="AL2">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM2">
         <v>400</v>
       </c>
       <c r="AN2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1042,13 +1060,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ2">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AR2">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AS2">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AT2">
         <v>5.9</v>
@@ -1057,10 +1075,10 @@
         <v>10.5</v>
       </c>
       <c r="AV2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
         <v>5.6</v>
@@ -1072,7 +1090,7 @@
         <v>34</v>
       </c>
       <c r="BA2">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
         <v>8.199999999999999</v>
@@ -1081,34 +1099,34 @@
         <v>14.5</v>
       </c>
       <c r="BD2">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BE2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="BF2">
         <v>5.9</v>
       </c>
       <c r="BG2">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BH2">
         <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ2">
         <v>16</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>3.5</v>
@@ -1126,19 +1144,19 @@
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BT2">
         <v>17.5</v>
       </c>
       <c r="BU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX2">
         <v>1000</v>
@@ -1147,13 +1165,13 @@
         <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA2">
         <v>12</v>
       </c>
       <c r="CB2" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1167,10 +1185,10 @@
         <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F3">
         <v>3.35</v>
@@ -1179,37 +1197,37 @@
         <v>3.5</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I3">
         <v>2.7</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K3">
         <v>3</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="M3">
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O3">
         <v>1.64</v>
       </c>
       <c r="P3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
         <v>6.4</v>
@@ -1263,10 +1281,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>860</v>
+        <v>830</v>
       </c>
       <c r="AK3">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1278,10 +1296,10 @@
         <v>1000</v>
       </c>
       <c r="AO3">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AP3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3">
         <v>6.6</v>
@@ -1296,7 +1314,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
         <v>12.5</v>
@@ -1311,7 +1329,7 @@
         <v>13</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA3">
         <v>36</v>
@@ -1395,7 +1413,7 @@
         <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1409,64 +1427,64 @@
         <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
         <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="M4">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R4">
         <v>1.17</v>
       </c>
       <c r="S4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T4">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U4">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V4">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="X4">
         <v>7.8</v>
@@ -1487,7 +1505,7 @@
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE4">
         <v>95</v>
@@ -1499,49 +1517,49 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AI4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
         <v>28</v>
       </c>
       <c r="AK4">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR4">
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU4">
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW4">
         <v>36</v>
@@ -1571,7 +1589,7 @@
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BG4">
         <v>42</v>
@@ -1580,10 +1598,10 @@
         <v>2.64</v>
       </c>
       <c r="BI4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
         <v>7.6</v>
@@ -1592,7 +1610,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1604,13 +1622,13 @@
         <v>19</v>
       </c>
       <c r="BQ4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR4">
         <v>48</v>
       </c>
       <c r="BS4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT4">
         <v>8</v>
@@ -1622,22 +1640,22 @@
         <v>55</v>
       </c>
       <c r="BW4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
+        <v>11</v>
+      </c>
+      <c r="BZ4">
+        <v>55</v>
+      </c>
+      <c r="CA4">
         <v>10.5</v>
       </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
-        <v>10</v>
-      </c>
       <c r="CB4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1651,13 +1669,13 @@
         <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F5">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="G5">
         <v>1.65</v>
@@ -1666,37 +1684,37 @@
         <v>6.6</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>4.2</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R5">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
         <v>2.12</v>
@@ -1705,7 +1723,7 @@
         <v>1.75</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W5">
         <v>2.52</v>
@@ -1717,16 +1735,16 @@
         <v>22</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA5">
         <v>270</v>
       </c>
       <c r="AB5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
         <v>30</v>
@@ -1735,10 +1753,10 @@
         <v>150</v>
       </c>
       <c r="AF5">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH5">
         <v>28</v>
@@ -1771,10 +1789,10 @@
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT5">
         <v>5.8</v>
@@ -1783,22 +1801,22 @@
         <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW5">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY5">
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA5">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -1807,16 +1825,16 @@
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -1879,7 +1897,7 @@
         <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1893,76 +1911,76 @@
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F6">
         <v>3.9</v>
       </c>
       <c r="G6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H6">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I6">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M6">
         <v>1.09</v>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O6">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q6">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
         <v>1.27</v>
       </c>
       <c r="S6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U6">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V6">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X6">
         <v>13.5</v>
       </c>
       <c r="Y6">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA6">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AB6">
         <v>15</v>
@@ -1986,22 +2004,22 @@
         <v>23</v>
       </c>
       <c r="AI6">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
         <v>110</v>
       </c>
       <c r="AK6">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM6">
         <v>150</v>
       </c>
       <c r="AN6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO6">
         <v>24</v>
@@ -2010,7 +2028,7 @@
         <v>9</v>
       </c>
       <c r="AQ6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR6">
         <v>9.800000000000001</v>
@@ -2025,13 +2043,13 @@
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
         <v>19</v>
       </c>
       <c r="AX6">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AY6">
         <v>13</v>
@@ -2040,22 +2058,22 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>32</v>
+        <v>5.6</v>
       </c>
       <c r="BB6">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BC6">
-        <v>5.2</v>
+        <v>42</v>
       </c>
       <c r="BD6">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BE6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF6">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG6">
         <v>15.5</v>
@@ -2094,7 +2112,7 @@
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="BT6">
         <v>4.9</v>
@@ -2112,7 +2130,7 @@
         <v>36</v>
       </c>
       <c r="BY6">
-        <v>8.199999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="BZ6">
         <v>34</v>
@@ -2121,7 +2139,7 @@
         <v>8</v>
       </c>
       <c r="CB6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2135,25 +2153,25 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="G7">
         <v>990</v>
       </c>
       <c r="H7">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2189,10 +2207,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2363,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2377,10 +2395,10 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2605,7 +2623,491 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>107</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9">
+        <v>2.12</v>
+      </c>
+      <c r="G9">
+        <v>2.4</v>
+      </c>
+      <c r="H9">
+        <v>3.85</v>
+      </c>
+      <c r="I9">
+        <v>4.4</v>
+      </c>
+      <c r="J9">
+        <v>3.05</v>
+      </c>
+      <c r="K9">
+        <v>3.35</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.11</v>
+      </c>
+      <c r="N9">
+        <v>2.46</v>
+      </c>
+      <c r="O9">
+        <v>1.29</v>
+      </c>
+      <c r="P9">
+        <v>1.57</v>
+      </c>
+      <c r="Q9">
+        <v>2.42</v>
+      </c>
+      <c r="R9">
+        <v>1.18</v>
+      </c>
+      <c r="S9">
+        <v>4</v>
+      </c>
+      <c r="T9">
+        <v>1.87</v>
+      </c>
+      <c r="U9">
+        <v>1.64</v>
+      </c>
+      <c r="V9">
+        <v>1.29</v>
+      </c>
+      <c r="W9">
+        <v>1.71</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>16</v>
+      </c>
+      <c r="Z9">
+        <v>40</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>10</v>
+      </c>
+      <c r="AC9">
+        <v>10</v>
+      </c>
+      <c r="AD9">
+        <v>24</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>17.5</v>
+      </c>
+      <c r="AG9">
+        <v>16</v>
+      </c>
+      <c r="AH9">
+        <v>950</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>44</v>
+      </c>
+      <c r="AK9">
+        <v>40</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>2.12</v>
+      </c>
+      <c r="AQ9">
+        <v>7.4</v>
+      </c>
+      <c r="AR9">
+        <v>17.5</v>
+      </c>
+      <c r="AS9">
+        <v>2.12</v>
+      </c>
+      <c r="AT9">
+        <v>5</v>
+      </c>
+      <c r="AU9">
+        <v>1.75</v>
+      </c>
+      <c r="AV9">
+        <v>11</v>
+      </c>
+      <c r="AW9">
+        <v>2.12</v>
+      </c>
+      <c r="AX9">
+        <v>8.4</v>
+      </c>
+      <c r="AY9">
+        <v>7.4</v>
+      </c>
+      <c r="AZ9">
+        <v>1.99</v>
+      </c>
+      <c r="BA9">
+        <v>2.12</v>
+      </c>
+      <c r="BB9">
+        <v>19</v>
+      </c>
+      <c r="BC9">
+        <v>18.5</v>
+      </c>
+      <c r="BD9">
+        <v>2.12</v>
+      </c>
+      <c r="BE9">
+        <v>2.12</v>
+      </c>
+      <c r="BF9">
+        <v>2.12</v>
+      </c>
+      <c r="BG9">
+        <v>2.12</v>
+      </c>
+      <c r="BH9">
+        <v>3.6</v>
+      </c>
+      <c r="BI9">
+        <v>2.14</v>
+      </c>
+      <c r="BJ9">
+        <v>15</v>
+      </c>
+      <c r="BK9">
+        <v>2.8</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>3.4</v>
+      </c>
+      <c r="BN9">
+        <v>6.4</v>
+      </c>
+      <c r="BO9">
+        <v>3.35</v>
+      </c>
+      <c r="BP9">
+        <v>25</v>
+      </c>
+      <c r="BQ9">
+        <v>3</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>3.2</v>
+      </c>
+      <c r="BT9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU9">
+        <v>4.8</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>3.2</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>3.3</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>3.2</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10">
+        <v>1.94</v>
+      </c>
+      <c r="G10">
+        <v>2.14</v>
+      </c>
+      <c r="H10">
+        <v>4.2</v>
+      </c>
+      <c r="I10">
+        <v>4.8</v>
+      </c>
+      <c r="J10">
+        <v>3.3</v>
+      </c>
+      <c r="K10">
+        <v>3.75</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>3.1</v>
+      </c>
+      <c r="O10">
+        <v>1.37</v>
+      </c>
+      <c r="P10">
+        <v>1.73</v>
+      </c>
+      <c r="Q10">
+        <v>2.12</v>
+      </c>
+      <c r="R10">
+        <v>1.2</v>
+      </c>
+      <c r="S10">
+        <v>3.85</v>
+      </c>
+      <c r="T10">
+        <v>1.87</v>
+      </c>
+      <c r="U10">
+        <v>1.11</v>
+      </c>
+      <c r="V10">
+        <v>1.26</v>
+      </c>
+      <c r="W10">
+        <v>1.87</v>
+      </c>
+      <c r="X10">
+        <v>1000</v>
+      </c>
+      <c r="Y10">
+        <v>1000</v>
+      </c>
+      <c r="Z10">
+        <v>1000</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC10">
+        <v>1000</v>
+      </c>
+      <c r="AD10">
+        <v>1000</v>
+      </c>
+      <c r="AE10">
+        <v>65</v>
+      </c>
+      <c r="AF10">
+        <v>1000</v>
+      </c>
+      <c r="AG10">
+        <v>1000</v>
+      </c>
+      <c r="AH10">
+        <v>1000</v>
+      </c>
+      <c r="AI10">
+        <v>75</v>
+      </c>
+      <c r="AJ10">
+        <v>1000</v>
+      </c>
+      <c r="AK10">
+        <v>1000</v>
+      </c>
+      <c r="AL10">
+        <v>1000</v>
+      </c>
+      <c r="AM10">
+        <v>1000</v>
+      </c>
+      <c r="AN10">
+        <v>1000</v>
+      </c>
+      <c r="AO10">
+        <v>1000</v>
+      </c>
+      <c r="AP10">
+        <v>1.15</v>
+      </c>
+      <c r="AQ10">
+        <v>1.15</v>
+      </c>
+      <c r="AR10">
+        <v>1.15</v>
+      </c>
+      <c r="AS10">
+        <v>1.15</v>
+      </c>
+      <c r="AT10">
+        <v>1.03</v>
+      </c>
+      <c r="AU10">
+        <v>1.15</v>
+      </c>
+      <c r="AV10">
+        <v>1.15</v>
+      </c>
+      <c r="AW10">
+        <v>1.13</v>
+      </c>
+      <c r="AX10">
+        <v>1.15</v>
+      </c>
+      <c r="AY10">
+        <v>1.15</v>
+      </c>
+      <c r="AZ10">
+        <v>1.15</v>
+      </c>
+      <c r="BA10">
+        <v>1.14</v>
+      </c>
+      <c r="BB10">
+        <v>1.15</v>
+      </c>
+      <c r="BC10">
+        <v>1.15</v>
+      </c>
+      <c r="BD10">
+        <v>1.15</v>
+      </c>
+      <c r="BE10">
+        <v>1.15</v>
+      </c>
+      <c r="BF10">
+        <v>1.15</v>
+      </c>
+      <c r="BG10">
+        <v>1.15</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.04</v>
+      </c>
+      <c r="BJ10">
+        <v>1000</v>
+      </c>
+      <c r="BK10">
+        <v>1.04</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.04</v>
+      </c>
+      <c r="BN10">
+        <v>1000</v>
+      </c>
+      <c r="BO10">
+        <v>1.04</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.04</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.04</v>
+      </c>
+      <c r="BT10">
+        <v>1000</v>
+      </c>
+      <c r="BU10">
+        <v>1.04</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.04</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.04</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.04</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -355,7 +355,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 01:08:30</t>
+    <t>2026-08-03 03:16:47</t>
   </si>
 </sst>
 </file>
@@ -955,67 +955,67 @@
         <v>1.36</v>
       </c>
       <c r="H2">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="I2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K2">
         <v>5.8</v>
       </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
         <v>1.92</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R2">
         <v>1.34</v>
       </c>
       <c r="S2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="U2">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="V2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="X2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y2">
         <v>42</v>
       </c>
       <c r="Z2">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC2">
         <v>13</v>
@@ -1033,10 +1033,10 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="AI2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AJ2">
         <v>9.800000000000001</v>
@@ -1051,7 +1051,7 @@
         <v>400</v>
       </c>
       <c r="AN2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1063,10 +1063,10 @@
         <v>21</v>
       </c>
       <c r="AR2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT2">
         <v>5.9</v>
@@ -1075,10 +1075,10 @@
         <v>10.5</v>
       </c>
       <c r="AV2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX2">
         <v>5.6</v>
@@ -1090,7 +1090,7 @@
         <v>34</v>
       </c>
       <c r="BA2">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
         <v>8.199999999999999</v>
@@ -1099,19 +1099,19 @@
         <v>14.5</v>
       </c>
       <c r="BD2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI2">
         <v>3.1</v>
@@ -1120,22 +1120,22 @@
         <v>16</v>
       </c>
       <c r="BK2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BO2">
         <v>3</v>
       </c>
       <c r="BP2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BQ2">
         <v>5.8</v>
@@ -1144,25 +1144,25 @@
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BT2">
         <v>17.5</v>
       </c>
       <c r="BU2">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BZ2">
         <v>16</v>
@@ -1194,10 +1194,10 @@
         <v>3.35</v>
       </c>
       <c r="G3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I3">
         <v>2.7</v>
@@ -1206,7 +1206,7 @@
         <v>2.98</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L3">
         <v>1.65</v>
@@ -1215,10 +1215,10 @@
         <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O3">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P3">
         <v>1.48</v>
@@ -1239,7 +1239,7 @@
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W3">
         <v>1.4</v>
@@ -1254,7 +1254,7 @@
         <v>15</v>
       </c>
       <c r="AA3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB3">
         <v>8.800000000000001</v>
@@ -1266,7 +1266,7 @@
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>21</v>
@@ -1278,25 +1278,25 @@
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ3">
-        <v>830</v>
+        <v>70</v>
       </c>
       <c r="AK3">
-        <v>360</v>
+        <v>65</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM3">
         <v>1000</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO3">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AP3">
         <v>6.8</v>
@@ -1314,10 +1314,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
         <v>36</v>
@@ -1326,7 +1326,7 @@
         <v>17</v>
       </c>
       <c r="AY3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ3">
         <v>19.5</v>
@@ -1353,64 +1353,64 @@
         <v>38</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="CB3" t="s">
         <v>113</v>
@@ -1433,25 +1433,25 @@
         <v>106</v>
       </c>
       <c r="F4">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="G4">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
+        <v>4.4</v>
+      </c>
+      <c r="I4">
         <v>4.6</v>
-      </c>
-      <c r="I4">
-        <v>4.8</v>
       </c>
       <c r="J4">
         <v>3.05</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M4">
         <v>1.15</v>
@@ -1460,7 +1460,7 @@
         <v>2.48</v>
       </c>
       <c r="O4">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="P4">
         <v>1.48</v>
@@ -1469,10 +1469,10 @@
         <v>3</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="T4">
         <v>2.36</v>
@@ -1481,52 +1481,52 @@
         <v>1.67</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="X4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA4">
         <v>130</v>
       </c>
       <c r="AB4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF4">
         <v>11</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AI4">
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AK4">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AL4">
         <v>75</v>
@@ -1535,34 +1535,34 @@
         <v>260</v>
       </c>
       <c r="AN4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO4">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4">
         <v>10</v>
       </c>
       <c r="AR4">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AS4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU4">
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AW4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AX4">
         <v>10</v>
@@ -1583,7 +1583,7 @@
         <v>28</v>
       </c>
       <c r="BD4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE4">
         <v>50</v>
@@ -1598,7 +1598,7 @@
         <v>2.64</v>
       </c>
       <c r="BI4">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ4">
         <v>12.5</v>
@@ -1610,7 +1610,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1622,22 +1622,22 @@
         <v>19</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV4">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
         <v>10.5</v>
@@ -1646,13 +1646,13 @@
         <v>1000</v>
       </c>
       <c r="BY4">
+        <v>11.5</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
         <v>11</v>
-      </c>
-      <c r="BZ4">
-        <v>55</v>
-      </c>
-      <c r="CA4">
-        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>113</v>
@@ -1681,16 +1681,16 @@
         <v>1.65</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
         <v>3.9</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1708,19 +1708,19 @@
         <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V5">
         <v>1.16</v>
@@ -1753,19 +1753,19 @@
         <v>150</v>
       </c>
       <c r="AF5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI5">
         <v>140</v>
       </c>
       <c r="AJ5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK5">
         <v>23</v>
@@ -1780,7 +1780,7 @@
         <v>14</v>
       </c>
       <c r="AO5">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1789,22 +1789,22 @@
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU5">
         <v>7.8</v>
       </c>
       <c r="AV5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
@@ -1813,10 +1813,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -1825,76 +1825,76 @@
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
         <v>10</v>
       </c>
       <c r="BG5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH5">
+        <v>3.3</v>
+      </c>
+      <c r="BI5">
+        <v>2.64</v>
+      </c>
+      <c r="BJ5">
+        <v>12.5</v>
+      </c>
+      <c r="BK5">
+        <v>5.6</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>9.6</v>
+      </c>
+      <c r="BN5">
+        <v>4.1</v>
+      </c>
+      <c r="BO5">
+        <v>3.2</v>
+      </c>
+      <c r="BP5">
+        <v>11.5</v>
+      </c>
+      <c r="BQ5">
+        <v>8.4</v>
+      </c>
+      <c r="BR5">
+        <v>34</v>
+      </c>
+      <c r="BS5">
         <v>7.8</v>
       </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.04</v>
-      </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB5" t="s">
         <v>113</v>
@@ -1926,7 +1926,7 @@
         <v>2.06</v>
       </c>
       <c r="I6">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J6">
         <v>3.3</v>
@@ -1962,10 +1962,10 @@
         <v>1.91</v>
       </c>
       <c r="U6">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V6">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W6">
         <v>1.3</v>
@@ -1977,31 +1977,31 @@
         <v>8.6</v>
       </c>
       <c r="Z6">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA6">
         <v>28</v>
       </c>
       <c r="AB6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC6">
         <v>8.199999999999999</v>
       </c>
       <c r="AD6">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF6">
         <v>34</v>
       </c>
       <c r="AG6">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AH6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI6">
         <v>46</v>
@@ -2022,13 +2022,13 @@
         <v>75</v>
       </c>
       <c r="AO6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AP6">
         <v>9</v>
       </c>
       <c r="AQ6">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AR6">
         <v>9.800000000000001</v>
@@ -2043,13 +2043,13 @@
         <v>6</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW6">
         <v>19</v>
       </c>
       <c r="AX6">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY6">
         <v>13</v>
@@ -2058,22 +2058,22 @@
         <v>15</v>
       </c>
       <c r="BA6">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BB6">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BC6">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BD6">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE6">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BF6">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG6">
         <v>15.5</v>
@@ -2094,7 +2094,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6">
         <v>7.6</v>
@@ -2106,13 +2106,13 @@
         <v>38</v>
       </c>
       <c r="BQ6">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>2.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
         <v>4.9</v>
@@ -2130,7 +2130,7 @@
         <v>36</v>
       </c>
       <c r="BY6">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
         <v>34</v>
@@ -2159,19 +2159,19 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="G7">
-        <v>990</v>
+        <v>2.92</v>
       </c>
       <c r="H7">
-        <v>1.17</v>
+        <v>2.24</v>
       </c>
       <c r="I7">
         <v>990</v>
       </c>
       <c r="J7">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2192,13 +2192,13 @@
         <v>1.29</v>
       </c>
       <c r="Q7">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="R7">
         <v>1.15</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="T7">
         <v>1.11</v>
@@ -2207,10 +2207,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2643,22 +2643,22 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="G9">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H9">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I9">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2670,13 +2670,13 @@
         <v>2.46</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="P9">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q9">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2691,10 +2691,10 @@
         <v>1.64</v>
       </c>
       <c r="V9">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2763,7 +2763,7 @@
         <v>2.12</v>
       </c>
       <c r="AT9">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU9">
         <v>1.75</v>
@@ -2885,13 +2885,13 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G10">
         <v>2.14</v>
       </c>
       <c r="H10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
         <v>4.8</v>
@@ -2900,19 +2900,19 @@
         <v>3.3</v>
       </c>
       <c r="K10">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O10">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P10">
         <v>1.73</v>
@@ -2921,16 +2921,16 @@
         <v>2.12</v>
       </c>
       <c r="R10">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T10">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V10">
         <v>1.26</v>
@@ -2939,172 +2939,172 @@
         <v>1.87</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB10">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE10">
         <v>65</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI10">
         <v>75</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP10">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="AQ10">
-        <v>1.15</v>
+        <v>11.5</v>
       </c>
       <c r="AR10">
-        <v>1.15</v>
+        <v>4</v>
       </c>
       <c r="AS10">
-        <v>1.15</v>
+        <v>4.3</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU10">
-        <v>1.15</v>
+        <v>6.6</v>
       </c>
       <c r="AV10">
-        <v>1.15</v>
+        <v>15</v>
       </c>
       <c r="AW10">
-        <v>1.13</v>
+        <v>4.2</v>
       </c>
       <c r="AX10">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="AY10">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="AZ10">
-        <v>1.15</v>
+        <v>17</v>
       </c>
       <c r="BA10">
-        <v>1.14</v>
+        <v>4.2</v>
       </c>
       <c r="BB10">
-        <v>1.15</v>
+        <v>21</v>
       </c>
       <c r="BC10">
-        <v>1.15</v>
+        <v>20</v>
       </c>
       <c r="BD10">
-        <v>1.15</v>
+        <v>4.1</v>
       </c>
       <c r="BE10">
-        <v>1.15</v>
+        <v>4.3</v>
       </c>
       <c r="BF10">
-        <v>1.15</v>
+        <v>13.5</v>
       </c>
       <c r="BG10">
-        <v>1.15</v>
+        <v>4.3</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>1.59</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="CB10" t="s">
         <v>113</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -355,7 +355,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 03:16:47</t>
+    <t>2026-08-03 05:24:55</t>
   </si>
 </sst>
 </file>
@@ -949,40 +949,40 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="G2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K2">
         <v>5.8</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R2">
         <v>1.34</v>
@@ -991,13 +991,13 @@
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="U2">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W2">
         <v>3.75</v>
@@ -1006,25 +1006,25 @@
         <v>17</v>
       </c>
       <c r="Y2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Z2">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AD2">
         <v>950</v>
       </c>
       <c r="AE2">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="AF2">
         <v>6.6</v>
@@ -1033,7 +1033,7 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AI2">
         <v>310</v>
@@ -1048,7 +1048,7 @@
         <v>70</v>
       </c>
       <c r="AM2">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="AN2">
         <v>7.2</v>
@@ -1057,28 +1057,28 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AQ2">
         <v>21</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AT2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
         <v>10.5</v>
       </c>
       <c r="AV2">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="AW2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
         <v>5.6</v>
@@ -1090,31 +1090,31 @@
         <v>34</v>
       </c>
       <c r="BA2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BC2">
         <v>14.5</v>
       </c>
       <c r="BD2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF2">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH2">
         <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2">
         <v>16</v>
@@ -1126,7 +1126,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN2">
         <v>3.45</v>
@@ -1141,7 +1141,7 @@
         <v>5.8</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS2">
         <v>9.6</v>
@@ -1162,7 +1162,7 @@
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>16</v>
@@ -1191,25 +1191,25 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H3">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I3">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J3">
+        <v>2.94</v>
+      </c>
+      <c r="K3">
         <v>2.98</v>
       </c>
-      <c r="K3">
-        <v>3.1</v>
-      </c>
       <c r="L3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M3">
         <v>1.15</v>
@@ -1227,7 +1227,7 @@
         <v>3</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S3">
         <v>6.4</v>
@@ -1239,22 +1239,22 @@
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W3">
         <v>1.4</v>
       </c>
       <c r="X3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="Y3">
         <v>7.6</v>
       </c>
       <c r="Z3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB3">
         <v>8.800000000000001</v>
@@ -1266,7 +1266,7 @@
         <v>14</v>
       </c>
       <c r="AE3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF3">
         <v>21</v>
@@ -1278,19 +1278,19 @@
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ3">
         <v>70</v>
       </c>
       <c r="AK3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL3">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN3">
         <v>85</v>
@@ -1302,43 +1302,43 @@
         <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR3">
         <v>13.5</v>
       </c>
       <c r="AS3">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT3">
         <v>8.199999999999999</v>
       </c>
       <c r="AU3">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
         <v>36</v>
       </c>
       <c r="AX3">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AY3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BA3">
         <v>36</v>
       </c>
       <c r="BB3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="BC3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BD3">
         <v>65</v>
@@ -1347,7 +1347,7 @@
         <v>50</v>
       </c>
       <c r="BF3">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BG3">
         <v>38</v>
@@ -1433,16 +1433,16 @@
         <v>106</v>
       </c>
       <c r="F4">
+        <v>2.18</v>
+      </c>
+      <c r="G4">
         <v>2.2</v>
-      </c>
-      <c r="G4">
-        <v>2.22</v>
       </c>
       <c r="H4">
         <v>4.4</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4">
         <v>3.05</v>
@@ -1475,19 +1475,19 @@
         <v>6.6</v>
       </c>
       <c r="T4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Y4">
         <v>11</v>
@@ -1499,7 +1499,7 @@
         <v>130</v>
       </c>
       <c r="AB4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
@@ -1508,10 +1508,10 @@
         <v>21</v>
       </c>
       <c r="AE4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
         <v>12.5</v>
@@ -1520,7 +1520,7 @@
         <v>29</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ4">
         <v>32</v>
@@ -1529,10 +1529,10 @@
         <v>34</v>
       </c>
       <c r="AL4">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>36</v>
@@ -1541,7 +1541,7 @@
         <v>150</v>
       </c>
       <c r="AP4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
         <v>10</v>
@@ -1559,7 +1559,7 @@
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW4">
         <v>34</v>
@@ -1678,37 +1678,37 @@
         <v>1.64</v>
       </c>
       <c r="G5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H5">
         <v>6.8</v>
       </c>
       <c r="I5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5">
         <v>1.46</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
         <v>1.78</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R5">
         <v>1.29</v>
@@ -1717,19 +1717,19 @@
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V5">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
         <v>2.52</v>
       </c>
       <c r="X5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y5">
         <v>22</v>
@@ -1744,7 +1744,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD5">
         <v>30</v>
@@ -1759,13 +1759,13 @@
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI5">
         <v>140</v>
       </c>
       <c r="AJ5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK5">
         <v>23</v>
@@ -1789,22 +1789,22 @@
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
         <v>6</v>
       </c>
       <c r="AU5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX5">
         <v>7.2</v>
@@ -1816,7 +1816,7 @@
         <v>6.6</v>
       </c>
       <c r="BA5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
         <v>13</v>
@@ -1825,16 +1825,16 @@
         <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
         <v>3.3</v>
@@ -1846,7 +1846,7 @@
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -1861,16 +1861,16 @@
         <v>3.2</v>
       </c>
       <c r="BP5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT5">
         <v>11</v>
@@ -1882,7 +1882,7 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -1917,7 +1917,7 @@
         <v>108</v>
       </c>
       <c r="F6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G6">
         <v>4.4</v>
@@ -1947,19 +1947,19 @@
         <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q6">
         <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S6">
         <v>4.1</v>
       </c>
       <c r="T6">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U6">
         <v>1.94</v>
@@ -1995,7 +1995,7 @@
         <v>26</v>
       </c>
       <c r="AF6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG6">
         <v>18</v>
@@ -2013,7 +2013,7 @@
         <v>60</v>
       </c>
       <c r="AL6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM6">
         <v>150</v>
@@ -2028,7 +2028,7 @@
         <v>9</v>
       </c>
       <c r="AQ6">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR6">
         <v>9.800000000000001</v>
@@ -2037,13 +2037,13 @@
         <v>20</v>
       </c>
       <c r="AT6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU6">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
         <v>19</v>
@@ -2052,28 +2052,28 @@
         <v>6.6</v>
       </c>
       <c r="AY6">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BA6">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="BB6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC6">
         <v>38</v>
       </c>
       <c r="BD6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG6">
         <v>15.5</v>
@@ -2094,7 +2094,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN6">
         <v>7.6</v>
@@ -2106,13 +2106,13 @@
         <v>38</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT6">
         <v>4.9</v>
@@ -2121,7 +2121,7 @@
         <v>3.8</v>
       </c>
       <c r="BV6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BW6">
         <v>6.4</v>
@@ -2136,7 +2136,7 @@
         <v>34</v>
       </c>
       <c r="CA6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB6" t="s">
         <v>113</v>
@@ -2159,7 +2159,7 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="G7">
         <v>2.92</v>
@@ -2171,7 +2171,7 @@
         <v>990</v>
       </c>
       <c r="J7">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="K7">
         <v>950</v>
@@ -2183,16 +2183,16 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O7">
         <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R7">
         <v>1.15</v>
@@ -2207,10 +2207,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2643,16 +2643,16 @@
         <v>111</v>
       </c>
       <c r="F9">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="G9">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H9">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I9">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J9">
         <v>3.1</v>
@@ -2691,10 +2691,10 @@
         <v>1.64</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W9">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2820,13 +2820,13 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BN9">
         <v>6.4</v>
       </c>
       <c r="BO9">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BP9">
         <v>25</v>
@@ -2838,7 +2838,7 @@
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BT9">
         <v>9.800000000000001</v>
@@ -2850,7 +2850,7 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -2862,7 +2862,7 @@
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="CB9" t="s">
         <v>113</v>
@@ -2885,10 +2885,10 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G10">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H10">
         <v>4.1</v>
@@ -2900,7 +2900,7 @@
         <v>3.3</v>
       </c>
       <c r="K10">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2936,7 +2936,7 @@
         <v>1.26</v>
       </c>
       <c r="W10">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X10">
         <v>14</v>
@@ -2945,10 +2945,10 @@
         <v>16.5</v>
       </c>
       <c r="Z10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA10">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB10">
         <v>9.6</v>
@@ -2975,10 +2975,10 @@
         <v>75</v>
       </c>
       <c r="AJ10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK10">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL10">
         <v>55</v>
@@ -2990,7 +2990,7 @@
         <v>23</v>
       </c>
       <c r="AO10">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP10">
         <v>10</v>
@@ -2999,10 +2999,10 @@
         <v>11.5</v>
       </c>
       <c r="AR10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT10">
         <v>6.8</v>
@@ -3014,7 +3014,7 @@
         <v>15</v>
       </c>
       <c r="AW10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX10">
         <v>10</v>
@@ -3026,7 +3026,7 @@
         <v>17</v>
       </c>
       <c r="BA10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB10">
         <v>21</v>
@@ -3035,16 +3035,16 @@
         <v>20</v>
       </c>
       <c r="BD10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF10">
         <v>13.5</v>
       </c>
       <c r="BG10">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH10">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -355,7 +355,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 05:24:55</t>
+    <t>2026-08-03 07:32:48</t>
   </si>
 </sst>
 </file>
@@ -952,64 +952,64 @@
         <v>1.34</v>
       </c>
       <c r="G2">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="J2">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L2">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="U2">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="V2">
         <v>1.08</v>
       </c>
       <c r="W2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Y2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z2">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1018,151 +1018,151 @@
         <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AD2">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AE2">
-        <v>410</v>
+        <v>270</v>
       </c>
       <c r="AF2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AI2">
-        <v>310</v>
+        <v>210</v>
       </c>
       <c r="AJ2">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AK2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AM2">
-        <v>430</v>
+        <v>300</v>
       </c>
       <c r="AN2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP2">
+        <v>16</v>
+      </c>
+      <c r="AQ2">
+        <v>22</v>
+      </c>
+      <c r="AR2">
+        <v>8</v>
+      </c>
+      <c r="AS2">
+        <v>8.6</v>
+      </c>
+      <c r="AT2">
+        <v>6.4</v>
+      </c>
+      <c r="AU2">
         <v>11</v>
       </c>
-      <c r="AQ2">
-        <v>21</v>
-      </c>
-      <c r="AR2">
-        <v>7.6</v>
-      </c>
-      <c r="AS2">
-        <v>8</v>
-      </c>
-      <c r="AT2">
+      <c r="AV2">
+        <v>29</v>
+      </c>
+      <c r="AW2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX2">
         <v>6.2</v>
       </c>
-      <c r="AU2">
-        <v>10.5</v>
-      </c>
-      <c r="AV2">
-        <v>36</v>
-      </c>
-      <c r="AW2">
-        <v>7.8</v>
-      </c>
-      <c r="AX2">
-        <v>5.6</v>
-      </c>
       <c r="AY2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="BA2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BC2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD2">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BE2">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2">
         <v>5.7</v>
       </c>
       <c r="BG2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ2">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BK2">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BO2">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BP2">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BQ2">
         <v>5.8</v>
       </c>
       <c r="BR2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS2">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT2">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU2">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>16</v>
@@ -1191,61 +1191,61 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I3">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="J3">
+        <v>2.9</v>
+      </c>
+      <c r="K3">
         <v>2.94</v>
       </c>
-      <c r="K3">
-        <v>2.98</v>
-      </c>
       <c r="L3">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M3">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="P3">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R3">
         <v>1.16</v>
       </c>
       <c r="S3">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V3">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
         <v>1.4</v>
       </c>
       <c r="X3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y3">
         <v>7.6</v>
@@ -1254,7 +1254,7 @@
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB3">
         <v>8.800000000000001</v>
@@ -1263,22 +1263,22 @@
         <v>7.2</v>
       </c>
       <c r="AD3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH3">
         <v>27</v>
       </c>
       <c r="AI3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
         <v>70</v>
@@ -1287,22 +1287,22 @@
         <v>60</v>
       </c>
       <c r="AL3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM3">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AN3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO3">
         <v>55</v>
       </c>
       <c r="AP3">
+        <v>6.6</v>
+      </c>
+      <c r="AQ3">
         <v>6.8</v>
-      </c>
-      <c r="AQ3">
-        <v>7</v>
       </c>
       <c r="AR3">
         <v>13.5</v>
@@ -1311,7 +1311,7 @@
         <v>38</v>
       </c>
       <c r="AT3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AU3">
         <v>6.6</v>
@@ -1323,10 +1323,10 @@
         <v>36</v>
       </c>
       <c r="AX3">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ3">
         <v>24</v>
@@ -1353,10 +1353,10 @@
         <v>38</v>
       </c>
       <c r="BH3">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BI3">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="BJ3">
         <v>12.5</v>
@@ -1374,34 +1374,34 @@
         <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU3">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BW3">
         <v>7.8</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY3">
         <v>9.4</v>
@@ -1410,7 +1410,7 @@
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="CB3" t="s">
         <v>113</v>
@@ -1436,7 +1436,7 @@
         <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
         <v>4.4</v>
@@ -1463,7 +1463,7 @@
         <v>1.64</v>
       </c>
       <c r="P4">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="Q4">
         <v>3</v>
@@ -1472,10 +1472,10 @@
         <v>1.16</v>
       </c>
       <c r="S4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="T4">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="U4">
         <v>1.68</v>
@@ -1484,7 +1484,7 @@
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="X4">
         <v>7.6</v>
@@ -1523,10 +1523,10 @@
         <v>130</v>
       </c>
       <c r="AJ4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AL4">
         <v>1000</v>
@@ -1538,7 +1538,7 @@
         <v>36</v>
       </c>
       <c r="AO4">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AP4">
         <v>7</v>
@@ -1702,25 +1702,25 @@
         <v>3.4</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="V5">
         <v>1.15</v>
@@ -1732,7 +1732,7 @@
         <v>13.5</v>
       </c>
       <c r="Y5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z5">
         <v>65</v>
@@ -1741,46 +1741,46 @@
         <v>270</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
         <v>30</v>
       </c>
       <c r="AE5">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF5">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ5">
         <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AL5">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM5">
+        <v>180</v>
+      </c>
+      <c r="AN5">
+        <v>12.5</v>
+      </c>
+      <c r="AO5">
         <v>210</v>
-      </c>
-      <c r="AN5">
-        <v>14</v>
-      </c>
-      <c r="AO5">
-        <v>250</v>
       </c>
       <c r="AP5">
         <v>10</v>
@@ -1789,52 +1789,52 @@
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU5">
         <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AW5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX5">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY5">
         <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB5">
         <v>13</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BD5">
-        <v>7.6</v>
+        <v>34</v>
       </c>
       <c r="BE5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH5">
         <v>3.3</v>
@@ -1864,7 +1864,7 @@
         <v>12</v>
       </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
         <v>32</v>
@@ -1920,52 +1920,52 @@
         <v>3.95</v>
       </c>
       <c r="G6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H6">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K6">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P6">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U6">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V6">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W6">
         <v>1.3</v>
@@ -1974,7 +1974,7 @@
         <v>13.5</v>
       </c>
       <c r="Y6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="Z6">
         <v>13.5</v>
@@ -1995,19 +1995,19 @@
         <v>26</v>
       </c>
       <c r="AF6">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG6">
         <v>18</v>
       </c>
       <c r="AH6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6">
         <v>46</v>
       </c>
       <c r="AJ6">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AK6">
         <v>60</v>
@@ -2016,13 +2016,13 @@
         <v>70</v>
       </c>
       <c r="AM6">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP6">
         <v>9</v>
@@ -2049,7 +2049,7 @@
         <v>19</v>
       </c>
       <c r="AX6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY6">
         <v>14.5</v>
@@ -2061,34 +2061,34 @@
         <v>32</v>
       </c>
       <c r="BB6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC6">
         <v>38</v>
       </c>
       <c r="BD6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BE6">
+        <v>8.6</v>
+      </c>
+      <c r="BF6">
         <v>8</v>
-      </c>
-      <c r="BF6">
-        <v>7.6</v>
       </c>
       <c r="BG6">
         <v>15.5</v>
       </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BI6">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
@@ -2109,10 +2109,10 @@
         <v>8.4</v>
       </c>
       <c r="BR6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BS6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
         <v>4.9</v>
@@ -2121,22 +2121,22 @@
         <v>3.8</v>
       </c>
       <c r="BV6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BW6">
         <v>6.4</v>
       </c>
       <c r="BX6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BY6">
         <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="CA6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="CB6" t="s">
         <v>113</v>
@@ -2159,7 +2159,7 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="G7">
         <v>2.92</v>
@@ -2207,10 +2207,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W7">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2646,19 +2646,19 @@
         <v>2.12</v>
       </c>
       <c r="G9">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H9">
         <v>3.8</v>
       </c>
       <c r="I9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J9">
         <v>3.1</v>
       </c>
       <c r="K9">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2676,7 +2676,7 @@
         <v>1.59</v>
       </c>
       <c r="Q9">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2691,10 +2691,10 @@
         <v>1.64</v>
       </c>
       <c r="V9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W9">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2915,7 +2915,7 @@
         <v>1.38</v>
       </c>
       <c r="P10">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q10">
         <v>2.12</v>
@@ -2930,7 +2930,7 @@
         <v>1.89</v>
       </c>
       <c r="U10">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V10">
         <v>1.26</v>
@@ -2990,7 +2990,7 @@
         <v>23</v>
       </c>
       <c r="AO10">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP10">
         <v>10</v>
@@ -3038,7 +3038,7 @@
         <v>4.2</v>
       </c>
       <c r="BE10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF10">
         <v>13.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -355,7 +355,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 07:32:48</t>
+    <t>2026-08-03 09:40:53</t>
   </si>
 </sst>
 </file>
@@ -949,52 +949,52 @@
         <v>104</v>
       </c>
       <c r="F2">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="G2">
         <v>1.35</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K2">
         <v>6</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O2">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P2">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V2">
         <v>1.08</v>
@@ -1003,70 +1003,70 @@
         <v>3.85</v>
       </c>
       <c r="X2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="Y2">
         <v>32</v>
       </c>
       <c r="Z2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>760</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD2">
         <v>55</v>
       </c>
       <c r="AE2">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="AF2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AG2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AI2">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AJ2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK2">
         <v>17</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AN2">
         <v>7</v>
       </c>
       <c r="AO2">
-        <v>460</v>
+        <v>540</v>
       </c>
       <c r="AP2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AR2">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="AS2">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
@@ -1075,67 +1075,67 @@
         <v>11</v>
       </c>
       <c r="AV2">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AW2">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AX2">
         <v>6.2</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
         <v>26</v>
       </c>
       <c r="BA2">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BB2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD2">
         <v>38</v>
       </c>
       <c r="BE2">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BF2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ2">
+        <v>14.5</v>
+      </c>
+      <c r="BK2">
+        <v>7</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
         <v>13.5</v>
       </c>
-      <c r="BK2">
-        <v>6.2</v>
-      </c>
-      <c r="BL2">
-        <v>1000</v>
-      </c>
-      <c r="BM2">
-        <v>11</v>
-      </c>
       <c r="BN2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BO2">
         <v>3.2</v>
       </c>
       <c r="BP2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BQ2">
         <v>5.8</v>
@@ -1144,25 +1144,25 @@
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BU2">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2">
         <v>16</v>
@@ -1191,19 +1191,19 @@
         <v>105</v>
       </c>
       <c r="F3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I3">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J3">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
         <v>2.94</v>
@@ -1221,7 +1221,7 @@
         <v>1.68</v>
       </c>
       <c r="P3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q3">
         <v>3.1</v>
@@ -1236,13 +1236,13 @@
         <v>2.34</v>
       </c>
       <c r="U3">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X3">
         <v>7.2</v>
@@ -1254,19 +1254,19 @@
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE3">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>20</v>
@@ -1287,7 +1287,7 @@
         <v>60</v>
       </c>
       <c r="AL3">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM3">
         <v>250</v>
@@ -1296,13 +1296,13 @@
         <v>90</v>
       </c>
       <c r="AO3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP3">
         <v>6.6</v>
       </c>
       <c r="AQ3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR3">
         <v>13.5</v>
@@ -1311,13 +1311,13 @@
         <v>38</v>
       </c>
       <c r="AT3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
         <v>36</v>
@@ -1332,10 +1332,10 @@
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BB3">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BC3">
         <v>50</v>
@@ -1353,25 +1353,25 @@
         <v>38</v>
       </c>
       <c r="BH3">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="BI3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="BJ3">
         <v>12.5</v>
       </c>
       <c r="BK3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
         <v>4.7</v>
@@ -1380,37 +1380,37 @@
         <v>36</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT3">
         <v>5.6</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV3">
         <v>27</v>
       </c>
       <c r="BW3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BX3">
         <v>60</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>113</v>
@@ -1442,7 +1442,7 @@
         <v>4.4</v>
       </c>
       <c r="I4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
         <v>3.05</v>
@@ -1457,28 +1457,28 @@
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O4">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R4">
         <v>1.16</v>
       </c>
       <c r="S4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="U4">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="V4">
         <v>1.27</v>
@@ -1487,7 +1487,7 @@
         <v>1.81</v>
       </c>
       <c r="X4">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Y4">
         <v>11</v>
@@ -1520,13 +1520,13 @@
         <v>29</v>
       </c>
       <c r="AI4">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK4">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AL4">
         <v>1000</v>
@@ -1541,7 +1541,7 @@
         <v>160</v>
       </c>
       <c r="AP4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4">
         <v>10</v>
@@ -1550,10 +1550,10 @@
         <v>26</v>
       </c>
       <c r="AS4">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AT4">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU4">
         <v>6.8</v>
@@ -1562,13 +1562,13 @@
         <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AX4">
         <v>10</v>
       </c>
       <c r="AY4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4">
         <v>25</v>
@@ -1577,7 +1577,7 @@
         <v>42</v>
       </c>
       <c r="BB4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC4">
         <v>28</v>
@@ -1589,13 +1589,13 @@
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG4">
         <v>42</v>
       </c>
       <c r="BH4">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BI4">
         <v>2.22</v>
@@ -1610,7 +1610,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN4">
         <v>4.7</v>
@@ -1622,13 +1622,13 @@
         <v>19</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4">
         <v>7.8</v>
@@ -1640,19 +1640,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
+        <v>12</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
         <v>11.5</v>
-      </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
-        <v>11</v>
       </c>
       <c r="CB4" t="s">
         <v>113</v>
@@ -1675,22 +1675,22 @@
         <v>107</v>
       </c>
       <c r="F5">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G5">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>3.85</v>
       </c>
       <c r="K5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L5">
         <v>1.46</v>
@@ -1699,34 +1699,34 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R5">
         <v>1.3</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U5">
         <v>1.8</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="X5">
         <v>13.5</v>
@@ -1741,13 +1741,13 @@
         <v>270</v>
       </c>
       <c r="AB5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE5">
         <v>130</v>
@@ -1768,10 +1768,10 @@
         <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL5">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM5">
         <v>180</v>
@@ -1789,13 +1789,13 @@
         <v>16</v>
       </c>
       <c r="AR5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS5">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AT5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU5">
         <v>7.6</v>
@@ -1804,7 +1804,7 @@
         <v>21</v>
       </c>
       <c r="AW5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX5">
         <v>7.8</v>
@@ -1816,25 +1816,25 @@
         <v>19</v>
       </c>
       <c r="BA5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
         <v>13</v>
       </c>
       <c r="BC5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BE5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF5">
         <v>9.4</v>
       </c>
       <c r="BG5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH5">
         <v>3.3</v>
@@ -1846,13 +1846,13 @@
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
         <v>4.1</v>
@@ -1864,37 +1864,37 @@
         <v>12</v>
       </c>
       <c r="BQ5">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ5">
         <v>26</v>
       </c>
       <c r="CA5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB5" t="s">
         <v>113</v>
@@ -1959,13 +1959,13 @@
         <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U6">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V6">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W6">
         <v>1.3</v>
@@ -2159,7 +2159,7 @@
         <v>109</v>
       </c>
       <c r="F7">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="G7">
         <v>2.92</v>
@@ -2183,16 +2183,16 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O7">
         <v>1.33</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R7">
         <v>1.15</v>
@@ -2207,7 +2207,7 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W7">
         <v>1.52</v>
@@ -2670,13 +2670,13 @@
         <v>2.46</v>
       </c>
       <c r="O9">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="P9">
         <v>1.59</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R9">
         <v>1.18</v>
@@ -2685,10 +2685,10 @@
         <v>4</v>
       </c>
       <c r="T9">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U9">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V9">
         <v>1.3</v>
@@ -2700,10 +2700,10 @@
         <v>1000</v>
       </c>
       <c r="Y9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2715,7 +2715,7 @@
         <v>10</v>
       </c>
       <c r="AD9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE9">
         <v>1000</v>
@@ -2724,7 +2724,7 @@
         <v>17.5</v>
       </c>
       <c r="AG9">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH9">
         <v>950</v>
@@ -2733,7 +2733,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK9">
         <v>40</v>
@@ -2751,7 +2751,7 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AQ9">
         <v>7.4</v>
@@ -2760,19 +2760,19 @@
         <v>17.5</v>
       </c>
       <c r="AS9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AT9">
         <v>5.1</v>
       </c>
       <c r="AU9">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AV9">
         <v>11</v>
       </c>
       <c r="AW9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AX9">
         <v>8.4</v>
@@ -2781,10 +2781,10 @@
         <v>7.4</v>
       </c>
       <c r="AZ9">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="BA9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BB9">
         <v>19</v>
@@ -2793,52 +2793,52 @@
         <v>18.5</v>
       </c>
       <c r="BD9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BE9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BF9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BG9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="BH9">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="BJ9">
         <v>15</v>
       </c>
       <c r="BK9">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>3.45</v>
+        <v>1.76</v>
       </c>
       <c r="BN9">
         <v>6.4</v>
       </c>
       <c r="BO9">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BP9">
         <v>25</v>
       </c>
       <c r="BQ9">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>3.25</v>
+        <v>1.71</v>
       </c>
       <c r="BT9">
         <v>9.800000000000001</v>
@@ -2850,19 +2850,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>3.25</v>
+        <v>1.71</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>3.3</v>
+        <v>1.72</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>3.25</v>
+        <v>1.71</v>
       </c>
       <c r="CB9" t="s">
         <v>113</v>
@@ -2885,7 +2885,7 @@
         <v>112</v>
       </c>
       <c r="F10">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G10">
         <v>2.12</v>
@@ -2897,7 +2897,7 @@
         <v>4.8</v>
       </c>
       <c r="J10">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10">
         <v>3.75</v>
@@ -2909,7 +2909,7 @@
         <v>1.08</v>
       </c>
       <c r="N10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O10">
         <v>1.38</v>
@@ -3068,7 +3068,7 @@
         <v>6.4</v>
       </c>
       <c r="BO10">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BP10">
         <v>22</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
+    <t>Bolivian Liga de Futbol Profesional</t>
+  </si>
+  <si>
     <t>2026-08-04</t>
   </si>
   <si>
@@ -295,9 +298,15 @@
     <t>18:30:00</t>
   </si>
   <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
     <t>21:10:00</t>
   </si>
   <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
     <t>23:15:00</t>
   </si>
   <si>
@@ -322,9 +331,15 @@
     <t>Thor</t>
   </si>
   <si>
+    <t>Academia de Balompie Boliviano</t>
+  </si>
+  <si>
     <t>Llaneros FC</t>
   </si>
   <si>
+    <t>Club Independiente Petrolero</t>
+  </si>
+  <si>
     <t>Tolima</t>
   </si>
   <si>
@@ -349,13 +364,19 @@
     <t>Breidablik</t>
   </si>
   <si>
+    <t>CDT Real Oruro</t>
+  </si>
+  <si>
     <t>Fortaleza FC</t>
   </si>
   <si>
+    <t>Aurora</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 09:40:53</t>
+    <t>2026-08-03 11:49:47</t>
   </si>
 </sst>
 </file>
@@ -687,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -937,196 +958,196 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="G2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P2">
         <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T2">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="X2">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y2">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Z2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA2">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD2">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AE2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AF2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AG2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI2">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="AJ2">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AK2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM2">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="AN2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO2">
-        <v>540</v>
+        <v>580</v>
       </c>
       <c r="AP2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AQ2">
         <v>27</v>
       </c>
       <c r="AR2">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="AS2">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV2">
         <v>38</v>
       </c>
       <c r="AW2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AX2">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BA2">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BB2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC2">
+        <v>14.5</v>
+      </c>
+      <c r="BD2">
+        <v>12</v>
+      </c>
+      <c r="BE2">
+        <v>14.5</v>
+      </c>
+      <c r="BF2">
+        <v>5.7</v>
+      </c>
+      <c r="BG2">
         <v>15</v>
       </c>
-      <c r="BD2">
-        <v>38</v>
-      </c>
-      <c r="BE2">
-        <v>13</v>
-      </c>
-      <c r="BF2">
-        <v>6</v>
-      </c>
-      <c r="BG2">
-        <v>13</v>
-      </c>
       <c r="BH2">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BI2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ2">
         <v>14.5</v>
       </c>
       <c r="BK2">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>3.6</v>
@@ -1138,40 +1159,40 @@
         <v>8</v>
       </c>
       <c r="BQ2">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT2">
         <v>15.5</v>
       </c>
       <c r="BU2">
-        <v>7.4</v>
+        <v>12</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>16</v>
       </c>
       <c r="CA2">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="CB2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1179,28 +1200,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G3">
         <v>3.4</v>
       </c>
       <c r="H3">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="I3">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J3">
         <v>2.92</v>
@@ -1218,7 +1239,7 @@
         <v>2.44</v>
       </c>
       <c r="O3">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="P3">
         <v>1.46</v>
@@ -1233,13 +1254,13 @@
         <v>6.8</v>
       </c>
       <c r="T3">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="U3">
         <v>1.71</v>
       </c>
       <c r="V3">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W3">
         <v>1.41</v>
@@ -1248,16 +1269,16 @@
         <v>7.2</v>
       </c>
       <c r="Y3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z3">
         <v>15.5</v>
       </c>
       <c r="AA3">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB3">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC3">
         <v>6.8</v>
@@ -1290,7 +1311,7 @@
         <v>95</v>
       </c>
       <c r="AM3">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN3">
         <v>90</v>
@@ -1299,10 +1320,10 @@
         <v>60</v>
       </c>
       <c r="AP3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR3">
         <v>13.5</v>
@@ -1317,31 +1338,31 @@
         <v>6.4</v>
       </c>
       <c r="AV3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AX3">
         <v>18</v>
       </c>
       <c r="AY3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AZ3">
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BC3">
         <v>50</v>
       </c>
       <c r="BD3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BE3">
         <v>50</v>
@@ -1350,70 +1371,70 @@
         <v>55</v>
       </c>
       <c r="BG3">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BH3">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1421,28 +1442,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G4">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4">
         <v>3.05</v>
@@ -1457,16 +1478,16 @@
         <v>1.15</v>
       </c>
       <c r="N4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
         <v>1.65</v>
       </c>
       <c r="P4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="Q4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R4">
         <v>1.16</v>
@@ -1475,7 +1496,7 @@
         <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U4">
         <v>1.67</v>
@@ -1484,7 +1505,7 @@
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X4">
         <v>7.4</v>
@@ -1493,7 +1514,7 @@
         <v>11</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA4">
         <v>130</v>
@@ -1502,7 +1523,7 @@
         <v>6.4</v>
       </c>
       <c r="AC4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD4">
         <v>21</v>
@@ -1523,13 +1544,13 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK4">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM4">
         <v>1000</v>
@@ -1550,7 +1571,7 @@
         <v>26</v>
       </c>
       <c r="AS4">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AT4">
         <v>5.9</v>
@@ -1559,10 +1580,10 @@
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW4">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AX4">
         <v>10</v>
@@ -1574,7 +1595,7 @@
         <v>25</v>
       </c>
       <c r="BA4">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BB4">
         <v>26</v>
@@ -1586,7 +1607,7 @@
         <v>60</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="BF4">
         <v>30</v>
@@ -1595,67 +1616,67 @@
         <v>42</v>
       </c>
       <c r="BH4">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="BI4">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK4">
+        <v>7.4</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>16.5</v>
+      </c>
+      <c r="BN4">
+        <v>4.6</v>
+      </c>
+      <c r="BO4">
+        <v>4.2</v>
+      </c>
+      <c r="BP4">
+        <v>20</v>
+      </c>
+      <c r="BQ4">
+        <v>9.4</v>
+      </c>
+      <c r="BR4">
+        <v>50</v>
+      </c>
+      <c r="BS4">
+        <v>13</v>
+      </c>
+      <c r="BT4">
         <v>7.6</v>
       </c>
-      <c r="BL4">
-        <v>1000</v>
-      </c>
-      <c r="BM4">
+      <c r="BU4">
+        <v>5.7</v>
+      </c>
+      <c r="BV4">
+        <v>55</v>
+      </c>
+      <c r="BW4">
+        <v>13</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>14.5</v>
+      </c>
+      <c r="BZ4">
+        <v>60</v>
+      </c>
+      <c r="CA4">
         <v>13.5</v>
       </c>
-      <c r="BN4">
-        <v>4.7</v>
-      </c>
-      <c r="BO4">
-        <v>4</v>
-      </c>
-      <c r="BP4">
-        <v>19</v>
-      </c>
-      <c r="BQ4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BR4">
-        <v>1000</v>
-      </c>
-      <c r="BS4">
-        <v>11</v>
-      </c>
-      <c r="BT4">
-        <v>7.8</v>
-      </c>
-      <c r="BU4">
-        <v>5</v>
-      </c>
-      <c r="BV4">
-        <v>1000</v>
-      </c>
-      <c r="BW4">
-        <v>11</v>
-      </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>12</v>
-      </c>
-      <c r="BZ4">
-        <v>1000</v>
-      </c>
-      <c r="CA4">
-        <v>11.5</v>
-      </c>
       <c r="CB4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1663,16 +1684,16 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F5">
         <v>1.65</v>
@@ -1702,13 +1723,13 @@
         <v>3.35</v>
       </c>
       <c r="O5">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
         <v>1.79</v>
       </c>
       <c r="Q5">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R5">
         <v>1.3</v>
@@ -1717,7 +1738,7 @@
         <v>4.2</v>
       </c>
       <c r="T5">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
         <v>1.8</v>
@@ -1729,13 +1750,13 @@
         <v>2.44</v>
       </c>
       <c r="X5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA5">
         <v>270</v>
@@ -1744,7 +1765,7 @@
         <v>7.4</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5">
         <v>28</v>
@@ -1756,7 +1777,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG5">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH5">
         <v>25</v>
@@ -1777,64 +1798,64 @@
         <v>180</v>
       </c>
       <c r="AN5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO5">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AP5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR5">
-        <v>7.8</v>
+        <v>40</v>
       </c>
       <c r="AS5">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT5">
         <v>6.4</v>
       </c>
       <c r="AU5">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5">
-        <v>8.4</v>
+        <v>65</v>
       </c>
       <c r="AX5">
         <v>7.8</v>
       </c>
       <c r="AY5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>8.4</v>
+        <v>65</v>
       </c>
       <c r="BB5">
         <v>13</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD5">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="BE5">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF5">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG5">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH5">
         <v>3.3</v>
@@ -1846,10 +1867,10 @@
         <v>12.5</v>
       </c>
       <c r="BK5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM5">
         <v>9.800000000000001</v>
@@ -1861,31 +1882,31 @@
         <v>3.2</v>
       </c>
       <c r="BP5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS5">
         <v>7.8</v>
       </c>
       <c r="BT5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU5">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BW5">
         <v>9</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY5">
         <v>9.199999999999999</v>
@@ -1897,7 +1918,7 @@
         <v>7.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1905,16 +1926,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F6">
         <v>3.95</v>
@@ -1923,7 +1944,7 @@
         <v>4.3</v>
       </c>
       <c r="H6">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I6">
         <v>2.16</v>
@@ -1932,7 +1953,7 @@
         <v>3.55</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L6">
         <v>1.45</v>
@@ -1959,7 +1980,7 @@
         <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U6">
         <v>1.99</v>
@@ -1980,10 +2001,10 @@
         <v>13.5</v>
       </c>
       <c r="AA6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC6">
         <v>8.199999999999999</v>
@@ -1992,22 +2013,22 @@
         <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH6">
         <v>20</v>
       </c>
       <c r="AI6">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK6">
         <v>60</v>
@@ -2016,43 +2037,43 @@
         <v>70</v>
       </c>
       <c r="AM6">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AN6">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AO6">
         <v>19</v>
       </c>
       <c r="AP6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ6">
+        <v>7.4</v>
+      </c>
+      <c r="AR6">
+        <v>10.5</v>
+      </c>
+      <c r="AS6">
+        <v>21</v>
+      </c>
+      <c r="AT6">
+        <v>11.5</v>
+      </c>
+      <c r="AU6">
+        <v>6.8</v>
+      </c>
+      <c r="AV6">
         <v>9</v>
       </c>
-      <c r="AQ6">
-        <v>7</v>
-      </c>
-      <c r="AR6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AS6">
+      <c r="AW6">
         <v>20</v>
       </c>
-      <c r="AT6">
-        <v>11</v>
-      </c>
-      <c r="AU6">
-        <v>6.6</v>
-      </c>
-      <c r="AV6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW6">
-        <v>19</v>
-      </c>
       <c r="AX6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AY6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ6">
         <v>16.5</v>
@@ -2061,22 +2082,22 @@
         <v>32</v>
       </c>
       <c r="BB6">
+        <v>55</v>
+      </c>
+      <c r="BC6">
+        <v>36</v>
+      </c>
+      <c r="BD6">
+        <v>46</v>
+      </c>
+      <c r="BE6">
         <v>8.4</v>
       </c>
-      <c r="BC6">
-        <v>38</v>
-      </c>
-      <c r="BD6">
-        <v>8</v>
-      </c>
-      <c r="BE6">
-        <v>8.6</v>
-      </c>
       <c r="BF6">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="BG6">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH6">
         <v>3.35</v>
@@ -2139,7 +2160,7 @@
         <v>7.8</v>
       </c>
       <c r="CB6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2147,25 +2168,25 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F7">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G7">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="H7">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="I7">
         <v>990</v>
@@ -2183,16 +2204,16 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O7">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P7">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R7">
         <v>1.15</v>
@@ -2207,10 +2228,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2381,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2389,16 +2410,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2623,204 +2644,204 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F9">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="G9">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H9">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="I9">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="J9">
+        <v>4.2</v>
+      </c>
+      <c r="K9">
+        <v>5.3</v>
+      </c>
+      <c r="L9">
+        <v>1.18</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.1</v>
+      </c>
+      <c r="O9">
+        <v>1.1</v>
+      </c>
+      <c r="P9">
+        <v>3.3</v>
+      </c>
+      <c r="Q9">
+        <v>1.32</v>
+      </c>
+      <c r="R9">
+        <v>1.95</v>
+      </c>
+      <c r="S9">
+        <v>1.79</v>
+      </c>
+      <c r="T9">
+        <v>1.37</v>
+      </c>
+      <c r="U9">
         <v>3.1</v>
       </c>
-      <c r="K9">
-        <v>3.35</v>
-      </c>
-      <c r="L9">
-        <v>1.01</v>
-      </c>
-      <c r="M9">
-        <v>1.11</v>
-      </c>
-      <c r="N9">
-        <v>2.46</v>
-      </c>
-      <c r="O9">
-        <v>1.47</v>
-      </c>
-      <c r="P9">
-        <v>1.59</v>
-      </c>
-      <c r="Q9">
-        <v>2.38</v>
-      </c>
-      <c r="R9">
-        <v>1.18</v>
-      </c>
-      <c r="S9">
-        <v>4</v>
-      </c>
-      <c r="T9">
-        <v>1.86</v>
-      </c>
-      <c r="U9">
-        <v>1.68</v>
-      </c>
       <c r="V9">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y9">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="Z9">
         <v>38</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AC9">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AD9">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF9">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="AG9">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH9">
-        <v>950</v>
+        <v>16.5</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ9">
+        <v>32</v>
+      </c>
+      <c r="AK9">
+        <v>22</v>
+      </c>
+      <c r="AL9">
+        <v>24</v>
+      </c>
+      <c r="AM9">
         <v>40</v>
       </c>
-      <c r="AK9">
-        <v>40</v>
-      </c>
-      <c r="AL9">
-        <v>1000</v>
-      </c>
-      <c r="AM9">
-        <v>1000</v>
-      </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP9">
-        <v>2.16</v>
+        <v>5.4</v>
       </c>
       <c r="AQ9">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AR9">
-        <v>17.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS9">
-        <v>2.16</v>
+        <v>5.5</v>
       </c>
       <c r="AT9">
+        <v>4.8</v>
+      </c>
+      <c r="AU9">
+        <v>4.3</v>
+      </c>
+      <c r="AV9">
+        <v>4.5</v>
+      </c>
+      <c r="AW9">
         <v>5.1</v>
       </c>
-      <c r="AU9">
-        <v>1.78</v>
-      </c>
-      <c r="AV9">
-        <v>11</v>
-      </c>
-      <c r="AW9">
-        <v>2.16</v>
-      </c>
       <c r="AX9">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY9">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ9">
-        <v>2.02</v>
+        <v>4.4</v>
       </c>
       <c r="BA9">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="BB9">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="BC9">
-        <v>18.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD9">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
       <c r="BE9">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="BF9">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="BG9">
-        <v>2.16</v>
+        <v>4.2</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI9">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BK9">
-        <v>1.58</v>
+        <v>4.1</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.76</v>
+        <v>7</v>
       </c>
       <c r="BN9">
         <v>6.4</v>
@@ -2829,43 +2850,43 @@
         <v>3.55</v>
       </c>
       <c r="BP9">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="BQ9">
-        <v>1.65</v>
+        <v>5.1</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BS9">
-        <v>1.71</v>
+        <v>5.6</v>
       </c>
       <c r="BT9">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW9">
-        <v>1.71</v>
+        <v>5.9</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY9">
-        <v>1.72</v>
+        <v>6</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2873,217 +2894,217 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="F10">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="G10">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="H10">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I10">
+        <v>4.3</v>
+      </c>
+      <c r="J10">
+        <v>3.05</v>
+      </c>
+      <c r="K10">
+        <v>3.35</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.11</v>
+      </c>
+      <c r="N10">
+        <v>2.7</v>
+      </c>
+      <c r="O10">
+        <v>1.48</v>
+      </c>
+      <c r="P10">
+        <v>1.57</v>
+      </c>
+      <c r="Q10">
+        <v>2.42</v>
+      </c>
+      <c r="R10">
+        <v>1.2</v>
+      </c>
+      <c r="S10">
         <v>4.8</v>
       </c>
-      <c r="J10">
-        <v>3.35</v>
-      </c>
-      <c r="K10">
-        <v>3.75</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.08</v>
-      </c>
-      <c r="N10">
-        <v>3.2</v>
-      </c>
-      <c r="O10">
-        <v>1.38</v>
-      </c>
-      <c r="P10">
-        <v>1.74</v>
-      </c>
-      <c r="Q10">
-        <v>2.12</v>
-      </c>
-      <c r="R10">
-        <v>1.27</v>
-      </c>
-      <c r="S10">
-        <v>3.95</v>
-      </c>
       <c r="T10">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="U10">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="V10">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W10">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="X10">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y10">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="Z10">
         <v>38</v>
       </c>
       <c r="AA10">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB10">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC10">
+        <v>7.8</v>
+      </c>
+      <c r="AD10">
+        <v>18</v>
+      </c>
+      <c r="AE10">
+        <v>75</v>
+      </c>
+      <c r="AF10">
+        <v>13.5</v>
+      </c>
+      <c r="AG10">
+        <v>12.5</v>
+      </c>
+      <c r="AH10">
+        <v>24</v>
+      </c>
+      <c r="AI10">
+        <v>95</v>
+      </c>
+      <c r="AJ10">
+        <v>34</v>
+      </c>
+      <c r="AK10">
+        <v>32</v>
+      </c>
+      <c r="AL10">
+        <v>65</v>
+      </c>
+      <c r="AM10">
+        <v>200</v>
+      </c>
+      <c r="AN10">
+        <v>40</v>
+      </c>
+      <c r="AO10">
+        <v>110</v>
+      </c>
+      <c r="AP10">
+        <v>7.4</v>
+      </c>
+      <c r="AQ10">
         <v>9.4</v>
       </c>
-      <c r="AD10">
-        <v>22</v>
-      </c>
-      <c r="AE10">
-        <v>65</v>
-      </c>
-      <c r="AF10">
-        <v>14.5</v>
-      </c>
-      <c r="AG10">
-        <v>13</v>
-      </c>
-      <c r="AH10">
-        <v>25</v>
-      </c>
-      <c r="AI10">
-        <v>75</v>
-      </c>
-      <c r="AJ10">
-        <v>30</v>
-      </c>
-      <c r="AK10">
-        <v>29</v>
-      </c>
-      <c r="AL10">
-        <v>55</v>
-      </c>
-      <c r="AM10">
-        <v>160</v>
-      </c>
-      <c r="AN10">
-        <v>23</v>
-      </c>
-      <c r="AO10">
-        <v>90</v>
-      </c>
-      <c r="AP10">
-        <v>10</v>
-      </c>
-      <c r="AQ10">
-        <v>11.5</v>
-      </c>
       <c r="AR10">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="AS10">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT10">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV10">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW10">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AX10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY10">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA10">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BB10">
+        <v>19</v>
+      </c>
+      <c r="BC10">
+        <v>18.5</v>
+      </c>
+      <c r="BD10">
+        <v>7</v>
+      </c>
+      <c r="BE10">
+        <v>7.4</v>
+      </c>
+      <c r="BF10">
         <v>21</v>
       </c>
-      <c r="BC10">
-        <v>20</v>
-      </c>
-      <c r="BD10">
-        <v>4.2</v>
-      </c>
-      <c r="BE10">
-        <v>4.5</v>
-      </c>
-      <c r="BF10">
-        <v>13.5</v>
-      </c>
       <c r="BG10">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BJ10">
         <v>15</v>
       </c>
       <c r="BK10">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="BN10">
         <v>6.4</v>
       </c>
       <c r="BO10">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="BP10">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BQ10">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BR10">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BT10">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU10">
         <v>4.8</v>
@@ -3092,22 +3113,506 @@
         <v>1000</v>
       </c>
       <c r="BW10">
+        <v>1.7</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
         <v>1.72</v>
       </c>
-      <c r="BX10">
-        <v>1000</v>
-      </c>
-      <c r="BY10">
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.7</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11">
+        <v>1.04</v>
+      </c>
+      <c r="G11">
+        <v>990</v>
+      </c>
+      <c r="H11">
+        <v>1.04</v>
+      </c>
+      <c r="I11">
+        <v>990</v>
+      </c>
+      <c r="J11">
+        <v>1.02</v>
+      </c>
+      <c r="K11">
+        <v>950</v>
+      </c>
+      <c r="L11">
+        <v>1.01</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>1.3</v>
+      </c>
+      <c r="O11">
+        <v>1.15</v>
+      </c>
+      <c r="P11">
+        <v>1.3</v>
+      </c>
+      <c r="Q11">
+        <v>1.15</v>
+      </c>
+      <c r="R11">
+        <v>1.25</v>
+      </c>
+      <c r="S11">
+        <v>1.14</v>
+      </c>
+      <c r="T11">
+        <v>1.11</v>
+      </c>
+      <c r="U11">
+        <v>1.11</v>
+      </c>
+      <c r="V11">
+        <v>1.01</v>
+      </c>
+      <c r="W11">
+        <v>1.01</v>
+      </c>
+      <c r="X11">
+        <v>1000</v>
+      </c>
+      <c r="Y11">
+        <v>1000</v>
+      </c>
+      <c r="Z11">
+        <v>1000</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>1000</v>
+      </c>
+      <c r="AC11">
+        <v>1000</v>
+      </c>
+      <c r="AD11">
+        <v>1000</v>
+      </c>
+      <c r="AE11">
+        <v>1000</v>
+      </c>
+      <c r="AF11">
+        <v>1000</v>
+      </c>
+      <c r="AG11">
+        <v>1000</v>
+      </c>
+      <c r="AH11">
+        <v>1000</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>1000</v>
+      </c>
+      <c r="AK11">
+        <v>1000</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>1000</v>
+      </c>
+      <c r="AN11">
+        <v>1000</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>1.01</v>
+      </c>
+      <c r="AQ11">
+        <v>1.01</v>
+      </c>
+      <c r="AR11">
+        <v>1.01</v>
+      </c>
+      <c r="AS11">
+        <v>1.01</v>
+      </c>
+      <c r="AT11">
+        <v>1.01</v>
+      </c>
+      <c r="AU11">
+        <v>1.01</v>
+      </c>
+      <c r="AV11">
+        <v>1.01</v>
+      </c>
+      <c r="AW11">
+        <v>1.01</v>
+      </c>
+      <c r="AX11">
+        <v>1.01</v>
+      </c>
+      <c r="AY11">
+        <v>1.01</v>
+      </c>
+      <c r="AZ11">
+        <v>1.01</v>
+      </c>
+      <c r="BA11">
+        <v>1.01</v>
+      </c>
+      <c r="BB11">
+        <v>1.01</v>
+      </c>
+      <c r="BC11">
+        <v>1.01</v>
+      </c>
+      <c r="BD11">
+        <v>1.01</v>
+      </c>
+      <c r="BE11">
+        <v>1.01</v>
+      </c>
+      <c r="BF11">
+        <v>1.01</v>
+      </c>
+      <c r="BG11">
+        <v>1.01</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.04</v>
+      </c>
+      <c r="BJ11">
+        <v>1000</v>
+      </c>
+      <c r="BK11">
+        <v>1.04</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.04</v>
+      </c>
+      <c r="BN11">
+        <v>1000</v>
+      </c>
+      <c r="BO11">
+        <v>1.04</v>
+      </c>
+      <c r="BP11">
+        <v>1000</v>
+      </c>
+      <c r="BQ11">
+        <v>1.04</v>
+      </c>
+      <c r="BR11">
+        <v>1000</v>
+      </c>
+      <c r="BS11">
+        <v>1.04</v>
+      </c>
+      <c r="BT11">
+        <v>1000</v>
+      </c>
+      <c r="BU11">
+        <v>1.04</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.04</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.04</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12">
+        <v>1.97</v>
+      </c>
+      <c r="G12">
+        <v>2.14</v>
+      </c>
+      <c r="H12">
+        <v>4.1</v>
+      </c>
+      <c r="I12">
+        <v>4.7</v>
+      </c>
+      <c r="J12">
+        <v>3.35</v>
+      </c>
+      <c r="K12">
+        <v>3.8</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.08</v>
+      </c>
+      <c r="N12">
+        <v>3.15</v>
+      </c>
+      <c r="O12">
+        <v>1.38</v>
+      </c>
+      <c r="P12">
         <v>1.74</v>
       </c>
-      <c r="BZ10">
+      <c r="Q12">
+        <v>2.14</v>
+      </c>
+      <c r="R12">
+        <v>1.27</v>
+      </c>
+      <c r="S12">
+        <v>4</v>
+      </c>
+      <c r="T12">
+        <v>1.89</v>
+      </c>
+      <c r="U12">
+        <v>1.91</v>
+      </c>
+      <c r="V12">
+        <v>1.27</v>
+      </c>
+      <c r="W12">
+        <v>1.89</v>
+      </c>
+      <c r="X12">
+        <v>14.5</v>
+      </c>
+      <c r="Y12">
+        <v>16.5</v>
+      </c>
+      <c r="Z12">
+        <v>38</v>
+      </c>
+      <c r="AA12">
+        <v>120</v>
+      </c>
+      <c r="AB12">
+        <v>9.6</v>
+      </c>
+      <c r="AC12">
+        <v>9.6</v>
+      </c>
+      <c r="AD12">
+        <v>22</v>
+      </c>
+      <c r="AE12">
+        <v>65</v>
+      </c>
+      <c r="AF12">
+        <v>14.5</v>
+      </c>
+      <c r="AG12">
+        <v>13</v>
+      </c>
+      <c r="AH12">
+        <v>25</v>
+      </c>
+      <c r="AI12">
+        <v>85</v>
+      </c>
+      <c r="AJ12">
+        <v>30</v>
+      </c>
+      <c r="AK12">
+        <v>29</v>
+      </c>
+      <c r="AL12">
         <v>46</v>
       </c>
-      <c r="CA10">
+      <c r="AM12">
+        <v>160</v>
+      </c>
+      <c r="AN12">
+        <v>23</v>
+      </c>
+      <c r="AO12">
+        <v>80</v>
+      </c>
+      <c r="AP12">
+        <v>10</v>
+      </c>
+      <c r="AQ12">
+        <v>10</v>
+      </c>
+      <c r="AR12">
+        <v>4.1</v>
+      </c>
+      <c r="AS12">
+        <v>4.4</v>
+      </c>
+      <c r="AT12">
+        <v>7</v>
+      </c>
+      <c r="AU12">
+        <v>6</v>
+      </c>
+      <c r="AV12">
+        <v>13</v>
+      </c>
+      <c r="AW12">
+        <v>4.3</v>
+      </c>
+      <c r="AX12">
+        <v>10</v>
+      </c>
+      <c r="AY12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12">
+        <v>15</v>
+      </c>
+      <c r="BA12">
+        <v>4.3</v>
+      </c>
+      <c r="BB12">
+        <v>21</v>
+      </c>
+      <c r="BC12">
+        <v>20</v>
+      </c>
+      <c r="BD12">
+        <v>4.1</v>
+      </c>
+      <c r="BE12">
+        <v>4.4</v>
+      </c>
+      <c r="BF12">
+        <v>15.5</v>
+      </c>
+      <c r="BG12">
+        <v>4.3</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.78</v>
+      </c>
+      <c r="BJ12">
+        <v>15</v>
+      </c>
+      <c r="BK12">
+        <v>1.59</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.78</v>
+      </c>
+      <c r="BN12">
+        <v>6.4</v>
+      </c>
+      <c r="BO12">
+        <v>3.35</v>
+      </c>
+      <c r="BP12">
+        <v>22</v>
+      </c>
+      <c r="BQ12">
+        <v>1.65</v>
+      </c>
+      <c r="BR12">
+        <v>48</v>
+      </c>
+      <c r="BS12">
+        <v>1.72</v>
+      </c>
+      <c r="BT12">
+        <v>10.5</v>
+      </c>
+      <c r="BU12">
+        <v>4.8</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.72</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.74</v>
+      </c>
+      <c r="BZ12">
+        <v>46</v>
+      </c>
+      <c r="CA12">
         <v>1.71</v>
       </c>
-      <c r="CB10" t="s">
-        <v>113</v>
+      <c r="CB12" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="130">
   <si>
     <t>League</t>
   </si>
@@ -277,6 +277,9 @@
     <t>Bolivian Liga de Futbol Profesional</t>
   </si>
   <si>
+    <t>Venezuelan Primera Division</t>
+  </si>
+  <si>
     <t>2026-08-04</t>
   </si>
   <si>
@@ -301,12 +304,18 @@
     <t>19:00:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
     <t>21:10:00</t>
   </si>
   <si>
     <t>22:00:00</t>
   </si>
   <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
     <t>23:15:00</t>
   </si>
   <si>
@@ -334,12 +343,21 @@
     <t>Academia de Balompie Boliviano</t>
   </si>
   <si>
+    <t>Carabobo FC</t>
+  </si>
+  <si>
     <t>Llaneros FC</t>
   </si>
   <si>
     <t>Club Independiente Petrolero</t>
   </si>
   <si>
+    <t>Universidad de Venezuela</t>
+  </si>
+  <si>
+    <t>Deportivo Tachira</t>
+  </si>
+  <si>
     <t>Tolima</t>
   </si>
   <si>
@@ -367,16 +385,25 @@
     <t>CDT Real Oruro</t>
   </si>
   <si>
+    <t>Trujillanos</t>
+  </si>
+  <si>
     <t>Fortaleza FC</t>
   </si>
   <si>
     <t>Aurora</t>
   </si>
   <si>
+    <t>Monagas</t>
+  </si>
+  <si>
+    <t>Portuguesa FC</t>
+  </si>
+  <si>
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 11:49:47</t>
+    <t>2026-08-03 13:58:24</t>
   </si>
 </sst>
 </file>
@@ -708,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -958,76 +985,76 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="F2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K2">
         <v>6.2</v>
       </c>
       <c r="L2">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q2">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T2">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="U2">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V2">
         <v>1.07</v>
       </c>
       <c r="W2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y2">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="Z2">
         <v>140</v>
@@ -1036,7 +1063,7 @@
         <v>800</v>
       </c>
       <c r="AB2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
         <v>13.5</v>
@@ -1045,10 +1072,10 @@
         <v>65</v>
       </c>
       <c r="AE2">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="AF2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1060,7 +1087,7 @@
         <v>310</v>
       </c>
       <c r="AJ2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AK2">
         <v>16.5</v>
@@ -1072,25 +1099,25 @@
         <v>340</v>
       </c>
       <c r="AN2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO2">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="AP2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AQ2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AR2">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="AS2">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>12</v>
@@ -1102,7 +1129,7 @@
         <v>14.5</v>
       </c>
       <c r="AX2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY2">
         <v>10</v>
@@ -1111,7 +1138,7 @@
         <v>36</v>
       </c>
       <c r="BA2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB2">
         <v>8.6</v>
@@ -1120,79 +1147,79 @@
         <v>14.5</v>
       </c>
       <c r="BD2">
+        <v>44</v>
+      </c>
+      <c r="BE2">
         <v>12</v>
-      </c>
-      <c r="BE2">
-        <v>14.5</v>
       </c>
       <c r="BF2">
         <v>5.7</v>
       </c>
       <c r="BG2">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BH2">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="BI2">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2">
         <v>14.5</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="BN2">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BO2">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BP2">
         <v>8</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BT2">
+        <v>16</v>
+      </c>
+      <c r="BU2">
+        <v>11.5</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>7.6</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>7.4</v>
+      </c>
+      <c r="BZ2">
         <v>15.5</v>
       </c>
-      <c r="BU2">
-        <v>12</v>
-      </c>
-      <c r="BV2">
-        <v>1000</v>
-      </c>
-      <c r="BW2">
-        <v>10.5</v>
-      </c>
-      <c r="BX2">
-        <v>1000</v>
-      </c>
-      <c r="BY2">
-        <v>10.5</v>
-      </c>
-      <c r="BZ2">
-        <v>16</v>
-      </c>
       <c r="CA2">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="CB2" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1200,28 +1227,28 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F3">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
         <v>2.72</v>
       </c>
       <c r="I3">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J3">
         <v>2.92</v>
@@ -1236,34 +1263,34 @@
         <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="O3">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="P3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U3">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X3">
         <v>7.2</v>
@@ -1278,10 +1305,10 @@
         <v>46</v>
       </c>
       <c r="AB3">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AD3">
         <v>14</v>
@@ -1293,7 +1320,7 @@
         <v>20</v>
       </c>
       <c r="AG3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH3">
         <v>27</v>
@@ -1308,10 +1335,10 @@
         <v>60</v>
       </c>
       <c r="AL3">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM3">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN3">
         <v>90</v>
@@ -1320,7 +1347,7 @@
         <v>60</v>
       </c>
       <c r="AP3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3">
         <v>6.8</v>
@@ -1335,25 +1362,25 @@
         <v>8</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW3">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AX3">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY3">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ3">
         <v>24</v>
       </c>
       <c r="BA3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BB3">
         <v>60</v>
@@ -1362,7 +1389,7 @@
         <v>50</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE3">
         <v>50</v>
@@ -1371,70 +1398,70 @@
         <v>55</v>
       </c>
       <c r="BG3">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="CB3" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1442,28 +1469,28 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G4">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H4">
         <v>4.5</v>
       </c>
       <c r="I4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
         <v>3.05</v>
@@ -1472,55 +1499,55 @@
         <v>3.1</v>
       </c>
       <c r="L4">
+        <v>1.67</v>
+      </c>
+      <c r="M4">
+        <v>1.16</v>
+      </c>
+      <c r="N4">
+        <v>2.4</v>
+      </c>
+      <c r="O4">
+        <v>1.68</v>
+      </c>
+      <c r="P4">
+        <v>1.45</v>
+      </c>
+      <c r="Q4">
+        <v>3.15</v>
+      </c>
+      <c r="R4">
+        <v>1.15</v>
+      </c>
+      <c r="S4">
+        <v>7</v>
+      </c>
+      <c r="T4">
+        <v>2.48</v>
+      </c>
+      <c r="U4">
         <v>1.65</v>
-      </c>
-      <c r="M4">
-        <v>1.15</v>
-      </c>
-      <c r="N4">
-        <v>2.48</v>
-      </c>
-      <c r="O4">
-        <v>1.65</v>
-      </c>
-      <c r="P4">
-        <v>1.48</v>
-      </c>
-      <c r="Q4">
-        <v>3</v>
-      </c>
-      <c r="R4">
-        <v>1.16</v>
-      </c>
-      <c r="S4">
-        <v>6.8</v>
-      </c>
-      <c r="T4">
-        <v>2.36</v>
-      </c>
-      <c r="U4">
-        <v>1.67</v>
       </c>
       <c r="V4">
         <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y4">
         <v>11</v>
       </c>
       <c r="Z4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC4">
         <v>7.2</v>
@@ -1529,52 +1556,52 @@
         <v>21</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF4">
         <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH4">
         <v>29</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ4">
         <v>30</v>
       </c>
       <c r="AK4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL4">
         <v>80</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AN4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP4">
         <v>6.8</v>
       </c>
       <c r="AQ4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU4">
         <v>6.8</v>
@@ -1583,7 +1610,7 @@
         <v>19</v>
       </c>
       <c r="AW4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX4">
         <v>10</v>
@@ -1595,13 +1622,13 @@
         <v>25</v>
       </c>
       <c r="BA4">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="BB4">
         <v>26</v>
       </c>
       <c r="BC4">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BD4">
         <v>60</v>
@@ -1613,25 +1640,25 @@
         <v>30</v>
       </c>
       <c r="BG4">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BH4">
         <v>2.52</v>
       </c>
       <c r="BI4">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="BJ4">
         <v>13</v>
       </c>
       <c r="BK4">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16.5</v>
+        <v>2.18</v>
       </c>
       <c r="BN4">
         <v>4.6</v>
@@ -1643,7 +1670,7 @@
         <v>20</v>
       </c>
       <c r="BQ4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR4">
         <v>50</v>
@@ -1655,7 +1682,7 @@
         <v>7.6</v>
       </c>
       <c r="BU4">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
         <v>55</v>
@@ -1676,7 +1703,7 @@
         <v>13.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1684,31 +1711,31 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F5">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="G5">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H5">
         <v>6.6</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K5">
         <v>4.1</v>
@@ -1717,25 +1744,25 @@
         <v>1.46</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O5">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P5">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q5">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T5">
         <v>2.12</v>
@@ -1747,16 +1774,16 @@
         <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X5">
         <v>13</v>
       </c>
       <c r="Y5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z5">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA5">
         <v>270</v>
@@ -1765,22 +1792,22 @@
         <v>7.4</v>
       </c>
       <c r="AC5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD5">
         <v>28</v>
       </c>
       <c r="AE5">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI5">
         <v>130</v>
@@ -1789,22 +1816,22 @@
         <v>16.5</v>
       </c>
       <c r="AK5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
         <v>46</v>
       </c>
       <c r="AM5">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO5">
         <v>220</v>
       </c>
       <c r="AP5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ5">
         <v>17</v>
@@ -1813,7 +1840,7 @@
         <v>40</v>
       </c>
       <c r="AS5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT5">
         <v>6.4</v>
@@ -1822,103 +1849,103 @@
         <v>8</v>
       </c>
       <c r="AV5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW5">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="AX5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY5">
         <v>9</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="BB5">
         <v>13</v>
       </c>
       <c r="BC5">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BD5">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF5">
+        <v>9.4</v>
+      </c>
+      <c r="BG5">
         <v>10</v>
       </c>
-      <c r="BG5">
-        <v>10.5</v>
-      </c>
       <c r="BH5">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BI5">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BJ5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK5">
+        <v>4.1</v>
+      </c>
+      <c r="BL5">
+        <v>210</v>
+      </c>
+      <c r="BM5">
         <v>5.7</v>
       </c>
-      <c r="BL5">
-        <v>200</v>
-      </c>
-      <c r="BM5">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BN5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BO5">
         <v>3.2</v>
       </c>
       <c r="BP5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5">
+        <v>4</v>
+      </c>
+      <c r="BR5">
+        <v>36</v>
+      </c>
+      <c r="BS5">
+        <v>5</v>
+      </c>
+      <c r="BT5">
+        <v>12</v>
+      </c>
+      <c r="BU5">
+        <v>3.95</v>
+      </c>
+      <c r="BV5">
+        <v>80</v>
+      </c>
+      <c r="BW5">
         <v>5.4</v>
       </c>
-      <c r="BR5">
-        <v>32</v>
-      </c>
-      <c r="BS5">
-        <v>7.8</v>
-      </c>
-      <c r="BT5">
-        <v>11</v>
-      </c>
-      <c r="BU5">
-        <v>5.3</v>
-      </c>
-      <c r="BV5">
-        <v>75</v>
-      </c>
-      <c r="BW5">
-        <v>9</v>
-      </c>
       <c r="BX5">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BY5">
-        <v>9.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BZ5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA5">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="CB5" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1926,28 +1953,28 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F6">
+        <v>3.8</v>
+      </c>
+      <c r="G6">
         <v>3.95</v>
       </c>
-      <c r="G6">
-        <v>4.3</v>
-      </c>
       <c r="H6">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="I6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J6">
         <v>3.55</v>
@@ -1968,31 +1995,31 @@
         <v>1.37</v>
       </c>
       <c r="P6">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q6">
         <v>2.12</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
         <v>3.9</v>
       </c>
       <c r="T6">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U6">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="W6">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X6">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -2001,10 +2028,10 @@
         <v>13.5</v>
       </c>
       <c r="AA6">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC6">
         <v>8.199999999999999</v>
@@ -2013,37 +2040,37 @@
         <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF6">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AG6">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI6">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL6">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AM6">
         <v>150</v>
       </c>
       <c r="AN6">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP6">
         <v>9.800000000000001</v>
@@ -2070,7 +2097,7 @@
         <v>20</v>
       </c>
       <c r="AX6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY6">
         <v>14</v>
@@ -2082,7 +2109,7 @@
         <v>32</v>
       </c>
       <c r="BB6">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BC6">
         <v>36</v>
@@ -2091,76 +2118,76 @@
         <v>46</v>
       </c>
       <c r="BE6">
-        <v>8.4</v>
+        <v>85</v>
       </c>
       <c r="BF6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="BG6">
         <v>15</v>
       </c>
       <c r="BH6">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI6">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6">
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO6">
         <v>5.7</v>
       </c>
       <c r="BP6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BQ6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR6">
         <v>50</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BT6">
         <v>4.9</v>
       </c>
       <c r="BU6">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BV6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BW6">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BX6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6">
         <v>30</v>
       </c>
       <c r="CA6">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="CB6" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2168,232 +2195,232 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F7">
-        <v>1.31</v>
+        <v>2.38</v>
       </c>
       <c r="G7">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="H7">
+        <v>3.05</v>
+      </c>
+      <c r="I7">
+        <v>3.7</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <v>3.6</v>
+      </c>
+      <c r="L7">
+        <v>1.46</v>
+      </c>
+      <c r="M7">
+        <v>1.09</v>
+      </c>
+      <c r="N7">
+        <v>2.96</v>
+      </c>
+      <c r="O7">
+        <v>1.39</v>
+      </c>
+      <c r="P7">
+        <v>1.68</v>
+      </c>
+      <c r="Q7">
+        <v>2.12</v>
+      </c>
+      <c r="R7">
+        <v>1.25</v>
+      </c>
+      <c r="S7">
+        <v>3.55</v>
+      </c>
+      <c r="T7">
+        <v>1.84</v>
+      </c>
+      <c r="U7">
+        <v>1.93</v>
+      </c>
+      <c r="V7">
+        <v>1.4</v>
+      </c>
+      <c r="W7">
+        <v>1.59</v>
+      </c>
+      <c r="X7">
+        <v>13.5</v>
+      </c>
+      <c r="Y7">
+        <v>13.5</v>
+      </c>
+      <c r="Z7">
+        <v>26</v>
+      </c>
+      <c r="AA7">
+        <v>75</v>
+      </c>
+      <c r="AB7">
+        <v>11.5</v>
+      </c>
+      <c r="AC7">
+        <v>7.8</v>
+      </c>
+      <c r="AD7">
+        <v>15</v>
+      </c>
+      <c r="AE7">
+        <v>55</v>
+      </c>
+      <c r="AF7">
+        <v>19.5</v>
+      </c>
+      <c r="AG7">
+        <v>14.5</v>
+      </c>
+      <c r="AH7">
+        <v>23</v>
+      </c>
+      <c r="AI7">
+        <v>70</v>
+      </c>
+      <c r="AJ7">
+        <v>48</v>
+      </c>
+      <c r="AK7">
+        <v>38</v>
+      </c>
+      <c r="AL7">
+        <v>60</v>
+      </c>
+      <c r="AM7">
+        <v>150</v>
+      </c>
+      <c r="AN7">
+        <v>32</v>
+      </c>
+      <c r="AO7">
+        <v>55</v>
+      </c>
+      <c r="AP7">
+        <v>3.6</v>
+      </c>
+      <c r="AQ7">
+        <v>3.6</v>
+      </c>
+      <c r="AR7">
+        <v>4.1</v>
+      </c>
+      <c r="AS7">
+        <v>4.6</v>
+      </c>
+      <c r="AT7">
+        <v>3.45</v>
+      </c>
+      <c r="AU7">
+        <v>3</v>
+      </c>
+      <c r="AV7">
+        <v>3.7</v>
+      </c>
+      <c r="AW7">
+        <v>4.5</v>
+      </c>
+      <c r="AX7">
+        <v>3.9</v>
+      </c>
+      <c r="AY7">
+        <v>3.65</v>
+      </c>
+      <c r="AZ7">
+        <v>4</v>
+      </c>
+      <c r="BA7">
+        <v>4.6</v>
+      </c>
+      <c r="BB7">
+        <v>4.4</v>
+      </c>
+      <c r="BC7">
+        <v>4.3</v>
+      </c>
+      <c r="BD7">
+        <v>4.5</v>
+      </c>
+      <c r="BE7">
+        <v>4.7</v>
+      </c>
+      <c r="BF7">
+        <v>4.2</v>
+      </c>
+      <c r="BG7">
+        <v>4.5</v>
+      </c>
+      <c r="BH7">
+        <v>3.55</v>
+      </c>
+      <c r="BI7">
         <v>2.48</v>
       </c>
-      <c r="I7">
-        <v>990</v>
-      </c>
-      <c r="J7">
-        <v>1.01</v>
-      </c>
-      <c r="K7">
-        <v>950</v>
-      </c>
-      <c r="L7">
-        <v>1.01</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>1.32</v>
-      </c>
-      <c r="O7">
-        <v>1.35</v>
-      </c>
-      <c r="P7">
-        <v>1.32</v>
-      </c>
-      <c r="Q7">
-        <v>1.35</v>
-      </c>
-      <c r="R7">
-        <v>1.15</v>
-      </c>
-      <c r="S7">
-        <v>2.8</v>
-      </c>
-      <c r="T7">
-        <v>1.11</v>
-      </c>
-      <c r="U7">
-        <v>1.11</v>
-      </c>
-      <c r="V7">
-        <v>1.18</v>
-      </c>
-      <c r="W7">
-        <v>1.55</v>
-      </c>
-      <c r="X7">
-        <v>1000</v>
-      </c>
-      <c r="Y7">
-        <v>1000</v>
-      </c>
-      <c r="Z7">
-        <v>1000</v>
-      </c>
-      <c r="AA7">
-        <v>1000</v>
-      </c>
-      <c r="AB7">
-        <v>1000</v>
-      </c>
-      <c r="AC7">
-        <v>1000</v>
-      </c>
-      <c r="AD7">
-        <v>1000</v>
-      </c>
-      <c r="AE7">
-        <v>1000</v>
-      </c>
-      <c r="AF7">
-        <v>1000</v>
-      </c>
-      <c r="AG7">
-        <v>1000</v>
-      </c>
-      <c r="AH7">
-        <v>1000</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>1000</v>
-      </c>
-      <c r="AK7">
-        <v>1000</v>
-      </c>
-      <c r="AL7">
-        <v>1000</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>1000</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>1.01</v>
-      </c>
-      <c r="AQ7">
-        <v>1.01</v>
-      </c>
-      <c r="AR7">
-        <v>1.01</v>
-      </c>
-      <c r="AS7">
-        <v>1.01</v>
-      </c>
-      <c r="AT7">
-        <v>1.01</v>
-      </c>
-      <c r="AU7">
-        <v>1.01</v>
-      </c>
-      <c r="AV7">
-        <v>1.01</v>
-      </c>
-      <c r="AW7">
-        <v>1.01</v>
-      </c>
-      <c r="AX7">
-        <v>1.01</v>
-      </c>
-      <c r="AY7">
-        <v>1.01</v>
-      </c>
-      <c r="AZ7">
-        <v>1.01</v>
-      </c>
-      <c r="BA7">
-        <v>1.01</v>
-      </c>
-      <c r="BB7">
-        <v>1.01</v>
-      </c>
-      <c r="BC7">
-        <v>1.01</v>
-      </c>
-      <c r="BD7">
-        <v>1.01</v>
-      </c>
-      <c r="BE7">
-        <v>1.01</v>
-      </c>
-      <c r="BF7">
-        <v>1.01</v>
-      </c>
-      <c r="BG7">
-        <v>1.01</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2402,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2410,16 +2437,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2644,7 +2671,7 @@
         <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2652,34 +2679,34 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F9">
-        <v>1.95</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="H9">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="I9">
-        <v>3.75</v>
+        <v>990</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="K9">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L9">
         <v>1.18</v>
@@ -2688,37 +2715,37 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O9">
         <v>1.1</v>
       </c>
       <c r="P9">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Q9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R9">
         <v>1.95</v>
       </c>
       <c r="S9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="T9">
         <v>1.37</v>
       </c>
       <c r="U9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="X9">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
         <v>32</v>
@@ -2727,103 +2754,103 @@
         <v>38</v>
       </c>
       <c r="AA9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AE9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF9">
         <v>25</v>
       </c>
       <c r="AG9">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI9">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ9">
         <v>32</v>
       </c>
       <c r="AK9">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM9">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AN9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO9">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AP9">
-        <v>5.4</v>
+        <v>2.4</v>
       </c>
       <c r="AQ9">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="AR9">
-        <v>5.1</v>
+        <v>2.26</v>
       </c>
       <c r="AS9">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="AT9">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="AU9">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="AV9">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="AW9">
-        <v>5.1</v>
+        <v>2.24</v>
       </c>
       <c r="AX9">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="AY9">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="AZ9">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="BA9">
-        <v>5</v>
+        <v>2.22</v>
       </c>
       <c r="BB9">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="BC9">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="BD9">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="BE9">
-        <v>5.2</v>
+        <v>2.28</v>
       </c>
       <c r="BF9">
-        <v>3.25</v>
+        <v>1.82</v>
       </c>
       <c r="BG9">
-        <v>4.2</v>
+        <v>2.08</v>
       </c>
       <c r="BH9">
         <v>6.2</v>
@@ -2886,428 +2913,428 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F10">
-        <v>2.12</v>
+        <v>1.39</v>
       </c>
       <c r="G10">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="H10">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="I10">
-        <v>4.3</v>
+        <v>990</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="K10">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>1.26</v>
+      </c>
+      <c r="O10">
+        <v>1.25</v>
+      </c>
+      <c r="P10">
+        <v>1.86</v>
+      </c>
+      <c r="Q10">
+        <v>1.9</v>
+      </c>
+      <c r="R10">
+        <v>1.31</v>
+      </c>
+      <c r="S10">
+        <v>2.84</v>
+      </c>
+      <c r="T10">
         <v>1.11</v>
       </c>
-      <c r="N10">
-        <v>2.7</v>
-      </c>
-      <c r="O10">
-        <v>1.48</v>
-      </c>
-      <c r="P10">
-        <v>1.57</v>
-      </c>
-      <c r="Q10">
-        <v>2.42</v>
-      </c>
-      <c r="R10">
-        <v>1.2</v>
-      </c>
-      <c r="S10">
-        <v>4.8</v>
-      </c>
-      <c r="T10">
-        <v>2.02</v>
-      </c>
       <c r="U10">
-        <v>1.8</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.72</v>
+        <v>2.8</v>
       </c>
       <c r="X10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.72</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>2.38</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L11">
         <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N11">
+        <v>2.7</v>
+      </c>
+      <c r="O11">
+        <v>1.48</v>
+      </c>
+      <c r="P11">
+        <v>1.57</v>
+      </c>
+      <c r="Q11">
+        <v>2.42</v>
+      </c>
+      <c r="R11">
+        <v>1.2</v>
+      </c>
+      <c r="S11">
+        <v>4.8</v>
+      </c>
+      <c r="T11">
+        <v>2.02</v>
+      </c>
+      <c r="U11">
+        <v>1.8</v>
+      </c>
+      <c r="V11">
         <v>1.3</v>
       </c>
-      <c r="O11">
-        <v>1.15</v>
-      </c>
-      <c r="P11">
-        <v>1.3</v>
-      </c>
-      <c r="Q11">
-        <v>1.15</v>
-      </c>
-      <c r="R11">
-        <v>1.25</v>
-      </c>
-      <c r="S11">
-        <v>1.14</v>
-      </c>
-      <c r="T11">
-        <v>1.11</v>
-      </c>
-      <c r="U11">
-        <v>1.11</v>
-      </c>
-      <c r="V11">
-        <v>1.01</v>
-      </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH11">
         <v>1000</v>
@@ -3364,255 +3391,981 @@
         <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" t="s">
+        <v>125</v>
+      </c>
+      <c r="F12">
+        <v>1.19</v>
+      </c>
+      <c r="G12">
+        <v>990</v>
+      </c>
+      <c r="H12">
+        <v>1.19</v>
+      </c>
+      <c r="I12">
+        <v>990</v>
+      </c>
+      <c r="J12">
+        <v>1.03</v>
+      </c>
+      <c r="K12">
+        <v>6.6</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
+        <v>1.03</v>
+      </c>
+      <c r="N12">
+        <v>1.31</v>
+      </c>
+      <c r="O12">
+        <v>1.16</v>
+      </c>
+      <c r="P12">
+        <v>1.31</v>
+      </c>
+      <c r="Q12">
+        <v>1.37</v>
+      </c>
+      <c r="R12">
+        <v>1.24</v>
+      </c>
+      <c r="S12">
+        <v>1.51</v>
+      </c>
+      <c r="T12">
+        <v>1.11</v>
+      </c>
+      <c r="U12">
+        <v>1.11</v>
+      </c>
+      <c r="V12">
+        <v>1.01</v>
+      </c>
+      <c r="W12">
+        <v>1.01</v>
+      </c>
+      <c r="X12">
+        <v>1000</v>
+      </c>
+      <c r="Y12">
+        <v>1000</v>
+      </c>
+      <c r="Z12">
+        <v>1000</v>
+      </c>
+      <c r="AA12">
+        <v>1000</v>
+      </c>
+      <c r="AB12">
+        <v>1000</v>
+      </c>
+      <c r="AC12">
+        <v>1000</v>
+      </c>
+      <c r="AD12">
+        <v>1000</v>
+      </c>
+      <c r="AE12">
+        <v>1000</v>
+      </c>
+      <c r="AF12">
+        <v>1000</v>
+      </c>
+      <c r="AG12">
+        <v>1000</v>
+      </c>
+      <c r="AH12">
+        <v>1000</v>
+      </c>
+      <c r="AI12">
+        <v>1000</v>
+      </c>
+      <c r="AJ12">
+        <v>1000</v>
+      </c>
+      <c r="AK12">
+        <v>1000</v>
+      </c>
+      <c r="AL12">
+        <v>1000</v>
+      </c>
+      <c r="AM12">
+        <v>1000</v>
+      </c>
+      <c r="AN12">
+        <v>1000</v>
+      </c>
+      <c r="AO12">
+        <v>1000</v>
+      </c>
+      <c r="AP12">
+        <v>1.01</v>
+      </c>
+      <c r="AQ12">
+        <v>1.01</v>
+      </c>
+      <c r="AR12">
+        <v>1.01</v>
+      </c>
+      <c r="AS12">
+        <v>1.01</v>
+      </c>
+      <c r="AT12">
+        <v>1.01</v>
+      </c>
+      <c r="AU12">
+        <v>1.01</v>
+      </c>
+      <c r="AV12">
+        <v>1.01</v>
+      </c>
+      <c r="AW12">
+        <v>1.01</v>
+      </c>
+      <c r="AX12">
+        <v>1.01</v>
+      </c>
+      <c r="AY12">
+        <v>1.01</v>
+      </c>
+      <c r="AZ12">
+        <v>1.01</v>
+      </c>
+      <c r="BA12">
+        <v>1.01</v>
+      </c>
+      <c r="BB12">
+        <v>1.01</v>
+      </c>
+      <c r="BC12">
+        <v>1.01</v>
+      </c>
+      <c r="BD12">
+        <v>1.01</v>
+      </c>
+      <c r="BE12">
+        <v>1.01</v>
+      </c>
+      <c r="BF12">
+        <v>1.01</v>
+      </c>
+      <c r="BG12">
+        <v>1.01</v>
+      </c>
+      <c r="BH12">
+        <v>1000</v>
+      </c>
+      <c r="BI12">
+        <v>1.04</v>
+      </c>
+      <c r="BJ12">
+        <v>1000</v>
+      </c>
+      <c r="BK12">
+        <v>1.04</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>1.04</v>
+      </c>
+      <c r="BN12">
+        <v>1000</v>
+      </c>
+      <c r="BO12">
+        <v>1.04</v>
+      </c>
+      <c r="BP12">
+        <v>1000</v>
+      </c>
+      <c r="BQ12">
+        <v>1.04</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>1.04</v>
+      </c>
+      <c r="BT12">
+        <v>1000</v>
+      </c>
+      <c r="BU12">
+        <v>1.04</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
+        <v>1.04</v>
+      </c>
+      <c r="BX12">
+        <v>1000</v>
+      </c>
+      <c r="BY12">
+        <v>1.04</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13">
+        <v>1.04</v>
+      </c>
+      <c r="G13">
+        <v>990</v>
+      </c>
+      <c r="H13">
+        <v>1.04</v>
+      </c>
+      <c r="I13">
+        <v>990</v>
+      </c>
+      <c r="J13">
+        <v>1.01</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
+        <v>1.25</v>
+      </c>
+      <c r="O13">
+        <v>1.32</v>
+      </c>
+      <c r="P13">
+        <v>1.25</v>
+      </c>
+      <c r="Q13">
+        <v>1.32</v>
+      </c>
+      <c r="R13">
+        <v>1.18</v>
+      </c>
+      <c r="S13">
+        <v>1.31</v>
+      </c>
+      <c r="T13">
+        <v>1.11</v>
+      </c>
+      <c r="U13">
+        <v>1.11</v>
+      </c>
+      <c r="V13">
+        <v>1.01</v>
+      </c>
+      <c r="W13">
+        <v>1.01</v>
+      </c>
+      <c r="X13">
+        <v>1000</v>
+      </c>
+      <c r="Y13">
+        <v>1000</v>
+      </c>
+      <c r="Z13">
+        <v>1000</v>
+      </c>
+      <c r="AA13">
+        <v>1000</v>
+      </c>
+      <c r="AB13">
+        <v>1000</v>
+      </c>
+      <c r="AC13">
+        <v>1000</v>
+      </c>
+      <c r="AD13">
+        <v>1000</v>
+      </c>
+      <c r="AE13">
+        <v>1000</v>
+      </c>
+      <c r="AF13">
+        <v>1000</v>
+      </c>
+      <c r="AG13">
+        <v>1000</v>
+      </c>
+      <c r="AH13">
+        <v>1000</v>
+      </c>
+      <c r="AI13">
+        <v>1000</v>
+      </c>
+      <c r="AJ13">
+        <v>1000</v>
+      </c>
+      <c r="AK13">
+        <v>1000</v>
+      </c>
+      <c r="AL13">
+        <v>1000</v>
+      </c>
+      <c r="AM13">
+        <v>1000</v>
+      </c>
+      <c r="AN13">
+        <v>1000</v>
+      </c>
+      <c r="AO13">
+        <v>1000</v>
+      </c>
+      <c r="AP13">
+        <v>1.01</v>
+      </c>
+      <c r="AQ13">
+        <v>1.01</v>
+      </c>
+      <c r="AR13">
+        <v>1.01</v>
+      </c>
+      <c r="AS13">
+        <v>1.01</v>
+      </c>
+      <c r="AT13">
+        <v>1.01</v>
+      </c>
+      <c r="AU13">
+        <v>1.01</v>
+      </c>
+      <c r="AV13">
+        <v>1.01</v>
+      </c>
+      <c r="AW13">
+        <v>1.01</v>
+      </c>
+      <c r="AX13">
+        <v>1.01</v>
+      </c>
+      <c r="AY13">
+        <v>1.01</v>
+      </c>
+      <c r="AZ13">
+        <v>1.01</v>
+      </c>
+      <c r="BA13">
+        <v>1.01</v>
+      </c>
+      <c r="BB13">
+        <v>1.01</v>
+      </c>
+      <c r="BC13">
+        <v>1.01</v>
+      </c>
+      <c r="BD13">
+        <v>1.01</v>
+      </c>
+      <c r="BE13">
+        <v>1.01</v>
+      </c>
+      <c r="BF13">
+        <v>1.01</v>
+      </c>
+      <c r="BG13">
+        <v>1.01</v>
+      </c>
+      <c r="BH13">
+        <v>1000</v>
+      </c>
+      <c r="BI13">
+        <v>1.04</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.04</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.04</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.04</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.04</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.04</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.04</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.04</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.04</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.04</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" t="s">
+        <v>127</v>
+      </c>
+      <c r="F14">
+        <v>1.33</v>
+      </c>
+      <c r="G14">
+        <v>1.72</v>
+      </c>
+      <c r="H14">
+        <v>5.8</v>
+      </c>
+      <c r="I14">
+        <v>990</v>
+      </c>
+      <c r="J14">
+        <v>3.8</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>2.82</v>
+      </c>
+      <c r="O14">
+        <v>1.3</v>
+      </c>
+      <c r="P14">
+        <v>1.67</v>
+      </c>
+      <c r="Q14">
+        <v>1.79</v>
+      </c>
+      <c r="R14">
+        <v>1.21</v>
+      </c>
+      <c r="S14">
+        <v>2.6</v>
+      </c>
+      <c r="T14">
+        <v>1.11</v>
+      </c>
+      <c r="U14">
+        <v>1.11</v>
+      </c>
+      <c r="V14">
+        <v>1.03</v>
+      </c>
+      <c r="W14">
+        <v>2.38</v>
+      </c>
+      <c r="X14">
+        <v>1000</v>
+      </c>
+      <c r="Y14">
+        <v>1000</v>
+      </c>
+      <c r="Z14">
+        <v>1000</v>
+      </c>
+      <c r="AA14">
+        <v>1000</v>
+      </c>
+      <c r="AB14">
+        <v>1000</v>
+      </c>
+      <c r="AC14">
+        <v>1000</v>
+      </c>
+      <c r="AD14">
+        <v>1000</v>
+      </c>
+      <c r="AE14">
+        <v>1000</v>
+      </c>
+      <c r="AF14">
+        <v>1000</v>
+      </c>
+      <c r="AG14">
+        <v>1000</v>
+      </c>
+      <c r="AH14">
+        <v>1000</v>
+      </c>
+      <c r="AI14">
+        <v>1000</v>
+      </c>
+      <c r="AJ14">
+        <v>1000</v>
+      </c>
+      <c r="AK14">
+        <v>1000</v>
+      </c>
+      <c r="AL14">
+        <v>1000</v>
+      </c>
+      <c r="AM14">
+        <v>1000</v>
+      </c>
+      <c r="AN14">
+        <v>1000</v>
+      </c>
+      <c r="AO14">
+        <v>1000</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.01</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.01</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.01</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.04</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.04</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.04</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.04</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.04</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.04</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.04</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.04</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.04</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.04</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
         <v>82</v>
       </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12">
-        <v>1.97</v>
-      </c>
-      <c r="G12">
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15">
+        <v>1.96</v>
+      </c>
+      <c r="G15">
         <v>2.14</v>
       </c>
-      <c r="H12">
+      <c r="H15">
         <v>4.1</v>
       </c>
-      <c r="I12">
+      <c r="I15">
         <v>4.7</v>
       </c>
-      <c r="J12">
-        <v>3.35</v>
-      </c>
-      <c r="K12">
+      <c r="J15">
+        <v>3.3</v>
+      </c>
+      <c r="K15">
         <v>3.8</v>
       </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
+      <c r="L15">
+        <v>1.38</v>
+      </c>
+      <c r="M15">
         <v>1.08</v>
       </c>
-      <c r="N12">
+      <c r="N15">
         <v>3.15</v>
       </c>
-      <c r="O12">
+      <c r="O15">
         <v>1.38</v>
       </c>
-      <c r="P12">
+      <c r="P15">
         <v>1.74</v>
       </c>
-      <c r="Q12">
-        <v>2.14</v>
-      </c>
-      <c r="R12">
+      <c r="Q15">
+        <v>2.1</v>
+      </c>
+      <c r="R15">
+        <v>1.28</v>
+      </c>
+      <c r="S15">
+        <v>3.95</v>
+      </c>
+      <c r="T15">
+        <v>1.89</v>
+      </c>
+      <c r="U15">
+        <v>1.91</v>
+      </c>
+      <c r="V15">
         <v>1.27</v>
       </c>
-      <c r="S12">
-        <v>4</v>
-      </c>
-      <c r="T12">
-        <v>1.89</v>
-      </c>
-      <c r="U12">
-        <v>1.91</v>
-      </c>
-      <c r="V12">
-        <v>1.27</v>
-      </c>
-      <c r="W12">
-        <v>1.89</v>
-      </c>
-      <c r="X12">
+      <c r="W15">
+        <v>1.87</v>
+      </c>
+      <c r="X15">
         <v>14.5</v>
       </c>
-      <c r="Y12">
+      <c r="Y15">
         <v>16.5</v>
       </c>
-      <c r="Z12">
+      <c r="Z15">
         <v>38</v>
       </c>
-      <c r="AA12">
+      <c r="AA15">
         <v>120</v>
       </c>
-      <c r="AB12">
+      <c r="AB15">
         <v>9.6</v>
       </c>
-      <c r="AC12">
+      <c r="AC15">
         <v>9.6</v>
       </c>
-      <c r="AD12">
+      <c r="AD15">
         <v>22</v>
       </c>
-      <c r="AE12">
+      <c r="AE15">
         <v>65</v>
       </c>
-      <c r="AF12">
+      <c r="AF15">
         <v>14.5</v>
       </c>
-      <c r="AG12">
+      <c r="AG15">
         <v>13</v>
       </c>
-      <c r="AH12">
+      <c r="AH15">
         <v>25</v>
       </c>
-      <c r="AI12">
+      <c r="AI15">
         <v>85</v>
       </c>
-      <c r="AJ12">
+      <c r="AJ15">
         <v>30</v>
       </c>
-      <c r="AK12">
+      <c r="AK15">
         <v>29</v>
       </c>
-      <c r="AL12">
+      <c r="AL15">
         <v>46</v>
       </c>
-      <c r="AM12">
+      <c r="AM15">
         <v>160</v>
       </c>
-      <c r="AN12">
+      <c r="AN15">
         <v>23</v>
       </c>
-      <c r="AO12">
+      <c r="AO15">
         <v>80</v>
       </c>
-      <c r="AP12">
+      <c r="AP15">
         <v>10</v>
       </c>
-      <c r="AQ12">
+      <c r="AQ15">
         <v>10</v>
       </c>
-      <c r="AR12">
+      <c r="AR15">
         <v>4.1</v>
       </c>
-      <c r="AS12">
+      <c r="AS15">
         <v>4.4</v>
       </c>
-      <c r="AT12">
+      <c r="AT15">
         <v>7</v>
       </c>
-      <c r="AU12">
-        <v>6</v>
-      </c>
-      <c r="AV12">
+      <c r="AU15">
+        <v>6.8</v>
+      </c>
+      <c r="AV15">
         <v>13</v>
       </c>
-      <c r="AW12">
+      <c r="AW15">
         <v>4.3</v>
       </c>
-      <c r="AX12">
+      <c r="AX15">
         <v>10</v>
       </c>
-      <c r="AY12">
+      <c r="AY15">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ12">
-        <v>15</v>
-      </c>
-      <c r="BA12">
+      <c r="AZ15">
+        <v>17</v>
+      </c>
+      <c r="BA15">
         <v>4.3</v>
       </c>
-      <c r="BB12">
+      <c r="BB15">
         <v>21</v>
       </c>
-      <c r="BC12">
+      <c r="BC15">
         <v>20</v>
       </c>
-      <c r="BD12">
+      <c r="BD15">
         <v>4.1</v>
       </c>
-      <c r="BE12">
+      <c r="BE15">
         <v>4.4</v>
       </c>
-      <c r="BF12">
+      <c r="BF15">
         <v>15.5</v>
       </c>
-      <c r="BG12">
+      <c r="BG15">
         <v>4.3</v>
       </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.78</v>
-      </c>
-      <c r="BJ12">
-        <v>15</v>
-      </c>
-      <c r="BK12">
-        <v>1.59</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.78</v>
-      </c>
-      <c r="BN12">
-        <v>6.4</v>
-      </c>
-      <c r="BO12">
-        <v>3.35</v>
-      </c>
-      <c r="BP12">
-        <v>22</v>
-      </c>
-      <c r="BQ12">
-        <v>1.65</v>
-      </c>
-      <c r="BR12">
+      <c r="BH15">
+        <v>3.6</v>
+      </c>
+      <c r="BI15">
+        <v>2.54</v>
+      </c>
+      <c r="BJ15">
+        <v>12.5</v>
+      </c>
+      <c r="BK15">
+        <v>3.5</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>4.8</v>
+      </c>
+      <c r="BN15">
+        <v>5.5</v>
+      </c>
+      <c r="BO15">
+        <v>3.6</v>
+      </c>
+      <c r="BP15">
+        <v>18.5</v>
+      </c>
+      <c r="BQ15">
+        <v>3.9</v>
+      </c>
+      <c r="BR15">
+        <v>40</v>
+      </c>
+      <c r="BS15">
+        <v>4.4</v>
+      </c>
+      <c r="BT15">
+        <v>9</v>
+      </c>
+      <c r="BU15">
+        <v>5.6</v>
+      </c>
+      <c r="BV15">
         <v>48</v>
       </c>
-      <c r="BS12">
-        <v>1.72</v>
-      </c>
-      <c r="BT12">
-        <v>10.5</v>
-      </c>
-      <c r="BU12">
-        <v>4.8</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.72</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.74</v>
-      </c>
-      <c r="BZ12">
-        <v>46</v>
-      </c>
-      <c r="CA12">
-        <v>1.71</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>120</v>
+      <c r="BW15">
+        <v>4.4</v>
+      </c>
+      <c r="BX15">
+        <v>65</v>
+      </c>
+      <c r="BY15">
+        <v>4.5</v>
+      </c>
+      <c r="BZ15">
+        <v>38</v>
+      </c>
+      <c r="CA15">
+        <v>4.3</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="137">
   <si>
     <t>League</t>
   </si>
@@ -256,6 +256,9 @@
     <t>SnapshotTS</t>
   </si>
   <si>
+    <t>Chilean Primera B</t>
+  </si>
+  <si>
     <t>Ecuadorian Serie A</t>
   </si>
   <si>
@@ -271,6 +274,9 @@
     <t>Romanian Liga II</t>
   </si>
   <si>
+    <t>Argentinian Primera C</t>
+  </si>
+  <si>
     <t>Icelandic Urvalsdeild</t>
   </si>
   <si>
@@ -298,6 +304,9 @@
     <t>15:00:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>18:30:00</t>
   </si>
   <si>
@@ -319,6 +328,9 @@
     <t>23:15:00</t>
   </si>
   <si>
+    <t>Deportes Temuco</t>
+  </si>
+  <si>
     <t>LDU</t>
   </si>
   <si>
@@ -337,6 +349,9 @@
     <t>Politehnica Timisoara</t>
   </si>
   <si>
+    <t>CSR Espanol BA</t>
+  </si>
+  <si>
     <t>Thor</t>
   </si>
   <si>
@@ -361,6 +376,9 @@
     <t>Tolima</t>
   </si>
   <si>
+    <t>Deportes Copiapo</t>
+  </si>
+  <si>
     <t>Delfin</t>
   </si>
   <si>
@@ -379,6 +397,9 @@
     <t>Chindia Targoviste</t>
   </si>
   <si>
+    <t>Leones de Rosario</t>
+  </si>
+  <si>
     <t>Breidablik</t>
   </si>
   <si>
@@ -403,7 +424,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 13:58:24</t>
+    <t>2026-08-03 16:06:25</t>
   </si>
 </sst>
 </file>
@@ -735,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB15"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -985,241 +1006,241 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F2">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="G2">
+        <v>2.08</v>
+      </c>
+      <c r="H2">
+        <v>3.95</v>
+      </c>
+      <c r="I2">
+        <v>4.5</v>
+      </c>
+      <c r="J2">
+        <v>3.5</v>
+      </c>
+      <c r="K2">
+        <v>3.8</v>
+      </c>
+      <c r="L2">
+        <v>1.44</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
+        <v>3.6</v>
+      </c>
+      <c r="O2">
+        <v>1.34</v>
+      </c>
+      <c r="P2">
+        <v>1.86</v>
+      </c>
+      <c r="Q2">
+        <v>2.04</v>
+      </c>
+      <c r="R2">
         <v>1.32</v>
       </c>
-      <c r="H2">
-        <v>12</v>
-      </c>
-      <c r="I2">
-        <v>14.5</v>
-      </c>
-      <c r="J2">
-        <v>5.8</v>
-      </c>
-      <c r="K2">
-        <v>6.2</v>
-      </c>
-      <c r="L2">
-        <v>1.38</v>
-      </c>
-      <c r="M2">
-        <v>1.06</v>
-      </c>
-      <c r="N2">
-        <v>4.1</v>
-      </c>
-      <c r="O2">
-        <v>1.3</v>
-      </c>
-      <c r="P2">
-        <v>2.06</v>
-      </c>
-      <c r="Q2">
-        <v>1.87</v>
-      </c>
-      <c r="R2">
-        <v>1.4</v>
-      </c>
       <c r="S2">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="T2">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="U2">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="V2">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>4.1</v>
+        <v>1.92</v>
       </c>
       <c r="X2">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="Y2">
+        <v>15.5</v>
+      </c>
+      <c r="Z2">
         <v>34</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
+        <v>120</v>
+      </c>
+      <c r="AB2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC2">
+        <v>8.4</v>
+      </c>
+      <c r="AD2">
+        <v>18</v>
+      </c>
+      <c r="AE2">
+        <v>60</v>
+      </c>
+      <c r="AF2">
+        <v>13</v>
+      </c>
+      <c r="AG2">
+        <v>11</v>
+      </c>
+      <c r="AH2">
+        <v>19.5</v>
+      </c>
+      <c r="AI2">
+        <v>65</v>
+      </c>
+      <c r="AJ2">
+        <v>25</v>
+      </c>
+      <c r="AK2">
+        <v>23</v>
+      </c>
+      <c r="AL2">
+        <v>40</v>
+      </c>
+      <c r="AM2">
         <v>140</v>
       </c>
-      <c r="AA2">
-        <v>800</v>
-      </c>
-      <c r="AB2">
-        <v>7.4</v>
-      </c>
-      <c r="AC2">
-        <v>13.5</v>
-      </c>
-      <c r="AD2">
+      <c r="AN2">
+        <v>16.5</v>
+      </c>
+      <c r="AO2">
         <v>65</v>
       </c>
-      <c r="AE2">
-        <v>320</v>
-      </c>
-      <c r="AF2">
-        <v>6.8</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>44</v>
-      </c>
-      <c r="AI2">
-        <v>310</v>
-      </c>
-      <c r="AJ2">
-        <v>9.6</v>
-      </c>
-      <c r="AK2">
-        <v>16.5</v>
-      </c>
-      <c r="AL2">
-        <v>60</v>
-      </c>
-      <c r="AM2">
-        <v>340</v>
-      </c>
-      <c r="AN2">
-        <v>6.4</v>
-      </c>
-      <c r="AO2">
-        <v>510</v>
-      </c>
       <c r="AP2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ2">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="AS2">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>38</v>
+        <v>12.5</v>
       </c>
       <c r="AW2">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX2">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="BB2">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="BC2">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BD2">
-        <v>44</v>
+        <v>7.2</v>
       </c>
       <c r="BE2">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BF2">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BG2">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH2">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>2.94</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN2">
+        <v>4.9</v>
+      </c>
+      <c r="BO2">
         <v>3.65</v>
       </c>
-      <c r="BO2">
-        <v>3.1</v>
-      </c>
       <c r="BP2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BQ2">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BW2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY2">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="CA2">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1227,276 +1248,276 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F3">
-        <v>3.4</v>
+        <v>1.31</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>1.33</v>
       </c>
       <c r="H3">
-        <v>2.72</v>
+        <v>12.5</v>
       </c>
       <c r="I3">
-        <v>2.76</v>
+        <v>14.5</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>5.8</v>
       </c>
       <c r="K3">
+        <v>6.2</v>
+      </c>
+      <c r="L3">
+        <v>1.38</v>
+      </c>
+      <c r="M3">
+        <v>1.06</v>
+      </c>
+      <c r="N3">
+        <v>4.1</v>
+      </c>
+      <c r="O3">
+        <v>1.3</v>
+      </c>
+      <c r="P3">
+        <v>2.06</v>
+      </c>
+      <c r="Q3">
+        <v>1.89</v>
+      </c>
+      <c r="R3">
+        <v>1.4</v>
+      </c>
+      <c r="S3">
+        <v>3.35</v>
+      </c>
+      <c r="T3">
+        <v>2.44</v>
+      </c>
+      <c r="U3">
+        <v>1.61</v>
+      </c>
+      <c r="V3">
+        <v>1.07</v>
+      </c>
+      <c r="W3">
+        <v>4</v>
+      </c>
+      <c r="X3">
+        <v>22</v>
+      </c>
+      <c r="Y3">
+        <v>34</v>
+      </c>
+      <c r="Z3">
+        <v>140</v>
+      </c>
+      <c r="AA3">
+        <v>800</v>
+      </c>
+      <c r="AB3">
+        <v>7.4</v>
+      </c>
+      <c r="AC3">
+        <v>13.5</v>
+      </c>
+      <c r="AD3">
+        <v>48</v>
+      </c>
+      <c r="AE3">
+        <v>340</v>
+      </c>
+      <c r="AF3">
+        <v>6.8</v>
+      </c>
+      <c r="AG3">
+        <v>11.5</v>
+      </c>
+      <c r="AH3">
+        <v>44</v>
+      </c>
+      <c r="AI3">
+        <v>310</v>
+      </c>
+      <c r="AJ3">
+        <v>9.6</v>
+      </c>
+      <c r="AK3">
+        <v>16.5</v>
+      </c>
+      <c r="AL3">
+        <v>55</v>
+      </c>
+      <c r="AM3">
+        <v>300</v>
+      </c>
+      <c r="AN3">
+        <v>6.6</v>
+      </c>
+      <c r="AO3">
+        <v>490</v>
+      </c>
+      <c r="AP3">
+        <v>15</v>
+      </c>
+      <c r="AQ3">
+        <v>32</v>
+      </c>
+      <c r="AR3">
+        <v>44</v>
+      </c>
+      <c r="AS3">
+        <v>12</v>
+      </c>
+      <c r="AT3">
+        <v>6.6</v>
+      </c>
+      <c r="AU3">
+        <v>12</v>
+      </c>
+      <c r="AV3">
+        <v>38</v>
+      </c>
+      <c r="AW3">
+        <v>14</v>
+      </c>
+      <c r="AX3">
+        <v>6.2</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>36</v>
+      </c>
+      <c r="BA3">
+        <v>13.5</v>
+      </c>
+      <c r="BB3">
+        <v>8.6</v>
+      </c>
+      <c r="BC3">
+        <v>14.5</v>
+      </c>
+      <c r="BD3">
+        <v>46</v>
+      </c>
+      <c r="BE3">
+        <v>14</v>
+      </c>
+      <c r="BF3">
+        <v>6</v>
+      </c>
+      <c r="BG3">
+        <v>14</v>
+      </c>
+      <c r="BH3">
+        <v>4.3</v>
+      </c>
+      <c r="BI3">
         <v>2.94</v>
-      </c>
-      <c r="L3">
-        <v>1.68</v>
-      </c>
-      <c r="M3">
-        <v>1.16</v>
-      </c>
-      <c r="N3">
-        <v>2.42</v>
-      </c>
-      <c r="O3">
-        <v>1.68</v>
-      </c>
-      <c r="P3">
-        <v>1.45</v>
-      </c>
-      <c r="Q3">
-        <v>3.15</v>
-      </c>
-      <c r="R3">
-        <v>1.15</v>
-      </c>
-      <c r="S3">
-        <v>7</v>
-      </c>
-      <c r="T3">
-        <v>2.36</v>
-      </c>
-      <c r="U3">
-        <v>1.69</v>
-      </c>
-      <c r="V3">
-        <v>1.57</v>
-      </c>
-      <c r="W3">
-        <v>1.4</v>
-      </c>
-      <c r="X3">
-        <v>7.2</v>
-      </c>
-      <c r="Y3">
-        <v>7.4</v>
-      </c>
-      <c r="Z3">
-        <v>15.5</v>
-      </c>
-      <c r="AA3">
-        <v>46</v>
-      </c>
-      <c r="AB3">
-        <v>8.4</v>
-      </c>
-      <c r="AC3">
-        <v>6.6</v>
-      </c>
-      <c r="AD3">
-        <v>14</v>
-      </c>
-      <c r="AE3">
-        <v>46</v>
-      </c>
-      <c r="AF3">
-        <v>20</v>
-      </c>
-      <c r="AG3">
-        <v>16</v>
-      </c>
-      <c r="AH3">
-        <v>27</v>
-      </c>
-      <c r="AI3">
-        <v>85</v>
-      </c>
-      <c r="AJ3">
-        <v>70</v>
-      </c>
-      <c r="AK3">
-        <v>60</v>
-      </c>
-      <c r="AL3">
-        <v>100</v>
-      </c>
-      <c r="AM3">
-        <v>250</v>
-      </c>
-      <c r="AN3">
-        <v>90</v>
-      </c>
-      <c r="AO3">
-        <v>60</v>
-      </c>
-      <c r="AP3">
-        <v>6.6</v>
-      </c>
-      <c r="AQ3">
-        <v>6.8</v>
-      </c>
-      <c r="AR3">
-        <v>13.5</v>
-      </c>
-      <c r="AS3">
-        <v>38</v>
-      </c>
-      <c r="AT3">
-        <v>8</v>
-      </c>
-      <c r="AU3">
-        <v>6.2</v>
-      </c>
-      <c r="AV3">
-        <v>13</v>
-      </c>
-      <c r="AW3">
-        <v>38</v>
-      </c>
-      <c r="AX3">
-        <v>18.5</v>
-      </c>
-      <c r="AY3">
-        <v>15</v>
-      </c>
-      <c r="AZ3">
-        <v>24</v>
-      </c>
-      <c r="BA3">
-        <v>70</v>
-      </c>
-      <c r="BB3">
-        <v>60</v>
-      </c>
-      <c r="BC3">
-        <v>50</v>
-      </c>
-      <c r="BD3">
-        <v>60</v>
-      </c>
-      <c r="BE3">
-        <v>50</v>
-      </c>
-      <c r="BF3">
-        <v>55</v>
-      </c>
-      <c r="BG3">
-        <v>50</v>
-      </c>
-      <c r="BH3">
-        <v>2.82</v>
-      </c>
-      <c r="BI3">
-        <v>2.06</v>
       </c>
       <c r="BJ3">
         <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BN3">
-        <v>7.4</v>
+        <v>3.65</v>
       </c>
       <c r="BO3">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="BP3">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="BQ3">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BR3">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BU3">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
-        <v>80</v>
+        <v>15.5</v>
       </c>
       <c r="CA3">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:80">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F4">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="G4">
-        <v>2.22</v>
+        <v>3.45</v>
       </c>
       <c r="H4">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>2.76</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="L4">
         <v>1.67</v>
@@ -1505,205 +1526,205 @@
         <v>1.16</v>
       </c>
       <c r="N4">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="P4">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="R4">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="U4">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="X4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y4">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="Z4">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AA4">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="AB4">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE4">
+        <v>46</v>
+      </c>
+      <c r="AF4">
+        <v>20</v>
+      </c>
+      <c r="AG4">
+        <v>16</v>
+      </c>
+      <c r="AH4">
+        <v>27</v>
+      </c>
+      <c r="AI4">
+        <v>85</v>
+      </c>
+      <c r="AJ4">
+        <v>70</v>
+      </c>
+      <c r="AK4">
+        <v>60</v>
+      </c>
+      <c r="AL4">
         <v>95</v>
       </c>
-      <c r="AF4">
-        <v>11.5</v>
-      </c>
-      <c r="AG4">
-        <v>13</v>
-      </c>
-      <c r="AH4">
-        <v>29</v>
-      </c>
-      <c r="AI4">
-        <v>140</v>
-      </c>
-      <c r="AJ4">
-        <v>30</v>
-      </c>
-      <c r="AK4">
-        <v>36</v>
-      </c>
-      <c r="AL4">
-        <v>80</v>
-      </c>
       <c r="AM4">
-        <v>290</v>
+        <v>250</v>
       </c>
       <c r="AN4">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AO4">
-        <v>170</v>
+        <v>60</v>
       </c>
       <c r="AP4">
         <v>6.8</v>
       </c>
       <c r="AQ4">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AR4">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AT4">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AW4">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AX4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AY4">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA4">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="BB4">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="BC4">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BD4">
         <v>60</v>
       </c>
       <c r="BE4">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="BF4">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="BG4">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BH4">
-        <v>2.52</v>
+        <v>2.82</v>
       </c>
       <c r="BI4">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BJ4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="BM4">
-        <v>2.18</v>
+        <v>8</v>
       </c>
       <c r="BN4">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP4">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BQ4">
-        <v>9.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR4">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="BS4">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BT4">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="BV4">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="BW4">
-        <v>13</v>
+        <v>6.2</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="BZ4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="CA4">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1711,241 +1732,241 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F5">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="G5">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="I5">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="M5">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="N5">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="O5">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="P5">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="Q5">
-        <v>2.16</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="S5">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="U5">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="V5">
-        <v>1.16</v>
+        <v>1.26</v>
       </c>
       <c r="W5">
-        <v>2.48</v>
+        <v>1.84</v>
       </c>
       <c r="X5">
+        <v>7.2</v>
+      </c>
+      <c r="Y5">
+        <v>11</v>
+      </c>
+      <c r="Z5">
+        <v>30</v>
+      </c>
+      <c r="AA5">
+        <v>130</v>
+      </c>
+      <c r="AB5">
+        <v>6</v>
+      </c>
+      <c r="AC5">
+        <v>7.2</v>
+      </c>
+      <c r="AD5">
+        <v>21</v>
+      </c>
+      <c r="AE5">
+        <v>95</v>
+      </c>
+      <c r="AF5">
+        <v>11</v>
+      </c>
+      <c r="AG5">
+        <v>12.5</v>
+      </c>
+      <c r="AH5">
+        <v>29</v>
+      </c>
+      <c r="AI5">
+        <v>140</v>
+      </c>
+      <c r="AJ5">
+        <v>30</v>
+      </c>
+      <c r="AK5">
+        <v>36</v>
+      </c>
+      <c r="AL5">
+        <v>80</v>
+      </c>
+      <c r="AM5">
+        <v>290</v>
+      </c>
+      <c r="AN5">
+        <v>36</v>
+      </c>
+      <c r="AO5">
+        <v>170</v>
+      </c>
+      <c r="AP5">
+        <v>6.8</v>
+      </c>
+      <c r="AQ5">
+        <v>10</v>
+      </c>
+      <c r="AR5">
+        <v>27</v>
+      </c>
+      <c r="AS5">
+        <v>48</v>
+      </c>
+      <c r="AT5">
+        <v>5.7</v>
+      </c>
+      <c r="AU5">
+        <v>6.8</v>
+      </c>
+      <c r="AV5">
+        <v>19</v>
+      </c>
+      <c r="AW5">
+        <v>55</v>
+      </c>
+      <c r="AX5">
+        <v>10</v>
+      </c>
+      <c r="AY5">
+        <v>11.5</v>
+      </c>
+      <c r="AZ5">
+        <v>25</v>
+      </c>
+      <c r="BA5">
+        <v>50</v>
+      </c>
+      <c r="BB5">
+        <v>26</v>
+      </c>
+      <c r="BC5">
+        <v>30</v>
+      </c>
+      <c r="BD5">
+        <v>60</v>
+      </c>
+      <c r="BE5">
+        <v>110</v>
+      </c>
+      <c r="BF5">
+        <v>30</v>
+      </c>
+      <c r="BG5">
+        <v>55</v>
+      </c>
+      <c r="BH5">
+        <v>2.52</v>
+      </c>
+      <c r="BI5">
+        <v>2.34</v>
+      </c>
+      <c r="BJ5">
         <v>13</v>
       </c>
-      <c r="Y5">
-        <v>21</v>
-      </c>
-      <c r="Z5">
-        <v>65</v>
-      </c>
-      <c r="AA5">
-        <v>270</v>
-      </c>
-      <c r="AB5">
-        <v>7.4</v>
-      </c>
-      <c r="AC5">
+      <c r="BK5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>16.5</v>
+      </c>
+      <c r="BN5">
+        <v>4.6</v>
+      </c>
+      <c r="BO5">
+        <v>4.2</v>
+      </c>
+      <c r="BP5">
+        <v>20</v>
+      </c>
+      <c r="BQ5">
         <v>9.4</v>
       </c>
-      <c r="AD5">
-        <v>28</v>
-      </c>
-      <c r="AE5">
-        <v>140</v>
-      </c>
-      <c r="AF5">
-        <v>9</v>
-      </c>
-      <c r="AG5">
-        <v>11</v>
-      </c>
-      <c r="AH5">
-        <v>28</v>
-      </c>
-      <c r="AI5">
-        <v>130</v>
-      </c>
-      <c r="AJ5">
-        <v>16.5</v>
-      </c>
-      <c r="AK5">
-        <v>19.5</v>
-      </c>
-      <c r="AL5">
-        <v>46</v>
-      </c>
-      <c r="AM5">
-        <v>190</v>
-      </c>
-      <c r="AN5">
-        <v>11.5</v>
-      </c>
-      <c r="AO5">
-        <v>220</v>
-      </c>
-      <c r="AP5">
-        <v>11</v>
-      </c>
-      <c r="AQ5">
-        <v>17</v>
-      </c>
-      <c r="AR5">
-        <v>40</v>
-      </c>
-      <c r="AS5">
-        <v>10</v>
-      </c>
-      <c r="AT5">
-        <v>6.4</v>
-      </c>
-      <c r="AU5">
-        <v>8</v>
-      </c>
-      <c r="AV5">
-        <v>23</v>
-      </c>
-      <c r="AW5">
-        <v>10</v>
-      </c>
-      <c r="AX5">
+      <c r="BR5">
+        <v>50</v>
+      </c>
+      <c r="BS5">
+        <v>13</v>
+      </c>
+      <c r="BT5">
         <v>7.6</v>
       </c>
-      <c r="AY5">
-        <v>9</v>
-      </c>
-      <c r="AZ5">
-        <v>21</v>
-      </c>
-      <c r="BA5">
-        <v>10</v>
-      </c>
-      <c r="BB5">
+      <c r="BU5">
+        <v>5.8</v>
+      </c>
+      <c r="BV5">
+        <v>55</v>
+      </c>
+      <c r="BW5">
         <v>13</v>
       </c>
-      <c r="BC5">
-        <v>16</v>
-      </c>
-      <c r="BD5">
-        <v>34</v>
-      </c>
-      <c r="BE5">
-        <v>10</v>
-      </c>
-      <c r="BF5">
-        <v>9.4</v>
-      </c>
-      <c r="BG5">
-        <v>10</v>
-      </c>
-      <c r="BH5">
-        <v>3.6</v>
-      </c>
-      <c r="BI5">
-        <v>2.7</v>
-      </c>
-      <c r="BJ5">
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>14</v>
+      </c>
+      <c r="BZ5">
+        <v>60</v>
+      </c>
+      <c r="CA5">
         <v>13.5</v>
       </c>
-      <c r="BK5">
-        <v>4.1</v>
-      </c>
-      <c r="BL5">
-        <v>210</v>
-      </c>
-      <c r="BM5">
-        <v>5.7</v>
-      </c>
-      <c r="BN5">
-        <v>4.5</v>
-      </c>
-      <c r="BO5">
-        <v>3.2</v>
-      </c>
-      <c r="BP5">
-        <v>12.5</v>
-      </c>
-      <c r="BQ5">
-        <v>4</v>
-      </c>
-      <c r="BR5">
-        <v>36</v>
-      </c>
-      <c r="BS5">
-        <v>5</v>
-      </c>
-      <c r="BT5">
-        <v>12</v>
-      </c>
-      <c r="BU5">
-        <v>3.95</v>
-      </c>
-      <c r="BV5">
-        <v>80</v>
-      </c>
-      <c r="BW5">
-        <v>5.4</v>
-      </c>
-      <c r="BX5">
-        <v>90</v>
-      </c>
-      <c r="BY5">
-        <v>5.5</v>
-      </c>
-      <c r="BZ5">
-        <v>27</v>
-      </c>
-      <c r="CA5">
-        <v>4.8</v>
-      </c>
       <c r="CB5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1953,37 +1974,37 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F6">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="G6">
-        <v>3.95</v>
+        <v>1.65</v>
       </c>
       <c r="H6">
-        <v>2.14</v>
+        <v>6.6</v>
       </c>
       <c r="I6">
-        <v>2.18</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L6">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M6">
         <v>1.08</v>
@@ -1992,202 +2013,202 @@
         <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P6">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T6">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="V6">
-        <v>1.84</v>
+        <v>1.16</v>
       </c>
       <c r="W6">
-        <v>1.33</v>
+        <v>2.52</v>
       </c>
       <c r="X6">
+        <v>13</v>
+      </c>
+      <c r="Y6">
+        <v>21</v>
+      </c>
+      <c r="Z6">
+        <v>65</v>
+      </c>
+      <c r="AA6">
+        <v>320</v>
+      </c>
+      <c r="AB6">
+        <v>7.4</v>
+      </c>
+      <c r="AC6">
+        <v>9.4</v>
+      </c>
+      <c r="AD6">
+        <v>29</v>
+      </c>
+      <c r="AE6">
+        <v>150</v>
+      </c>
+      <c r="AF6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG6">
+        <v>11</v>
+      </c>
+      <c r="AH6">
+        <v>26</v>
+      </c>
+      <c r="AI6">
+        <v>150</v>
+      </c>
+      <c r="AJ6">
+        <v>16</v>
+      </c>
+      <c r="AK6">
+        <v>19.5</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
+        <v>190</v>
+      </c>
+      <c r="AN6">
+        <v>11.5</v>
+      </c>
+      <c r="AO6">
+        <v>240</v>
+      </c>
+      <c r="AP6">
+        <v>11</v>
+      </c>
+      <c r="AQ6">
+        <v>17.5</v>
+      </c>
+      <c r="AR6">
+        <v>42</v>
+      </c>
+      <c r="AS6">
+        <v>10.5</v>
+      </c>
+      <c r="AT6">
+        <v>6.2</v>
+      </c>
+      <c r="AU6">
+        <v>8</v>
+      </c>
+      <c r="AV6">
+        <v>24</v>
+      </c>
+      <c r="AW6">
+        <v>65</v>
+      </c>
+      <c r="AX6">
+        <v>7.6</v>
+      </c>
+      <c r="AY6">
+        <v>9</v>
+      </c>
+      <c r="AZ6">
+        <v>21</v>
+      </c>
+      <c r="BA6">
+        <v>10.5</v>
+      </c>
+      <c r="BB6">
+        <v>13</v>
+      </c>
+      <c r="BC6">
+        <v>16</v>
+      </c>
+      <c r="BD6">
+        <v>34</v>
+      </c>
+      <c r="BE6">
+        <v>10.5</v>
+      </c>
+      <c r="BF6">
+        <v>9.4</v>
+      </c>
+      <c r="BG6">
+        <v>10.5</v>
+      </c>
+      <c r="BH6">
+        <v>3.55</v>
+      </c>
+      <c r="BI6">
+        <v>2.64</v>
+      </c>
+      <c r="BJ6">
         <v>12.5</v>
       </c>
-      <c r="Y6">
-        <v>9</v>
-      </c>
-      <c r="Z6">
-        <v>13.5</v>
-      </c>
-      <c r="AA6">
-        <v>28</v>
-      </c>
-      <c r="AB6">
-        <v>14</v>
-      </c>
-      <c r="AC6">
+      <c r="BK6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BL6">
+        <v>230</v>
+      </c>
+      <c r="BM6">
+        <v>8</v>
+      </c>
+      <c r="BN6">
+        <v>4</v>
+      </c>
+      <c r="BO6">
+        <v>3.4</v>
+      </c>
+      <c r="BP6">
+        <v>12.5</v>
+      </c>
+      <c r="BQ6">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD6">
-        <v>11.5</v>
-      </c>
-      <c r="AE6">
-        <v>27</v>
-      </c>
-      <c r="AF6">
-        <v>29</v>
-      </c>
-      <c r="AG6">
-        <v>16.5</v>
-      </c>
-      <c r="AH6">
-        <v>19.5</v>
-      </c>
-      <c r="AI6">
-        <v>42</v>
-      </c>
-      <c r="AJ6">
+      <c r="BR6">
+        <v>34</v>
+      </c>
+      <c r="BS6">
+        <v>6.6</v>
+      </c>
+      <c r="BT6">
+        <v>11</v>
+      </c>
+      <c r="BU6">
+        <v>8.4</v>
+      </c>
+      <c r="BV6">
+        <v>80</v>
+      </c>
+      <c r="BW6">
+        <v>7.4</v>
+      </c>
+      <c r="BX6">
         <v>90</v>
       </c>
-      <c r="AK6">
-        <v>55</v>
-      </c>
-      <c r="AL6">
-        <v>85</v>
-      </c>
-      <c r="AM6">
-        <v>150</v>
-      </c>
-      <c r="AN6">
-        <v>65</v>
-      </c>
-      <c r="AO6">
-        <v>20</v>
-      </c>
-      <c r="AP6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ6">
-        <v>7.4</v>
-      </c>
-      <c r="AR6">
-        <v>10.5</v>
-      </c>
-      <c r="AS6">
-        <v>21</v>
-      </c>
-      <c r="AT6">
-        <v>11.5</v>
-      </c>
-      <c r="AU6">
-        <v>6.8</v>
-      </c>
-      <c r="AV6">
-        <v>9</v>
-      </c>
-      <c r="AW6">
-        <v>20</v>
-      </c>
-      <c r="AX6">
-        <v>21</v>
-      </c>
-      <c r="AY6">
-        <v>14</v>
-      </c>
-      <c r="AZ6">
-        <v>16.5</v>
-      </c>
-      <c r="BA6">
-        <v>32</v>
-      </c>
-      <c r="BB6">
-        <v>50</v>
-      </c>
-      <c r="BC6">
-        <v>36</v>
-      </c>
-      <c r="BD6">
-        <v>46</v>
-      </c>
-      <c r="BE6">
-        <v>85</v>
-      </c>
-      <c r="BF6">
-        <v>40</v>
-      </c>
-      <c r="BG6">
-        <v>15</v>
-      </c>
-      <c r="BH6">
-        <v>3.3</v>
-      </c>
-      <c r="BI6">
-        <v>2.9</v>
-      </c>
-      <c r="BJ6">
-        <v>10.5</v>
-      </c>
-      <c r="BK6">
-        <v>6.8</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>10.5</v>
-      </c>
-      <c r="BN6">
-        <v>7.2</v>
-      </c>
-      <c r="BO6">
-        <v>5.7</v>
-      </c>
-      <c r="BP6">
-        <v>34</v>
-      </c>
-      <c r="BQ6">
-        <v>8.6</v>
-      </c>
-      <c r="BR6">
-        <v>50</v>
-      </c>
-      <c r="BS6">
-        <v>9.4</v>
-      </c>
-      <c r="BT6">
-        <v>4.9</v>
-      </c>
-      <c r="BU6">
-        <v>4.1</v>
-      </c>
-      <c r="BV6">
-        <v>19</v>
-      </c>
-      <c r="BW6">
-        <v>10</v>
-      </c>
-      <c r="BX6">
-        <v>32</v>
-      </c>
       <c r="BY6">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ6">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="CA6">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2195,241 +2216,241 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F7">
-        <v>2.38</v>
+        <v>3.8</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>3.95</v>
       </c>
       <c r="H7">
-        <v>3.05</v>
+        <v>2.14</v>
       </c>
       <c r="I7">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K7">
         <v>3.6</v>
       </c>
       <c r="L7">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P7">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="Q7">
         <v>2.12</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="T7">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U7">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="W7">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="X7">
+        <v>12.5</v>
+      </c>
+      <c r="Y7">
+        <v>9</v>
+      </c>
+      <c r="Z7">
         <v>13.5</v>
       </c>
-      <c r="Y7">
-        <v>13.5</v>
-      </c>
-      <c r="Z7">
-        <v>26</v>
-      </c>
       <c r="AA7">
-        <v>75</v>
+        <v>28</v>
       </c>
       <c r="AB7">
+        <v>14</v>
+      </c>
+      <c r="AC7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7">
         <v>11.5</v>
       </c>
-      <c r="AC7">
-        <v>7.8</v>
-      </c>
-      <c r="AD7">
-        <v>15</v>
-      </c>
       <c r="AE7">
+        <v>27</v>
+      </c>
+      <c r="AF7">
+        <v>29</v>
+      </c>
+      <c r="AG7">
+        <v>16.5</v>
+      </c>
+      <c r="AH7">
+        <v>19.5</v>
+      </c>
+      <c r="AI7">
+        <v>42</v>
+      </c>
+      <c r="AJ7">
+        <v>90</v>
+      </c>
+      <c r="AK7">
         <v>55</v>
       </c>
-      <c r="AF7">
-        <v>19.5</v>
-      </c>
-      <c r="AG7">
-        <v>14.5</v>
-      </c>
-      <c r="AH7">
-        <v>23</v>
-      </c>
-      <c r="AI7">
-        <v>70</v>
-      </c>
-      <c r="AJ7">
-        <v>48</v>
-      </c>
-      <c r="AK7">
-        <v>38</v>
-      </c>
       <c r="AL7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM7">
         <v>150</v>
       </c>
       <c r="AN7">
+        <v>75</v>
+      </c>
+      <c r="AO7">
+        <v>20</v>
+      </c>
+      <c r="AP7">
+        <v>10.5</v>
+      </c>
+      <c r="AQ7">
+        <v>7.4</v>
+      </c>
+      <c r="AR7">
+        <v>10.5</v>
+      </c>
+      <c r="AS7">
+        <v>21</v>
+      </c>
+      <c r="AT7">
+        <v>11.5</v>
+      </c>
+      <c r="AU7">
+        <v>6.8</v>
+      </c>
+      <c r="AV7">
+        <v>9</v>
+      </c>
+      <c r="AW7">
+        <v>20</v>
+      </c>
+      <c r="AX7">
+        <v>22</v>
+      </c>
+      <c r="AY7">
+        <v>14</v>
+      </c>
+      <c r="AZ7">
+        <v>16.5</v>
+      </c>
+      <c r="BA7">
         <v>32</v>
       </c>
-      <c r="AO7">
-        <v>55</v>
-      </c>
-      <c r="AP7">
-        <v>3.6</v>
-      </c>
-      <c r="AQ7">
-        <v>3.6</v>
-      </c>
-      <c r="AR7">
-        <v>4.1</v>
-      </c>
-      <c r="AS7">
-        <v>4.6</v>
-      </c>
-      <c r="AT7">
-        <v>3.45</v>
-      </c>
-      <c r="AU7">
-        <v>3</v>
-      </c>
-      <c r="AV7">
-        <v>3.7</v>
-      </c>
-      <c r="AW7">
-        <v>4.5</v>
-      </c>
-      <c r="AX7">
-        <v>3.9</v>
-      </c>
-      <c r="AY7">
-        <v>3.65</v>
-      </c>
-      <c r="AZ7">
-        <v>4</v>
-      </c>
-      <c r="BA7">
-        <v>4.6</v>
-      </c>
       <c r="BB7">
-        <v>4.4</v>
+        <v>50</v>
       </c>
       <c r="BC7">
-        <v>4.3</v>
+        <v>36</v>
       </c>
       <c r="BD7">
-        <v>4.5</v>
+        <v>44</v>
       </c>
       <c r="BE7">
-        <v>4.7</v>
+        <v>85</v>
       </c>
       <c r="BF7">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="BG7">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="BH7">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BI7">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BN7">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BO7">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="BP7">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="BQ7">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BR7">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BS7">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BT7">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BU7">
         <v>4.1</v>
       </c>
       <c r="BV7">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="BW7">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="BX7">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BY7">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2437,241 +2458,241 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N8">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="O8">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="Q8">
-        <v>1.08</v>
+        <v>2.14</v>
       </c>
       <c r="R8">
         <v>1.25</v>
       </c>
       <c r="S8">
-        <v>1.08</v>
+        <v>3.55</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2679,79 +2700,79 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="G9">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="K9">
         <v>950</v>
       </c>
       <c r="L9">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>3.15</v>
+        <v>1.26</v>
       </c>
       <c r="O9">
-        <v>1.1</v>
+        <v>1.58</v>
       </c>
       <c r="P9">
-        <v>3.15</v>
+        <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="R9">
-        <v>1.95</v>
+        <v>1.12</v>
       </c>
       <c r="S9">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="T9">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
         <v>1000</v>
       </c>
       <c r="Y9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
         <v>1000</v>
@@ -2763,157 +2784,157 @@
         <v>1000</v>
       </c>
       <c r="AD9">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
         <v>1000</v>
       </c>
       <c r="AH9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
         <v>1000</v>
       </c>
       <c r="AL9">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>2.12</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>2.08</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2921,178 +2942,178 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F10">
-        <v>1.39</v>
+        <v>3.85</v>
       </c>
       <c r="G10">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="H10">
-        <v>2.88</v>
+        <v>1.71</v>
       </c>
       <c r="I10">
-        <v>990</v>
+        <v>1.89</v>
       </c>
       <c r="J10">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L10">
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10">
-        <v>1.26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O10">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="P10">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="Q10">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="R10">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="S10">
-        <v>2.84</v>
+        <v>1.87</v>
       </c>
       <c r="T10">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="U10">
-        <v>1.11</v>
+        <v>2.98</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="W10">
-        <v>2.8</v>
+        <v>1.28</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -3155,428 +3176,428 @@
         <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F11">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="H11">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="I11">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="J11">
+        <v>3.65</v>
+      </c>
+      <c r="K11">
+        <v>4.5</v>
+      </c>
+      <c r="L11">
+        <v>1.18</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>3.2</v>
+      </c>
+      <c r="O11">
+        <v>1.1</v>
+      </c>
+      <c r="P11">
+        <v>3.3</v>
+      </c>
+      <c r="Q11">
+        <v>1.32</v>
+      </c>
+      <c r="R11">
+        <v>1.96</v>
+      </c>
+      <c r="S11">
+        <v>1.79</v>
+      </c>
+      <c r="T11">
+        <v>1.37</v>
+      </c>
+      <c r="U11">
         <v>3.05</v>
       </c>
-      <c r="K11">
-        <v>3.35</v>
-      </c>
-      <c r="L11">
-        <v>1.01</v>
-      </c>
-      <c r="M11">
-        <v>1.11</v>
-      </c>
-      <c r="N11">
-        <v>2.7</v>
-      </c>
-      <c r="O11">
-        <v>1.48</v>
-      </c>
-      <c r="P11">
-        <v>1.57</v>
-      </c>
-      <c r="Q11">
-        <v>2.42</v>
-      </c>
-      <c r="R11">
-        <v>1.2</v>
-      </c>
-      <c r="S11">
-        <v>4.8</v>
-      </c>
-      <c r="T11">
-        <v>2.02</v>
-      </c>
-      <c r="U11">
-        <v>1.8</v>
-      </c>
       <c r="V11">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W11">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="Y11">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="Z11">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="AA11">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AB11">
-        <v>7.8</v>
+        <v>26</v>
       </c>
       <c r="AC11">
-        <v>7.8</v>
+        <v>15.5</v>
       </c>
       <c r="AD11">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE11">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="AF11">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AG11">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AH11">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AI11">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AJ11">
         <v>34</v>
       </c>
       <c r="AK11">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AL11">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AM11">
-        <v>200</v>
+        <v>44</v>
       </c>
       <c r="AN11">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="AO11">
-        <v>110</v>
+        <v>15.5</v>
       </c>
       <c r="AP11">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
-        <v>9.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR11">
+        <v>4.9</v>
+      </c>
+      <c r="AS11">
+        <v>5.1</v>
+      </c>
+      <c r="AT11">
+        <v>4.6</v>
+      </c>
+      <c r="AU11">
+        <v>4.1</v>
+      </c>
+      <c r="AV11">
+        <v>4.2</v>
+      </c>
+      <c r="AW11">
+        <v>4.8</v>
+      </c>
+      <c r="AX11">
+        <v>4.5</v>
+      </c>
+      <c r="AY11">
+        <v>4</v>
+      </c>
+      <c r="AZ11">
+        <v>4.1</v>
+      </c>
+      <c r="BA11">
+        <v>4.7</v>
+      </c>
+      <c r="BB11">
+        <v>4.8</v>
+      </c>
+      <c r="BC11">
+        <v>4.4</v>
+      </c>
+      <c r="BD11">
+        <v>4.5</v>
+      </c>
+      <c r="BE11">
+        <v>4.9</v>
+      </c>
+      <c r="BF11">
+        <v>3.15</v>
+      </c>
+      <c r="BG11">
+        <v>4.1</v>
+      </c>
+      <c r="BH11">
+        <v>6.2</v>
+      </c>
+      <c r="BI11">
+        <v>3.5</v>
+      </c>
+      <c r="BJ11">
+        <v>8.6</v>
+      </c>
+      <c r="BK11">
+        <v>4.1</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>7</v>
+      </c>
+      <c r="BN11">
         <v>6.4</v>
       </c>
-      <c r="AS11">
-        <v>7.8</v>
-      </c>
-      <c r="AT11">
-        <v>6.4</v>
-      </c>
-      <c r="AU11">
-        <v>6.4</v>
-      </c>
-      <c r="AV11">
+      <c r="BO11">
+        <v>3.55</v>
+      </c>
+      <c r="BP11">
         <v>14</v>
       </c>
-      <c r="AW11">
-        <v>7.6</v>
-      </c>
-      <c r="AX11">
-        <v>11</v>
-      </c>
-      <c r="AY11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11">
+      <c r="BQ11">
+        <v>5.1</v>
+      </c>
+      <c r="BR11">
         <v>19</v>
       </c>
-      <c r="BA11">
-        <v>7.6</v>
-      </c>
-      <c r="BB11">
-        <v>6.6</v>
-      </c>
-      <c r="BC11">
-        <v>6.6</v>
-      </c>
-      <c r="BD11">
-        <v>7.4</v>
-      </c>
-      <c r="BE11">
-        <v>8</v>
-      </c>
-      <c r="BF11">
-        <v>21</v>
-      </c>
-      <c r="BG11">
-        <v>7.8</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.04</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.04</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.04</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>1.04</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F12">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="G12">
-        <v>990</v>
+        <v>1.48</v>
       </c>
       <c r="H12">
-        <v>1.19</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>990</v>
+        <v>13</v>
       </c>
       <c r="J12">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="L12">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N12">
-        <v>1.31</v>
+        <v>3.3</v>
       </c>
       <c r="O12">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="P12">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="Q12">
-        <v>1.37</v>
+        <v>1.98</v>
       </c>
       <c r="R12">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S12">
-        <v>1.51</v>
+        <v>3.2</v>
       </c>
       <c r="T12">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="U12">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="X12">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA12">
         <v>1000</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3633,192 +3654,192 @@
         <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F13">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="G13">
-        <v>990</v>
+        <v>2.36</v>
       </c>
       <c r="H13">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="I13">
-        <v>990</v>
+        <v>4.3</v>
       </c>
       <c r="J13">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>3.25</v>
       </c>
       <c r="L13">
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N13">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="O13">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q13">
-        <v>1.32</v>
+        <v>2.42</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S13">
-        <v>1.31</v>
+        <v>4.8</v>
       </c>
       <c r="T13">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U13">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3881,66 +3902,66 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F14">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G14">
-        <v>1.72</v>
+        <v>990</v>
       </c>
       <c r="H14">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="I14">
         <v>990</v>
       </c>
       <c r="J14">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>2.82</v>
+        <v>1.33</v>
       </c>
       <c r="O14">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="P14">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="Q14">
-        <v>1.79</v>
+        <v>1.16</v>
       </c>
       <c r="R14">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S14">
-        <v>2.6</v>
+        <v>1.51</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -3949,10 +3970,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4117,255 +4138,739 @@
         <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F15">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G15">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="H15">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="I15">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K15">
         <v>3.8</v>
       </c>
       <c r="L15">
+        <v>1.29</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.88</v>
+      </c>
+      <c r="O15">
+        <v>1.32</v>
+      </c>
+      <c r="P15">
+        <v>1.7</v>
+      </c>
+      <c r="Q15">
+        <v>1.79</v>
+      </c>
+      <c r="R15">
+        <v>1.25</v>
+      </c>
+      <c r="S15">
+        <v>2.5</v>
+      </c>
+      <c r="T15">
+        <v>1.11</v>
+      </c>
+      <c r="U15">
+        <v>1.11</v>
+      </c>
+      <c r="V15">
+        <v>1.24</v>
+      </c>
+      <c r="W15">
+        <v>1.74</v>
+      </c>
+      <c r="X15">
+        <v>1000</v>
+      </c>
+      <c r="Y15">
+        <v>1000</v>
+      </c>
+      <c r="Z15">
+        <v>1000</v>
+      </c>
+      <c r="AA15">
+        <v>1000</v>
+      </c>
+      <c r="AB15">
+        <v>1000</v>
+      </c>
+      <c r="AC15">
+        <v>1000</v>
+      </c>
+      <c r="AD15">
+        <v>1000</v>
+      </c>
+      <c r="AE15">
+        <v>1000</v>
+      </c>
+      <c r="AF15">
+        <v>1000</v>
+      </c>
+      <c r="AG15">
+        <v>1000</v>
+      </c>
+      <c r="AH15">
+        <v>1000</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>1000</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>1000</v>
+      </c>
+      <c r="AO15">
+        <v>1000</v>
+      </c>
+      <c r="AP15">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15">
+        <v>1.01</v>
+      </c>
+      <c r="AR15">
+        <v>1.01</v>
+      </c>
+      <c r="AS15">
+        <v>1.01</v>
+      </c>
+      <c r="AT15">
+        <v>1.01</v>
+      </c>
+      <c r="AU15">
+        <v>1.01</v>
+      </c>
+      <c r="AV15">
+        <v>1.01</v>
+      </c>
+      <c r="AW15">
+        <v>1.01</v>
+      </c>
+      <c r="AX15">
+        <v>1.01</v>
+      </c>
+      <c r="AY15">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15">
+        <v>1.01</v>
+      </c>
+      <c r="BA15">
+        <v>1.01</v>
+      </c>
+      <c r="BB15">
+        <v>1.01</v>
+      </c>
+      <c r="BC15">
+        <v>1.01</v>
+      </c>
+      <c r="BD15">
+        <v>1.01</v>
+      </c>
+      <c r="BE15">
+        <v>1.01</v>
+      </c>
+      <c r="BF15">
+        <v>1.01</v>
+      </c>
+      <c r="BG15">
+        <v>1.01</v>
+      </c>
+      <c r="BH15">
+        <v>1000</v>
+      </c>
+      <c r="BI15">
+        <v>1.04</v>
+      </c>
+      <c r="BJ15">
+        <v>1000</v>
+      </c>
+      <c r="BK15">
+        <v>1.04</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.04</v>
+      </c>
+      <c r="BN15">
+        <v>1000</v>
+      </c>
+      <c r="BO15">
+        <v>1.04</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>1.04</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>1.04</v>
+      </c>
+      <c r="BT15">
+        <v>1000</v>
+      </c>
+      <c r="BU15">
+        <v>1.04</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>1.04</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>1.04</v>
+      </c>
+      <c r="BZ15">
+        <v>1000</v>
+      </c>
+      <c r="CA15">
+        <v>1.04</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F16">
+        <v>1.33</v>
+      </c>
+      <c r="G16">
+        <v>1.68</v>
+      </c>
+      <c r="H16">
+        <v>6.6</v>
+      </c>
+      <c r="I16">
+        <v>110</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>11.5</v>
+      </c>
+      <c r="L16">
+        <v>1.31</v>
+      </c>
+      <c r="M16">
+        <v>1.01</v>
+      </c>
+      <c r="N16">
+        <v>2.36</v>
+      </c>
+      <c r="O16">
+        <v>1.29</v>
+      </c>
+      <c r="P16">
+        <v>1.67</v>
+      </c>
+      <c r="Q16">
+        <v>1.79</v>
+      </c>
+      <c r="R16">
+        <v>1.21</v>
+      </c>
+      <c r="S16">
+        <v>2.6</v>
+      </c>
+      <c r="T16">
+        <v>1.11</v>
+      </c>
+      <c r="U16">
+        <v>1.11</v>
+      </c>
+      <c r="V16">
+        <v>1.04</v>
+      </c>
+      <c r="W16">
+        <v>2.48</v>
+      </c>
+      <c r="X16">
+        <v>1000</v>
+      </c>
+      <c r="Y16">
+        <v>1000</v>
+      </c>
+      <c r="Z16">
+        <v>1000</v>
+      </c>
+      <c r="AA16">
+        <v>1000</v>
+      </c>
+      <c r="AB16">
+        <v>1000</v>
+      </c>
+      <c r="AC16">
+        <v>1000</v>
+      </c>
+      <c r="AD16">
+        <v>1000</v>
+      </c>
+      <c r="AE16">
+        <v>1000</v>
+      </c>
+      <c r="AF16">
+        <v>1000</v>
+      </c>
+      <c r="AG16">
+        <v>1000</v>
+      </c>
+      <c r="AH16">
+        <v>1000</v>
+      </c>
+      <c r="AI16">
+        <v>1000</v>
+      </c>
+      <c r="AJ16">
+        <v>1000</v>
+      </c>
+      <c r="AK16">
+        <v>1000</v>
+      </c>
+      <c r="AL16">
+        <v>1000</v>
+      </c>
+      <c r="AM16">
+        <v>1000</v>
+      </c>
+      <c r="AN16">
+        <v>1000</v>
+      </c>
+      <c r="AO16">
+        <v>1000</v>
+      </c>
+      <c r="AP16">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16">
+        <v>1.01</v>
+      </c>
+      <c r="AR16">
+        <v>1.01</v>
+      </c>
+      <c r="AS16">
+        <v>1.01</v>
+      </c>
+      <c r="AT16">
+        <v>1.01</v>
+      </c>
+      <c r="AU16">
+        <v>1.01</v>
+      </c>
+      <c r="AV16">
+        <v>1.01</v>
+      </c>
+      <c r="AW16">
+        <v>1.01</v>
+      </c>
+      <c r="AX16">
+        <v>1.01</v>
+      </c>
+      <c r="AY16">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16">
+        <v>1.01</v>
+      </c>
+      <c r="BA16">
+        <v>1.01</v>
+      </c>
+      <c r="BB16">
+        <v>1.01</v>
+      </c>
+      <c r="BC16">
+        <v>1.01</v>
+      </c>
+      <c r="BD16">
+        <v>1.01</v>
+      </c>
+      <c r="BE16">
+        <v>1.01</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.04</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.04</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.04</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.04</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.04</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.04</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.04</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.04</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.04</v>
+      </c>
+      <c r="BZ16">
+        <v>1000</v>
+      </c>
+      <c r="CA16">
+        <v>1.04</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E17" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17">
+        <v>1.97</v>
+      </c>
+      <c r="G17">
+        <v>2.14</v>
+      </c>
+      <c r="H17">
+        <v>4.1</v>
+      </c>
+      <c r="I17">
+        <v>4.7</v>
+      </c>
+      <c r="J17">
+        <v>3.3</v>
+      </c>
+      <c r="K17">
+        <v>3.7</v>
+      </c>
+      <c r="L17">
         <v>1.38</v>
       </c>
-      <c r="M15">
+      <c r="M17">
         <v>1.08</v>
       </c>
-      <c r="N15">
+      <c r="N17">
         <v>3.15</v>
       </c>
-      <c r="O15">
+      <c r="O17">
         <v>1.38</v>
       </c>
-      <c r="P15">
+      <c r="P17">
         <v>1.74</v>
       </c>
-      <c r="Q15">
+      <c r="Q17">
         <v>2.1</v>
       </c>
-      <c r="R15">
+      <c r="R17">
         <v>1.28</v>
       </c>
-      <c r="S15">
+      <c r="S17">
         <v>3.95</v>
       </c>
-      <c r="T15">
+      <c r="T17">
         <v>1.89</v>
       </c>
-      <c r="U15">
-        <v>1.91</v>
-      </c>
-      <c r="V15">
+      <c r="U17">
+        <v>1.92</v>
+      </c>
+      <c r="V17">
         <v>1.27</v>
       </c>
-      <c r="W15">
+      <c r="W17">
         <v>1.87</v>
       </c>
-      <c r="X15">
+      <c r="X17">
         <v>14.5</v>
       </c>
-      <c r="Y15">
+      <c r="Y17">
         <v>16.5</v>
       </c>
-      <c r="Z15">
+      <c r="Z17">
         <v>38</v>
       </c>
-      <c r="AA15">
+      <c r="AA17">
         <v>120</v>
       </c>
-      <c r="AB15">
+      <c r="AB17">
         <v>9.6</v>
       </c>
-      <c r="AC15">
+      <c r="AC17">
         <v>9.6</v>
       </c>
-      <c r="AD15">
+      <c r="AD17">
         <v>22</v>
       </c>
-      <c r="AE15">
+      <c r="AE17">
         <v>65</v>
       </c>
-      <c r="AF15">
+      <c r="AF17">
         <v>14.5</v>
       </c>
-      <c r="AG15">
+      <c r="AG17">
         <v>13</v>
       </c>
-      <c r="AH15">
+      <c r="AH17">
         <v>25</v>
       </c>
-      <c r="AI15">
+      <c r="AI17">
         <v>85</v>
       </c>
-      <c r="AJ15">
+      <c r="AJ17">
         <v>30</v>
       </c>
-      <c r="AK15">
+      <c r="AK17">
         <v>29</v>
       </c>
-      <c r="AL15">
+      <c r="AL17">
         <v>46</v>
       </c>
-      <c r="AM15">
+      <c r="AM17">
         <v>160</v>
       </c>
-      <c r="AN15">
+      <c r="AN17">
         <v>23</v>
       </c>
-      <c r="AO15">
+      <c r="AO17">
         <v>80</v>
       </c>
-      <c r="AP15">
+      <c r="AP17">
         <v>10</v>
       </c>
-      <c r="AQ15">
+      <c r="AQ17">
         <v>10</v>
       </c>
-      <c r="AR15">
+      <c r="AR17">
         <v>4.1</v>
       </c>
-      <c r="AS15">
+      <c r="AS17">
         <v>4.4</v>
       </c>
-      <c r="AT15">
+      <c r="AT17">
         <v>7</v>
       </c>
-      <c r="AU15">
+      <c r="AU17">
         <v>6.8</v>
       </c>
-      <c r="AV15">
+      <c r="AV17">
         <v>13</v>
       </c>
-      <c r="AW15">
+      <c r="AW17">
         <v>4.3</v>
       </c>
-      <c r="AX15">
+      <c r="AX17">
         <v>10</v>
       </c>
-      <c r="AY15">
+      <c r="AY17">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ15">
+      <c r="AZ17">
         <v>17</v>
       </c>
-      <c r="BA15">
+      <c r="BA17">
         <v>4.3</v>
       </c>
-      <c r="BB15">
+      <c r="BB17">
         <v>21</v>
       </c>
-      <c r="BC15">
+      <c r="BC17">
         <v>20</v>
       </c>
-      <c r="BD15">
+      <c r="BD17">
         <v>4.1</v>
       </c>
-      <c r="BE15">
+      <c r="BE17">
         <v>4.4</v>
       </c>
-      <c r="BF15">
+      <c r="BF17">
         <v>15.5</v>
       </c>
-      <c r="BG15">
+      <c r="BG17">
         <v>4.3</v>
       </c>
-      <c r="BH15">
+      <c r="BH17">
         <v>3.6</v>
       </c>
-      <c r="BI15">
-        <v>2.54</v>
-      </c>
-      <c r="BJ15">
+      <c r="BI17">
+        <v>2.8</v>
+      </c>
+      <c r="BJ17">
         <v>12.5</v>
       </c>
-      <c r="BK15">
+      <c r="BK17">
         <v>3.5</v>
       </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
         <v>4.8</v>
       </c>
-      <c r="BN15">
+      <c r="BN17">
         <v>5.5</v>
       </c>
-      <c r="BO15">
+      <c r="BO17">
         <v>3.6</v>
       </c>
-      <c r="BP15">
+      <c r="BP17">
         <v>18.5</v>
       </c>
-      <c r="BQ15">
+      <c r="BQ17">
         <v>3.9</v>
       </c>
-      <c r="BR15">
+      <c r="BR17">
         <v>40</v>
       </c>
-      <c r="BS15">
+      <c r="BS17">
         <v>4.4</v>
       </c>
-      <c r="BT15">
+      <c r="BT17">
         <v>9</v>
       </c>
-      <c r="BU15">
+      <c r="BU17">
         <v>5.6</v>
       </c>
-      <c r="BV15">
+      <c r="BV17">
         <v>48</v>
       </c>
-      <c r="BW15">
+      <c r="BW17">
         <v>4.4</v>
       </c>
-      <c r="BX15">
+      <c r="BX17">
         <v>65</v>
       </c>
-      <c r="BY15">
+      <c r="BY17">
         <v>4.5</v>
       </c>
-      <c r="BZ15">
+      <c r="BZ17">
         <v>38</v>
       </c>
-      <c r="CA15">
+      <c r="CA17">
         <v>4.3</v>
       </c>
-      <c r="CB15" t="s">
-        <v>129</v>
+      <c r="CB17" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -424,7 +424,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 16:06:25</t>
+    <t>2026-08-03 18:13:16</t>
   </si>
 </sst>
 </file>
@@ -1018,13 +1018,13 @@
         <v>120</v>
       </c>
       <c r="F2">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G2">
         <v>2.08</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I2">
         <v>4.5</v>
@@ -1033,34 +1033,34 @@
         <v>3.5</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L2">
         <v>1.44</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
         <v>3.6</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q2">
         <v>2.04</v>
       </c>
       <c r="R2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S2">
         <v>3.7</v>
       </c>
       <c r="T2">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
         <v>2</v>
@@ -1075,7 +1075,7 @@
         <v>16.5</v>
       </c>
       <c r="Y2">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z2">
         <v>34</v>
@@ -1090,13 +1090,13 @@
         <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE2">
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG2">
         <v>11</v>
@@ -1111,73 +1111,73 @@
         <v>25</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL2">
         <v>40</v>
       </c>
       <c r="AM2">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AO2">
         <v>65</v>
       </c>
       <c r="AP2">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AS2">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AU2">
         <v>7</v>
       </c>
       <c r="AV2">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX2">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AY2">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BB2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD2">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE2">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -1189,13 +1189,13 @@
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN2">
         <v>4.9</v>
@@ -1207,13 +1207,13 @@
         <v>15</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
@@ -1225,19 +1225,19 @@
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
         <v>48</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>28</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="CB2" t="s">
         <v>136</v>
@@ -1263,13 +1263,13 @@
         <v>1.31</v>
       </c>
       <c r="G3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="H3">
         <v>12.5</v>
       </c>
       <c r="I3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>5.8</v>
@@ -1287,13 +1287,13 @@
         <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q3">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1302,7 +1302,7 @@
         <v>3.35</v>
       </c>
       <c r="T3">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U3">
         <v>1.61</v>
@@ -1314,70 +1314,70 @@
         <v>4</v>
       </c>
       <c r="X3">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA3">
-        <v>800</v>
+        <v>710</v>
       </c>
       <c r="AB3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC3">
         <v>13.5</v>
       </c>
       <c r="AD3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AE3">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="AF3">
         <v>6.8</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
         <v>44</v>
       </c>
       <c r="AI3">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AJ3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK3">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AL3">
         <v>55</v>
       </c>
       <c r="AM3">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AN3">
         <v>6.6</v>
       </c>
       <c r="AO3">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="AP3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="AR3">
         <v>44</v>
       </c>
       <c r="AS3">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AT3">
         <v>6.6</v>
@@ -1386,10 +1386,10 @@
         <v>12</v>
       </c>
       <c r="AV3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX3">
         <v>6.2</v>
@@ -1398,13 +1398,13 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="BA3">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB3">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3">
         <v>14.5</v>
@@ -1413,73 +1413,73 @@
         <v>46</v>
       </c>
       <c r="BE3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BF3">
         <v>6</v>
       </c>
       <c r="BG3">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BH3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BI3">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ3">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BN3">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BO3">
         <v>3.1</v>
       </c>
       <c r="BP3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BQ3">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BR3">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS3">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BU3">
-        <v>11.5</v>
+        <v>3.9</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ3">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="CB3" t="s">
         <v>136</v>
@@ -1502,7 +1502,7 @@
         <v>122</v>
       </c>
       <c r="F4">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="G4">
         <v>3.45</v>
@@ -1514,13 +1514,13 @@
         <v>2.76</v>
       </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K4">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="L4">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M4">
         <v>1.16</v>
@@ -1535,7 +1535,7 @@
         <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
         <v>1.16</v>
@@ -1586,7 +1586,7 @@
         <v>16</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI4">
         <v>85</v>
@@ -1601,7 +1601,7 @@
         <v>95</v>
       </c>
       <c r="AM4">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AN4">
         <v>90</v>
@@ -1631,10 +1631,10 @@
         <v>13</v>
       </c>
       <c r="AW4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AX4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY4">
         <v>14.5</v>
@@ -1643,7 +1643,7 @@
         <v>24</v>
       </c>
       <c r="BA4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BB4">
         <v>60</v>
@@ -1658,70 +1658,70 @@
         <v>50</v>
       </c>
       <c r="BF4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BG4">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BH4">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="BI4">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4">
         <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>4.9</v>
+        <v>10</v>
       </c>
       <c r="BL4">
         <v>300</v>
       </c>
       <c r="BM4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BN4">
         <v>6.6</v>
       </c>
       <c r="BO4">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BP4">
         <v>36</v>
       </c>
       <c r="BQ4">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BR4">
         <v>65</v>
       </c>
       <c r="BS4">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="BT4">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU4">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BV4">
         <v>27</v>
       </c>
       <c r="BW4">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY4">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="BZ4">
         <v>65</v>
       </c>
       <c r="CA4">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="s">
         <v>136</v>
@@ -1744,25 +1744,25 @@
         <v>123</v>
       </c>
       <c r="F5">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5">
         <v>3.1</v>
       </c>
       <c r="L5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M5">
         <v>1.16</v>
@@ -1774,13 +1774,13 @@
         <v>1.69</v>
       </c>
       <c r="P5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R5">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S5">
         <v>7</v>
@@ -1789,13 +1789,13 @@
         <v>2.46</v>
       </c>
       <c r="U5">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X5">
         <v>7.2</v>
@@ -1804,13 +1804,13 @@
         <v>11</v>
       </c>
       <c r="Z5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA5">
         <v>130</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1822,7 +1822,7 @@
         <v>95</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
@@ -1843,7 +1843,7 @@
         <v>80</v>
       </c>
       <c r="AM5">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN5">
         <v>36</v>
@@ -1852,22 +1852,22 @@
         <v>170</v>
       </c>
       <c r="AP5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR5">
         <v>27</v>
       </c>
       <c r="AS5">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AT5">
         <v>5.7</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
         <v>19</v>
@@ -1891,7 +1891,7 @@
         <v>26</v>
       </c>
       <c r="BC5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD5">
         <v>60</v>
@@ -1903,7 +1903,7 @@
         <v>30</v>
       </c>
       <c r="BG5">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BH5">
         <v>2.52</v>
@@ -1933,7 +1933,7 @@
         <v>20</v>
       </c>
       <c r="BQ5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>50</v>
@@ -1986,28 +1986,28 @@
         <v>124</v>
       </c>
       <c r="F6">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G6">
         <v>1.65</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>7.4</v>
       </c>
       <c r="J6">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6">
         <v>1.46</v>
       </c>
       <c r="M6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
         <v>3.4</v>
@@ -2019,25 +2019,25 @@
         <v>1.8</v>
       </c>
       <c r="Q6">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R6">
         <v>1.3</v>
       </c>
       <c r="S6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T6">
         <v>2.16</v>
       </c>
       <c r="U6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V6">
         <v>1.16</v>
       </c>
       <c r="W6">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X6">
         <v>13</v>
@@ -2049,10 +2049,10 @@
         <v>65</v>
       </c>
       <c r="AA6">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC6">
         <v>9.4</v>
@@ -2073,40 +2073,40 @@
         <v>26</v>
       </c>
       <c r="AI6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ6">
         <v>16</v>
       </c>
       <c r="AK6">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL6">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM6">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AN6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO6">
         <v>240</v>
       </c>
       <c r="AP6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR6">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AS6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT6">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU6">
         <v>8</v>
@@ -2124,7 +2124,7 @@
         <v>9</v>
       </c>
       <c r="AZ6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA6">
         <v>10.5</v>
@@ -2133,79 +2133,79 @@
         <v>13</v>
       </c>
       <c r="BC6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD6">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF6">
         <v>9.4</v>
       </c>
       <c r="BG6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BI6">
-        <v>2.64</v>
+        <v>2.9</v>
       </c>
       <c r="BJ6">
         <v>12.5</v>
       </c>
       <c r="BK6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BL6">
         <v>230</v>
       </c>
       <c r="BM6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BO6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP6">
         <v>12.5</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BR6">
         <v>34</v>
       </c>
       <c r="BS6">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT6">
         <v>11</v>
       </c>
       <c r="BU6">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BV6">
         <v>80</v>
       </c>
       <c r="BW6">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>90</v>
       </c>
       <c r="BY6">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>25</v>
       </c>
       <c r="CA6">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="CB6" t="s">
         <v>136</v>
@@ -2228,19 +2228,19 @@
         <v>125</v>
       </c>
       <c r="F7">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G7">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>2.14</v>
       </c>
       <c r="I7">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J7">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
         <v>3.6</v>
@@ -2249,13 +2249,13 @@
         <v>1.45</v>
       </c>
       <c r="M7">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7">
         <v>3.5</v>
       </c>
       <c r="O7">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P7">
         <v>1.82</v>
@@ -2264,7 +2264,7 @@
         <v>2.12</v>
       </c>
       <c r="R7">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S7">
         <v>3.95</v>
@@ -2276,10 +2276,10 @@
         <v>2</v>
       </c>
       <c r="V7">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W7">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X7">
         <v>12.5</v>
@@ -2363,7 +2363,7 @@
         <v>22</v>
       </c>
       <c r="AY7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AZ7">
         <v>16.5</v>
@@ -2479,13 +2479,13 @@
         <v>3.05</v>
       </c>
       <c r="I8">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L8">
         <v>1.46</v>
@@ -2503,22 +2503,22 @@
         <v>1.68</v>
       </c>
       <c r="Q8">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R8">
         <v>1.25</v>
       </c>
       <c r="S8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T8">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U8">
         <v>1.93</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W8">
         <v>1.59</v>
@@ -2572,64 +2572,64 @@
         <v>150</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO8">
         <v>55</v>
       </c>
       <c r="AP8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AQ8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AR8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT8">
         <v>3.45</v>
       </c>
       <c r="AU8">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AV8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AW8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AX8">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AY8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AZ8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BA8">
         <v>4.6</v>
       </c>
       <c r="BB8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC8">
         <v>4.3</v>
       </c>
       <c r="BD8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF8">
         <v>4.3</v>
       </c>
       <c r="BG8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH8">
         <v>3.55</v>
@@ -2638,52 +2638,52 @@
         <v>2.7</v>
       </c>
       <c r="BJ8">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK8">
+        <v>3.65</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>5.1</v>
+      </c>
+      <c r="BN8">
+        <v>6.4</v>
+      </c>
+      <c r="BO8">
+        <v>2.88</v>
+      </c>
+      <c r="BP8">
+        <v>25</v>
+      </c>
+      <c r="BQ8">
         <v>4.3</v>
       </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>7</v>
-      </c>
-      <c r="BN8">
-        <v>5.6</v>
-      </c>
-      <c r="BO8">
-        <v>4.2</v>
-      </c>
-      <c r="BP8">
-        <v>22</v>
-      </c>
-      <c r="BQ8">
-        <v>5.5</v>
-      </c>
       <c r="BR8">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BS8">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BT8">
         <v>6.6</v>
       </c>
       <c r="BU8">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="BV8">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BW8">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BX8">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BY8">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2712,19 +2712,19 @@
         <v>127</v>
       </c>
       <c r="F9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K9">
         <v>950</v>
@@ -2736,34 +2736,34 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.26</v>
+        <v>2.28</v>
       </c>
       <c r="O9">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P9">
         <v>1.25</v>
       </c>
       <c r="Q9">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R9">
         <v>1.12</v>
       </c>
       <c r="S9">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -2954,22 +2954,22 @@
         <v>128</v>
       </c>
       <c r="F10">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G10">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H10">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="I10">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="J10">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K10">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2978,13 +2978,13 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O10">
         <v>1.11</v>
       </c>
       <c r="P10">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q10">
         <v>1.35</v>
@@ -2999,13 +2999,13 @@
         <v>1.42</v>
       </c>
       <c r="U10">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="V10">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W10">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X10">
         <v>55</v>
@@ -3014,7 +3014,7 @@
         <v>21</v>
       </c>
       <c r="Z10">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA10">
         <v>26</v>
@@ -3029,16 +3029,16 @@
         <v>13</v>
       </c>
       <c r="AE10">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF10">
         <v>55</v>
       </c>
       <c r="AG10">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH10">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI10">
         <v>23</v>
@@ -3059,10 +3059,10 @@
         <v>25</v>
       </c>
       <c r="AO10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AP10">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AQ10">
         <v>16.5</v>
@@ -3098,7 +3098,7 @@
         <v>18</v>
       </c>
       <c r="BB10">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BC10">
         <v>28</v>
@@ -3196,22 +3196,22 @@
         <v>129</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="G11">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="H11">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="I11">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L11">
         <v>1.18</v>
@@ -3220,196 +3220,196 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>1.1</v>
       </c>
       <c r="P11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="Q11">
+        <v>1.34</v>
+      </c>
+      <c r="R11">
+        <v>2.1</v>
+      </c>
+      <c r="S11">
+        <v>1.8</v>
+      </c>
+      <c r="T11">
+        <v>1.38</v>
+      </c>
+      <c r="U11">
+        <v>3</v>
+      </c>
+      <c r="V11">
         <v>1.32</v>
       </c>
-      <c r="R11">
-        <v>1.96</v>
-      </c>
-      <c r="S11">
-        <v>1.79</v>
-      </c>
-      <c r="T11">
-        <v>1.37</v>
-      </c>
-      <c r="U11">
-        <v>3.05</v>
-      </c>
-      <c r="V11">
-        <v>1.38</v>
-      </c>
       <c r="W11">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="X11">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y11">
         <v>34</v>
       </c>
       <c r="Z11">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AA11">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AB11">
+        <v>22</v>
+      </c>
+      <c r="AC11">
+        <v>15</v>
+      </c>
+      <c r="AD11">
+        <v>21</v>
+      </c>
+      <c r="AE11">
+        <v>38</v>
+      </c>
+      <c r="AF11">
+        <v>21</v>
+      </c>
+      <c r="AG11">
+        <v>13.5</v>
+      </c>
+      <c r="AH11">
+        <v>16</v>
+      </c>
+      <c r="AI11">
+        <v>36</v>
+      </c>
+      <c r="AJ11">
         <v>26</v>
       </c>
-      <c r="AC11">
-        <v>15.5</v>
-      </c>
-      <c r="AD11">
-        <v>17.5</v>
-      </c>
-      <c r="AE11">
-        <v>34</v>
-      </c>
-      <c r="AF11">
-        <v>25</v>
-      </c>
-      <c r="AG11">
-        <v>15</v>
-      </c>
-      <c r="AH11">
-        <v>15.5</v>
-      </c>
-      <c r="AI11">
-        <v>32</v>
-      </c>
-      <c r="AJ11">
-        <v>34</v>
-      </c>
       <c r="AK11">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AL11">
         <v>25</v>
       </c>
       <c r="AM11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AN11">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AO11">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AP11">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AQ11">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AR11">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AS11">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AT11">
+        <v>17</v>
+      </c>
+      <c r="AU11">
+        <v>11</v>
+      </c>
+      <c r="AV11">
+        <v>15</v>
+      </c>
+      <c r="AW11">
+        <v>5.3</v>
+      </c>
+      <c r="AX11">
+        <v>16</v>
+      </c>
+      <c r="AY11">
+        <v>10</v>
+      </c>
+      <c r="AZ11">
+        <v>12</v>
+      </c>
+      <c r="BA11">
+        <v>5.3</v>
+      </c>
+      <c r="BB11">
+        <v>20</v>
+      </c>
+      <c r="BC11">
+        <v>14</v>
+      </c>
+      <c r="BD11">
+        <v>17</v>
+      </c>
+      <c r="BE11">
+        <v>5.4</v>
+      </c>
+      <c r="BF11">
         <v>4.6</v>
       </c>
-      <c r="AU11">
-        <v>4.1</v>
-      </c>
-      <c r="AV11">
-        <v>4.2</v>
-      </c>
-      <c r="AW11">
-        <v>4.8</v>
-      </c>
-      <c r="AX11">
-        <v>4.5</v>
-      </c>
-      <c r="AY11">
-        <v>4</v>
-      </c>
-      <c r="AZ11">
-        <v>4.1</v>
-      </c>
-      <c r="BA11">
-        <v>4.7</v>
-      </c>
-      <c r="BB11">
-        <v>4.8</v>
-      </c>
-      <c r="BC11">
-        <v>4.4</v>
-      </c>
-      <c r="BD11">
-        <v>4.5</v>
-      </c>
-      <c r="BE11">
-        <v>4.9</v>
-      </c>
-      <c r="BF11">
-        <v>3.15</v>
-      </c>
       <c r="BG11">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="BH11">
         <v>6.2</v>
       </c>
       <c r="BI11">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN11">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BO11">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="BP11">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BQ11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR11">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BS11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BT11">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU11">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BV11">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BW11">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BX11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BY11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3438,22 +3438,22 @@
         <v>130</v>
       </c>
       <c r="F12">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="G12">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J12">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="K12">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L12">
         <v>1.27</v>
@@ -3462,142 +3462,142 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O12">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P12">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q12">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="R12">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S12">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T12">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="U12">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="V12">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W12">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="X12">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y12">
+        <v>26</v>
+      </c>
+      <c r="Z12">
+        <v>95</v>
+      </c>
+      <c r="AA12">
+        <v>430</v>
+      </c>
+      <c r="AB12">
+        <v>7.4</v>
+      </c>
+      <c r="AC12">
+        <v>11</v>
+      </c>
+      <c r="AD12">
+        <v>40</v>
+      </c>
+      <c r="AE12">
+        <v>200</v>
+      </c>
+      <c r="AF12">
+        <v>8.6</v>
+      </c>
+      <c r="AG12">
+        <v>12.5</v>
+      </c>
+      <c r="AH12">
         <v>34</v>
       </c>
-      <c r="Z12">
-        <v>130</v>
-      </c>
-      <c r="AA12">
-        <v>1000</v>
-      </c>
-      <c r="AB12">
-        <v>7</v>
-      </c>
-      <c r="AC12">
-        <v>11.5</v>
-      </c>
-      <c r="AD12">
-        <v>55</v>
-      </c>
-      <c r="AE12">
-        <v>300</v>
-      </c>
-      <c r="AF12">
-        <v>7.8</v>
-      </c>
-      <c r="AG12">
-        <v>13</v>
-      </c>
-      <c r="AH12">
-        <v>42</v>
-      </c>
       <c r="AI12">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="AJ12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK12">
         <v>21</v>
       </c>
       <c r="AL12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM12">
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="AN12">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO12">
-        <v>570</v>
+        <v>330</v>
       </c>
       <c r="AP12">
         <v>4.6</v>
       </c>
       <c r="AQ12">
+        <v>5.1</v>
+      </c>
+      <c r="AR12">
+        <v>5.9</v>
+      </c>
+      <c r="AS12">
+        <v>6.2</v>
+      </c>
+      <c r="AT12">
         <v>5.4</v>
       </c>
-      <c r="AR12">
+      <c r="AU12">
+        <v>4</v>
+      </c>
+      <c r="AV12">
+        <v>5.4</v>
+      </c>
+      <c r="AW12">
+        <v>6</v>
+      </c>
+      <c r="AX12">
+        <v>3.65</v>
+      </c>
+      <c r="AY12">
+        <v>4.2</v>
+      </c>
+      <c r="AZ12">
+        <v>5.3</v>
+      </c>
+      <c r="BA12">
+        <v>6</v>
+      </c>
+      <c r="BB12">
+        <v>4.3</v>
+      </c>
+      <c r="BC12">
+        <v>4.8</v>
+      </c>
+      <c r="BD12">
+        <v>5.7</v>
+      </c>
+      <c r="BE12">
+        <v>6</v>
+      </c>
+      <c r="BF12">
+        <v>3.8</v>
+      </c>
+      <c r="BG12">
         <v>6.2</v>
-      </c>
-      <c r="AS12">
-        <v>6.4</v>
-      </c>
-      <c r="AT12">
-        <v>3.35</v>
-      </c>
-      <c r="AU12">
-        <v>4.1</v>
-      </c>
-      <c r="AV12">
-        <v>5.8</v>
-      </c>
-      <c r="AW12">
-        <v>6.2</v>
-      </c>
-      <c r="AX12">
-        <v>3.55</v>
-      </c>
-      <c r="AY12">
-        <v>4.3</v>
-      </c>
-      <c r="AZ12">
-        <v>5.6</v>
-      </c>
-      <c r="BA12">
-        <v>6.2</v>
-      </c>
-      <c r="BB12">
-        <v>4.2</v>
-      </c>
-      <c r="BC12">
-        <v>4.9</v>
-      </c>
-      <c r="BD12">
-        <v>5.9</v>
-      </c>
-      <c r="BE12">
-        <v>6.2</v>
-      </c>
-      <c r="BF12">
-        <v>3.7</v>
-      </c>
-      <c r="BG12">
-        <v>6.4</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3689,7 +3689,7 @@
         <v>3.8</v>
       </c>
       <c r="I13">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J13">
         <v>3.05</v>
@@ -3710,7 +3710,7 @@
         <v>1.48</v>
       </c>
       <c r="P13">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q13">
         <v>2.42</v>
@@ -3731,7 +3731,7 @@
         <v>1.3</v>
       </c>
       <c r="W13">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -3761,7 +3761,7 @@
         <v>13.5</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH13">
         <v>24</v>
@@ -3794,10 +3794,10 @@
         <v>9.4</v>
       </c>
       <c r="AR13">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT13">
         <v>6.4</v>
@@ -3809,7 +3809,7 @@
         <v>14</v>
       </c>
       <c r="AW13">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX13">
         <v>11</v>
@@ -3821,25 +3821,25 @@
         <v>19</v>
       </c>
       <c r="BA13">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB13">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC13">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE13">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF13">
         <v>21</v>
       </c>
       <c r="BG13">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3925,16 +3925,16 @@
         <v>1.35</v>
       </c>
       <c r="G14">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H14">
         <v>1.9</v>
       </c>
       <c r="I14">
-        <v>990</v>
+        <v>870</v>
       </c>
       <c r="J14">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
         <v>6.6</v>
@@ -4164,13 +4164,13 @@
         <v>133</v>
       </c>
       <c r="F15">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="G15">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I15">
         <v>5.1</v>
@@ -4203,7 +4203,7 @@
         <v>1.25</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4406,22 +4406,22 @@
         <v>134</v>
       </c>
       <c r="F16">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="G16">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="H16">
         <v>6.6</v>
       </c>
       <c r="I16">
-        <v>110</v>
+        <v>10.5</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K16">
-        <v>11.5</v>
+        <v>4.7</v>
       </c>
       <c r="L16">
         <v>1.31</v>
@@ -4430,19 +4430,19 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.36</v>
+        <v>2.68</v>
       </c>
       <c r="O16">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P16">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q16">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="R16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S16">
         <v>2.6</v>
@@ -4454,10 +4454,10 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W16">
-        <v>2.48</v>
+        <v>2.68</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4648,13 +4648,13 @@
         <v>135</v>
       </c>
       <c r="F17">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G17">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I17">
         <v>4.7</v>
@@ -4750,7 +4750,7 @@
         <v>160</v>
       </c>
       <c r="AN17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO17">
         <v>80</v>
@@ -4789,7 +4789,7 @@
         <v>17</v>
       </c>
       <c r="BA17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB17">
         <v>21</v>
@@ -4798,10 +4798,10 @@
         <v>20</v>
       </c>
       <c r="BD17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF17">
         <v>15.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -424,7 +424,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 18:13:16</t>
+    <t>2026-08-03 20:20:42</t>
   </si>
 </sst>
 </file>
@@ -1018,22 +1018,22 @@
         <v>120</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I2">
         <v>4.5</v>
       </c>
       <c r="J2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L2">
         <v>1.44</v>
@@ -1042,61 +1042,61 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P2">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q2">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R2">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T2">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V2">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X2">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Z2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA2">
         <v>120</v>
       </c>
       <c r="AB2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC2">
         <v>8.4</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AE2">
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>11</v>
@@ -1105,25 +1105,25 @@
         <v>19.5</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
         <v>25</v>
       </c>
       <c r="AK2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL2">
         <v>40</v>
       </c>
       <c r="AM2">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
@@ -1135,7 +1135,7 @@
         <v>22</v>
       </c>
       <c r="AS2">
-        <v>6.6</v>
+        <v>75</v>
       </c>
       <c r="AT2">
         <v>7.6</v>
@@ -1147,7 +1147,7 @@
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2">
         <v>10.5</v>
@@ -1159,7 +1159,7 @@
         <v>16</v>
       </c>
       <c r="BA2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB2">
         <v>20</v>
@@ -1168,76 +1168,76 @@
         <v>19</v>
       </c>
       <c r="BD2">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BE2">
-        <v>6.6</v>
+        <v>85</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="BJ2">
         <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="BN2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO2">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
         <v>15</v>
       </c>
       <c r="BQ2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR2">
         <v>32</v>
       </c>
       <c r="BS2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT2">
         <v>7.8</v>
       </c>
       <c r="BU2">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BV2">
         <v>38</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BY2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
         <v>28</v>
       </c>
       <c r="CA2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB2" t="s">
         <v>136</v>
@@ -1260,19 +1260,19 @@
         <v>121</v>
       </c>
       <c r="F3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="G3">
         <v>1.32</v>
       </c>
       <c r="H3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="K3">
         <v>6.2</v>
@@ -1287,13 +1287,13 @@
         <v>4.1</v>
       </c>
       <c r="O3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q3">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R3">
         <v>1.4</v>
@@ -1302,40 +1302,40 @@
         <v>3.35</v>
       </c>
       <c r="T3">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="U3">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V3">
         <v>1.07</v>
       </c>
       <c r="W3">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="X3">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="Y3">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="Z3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AA3">
-        <v>710</v>
+        <v>900</v>
       </c>
       <c r="AB3">
         <v>7.2</v>
       </c>
       <c r="AC3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AE3">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="AF3">
         <v>6.8</v>
@@ -1344,52 +1344,52 @@
         <v>11</v>
       </c>
       <c r="AH3">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AI3">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="AJ3">
         <v>9.4</v>
       </c>
       <c r="AK3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AL3">
         <v>55</v>
       </c>
       <c r="AM3">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AN3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO3">
-        <v>460</v>
+        <v>500</v>
       </c>
       <c r="AP3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="AR3">
         <v>44</v>
       </c>
       <c r="AS3">
-        <v>14.5</v>
+        <v>60</v>
       </c>
       <c r="AT3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
         <v>12</v>
       </c>
       <c r="AV3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="AW3">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AX3">
         <v>6.2</v>
@@ -1398,88 +1398,88 @@
         <v>10</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BA3">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="BB3">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD3">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BE3">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="BF3">
         <v>6</v>
       </c>
       <c r="BG3">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH3">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="BJ3">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>4.8</v>
+        <v>180</v>
       </c>
       <c r="BN3">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="BO3">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BP3">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BQ3">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS3">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="BU3">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="BZ3">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="CA3">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="CB3" t="s">
         <v>136</v>
@@ -1505,16 +1505,16 @@
         <v>3.35</v>
       </c>
       <c r="G4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H4">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="I4">
         <v>2.76</v>
       </c>
       <c r="J4">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K4">
         <v>2.96</v>
@@ -1535,7 +1535,7 @@
         <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R4">
         <v>1.16</v>
@@ -1544,16 +1544,16 @@
         <v>6.8</v>
       </c>
       <c r="T4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U4">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V4">
         <v>1.56</v>
       </c>
       <c r="W4">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X4">
         <v>7.4</v>
@@ -1586,10 +1586,10 @@
         <v>16</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="AJ4">
         <v>70</v>
@@ -1598,10 +1598,10 @@
         <v>60</v>
       </c>
       <c r="AL4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AM4">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
         <v>90</v>
@@ -1610,7 +1610,7 @@
         <v>60</v>
       </c>
       <c r="AP4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
         <v>6.8</v>
@@ -1619,7 +1619,7 @@
         <v>13.5</v>
       </c>
       <c r="AS4">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AT4">
         <v>8</v>
@@ -1634,7 +1634,7 @@
         <v>38</v>
       </c>
       <c r="AX4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY4">
         <v>14.5</v>
@@ -1655,13 +1655,13 @@
         <v>60</v>
       </c>
       <c r="BE4">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BF4">
         <v>70</v>
       </c>
       <c r="BG4">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH4">
         <v>2.48</v>
@@ -1673,16 +1673,16 @@
         <v>12.5</v>
       </c>
       <c r="BK4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BL4">
         <v>300</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BN4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO4">
         <v>5.7</v>
@@ -1691,13 +1691,13 @@
         <v>36</v>
       </c>
       <c r="BQ4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BR4">
         <v>65</v>
       </c>
       <c r="BS4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT4">
         <v>5.4</v>
@@ -1709,19 +1709,19 @@
         <v>27</v>
       </c>
       <c r="BW4">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BX4">
         <v>55</v>
       </c>
       <c r="BY4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
         <v>65</v>
       </c>
       <c r="CA4">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="CB4" t="s">
         <v>136</v>
@@ -1744,91 +1744,91 @@
         <v>123</v>
       </c>
       <c r="F5">
+        <v>2.16</v>
+      </c>
+      <c r="G5">
         <v>2.18</v>
       </c>
-      <c r="G5">
-        <v>2.2</v>
-      </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I5">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
         <v>3.05</v>
       </c>
-      <c r="K5">
-        <v>3.1</v>
-      </c>
       <c r="L5">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M5">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N5">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="O5">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="P5">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q5">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S5">
+        <v>7.6</v>
+      </c>
+      <c r="T5">
+        <v>2.52</v>
+      </c>
+      <c r="U5">
+        <v>1.61</v>
+      </c>
+      <c r="V5">
+        <v>1.26</v>
+      </c>
+      <c r="W5">
+        <v>1.84</v>
+      </c>
+      <c r="X5">
         <v>7</v>
       </c>
-      <c r="T5">
-        <v>2.46</v>
-      </c>
-      <c r="U5">
-        <v>1.66</v>
-      </c>
-      <c r="V5">
-        <v>1.27</v>
-      </c>
-      <c r="W5">
-        <v>1.83</v>
-      </c>
-      <c r="X5">
-        <v>7.2</v>
-      </c>
       <c r="Y5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA5">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB5">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI5">
         <v>140</v>
@@ -1837,43 +1837,43 @@
         <v>30</v>
       </c>
       <c r="AK5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AM5">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AN5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO5">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AP5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR5">
         <v>27</v>
       </c>
       <c r="AS5">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AT5">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW5">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="AX5">
         <v>10</v>
@@ -1882,10 +1882,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB5">
         <v>26</v>
@@ -1894,22 +1894,22 @@
         <v>32</v>
       </c>
       <c r="BD5">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BE5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BF5">
         <v>30</v>
       </c>
       <c r="BG5">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BH5">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="BI5">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ5">
         <v>13</v>
@@ -1921,7 +1921,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BN5">
         <v>4.6</v>
@@ -1933,37 +1933,37 @@
         <v>20</v>
       </c>
       <c r="BQ5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BR5">
         <v>50</v>
       </c>
       <c r="BS5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BT5">
         <v>7.6</v>
       </c>
       <c r="BU5">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BV5">
         <v>55</v>
       </c>
       <c r="BW5">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY5">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BZ5">
         <v>60</v>
       </c>
       <c r="CA5">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="CB5" t="s">
         <v>136</v>
@@ -1986,10 +1986,10 @@
         <v>124</v>
       </c>
       <c r="F6">
+        <v>1.6</v>
+      </c>
+      <c r="G6">
         <v>1.63</v>
-      </c>
-      <c r="G6">
-        <v>1.65</v>
       </c>
       <c r="H6">
         <v>7</v>
@@ -1998,10 +1998,10 @@
         <v>7.4</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L6">
         <v>1.46</v>
@@ -2013,7 +2013,7 @@
         <v>3.4</v>
       </c>
       <c r="O6">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6">
         <v>1.8</v>
@@ -2034,100 +2034,100 @@
         <v>1.76</v>
       </c>
       <c r="V6">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W6">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="X6">
         <v>13</v>
       </c>
       <c r="Y6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z6">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA6">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="AB6">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC6">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD6">
         <v>29</v>
       </c>
       <c r="AE6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI6">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ6">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK6">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL6">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM6">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN6">
         <v>12</v>
       </c>
       <c r="AO6">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AP6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR6">
         <v>50</v>
       </c>
       <c r="AS6">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="AT6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AV6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW6">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AX6">
         <v>7.6</v>
       </c>
       <c r="AY6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA6">
-        <v>10.5</v>
+        <v>70</v>
       </c>
       <c r="BB6">
         <v>13</v>
@@ -2136,16 +2136,16 @@
         <v>17</v>
       </c>
       <c r="BD6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE6">
-        <v>9.800000000000001</v>
+        <v>110</v>
       </c>
       <c r="BF6">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG6">
-        <v>9.800000000000001</v>
+        <v>200</v>
       </c>
       <c r="BH6">
         <v>3.2</v>
@@ -2160,13 +2160,13 @@
         <v>10</v>
       </c>
       <c r="BL6">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN6">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BO6">
         <v>3.5</v>
@@ -2175,13 +2175,13 @@
         <v>12.5</v>
       </c>
       <c r="BQ6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BS6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT6">
         <v>11</v>
@@ -2190,22 +2190,22 @@
         <v>9</v>
       </c>
       <c r="BV6">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BX6">
         <v>90</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
         <v>25</v>
       </c>
       <c r="CA6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB6" t="s">
         <v>136</v>
@@ -2231,16 +2231,16 @@
         <v>3.7</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H7">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I7">
         <v>2.24</v>
       </c>
       <c r="J7">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7">
         <v>3.6</v>
@@ -2249,7 +2249,7 @@
         <v>1.45</v>
       </c>
       <c r="M7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7">
         <v>3.5</v>
@@ -2258,7 +2258,7 @@
         <v>1.38</v>
       </c>
       <c r="P7">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q7">
         <v>2.12</v>
@@ -2267,13 +2267,13 @@
         <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V7">
         <v>1.8</v>
@@ -2282,10 +2282,10 @@
         <v>1.33</v>
       </c>
       <c r="X7">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
         <v>13.5</v>
@@ -2303,7 +2303,7 @@
         <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF7">
         <v>29</v>
@@ -2318,7 +2318,7 @@
         <v>42</v>
       </c>
       <c r="AJ7">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK7">
         <v>55</v>
@@ -2327,22 +2327,22 @@
         <v>80</v>
       </c>
       <c r="AM7">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AO7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP7">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR7">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS7">
         <v>21</v>
@@ -2354,7 +2354,7 @@
         <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW7">
         <v>20</v>
@@ -2375,16 +2375,16 @@
         <v>50</v>
       </c>
       <c r="BC7">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BD7">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BE7">
         <v>85</v>
       </c>
       <c r="BF7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG7">
         <v>15</v>
@@ -2473,19 +2473,19 @@
         <v>2.38</v>
       </c>
       <c r="G8">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H8">
         <v>3.05</v>
       </c>
       <c r="I8">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="J8">
         <v>3</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
         <v>1.46</v>
@@ -2494,7 +2494,7 @@
         <v>1.09</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O8">
         <v>1.39</v>
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="S8">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="T8">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="U8">
         <v>1.93</v>
@@ -2521,7 +2521,7 @@
         <v>1.39</v>
       </c>
       <c r="W8">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X8">
         <v>13.5</v>
@@ -2533,10 +2533,10 @@
         <v>26</v>
       </c>
       <c r="AA8">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB8">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC8">
         <v>7.8</v>
@@ -2545,130 +2545,130 @@
         <v>15</v>
       </c>
       <c r="AE8">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>19.5</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH8">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI8">
         <v>70</v>
       </c>
       <c r="AJ8">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK8">
         <v>34</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM8">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN8">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AO8">
         <v>55</v>
       </c>
       <c r="AP8">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AR8">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AS8">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT8">
+        <v>3.8</v>
+      </c>
+      <c r="AU8">
         <v>3.45</v>
       </c>
-      <c r="AU8">
-        <v>3</v>
-      </c>
       <c r="AV8">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AW8">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AX8">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="AY8">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="AZ8">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BA8">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB8">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BC8">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BD8">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE8">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BF8">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG8">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH8">
         <v>3.55</v>
       </c>
       <c r="BI8">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="BJ8">
         <v>12</v>
       </c>
       <c r="BK8">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BN8">
         <v>6.4</v>
       </c>
       <c r="BO8">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="BP8">
         <v>25</v>
       </c>
       <c r="BQ8">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BR8">
         <v>46</v>
       </c>
       <c r="BS8">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BT8">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU8">
         <v>2.92</v>
@@ -2677,13 +2677,13 @@
         <v>34</v>
       </c>
       <c r="BW8">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BX8">
         <v>55</v>
       </c>
       <c r="BY8">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2712,22 +2712,22 @@
         <v>127</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G9">
-        <v>990</v>
+        <v>3.45</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I9">
-        <v>990</v>
+        <v>17</v>
       </c>
       <c r="J9">
-        <v>1.06</v>
+        <v>2.48</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2736,19 +2736,19 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="O9">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q9">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
         <v>1.59</v>
@@ -2760,13 +2760,13 @@
         <v>1.11</v>
       </c>
       <c r="V9">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y9">
         <v>1000</v>
@@ -2775,13 +2775,13 @@
         <v>1000</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9">
         <v>1000</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AD9">
         <v>1000</v>
@@ -2802,7 +2802,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9">
         <v>1000</v>
@@ -2820,118 +2820,118 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH9">
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
         <v>136</v>
@@ -2963,7 +2963,7 @@
         <v>1.73</v>
       </c>
       <c r="I10">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J10">
         <v>4.7</v>
@@ -2999,7 +2999,7 @@
         <v>1.42</v>
       </c>
       <c r="U10">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V10">
         <v>2.16</v>
@@ -3014,28 +3014,28 @@
         <v>21</v>
       </c>
       <c r="Z10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA10">
         <v>26</v>
       </c>
       <c r="AB10">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AC10">
         <v>16</v>
       </c>
       <c r="AD10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE10">
         <v>17</v>
       </c>
       <c r="AF10">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AG10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH10">
         <v>16.5</v>
@@ -3044,7 +3044,7 @@
         <v>23</v>
       </c>
       <c r="AJ10">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AK10">
         <v>48</v>
@@ -3056,13 +3056,13 @@
         <v>55</v>
       </c>
       <c r="AN10">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO10">
         <v>6.8</v>
       </c>
       <c r="AP10">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10">
         <v>16.5</v>
@@ -3098,7 +3098,7 @@
         <v>18</v>
       </c>
       <c r="BB10">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC10">
         <v>28</v>
@@ -3196,19 +3196,19 @@
         <v>129</v>
       </c>
       <c r="F11">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G11">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I11">
         <v>4.2</v>
       </c>
       <c r="J11">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
         <v>5.4</v>
@@ -3220,25 +3220,25 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Q11">
         <v>1.34</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="S11">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T11">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U11">
         <v>3</v>
@@ -3247,31 +3247,31 @@
         <v>1.32</v>
       </c>
       <c r="W11">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X11">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="Y11">
         <v>34</v>
       </c>
       <c r="Z11">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AA11">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB11">
         <v>22</v>
       </c>
       <c r="AC11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD11">
         <v>21</v>
       </c>
       <c r="AE11">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF11">
         <v>21</v>
@@ -3283,52 +3283,52 @@
         <v>16</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ11">
         <v>26</v>
       </c>
       <c r="AK11">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL11">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM11">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="AN11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AP11">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AR11">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS11">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT11">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AU11">
         <v>11</v>
       </c>
       <c r="AV11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW11">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="AX11">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AY11">
         <v>10</v>
@@ -3337,7 +3337,7 @@
         <v>12</v>
       </c>
       <c r="BA11">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BB11">
         <v>20</v>
@@ -3346,22 +3346,22 @@
         <v>14</v>
       </c>
       <c r="BD11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BE11">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH11">
         <v>6.2</v>
       </c>
       <c r="BI11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ11">
         <v>8.800000000000001</v>
@@ -3388,7 +3388,7 @@
         <v>5</v>
       </c>
       <c r="BR11">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BS11">
         <v>5.7</v>
@@ -3400,7 +3400,7 @@
         <v>4.3</v>
       </c>
       <c r="BV11">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW11">
         <v>6.2</v>
@@ -3438,22 +3438,22 @@
         <v>130</v>
       </c>
       <c r="F12">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="G12">
         <v>1.58</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I12">
         <v>11.5</v>
       </c>
       <c r="J12">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K12">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L12">
         <v>1.27</v>
@@ -3465,139 +3465,139 @@
         <v>3.4</v>
       </c>
       <c r="O12">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P12">
         <v>1.85</v>
       </c>
       <c r="Q12">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R12">
         <v>1.32</v>
       </c>
       <c r="S12">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="T12">
         <v>2.08</v>
       </c>
       <c r="U12">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V12">
         <v>1.1</v>
       </c>
       <c r="W12">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X12">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y12">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z12">
         <v>95</v>
       </c>
       <c r="AA12">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AB12">
         <v>7.4</v>
       </c>
       <c r="AC12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AE12">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AF12">
         <v>8.6</v>
       </c>
       <c r="AG12">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH12">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AI12">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ12">
         <v>14</v>
       </c>
       <c r="AK12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL12">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM12">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN12">
         <v>9.6</v>
       </c>
       <c r="AO12">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AP12">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AQ12">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AR12">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AS12">
+        <v>8.6</v>
+      </c>
+      <c r="AT12">
+        <v>6</v>
+      </c>
+      <c r="AU12">
+        <v>4.8</v>
+      </c>
+      <c r="AV12">
+        <v>7</v>
+      </c>
+      <c r="AW12">
+        <v>8.4</v>
+      </c>
+      <c r="AX12">
         <v>6.2</v>
       </c>
-      <c r="AT12">
+      <c r="AY12">
+        <v>4.9</v>
+      </c>
+      <c r="AZ12">
+        <v>19</v>
+      </c>
+      <c r="BA12">
+        <v>8.4</v>
+      </c>
+      <c r="BB12">
         <v>5.4</v>
       </c>
-      <c r="AU12">
-        <v>4</v>
-      </c>
-      <c r="AV12">
-        <v>5.4</v>
-      </c>
-      <c r="AW12">
+      <c r="BC12">
         <v>6</v>
       </c>
-      <c r="AX12">
-        <v>3.65</v>
-      </c>
-      <c r="AY12">
-        <v>4.2</v>
-      </c>
-      <c r="AZ12">
-        <v>5.3</v>
-      </c>
-      <c r="BA12">
-        <v>6</v>
-      </c>
-      <c r="BB12">
-        <v>4.3</v>
-      </c>
-      <c r="BC12">
-        <v>4.8</v>
-      </c>
       <c r="BD12">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BE12">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BF12">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="BG12">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3683,22 +3683,22 @@
         <v>2.16</v>
       </c>
       <c r="G13">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H13">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K13">
         <v>3.25</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M13">
         <v>1.11</v>
@@ -3710,7 +3710,7 @@
         <v>1.48</v>
       </c>
       <c r="P13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q13">
         <v>2.42</v>
@@ -3722,7 +3722,7 @@
         <v>4.8</v>
       </c>
       <c r="T13">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U13">
         <v>1.8</v>
@@ -3731,7 +3731,7 @@
         <v>1.3</v>
       </c>
       <c r="W13">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -3740,10 +3740,10 @@
         <v>12</v>
       </c>
       <c r="Z13">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AA13">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AB13">
         <v>7.8</v>
@@ -3755,7 +3755,7 @@
         <v>18</v>
       </c>
       <c r="AE13">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="AF13">
         <v>13.5</v>
@@ -3767,25 +3767,25 @@
         <v>24</v>
       </c>
       <c r="AI13">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ13">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK13">
         <v>32</v>
       </c>
       <c r="AL13">
-        <v>65</v>
+        <v>290</v>
       </c>
       <c r="AM13">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN13">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AO13">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP13">
         <v>7.4</v>
@@ -3794,10 +3794,10 @@
         <v>9.4</v>
       </c>
       <c r="AR13">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AS13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT13">
         <v>6.4</v>
@@ -3821,13 +3821,13 @@
         <v>19</v>
       </c>
       <c r="BA13">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BB13">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="BC13">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BD13">
         <v>7.8</v>
@@ -3839,7 +3839,7 @@
         <v>21</v>
       </c>
       <c r="BG13">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3922,22 +3922,22 @@
         <v>132</v>
       </c>
       <c r="F14">
-        <v>1.35</v>
+        <v>2.78</v>
       </c>
       <c r="G14">
-        <v>600</v>
+        <v>3.35</v>
       </c>
       <c r="H14">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="I14">
-        <v>870</v>
+        <v>2.7</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3946,142 +3946,142 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="O14">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="P14">
-        <v>1.33</v>
+        <v>2.32</v>
       </c>
       <c r="Q14">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="R14">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="S14">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="T14">
         <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4164,19 +4164,19 @@
         <v>133</v>
       </c>
       <c r="F15">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="G15">
-        <v>2.34</v>
+        <v>2.22</v>
       </c>
       <c r="H15">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
         <v>3.8</v>
@@ -4185,37 +4185,37 @@
         <v>1.29</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="O15">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P15">
         <v>1.7</v>
       </c>
       <c r="Q15">
-        <v>1.79</v>
+        <v>1.51</v>
       </c>
       <c r="R15">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S15">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="T15">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="U15">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="V15">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W15">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4320,7 +4320,7 @@
         <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG15">
         <v>1.01</v>
@@ -4418,7 +4418,7 @@
         <v>10.5</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K16">
         <v>4.7</v>
@@ -4430,13 +4430,13 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O16">
         <v>1.33</v>
       </c>
       <c r="P16">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
         <v>1.93</v>
@@ -4463,7 +4463,7 @@
         <v>1000</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z16">
         <v>1000</v>
@@ -4472,10 +4472,10 @@
         <v>1000</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD16">
         <v>1000</v>
@@ -4484,10 +4484,10 @@
         <v>1000</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH16">
         <v>1000</v>
@@ -4496,76 +4496,76 @@
         <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM16">
         <v>1000</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4648,10 +4648,10 @@
         <v>135</v>
       </c>
       <c r="F17">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G17">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -4660,7 +4660,7 @@
         <v>4.7</v>
       </c>
       <c r="J17">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K17">
         <v>3.7</v>
@@ -4672,16 +4672,16 @@
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O17">
         <v>1.38</v>
       </c>
       <c r="P17">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q17">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R17">
         <v>1.28</v>
@@ -4690,16 +4690,16 @@
         <v>3.95</v>
       </c>
       <c r="T17">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U17">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V17">
         <v>1.27</v>
       </c>
       <c r="W17">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X17">
         <v>14.5</v>
@@ -4714,10 +4714,10 @@
         <v>120</v>
       </c>
       <c r="AB17">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC17">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD17">
         <v>22</v>
@@ -4762,10 +4762,10 @@
         <v>10</v>
       </c>
       <c r="AR17">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AS17">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT17">
         <v>7</v>
@@ -4777,7 +4777,7 @@
         <v>13</v>
       </c>
       <c r="AW17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AX17">
         <v>10</v>
@@ -4789,7 +4789,7 @@
         <v>17</v>
       </c>
       <c r="BA17">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB17">
         <v>21</v>
@@ -4798,22 +4798,22 @@
         <v>20</v>
       </c>
       <c r="BD17">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE17">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF17">
         <v>15.5</v>
       </c>
       <c r="BG17">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH17">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI17">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="BJ17">
         <v>12.5</v>
@@ -4825,7 +4825,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BN17">
         <v>5.5</v>
@@ -4837,13 +4837,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ17">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BR17">
         <v>40</v>
       </c>
       <c r="BS17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT17">
         <v>9</v>
@@ -4852,7 +4852,7 @@
         <v>5.6</v>
       </c>
       <c r="BV17">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW17">
         <v>4.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -424,7 +424,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-03 20:20:42</t>
+    <t>2026-08-03 22:27:01</t>
   </si>
 </sst>
 </file>
@@ -1018,226 +1018,226 @@
         <v>120</v>
       </c>
       <c r="F2">
-        <v>2.02</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="H2">
-        <v>4.1</v>
+        <v>1.56</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.35</v>
+        <v>2.98</v>
       </c>
       <c r="S2">
-        <v>3.75</v>
+        <v>1.45</v>
       </c>
       <c r="T2">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>2.78</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>1.09</v>
       </c>
       <c r="X2">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>3.7</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>9.6</v>
       </c>
       <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>4.9</v>
+      </c>
+      <c r="AI2">
         <v>13</v>
       </c>
-      <c r="AG2">
-        <v>11</v>
-      </c>
-      <c r="AH2">
-        <v>19.5</v>
-      </c>
-      <c r="AI2">
-        <v>110</v>
-      </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
+        <v>17.5</v>
+      </c>
+      <c r="AM2">
         <v>40</v>
       </c>
-      <c r="AM2">
-        <v>160</v>
-      </c>
       <c r="AN2">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="AO2">
-        <v>70</v>
+        <v>18.5</v>
       </c>
       <c r="AP2">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ2">
+        <v>5.2</v>
+      </c>
+      <c r="AR2">
+        <v>5.2</v>
+      </c>
+      <c r="AS2">
+        <v>5.2</v>
+      </c>
+      <c r="AT2">
+        <v>5.2</v>
+      </c>
+      <c r="AU2">
+        <v>5.2</v>
+      </c>
+      <c r="AV2">
+        <v>2.96</v>
+      </c>
+      <c r="AW2">
+        <v>5.9</v>
+      </c>
+      <c r="AX2">
+        <v>5.2</v>
+      </c>
+      <c r="AY2">
+        <v>5.2</v>
+      </c>
+      <c r="AZ2">
+        <v>3.85</v>
+      </c>
+      <c r="BA2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB2">
+        <v>5.2</v>
+      </c>
+      <c r="BC2">
+        <v>5.2</v>
+      </c>
+      <c r="BD2">
         <v>12.5</v>
       </c>
-      <c r="AR2">
-        <v>22</v>
-      </c>
-      <c r="AS2">
-        <v>75</v>
-      </c>
-      <c r="AT2">
-        <v>7.6</v>
-      </c>
-      <c r="AU2">
-        <v>7</v>
-      </c>
-      <c r="AV2">
-        <v>14.5</v>
-      </c>
-      <c r="AW2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX2">
-        <v>10.5</v>
-      </c>
-      <c r="AY2">
-        <v>9</v>
-      </c>
-      <c r="AZ2">
-        <v>16</v>
-      </c>
-      <c r="BA2">
-        <v>9</v>
-      </c>
-      <c r="BB2">
-        <v>20</v>
-      </c>
-      <c r="BC2">
-        <v>19</v>
-      </c>
-      <c r="BD2">
-        <v>13.5</v>
-      </c>
       <c r="BE2">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="BF2">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="BG2">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>136</v>
@@ -1260,226 +1260,226 @@
         <v>121</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="G3">
-        <v>1.32</v>
+        <v>1.84</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I3">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="J3">
-        <v>5.9</v>
+        <v>2.74</v>
       </c>
       <c r="K3">
-        <v>6.2</v>
+        <v>2.76</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="N3">
-        <v>4.1</v>
+        <v>1.45</v>
       </c>
       <c r="O3">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>2.08</v>
+        <v>1.1</v>
       </c>
       <c r="Q3">
-        <v>1.89</v>
+        <v>10</v>
       </c>
       <c r="R3">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>46</v>
       </c>
       <c r="T3">
-        <v>2.44</v>
+        <v>7.2</v>
       </c>
       <c r="U3">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="V3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W3">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>3.5</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z3">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB3">
-        <v>7.2</v>
+        <v>3.3</v>
       </c>
       <c r="AC3">
         <v>14</v>
       </c>
       <c r="AD3">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="AE3">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AH3">
-        <v>42</v>
+        <v>410</v>
       </c>
       <c r="AI3">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>9.4</v>
+        <v>34</v>
       </c>
       <c r="AK3">
-        <v>16.5</v>
+        <v>170</v>
       </c>
       <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>150</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>3.35</v>
+      </c>
+      <c r="AQ3">
+        <v>12.5</v>
+      </c>
+      <c r="AR3">
+        <v>100</v>
+      </c>
+      <c r="AS3">
+        <v>15.5</v>
+      </c>
+      <c r="AT3">
+        <v>3.05</v>
+      </c>
+      <c r="AU3">
+        <v>12.5</v>
+      </c>
+      <c r="AV3">
+        <v>85</v>
+      </c>
+      <c r="AW3">
+        <v>34</v>
+      </c>
+      <c r="AX3">
+        <v>6.6</v>
+      </c>
+      <c r="AY3">
+        <v>26</v>
+      </c>
+      <c r="AZ3">
+        <v>140</v>
+      </c>
+      <c r="BA3">
+        <v>75</v>
+      </c>
+      <c r="BB3">
+        <v>23</v>
+      </c>
+      <c r="BC3">
+        <v>70</v>
+      </c>
+      <c r="BD3">
+        <v>270</v>
+      </c>
+      <c r="BE3">
+        <v>90</v>
+      </c>
+      <c r="BF3">
         <v>55</v>
       </c>
-      <c r="AM3">
-        <v>300</v>
-      </c>
-      <c r="AN3">
-        <v>6.8</v>
-      </c>
-      <c r="AO3">
-        <v>500</v>
-      </c>
-      <c r="AP3">
-        <v>16</v>
-      </c>
-      <c r="AQ3">
-        <v>34</v>
-      </c>
-      <c r="AR3">
-        <v>44</v>
-      </c>
-      <c r="AS3">
-        <v>60</v>
-      </c>
-      <c r="AT3">
-        <v>6.4</v>
-      </c>
-      <c r="AU3">
-        <v>12</v>
-      </c>
-      <c r="AV3">
-        <v>10</v>
-      </c>
-      <c r="AW3">
-        <v>12.5</v>
-      </c>
-      <c r="AX3">
-        <v>6.2</v>
-      </c>
-      <c r="AY3">
-        <v>10</v>
-      </c>
-      <c r="AZ3">
-        <v>24</v>
-      </c>
-      <c r="BA3">
-        <v>12</v>
-      </c>
-      <c r="BB3">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC3">
-        <v>14</v>
-      </c>
-      <c r="BD3">
-        <v>32</v>
-      </c>
-      <c r="BE3">
-        <v>150</v>
-      </c>
-      <c r="BF3">
-        <v>6</v>
-      </c>
       <c r="BG3">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="BH3">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>136</v>
@@ -1502,226 +1502,226 @@
         <v>122</v>
       </c>
       <c r="F4">
+        <v>1.47</v>
+      </c>
+      <c r="G4">
+        <v>1.55</v>
+      </c>
+      <c r="H4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I4">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>3.9</v>
+      </c>
+      <c r="K4">
+        <v>4.5</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>1.02</v>
+      </c>
+      <c r="O4">
+        <v>1.38</v>
+      </c>
+      <c r="P4">
+        <v>1.5</v>
+      </c>
+      <c r="Q4">
+        <v>2.82</v>
+      </c>
+      <c r="R4">
+        <v>1.1</v>
+      </c>
+      <c r="S4">
+        <v>8.4</v>
+      </c>
+      <c r="T4">
+        <v>1.84</v>
+      </c>
+      <c r="U4">
+        <v>1.88</v>
+      </c>
+      <c r="V4">
+        <v>1.01</v>
+      </c>
+      <c r="W4">
+        <v>1.01</v>
+      </c>
+      <c r="X4">
+        <v>1000</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>3.8</v>
+      </c>
+      <c r="AC4">
+        <v>5.3</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>6.8</v>
+      </c>
+      <c r="AG4">
+        <v>480</v>
+      </c>
+      <c r="AH4">
+        <v>480</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.55</v>
+      </c>
+      <c r="AQ4">
+        <v>1.55</v>
+      </c>
+      <c r="AR4">
+        <v>1.55</v>
+      </c>
+      <c r="AS4">
+        <v>1.55</v>
+      </c>
+      <c r="AT4">
+        <v>3.3</v>
+      </c>
+      <c r="AU4">
         <v>3.35</v>
       </c>
-      <c r="G4">
-        <v>3.4</v>
-      </c>
-      <c r="H4">
-        <v>2.74</v>
-      </c>
-      <c r="I4">
-        <v>2.76</v>
-      </c>
-      <c r="J4">
-        <v>2.94</v>
-      </c>
-      <c r="K4">
-        <v>2.96</v>
-      </c>
-      <c r="L4">
-        <v>1.68</v>
-      </c>
-      <c r="M4">
-        <v>1.16</v>
-      </c>
-      <c r="N4">
-        <v>2.48</v>
-      </c>
-      <c r="O4">
-        <v>1.66</v>
-      </c>
-      <c r="P4">
-        <v>1.46</v>
-      </c>
-      <c r="Q4">
-        <v>3.05</v>
-      </c>
-      <c r="R4">
-        <v>1.16</v>
-      </c>
-      <c r="S4">
-        <v>6.8</v>
-      </c>
-      <c r="T4">
-        <v>2.34</v>
-      </c>
-      <c r="U4">
-        <v>1.71</v>
-      </c>
-      <c r="V4">
-        <v>1.56</v>
-      </c>
-      <c r="W4">
-        <v>1.41</v>
-      </c>
-      <c r="X4">
+      <c r="AV4">
+        <v>12</v>
+      </c>
+      <c r="AW4">
+        <v>50</v>
+      </c>
+      <c r="AX4">
+        <v>4.9</v>
+      </c>
+      <c r="AY4">
         <v>7.4</v>
       </c>
-      <c r="Y4">
-        <v>7.4</v>
-      </c>
-      <c r="Z4">
-        <v>15</v>
-      </c>
-      <c r="AA4">
-        <v>46</v>
-      </c>
-      <c r="AB4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC4">
-        <v>6.6</v>
-      </c>
-      <c r="AD4">
-        <v>14</v>
-      </c>
-      <c r="AE4">
-        <v>46</v>
-      </c>
-      <c r="AF4">
-        <v>20</v>
-      </c>
-      <c r="AG4">
-        <v>16</v>
-      </c>
-      <c r="AH4">
-        <v>27</v>
-      </c>
-      <c r="AI4">
-        <v>140</v>
-      </c>
-      <c r="AJ4">
-        <v>70</v>
-      </c>
-      <c r="AK4">
-        <v>60</v>
-      </c>
-      <c r="AL4">
-        <v>100</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>90</v>
-      </c>
-      <c r="AO4">
-        <v>60</v>
-      </c>
-      <c r="AP4">
-        <v>7</v>
-      </c>
-      <c r="AQ4">
-        <v>6.8</v>
-      </c>
-      <c r="AR4">
-        <v>13.5</v>
-      </c>
-      <c r="AS4">
-        <v>44</v>
-      </c>
-      <c r="AT4">
-        <v>8</v>
-      </c>
-      <c r="AU4">
-        <v>6.2</v>
-      </c>
-      <c r="AV4">
-        <v>13</v>
-      </c>
-      <c r="AW4">
-        <v>38</v>
-      </c>
-      <c r="AX4">
-        <v>18</v>
-      </c>
-      <c r="AY4">
-        <v>14.5</v>
-      </c>
       <c r="AZ4">
-        <v>24</v>
+        <v>2.6</v>
       </c>
       <c r="BA4">
         <v>70</v>
       </c>
       <c r="BB4">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="BC4">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BD4">
         <v>60</v>
       </c>
       <c r="BE4">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BF4">
-        <v>70</v>
+        <v>2.78</v>
       </c>
       <c r="BG4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BH4">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>136</v>
@@ -1744,226 +1744,226 @@
         <v>123</v>
       </c>
       <c r="F5">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="H5">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I5">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="K5">
-        <v>3.05</v>
+        <v>2.12</v>
       </c>
       <c r="L5">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1.17</v>
+        <v>1.54</v>
       </c>
       <c r="N5">
-        <v>2.34</v>
+        <v>1.37</v>
       </c>
       <c r="O5">
-        <v>1.73</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="Q5">
-        <v>3.25</v>
+        <v>12</v>
       </c>
       <c r="R5">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="S5">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="T5">
-        <v>2.52</v>
+        <v>5.8</v>
       </c>
       <c r="U5">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
       <c r="V5">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W5">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>2.76</v>
       </c>
       <c r="Y5">
+        <v>7.2</v>
+      </c>
+      <c r="Z5">
+        <v>40</v>
+      </c>
+      <c r="AA5">
+        <v>350</v>
+      </c>
+      <c r="AB5">
+        <v>4.8</v>
+      </c>
+      <c r="AC5">
         <v>10.5</v>
       </c>
-      <c r="Z5">
+      <c r="AD5">
+        <v>55</v>
+      </c>
+      <c r="AE5">
+        <v>520</v>
+      </c>
+      <c r="AF5">
+        <v>18</v>
+      </c>
+      <c r="AG5">
+        <v>40</v>
+      </c>
+      <c r="AH5">
+        <v>220</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>110</v>
+      </c>
+      <c r="AK5">
+        <v>260</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>620</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>2.68</v>
+      </c>
+      <c r="AQ5">
+        <v>6.6</v>
+      </c>
+      <c r="AR5">
         <v>34</v>
       </c>
-      <c r="AA5">
-        <v>140</v>
-      </c>
-      <c r="AB5">
-        <v>5.9</v>
-      </c>
-      <c r="AC5">
-        <v>7.2</v>
-      </c>
-      <c r="AD5">
-        <v>22</v>
-      </c>
-      <c r="AE5">
-        <v>100</v>
-      </c>
-      <c r="AF5">
-        <v>11</v>
-      </c>
-      <c r="AG5">
-        <v>13</v>
-      </c>
-      <c r="AH5">
-        <v>30</v>
-      </c>
-      <c r="AI5">
-        <v>140</v>
-      </c>
-      <c r="AJ5">
-        <v>30</v>
-      </c>
-      <c r="AK5">
-        <v>38</v>
-      </c>
-      <c r="AL5">
-        <v>90</v>
-      </c>
-      <c r="AM5">
-        <v>320</v>
-      </c>
-      <c r="AN5">
-        <v>38</v>
-      </c>
-      <c r="AO5">
-        <v>190</v>
-      </c>
-      <c r="AP5">
-        <v>6.4</v>
-      </c>
-      <c r="AQ5">
-        <v>9.6</v>
-      </c>
-      <c r="AR5">
-        <v>27</v>
-      </c>
       <c r="AS5">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="AT5">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AV5">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="AW5">
-        <v>40</v>
+        <v>380</v>
       </c>
       <c r="AX5">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="AY5">
-        <v>11.5</v>
+        <v>32</v>
       </c>
       <c r="AZ5">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="BA5">
-        <v>46</v>
+        <v>380</v>
       </c>
       <c r="BB5">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="BC5">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="BD5">
-        <v>36</v>
+        <v>310</v>
       </c>
       <c r="BE5">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="BF5">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="BG5">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="BH5">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
         <v>136</v>
@@ -1986,226 +1986,226 @@
         <v>124</v>
       </c>
       <c r="F6">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="G6">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="I6">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="J6">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>4.3</v>
+        <v>11</v>
       </c>
       <c r="L6">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>6.2</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>1.26</v>
+      </c>
+      <c r="S6">
+        <v>1.13</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>1.2</v>
+      </c>
+      <c r="W6">
+        <v>1.86</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>120</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>990</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>23</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>50</v>
+      </c>
+      <c r="AN6">
+        <v>8</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>2.82</v>
+      </c>
+      <c r="AQ6">
+        <v>2.38</v>
+      </c>
+      <c r="AR6">
+        <v>2.38</v>
+      </c>
+      <c r="AS6">
+        <v>2.38</v>
+      </c>
+      <c r="AT6">
+        <v>1.25</v>
+      </c>
+      <c r="AU6">
+        <v>6.8</v>
+      </c>
+      <c r="AV6">
+        <v>2.16</v>
+      </c>
+      <c r="AW6">
+        <v>2.38</v>
+      </c>
+      <c r="AX6">
+        <v>1.25</v>
+      </c>
+      <c r="AY6">
+        <v>1.25</v>
+      </c>
+      <c r="AZ6">
+        <v>3.15</v>
+      </c>
+      <c r="BA6">
+        <v>2.38</v>
+      </c>
+      <c r="BB6">
+        <v>1.25</v>
+      </c>
+      <c r="BC6">
+        <v>1.52</v>
+      </c>
+      <c r="BD6">
+        <v>1.25</v>
+      </c>
+      <c r="BE6">
         <v>3.4</v>
       </c>
-      <c r="O6">
-        <v>1.4</v>
-      </c>
-      <c r="P6">
-        <v>1.8</v>
-      </c>
-      <c r="Q6">
-        <v>2.18</v>
-      </c>
-      <c r="R6">
-        <v>1.3</v>
-      </c>
-      <c r="S6">
-        <v>4.1</v>
-      </c>
-      <c r="T6">
-        <v>2.16</v>
-      </c>
-      <c r="U6">
-        <v>1.76</v>
-      </c>
-      <c r="V6">
-        <v>1.15</v>
-      </c>
-      <c r="W6">
-        <v>2.58</v>
-      </c>
-      <c r="X6">
-        <v>13</v>
-      </c>
-      <c r="Y6">
+      <c r="BF6">
+        <v>2.06</v>
+      </c>
+      <c r="BG6">
         <v>20</v>
       </c>
-      <c r="Z6">
-        <v>60</v>
-      </c>
-      <c r="AA6">
-        <v>270</v>
-      </c>
-      <c r="AB6">
-        <v>7</v>
-      </c>
-      <c r="AC6">
-        <v>9.6</v>
-      </c>
-      <c r="AD6">
-        <v>29</v>
-      </c>
-      <c r="AE6">
-        <v>140</v>
-      </c>
-      <c r="AF6">
-        <v>8.6</v>
-      </c>
-      <c r="AG6">
-        <v>10.5</v>
-      </c>
-      <c r="AH6">
-        <v>27</v>
-      </c>
-      <c r="AI6">
-        <v>130</v>
-      </c>
-      <c r="AJ6">
-        <v>15.5</v>
-      </c>
-      <c r="AK6">
-        <v>19.5</v>
-      </c>
-      <c r="AL6">
-        <v>48</v>
-      </c>
-      <c r="AM6">
-        <v>200</v>
-      </c>
-      <c r="AN6">
-        <v>12</v>
-      </c>
-      <c r="AO6">
-        <v>270</v>
-      </c>
-      <c r="AP6">
-        <v>11</v>
-      </c>
-      <c r="AQ6">
-        <v>18</v>
-      </c>
-      <c r="AR6">
-        <v>50</v>
-      </c>
-      <c r="AS6">
-        <v>14.5</v>
-      </c>
-      <c r="AT6">
-        <v>6.2</v>
-      </c>
-      <c r="AU6">
-        <v>8.6</v>
-      </c>
-      <c r="AV6">
-        <v>25</v>
-      </c>
-      <c r="AW6">
-        <v>95</v>
-      </c>
-      <c r="AX6">
-        <v>7.6</v>
-      </c>
-      <c r="AY6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ6">
-        <v>24</v>
-      </c>
-      <c r="BA6">
-        <v>70</v>
-      </c>
-      <c r="BB6">
-        <v>13</v>
-      </c>
-      <c r="BC6">
-        <v>17</v>
-      </c>
-      <c r="BD6">
-        <v>42</v>
-      </c>
-      <c r="BE6">
-        <v>110</v>
-      </c>
-      <c r="BF6">
-        <v>10</v>
-      </c>
-      <c r="BG6">
-        <v>200</v>
-      </c>
       <c r="BH6">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.9</v>
+        <v>1.41</v>
       </c>
       <c r="BJ6">
-        <v>12.5</v>
+        <v>3.45</v>
       </c>
       <c r="BK6">
-        <v>10</v>
+        <v>1.74</v>
       </c>
       <c r="BL6">
-        <v>220</v>
+        <v>960</v>
       </c>
       <c r="BM6">
-        <v>12</v>
+        <v>1.41</v>
       </c>
       <c r="BN6">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3.5</v>
+        <v>1.41</v>
       </c>
       <c r="BP6">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>9.4</v>
+        <v>1.41</v>
       </c>
       <c r="BR6">
-        <v>32</v>
+        <v>860</v>
       </c>
       <c r="BS6">
-        <v>9.199999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="BT6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>9</v>
+        <v>1.41</v>
       </c>
       <c r="BV6">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>11</v>
+        <v>1.41</v>
       </c>
       <c r="BX6">
-        <v>90</v>
+        <v>870</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>1.41</v>
       </c>
       <c r="BZ6">
-        <v>25</v>
+        <v>960</v>
       </c>
       <c r="CA6">
-        <v>8.800000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="CB6" t="s">
         <v>136</v>
@@ -2228,13 +2228,13 @@
         <v>125</v>
       </c>
       <c r="F7">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G7">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H7">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I7">
         <v>2.24</v>
@@ -2264,22 +2264,22 @@
         <v>2.12</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
         <v>3.9</v>
       </c>
       <c r="T7">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U7">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V7">
         <v>1.8</v>
       </c>
       <c r="W7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X7">
         <v>14</v>
@@ -2294,7 +2294,7 @@
         <v>28</v>
       </c>
       <c r="AB7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC7">
         <v>8.199999999999999</v>
@@ -2306,7 +2306,7 @@
         <v>26</v>
       </c>
       <c r="AF7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG7">
         <v>16.5</v>
@@ -2321,13 +2321,13 @@
         <v>85</v>
       </c>
       <c r="AK7">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL7">
         <v>80</v>
       </c>
       <c r="AM7">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="AN7">
         <v>65</v>
@@ -2345,19 +2345,19 @@
         <v>11</v>
       </c>
       <c r="AS7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT7">
         <v>11.5</v>
       </c>
       <c r="AU7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX7">
         <v>22</v>
@@ -2372,10 +2372,10 @@
         <v>32</v>
       </c>
       <c r="BB7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BC7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD7">
         <v>48</v>
@@ -2384,13 +2384,13 @@
         <v>85</v>
       </c>
       <c r="BF7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG7">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH7">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI7">
         <v>2.9</v>
@@ -2399,55 +2399,55 @@
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>10.5</v>
+        <v>110</v>
       </c>
       <c r="BN7">
         <v>7.2</v>
       </c>
       <c r="BO7">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BP7">
         <v>34</v>
       </c>
       <c r="BQ7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BR7">
         <v>50</v>
       </c>
       <c r="BS7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT7">
         <v>4.9</v>
       </c>
       <c r="BU7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV7">
         <v>19</v>
       </c>
       <c r="BW7">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BX7">
         <v>32</v>
       </c>
       <c r="BY7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
         <v>30</v>
       </c>
       <c r="CA7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB7" t="s">
         <v>136</v>
@@ -2470,28 +2470,28 @@
         <v>126</v>
       </c>
       <c r="F8">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G8">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H8">
         <v>3.05</v>
       </c>
       <c r="I8">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="L8">
         <v>1.46</v>
       </c>
       <c r="M8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8">
         <v>2.96</v>
@@ -2500,22 +2500,22 @@
         <v>1.39</v>
       </c>
       <c r="P8">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="Q8">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="S8">
-        <v>3.4</v>
+        <v>1.78</v>
       </c>
       <c r="T8">
         <v>1.94</v>
       </c>
       <c r="U8">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="V8">
         <v>1.39</v>
@@ -2524,166 +2524,166 @@
         <v>1.58</v>
       </c>
       <c r="X8">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z8">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="AA8">
-        <v>65</v>
+        <v>900</v>
       </c>
       <c r="AB8">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="AD8">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE8">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AF8">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AG8">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH8">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="AI8">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ8">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AL8">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM8">
         <v>580</v>
       </c>
       <c r="AN8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>4.3</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8">
-        <v>4.3</v>
+        <v>1.47</v>
       </c>
       <c r="AR8">
-        <v>5</v>
+        <v>1.48</v>
       </c>
       <c r="AS8">
-        <v>5.7</v>
+        <v>1.49</v>
       </c>
       <c r="AT8">
-        <v>3.8</v>
+        <v>1.39</v>
       </c>
       <c r="AU8">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="AV8">
-        <v>4.4</v>
+        <v>1.42</v>
       </c>
       <c r="AW8">
-        <v>5.5</v>
+        <v>1.49</v>
       </c>
       <c r="AX8">
-        <v>4.7</v>
+        <v>1.47</v>
       </c>
       <c r="AY8">
-        <v>4.2</v>
+        <v>1.42</v>
       </c>
       <c r="AZ8">
-        <v>4.7</v>
+        <v>1.44</v>
       </c>
       <c r="BA8">
-        <v>5.7</v>
+        <v>1.49</v>
       </c>
       <c r="BB8">
-        <v>5.4</v>
+        <v>1.48</v>
       </c>
       <c r="BC8">
-        <v>5.3</v>
+        <v>1.48</v>
       </c>
       <c r="BD8">
-        <v>5.6</v>
+        <v>1.49</v>
       </c>
       <c r="BE8">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="BF8">
-        <v>5.2</v>
+        <v>1.55</v>
       </c>
       <c r="BG8">
-        <v>5.6</v>
+        <v>1.55</v>
       </c>
       <c r="BH8">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>2.92</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2715,16 +2715,16 @@
         <v>1.8</v>
       </c>
       <c r="G9">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="I9">
         <v>17</v>
       </c>
       <c r="J9">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="K9">
         <v>6.8</v>
@@ -2739,19 +2739,19 @@
         <v>2.48</v>
       </c>
       <c r="O9">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P9">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="Q9">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="R9">
         <v>1.13</v>
       </c>
       <c r="S9">
-        <v>1.59</v>
+        <v>2.72</v>
       </c>
       <c r="T9">
         <v>1.11</v>
@@ -2763,112 +2763,112 @@
         <v>1.21</v>
       </c>
       <c r="W9">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X9">
         <v>970</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC9">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ9">
         <v>900</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG9">
         <v>1.55</v>
@@ -2978,7 +2978,7 @@
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O10">
         <v>1.11</v>
@@ -3005,7 +3005,7 @@
         <v>2.16</v>
       </c>
       <c r="W10">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X10">
         <v>55</v>
@@ -3196,19 +3196,19 @@
         <v>129</v>
       </c>
       <c r="F11">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="G11">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H11">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I11">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
         <v>5.4</v>
@@ -3220,19 +3220,19 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="O11">
         <v>1.11</v>
       </c>
       <c r="P11">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q11">
         <v>1.34</v>
       </c>
       <c r="R11">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S11">
         <v>1.81</v>
@@ -3241,13 +3241,13 @@
         <v>1.39</v>
       </c>
       <c r="U11">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V11">
         <v>1.32</v>
       </c>
       <c r="W11">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X11">
         <v>110</v>
@@ -3262,7 +3262,7 @@
         <v>500</v>
       </c>
       <c r="AB11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC11">
         <v>14</v>
@@ -3271,13 +3271,13 @@
         <v>21</v>
       </c>
       <c r="AE11">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AF11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH11">
         <v>16</v>
@@ -3295,121 +3295,121 @@
         <v>23</v>
       </c>
       <c r="AM11">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN11">
         <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AP11">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="AQ11">
+        <v>4.9</v>
+      </c>
+      <c r="AR11">
+        <v>5</v>
+      </c>
+      <c r="AS11">
+        <v>5.5</v>
+      </c>
+      <c r="AT11">
+        <v>4.5</v>
+      </c>
+      <c r="AU11">
+        <v>4</v>
+      </c>
+      <c r="AV11">
+        <v>4.5</v>
+      </c>
+      <c r="AW11">
+        <v>5.3</v>
+      </c>
+      <c r="AX11">
+        <v>4.4</v>
+      </c>
+      <c r="AY11">
+        <v>3.95</v>
+      </c>
+      <c r="AZ11">
+        <v>4.2</v>
+      </c>
+      <c r="BA11">
+        <v>4.9</v>
+      </c>
+      <c r="BB11">
+        <v>4.7</v>
+      </c>
+      <c r="BC11">
+        <v>4.3</v>
+      </c>
+      <c r="BD11">
+        <v>4.6</v>
+      </c>
+      <c r="BE11">
+        <v>5.5</v>
+      </c>
+      <c r="BF11">
+        <v>3</v>
+      </c>
+      <c r="BG11">
+        <v>4.5</v>
+      </c>
+      <c r="BH11">
         <v>6</v>
-      </c>
-      <c r="AR11">
-        <v>6.2</v>
-      </c>
-      <c r="AS11">
-        <v>6.8</v>
-      </c>
-      <c r="AT11">
-        <v>15.5</v>
-      </c>
-      <c r="AU11">
-        <v>11</v>
-      </c>
-      <c r="AV11">
-        <v>14.5</v>
-      </c>
-      <c r="AW11">
-        <v>6.2</v>
-      </c>
-      <c r="AX11">
-        <v>14.5</v>
-      </c>
-      <c r="AY11">
-        <v>10</v>
-      </c>
-      <c r="AZ11">
-        <v>12</v>
-      </c>
-      <c r="BA11">
-        <v>6</v>
-      </c>
-      <c r="BB11">
-        <v>20</v>
-      </c>
-      <c r="BC11">
-        <v>14</v>
-      </c>
-      <c r="BD11">
-        <v>17.5</v>
-      </c>
-      <c r="BE11">
-        <v>6.4</v>
-      </c>
-      <c r="BF11">
-        <v>4.7</v>
-      </c>
-      <c r="BG11">
-        <v>14</v>
-      </c>
-      <c r="BH11">
-        <v>6.2</v>
       </c>
       <c r="BI11">
         <v>4.5</v>
       </c>
       <c r="BJ11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BN11">
         <v>6</v>
       </c>
       <c r="BO11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP11">
         <v>12.5</v>
       </c>
       <c r="BQ11">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BR11">
         <v>18.5</v>
       </c>
       <c r="BS11">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BT11">
         <v>8.800000000000001</v>
       </c>
       <c r="BU11">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV11">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BX11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BY11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BZ11">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>8.6</v>
       </c>
       <c r="I12">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -3471,7 +3471,7 @@
         <v>1.85</v>
       </c>
       <c r="Q12">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R12">
         <v>1.32</v>
@@ -3483,10 +3483,10 @@
         <v>2.08</v>
       </c>
       <c r="U12">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W12">
         <v>2.74</v>
@@ -3501,7 +3501,7 @@
         <v>95</v>
       </c>
       <c r="AA12">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AB12">
         <v>7.4</v>
@@ -3510,7 +3510,7 @@
         <v>10.5</v>
       </c>
       <c r="AD12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE12">
         <v>190</v>
@@ -3522,7 +3522,7 @@
         <v>11</v>
       </c>
       <c r="AH12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI12">
         <v>170</v>
@@ -3531,7 +3531,7 @@
         <v>14</v>
       </c>
       <c r="AK12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL12">
         <v>48</v>
@@ -3543,61 +3543,61 @@
         <v>9.6</v>
       </c>
       <c r="AO12">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AP12">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR12">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS12">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT12">
         <v>6</v>
       </c>
       <c r="AU12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AV12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12">
         <v>6.2</v>
       </c>
       <c r="AY12">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ12">
         <v>19</v>
       </c>
       <c r="BA12">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB12">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BC12">
         <v>6</v>
       </c>
       <c r="BD12">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE12">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12">
         <v>7</v>
       </c>
       <c r="BG12">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3707,7 +3707,7 @@
         <v>2.7</v>
       </c>
       <c r="O13">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P13">
         <v>1.58</v>
@@ -3719,10 +3719,10 @@
         <v>1.2</v>
       </c>
       <c r="S13">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U13">
         <v>1.8</v>
@@ -3809,7 +3809,7 @@
         <v>14</v>
       </c>
       <c r="AW13">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AX13">
         <v>11</v>
@@ -3824,22 +3824,22 @@
         <v>32</v>
       </c>
       <c r="BB13">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BC13">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="BD13">
-        <v>7.8</v>
+        <v>23</v>
       </c>
       <c r="BE13">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF13">
         <v>21</v>
       </c>
       <c r="BG13">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -3922,19 +3922,19 @@
         <v>132</v>
       </c>
       <c r="F14">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="G14">
         <v>3.35</v>
       </c>
       <c r="H14">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I14">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K14">
         <v>4.8</v>
@@ -3946,22 +3946,22 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.9</v>
+        <v>2.88</v>
       </c>
       <c r="O14">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="P14">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q14">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="R14">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S14">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -3988,13 +3988,13 @@
         <v>900</v>
       </c>
       <c r="AB14">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AC14">
         <v>42</v>
       </c>
       <c r="AD14">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE14">
         <v>500</v>
@@ -4003,7 +4003,7 @@
         <v>500</v>
       </c>
       <c r="AG14">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AH14">
         <v>500</v>
@@ -4030,52 +4030,52 @@
         <v>500</v>
       </c>
       <c r="AP14">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AR14">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AS14">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AT14">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AU14">
         <v>5.1</v>
       </c>
       <c r="AV14">
+        <v>1.79</v>
+      </c>
+      <c r="AW14">
+        <v>1.92</v>
+      </c>
+      <c r="AX14">
+        <v>1.93</v>
+      </c>
+      <c r="AY14">
+        <v>1.79</v>
+      </c>
+      <c r="AZ14">
         <v>1.81</v>
       </c>
-      <c r="AW14">
-        <v>1.95</v>
-      </c>
-      <c r="AX14">
-        <v>1.96</v>
-      </c>
-      <c r="AY14">
-        <v>1.81</v>
-      </c>
-      <c r="AZ14">
-        <v>1.83</v>
-      </c>
       <c r="BA14">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BB14">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="BC14">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BD14">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BE14">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="BF14">
         <v>3.3</v>
@@ -4173,10 +4173,10 @@
         <v>3.45</v>
       </c>
       <c r="I15">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K15">
         <v>3.8</v>
@@ -4188,7 +4188,7 @@
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O15">
         <v>1.27</v>
@@ -4197,19 +4197,19 @@
         <v>1.7</v>
       </c>
       <c r="Q15">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="R15">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
         <v>2.58</v>
       </c>
       <c r="T15">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="U15">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="V15">
         <v>1.27</v>
@@ -4442,10 +4442,10 @@
         <v>1.93</v>
       </c>
       <c r="R16">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S16">
-        <v>2.6</v>
+        <v>1.05</v>
       </c>
       <c r="T16">
         <v>1.11</v>
@@ -4648,13 +4648,13 @@
         <v>135</v>
       </c>
       <c r="F17">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G17">
         <v>2.14</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I17">
         <v>4.7</v>
@@ -4813,7 +4813,7 @@
         <v>3.65</v>
       </c>
       <c r="BI17">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="BJ17">
         <v>12.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="117">
   <si>
     <t>League</t>
   </si>
@@ -256,9 +256,6 @@
     <t>SnapshotTS</t>
   </si>
   <si>
-    <t>Costa Rican Primera Division</t>
-  </si>
-  <si>
     <t>Romanian Liga II</t>
   </si>
   <si>
@@ -280,9 +277,6 @@
     <t>2026-08-04</t>
   </si>
   <si>
-    <t>02:00:00</t>
-  </si>
-  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -310,9 +304,6 @@
     <t>23:15:00</t>
   </si>
   <si>
-    <t>Municipal Perez Zeledon</t>
-  </si>
-  <si>
     <t>Politehnica Timisoara</t>
   </si>
   <si>
@@ -343,9 +334,6 @@
     <t>Tolima</t>
   </si>
   <si>
-    <t>Cs Cartagines</t>
-  </si>
-  <si>
     <t>Chindia Targoviste</t>
   </si>
   <si>
@@ -376,7 +364,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-04 00:34:08</t>
+    <t>2026-08-04 02:41:30</t>
   </si>
 </sst>
 </file>
@@ -708,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -958,232 +946,232 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
         <v>87</v>
       </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F2">
+        <v>2.42</v>
+      </c>
+      <c r="G2">
+        <v>2.66</v>
+      </c>
+      <c r="H2">
+        <v>3.05</v>
+      </c>
+      <c r="I2">
+        <v>3.4</v>
+      </c>
+      <c r="J2">
+        <v>3.2</v>
+      </c>
+      <c r="K2">
+        <v>3.6</v>
+      </c>
+      <c r="L2">
+        <v>1.49</v>
+      </c>
+      <c r="M2">
+        <v>1.09</v>
+      </c>
+      <c r="N2">
+        <v>3.1</v>
+      </c>
+      <c r="O2">
+        <v>1.41</v>
+      </c>
+      <c r="P2">
+        <v>1.71</v>
+      </c>
+      <c r="Q2">
+        <v>2.26</v>
+      </c>
+      <c r="R2">
+        <v>1.26</v>
+      </c>
+      <c r="S2">
+        <v>4.2</v>
+      </c>
+      <c r="T2">
+        <v>1.94</v>
+      </c>
+      <c r="U2">
+        <v>1.89</v>
+      </c>
+      <c r="V2">
         <v>1.42</v>
       </c>
-      <c r="G2">
-        <v>1.45</v>
-      </c>
-      <c r="H2">
-        <v>17.5</v>
-      </c>
-      <c r="I2">
-        <v>21</v>
-      </c>
-      <c r="J2">
-        <v>3.9</v>
-      </c>
-      <c r="K2">
-        <v>4.1</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>2</v>
-      </c>
-      <c r="O2">
-        <v>1.95</v>
-      </c>
-      <c r="P2">
-        <v>1.18</v>
-      </c>
-      <c r="Q2">
-        <v>6</v>
-      </c>
-      <c r="R2">
-        <v>1.03</v>
-      </c>
-      <c r="S2">
-        <v>32</v>
-      </c>
-      <c r="T2">
-        <v>2.46</v>
-      </c>
-      <c r="U2">
-        <v>1.54</v>
-      </c>
-      <c r="V2">
-        <v>1.06</v>
-      </c>
       <c r="W2">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2">
-        <v>2.18</v>
+        <v>970</v>
       </c>
       <c r="AC2">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
         <v>970</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AG2">
         <v>970</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ2">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP2">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AQ2">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="AR2">
-        <v>5.9</v>
+        <v>2.08</v>
       </c>
       <c r="AS2">
-        <v>5.9</v>
+        <v>2.06</v>
       </c>
       <c r="AT2">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="AU2">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="AV2">
-        <v>16.5</v>
+        <v>5.3</v>
       </c>
       <c r="AW2">
-        <v>100</v>
+        <v>2.08</v>
       </c>
       <c r="AX2">
+        <v>5.7</v>
+      </c>
+      <c r="AY2">
+        <v>5.1</v>
+      </c>
+      <c r="AZ2">
+        <v>4.6</v>
+      </c>
+      <c r="BA2">
+        <v>2.1</v>
+      </c>
+      <c r="BB2">
+        <v>2.08</v>
+      </c>
+      <c r="BC2">
+        <v>2</v>
+      </c>
+      <c r="BD2">
+        <v>2.08</v>
+      </c>
+      <c r="BE2">
+        <v>2.12</v>
+      </c>
+      <c r="BF2">
+        <v>2.02</v>
+      </c>
+      <c r="BG2">
+        <v>2.12</v>
+      </c>
+      <c r="BH2">
+        <v>3.55</v>
+      </c>
+      <c r="BI2">
+        <v>2.48</v>
+      </c>
+      <c r="BJ2">
+        <v>12</v>
+      </c>
+      <c r="BK2">
+        <v>3.45</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>4.7</v>
+      </c>
+      <c r="BN2">
+        <v>6.4</v>
+      </c>
+      <c r="BO2">
+        <v>4.1</v>
+      </c>
+      <c r="BP2">
+        <v>25</v>
+      </c>
+      <c r="BQ2">
+        <v>4</v>
+      </c>
+      <c r="BR2">
+        <v>46</v>
+      </c>
+      <c r="BS2">
+        <v>4.3</v>
+      </c>
+      <c r="BT2">
         <v>7.4</v>
       </c>
-      <c r="AY2">
-        <v>14.5</v>
-      </c>
-      <c r="AZ2">
+      <c r="BU2">
+        <v>4.7</v>
+      </c>
+      <c r="BV2">
+        <v>34</v>
+      </c>
+      <c r="BW2">
+        <v>4.2</v>
+      </c>
+      <c r="BX2">
         <v>55</v>
       </c>
-      <c r="BA2">
-        <v>80</v>
-      </c>
-      <c r="BB2">
-        <v>55</v>
-      </c>
-      <c r="BC2">
-        <v>100</v>
-      </c>
-      <c r="BD2">
-        <v>80</v>
-      </c>
-      <c r="BE2">
-        <v>70</v>
-      </c>
-      <c r="BF2">
-        <v>5.9</v>
-      </c>
-      <c r="BG2">
-        <v>140</v>
-      </c>
-      <c r="BH2">
-        <v>0</v>
-      </c>
-      <c r="BI2">
-        <v>0</v>
-      </c>
-      <c r="BJ2">
-        <v>0</v>
-      </c>
-      <c r="BK2">
-        <v>0</v>
-      </c>
-      <c r="BL2">
-        <v>0</v>
-      </c>
-      <c r="BM2">
-        <v>0</v>
-      </c>
-      <c r="BN2">
-        <v>0</v>
-      </c>
-      <c r="BO2">
-        <v>0</v>
-      </c>
-      <c r="BP2">
-        <v>0</v>
-      </c>
-      <c r="BQ2">
-        <v>0</v>
-      </c>
-      <c r="BR2">
-        <v>0</v>
-      </c>
-      <c r="BS2">
-        <v>0</v>
-      </c>
-      <c r="BT2">
-        <v>0</v>
-      </c>
-      <c r="BU2">
-        <v>0</v>
-      </c>
-      <c r="BV2">
-        <v>0</v>
-      </c>
-      <c r="BW2">
-        <v>0</v>
-      </c>
-      <c r="BX2">
-        <v>0</v>
-      </c>
       <c r="BY2">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1192,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1200,241 +1188,241 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F3">
-        <v>2.38</v>
+        <v>1.71</v>
       </c>
       <c r="G3">
-        <v>2.66</v>
+        <v>4.8</v>
       </c>
       <c r="H3">
-        <v>3.1</v>
+        <v>2.54</v>
       </c>
       <c r="I3">
-        <v>3.55</v>
+        <v>17</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="L3">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.44</v>
+      </c>
+      <c r="O3">
+        <v>1.58</v>
+      </c>
+      <c r="P3">
+        <v>1.45</v>
+      </c>
+      <c r="Q3">
+        <v>1.6</v>
+      </c>
+      <c r="R3">
+        <v>1.13</v>
+      </c>
+      <c r="S3">
+        <v>1.6</v>
+      </c>
+      <c r="T3">
+        <v>1.11</v>
+      </c>
+      <c r="U3">
+        <v>1.11</v>
+      </c>
+      <c r="V3">
+        <v>1.21</v>
+      </c>
+      <c r="W3">
+        <v>1.47</v>
+      </c>
+      <c r="X3">
+        <v>970</v>
+      </c>
+      <c r="Y3">
+        <v>950</v>
+      </c>
+      <c r="Z3">
+        <v>500</v>
+      </c>
+      <c r="AA3">
+        <v>900</v>
+      </c>
+      <c r="AB3">
+        <v>950</v>
+      </c>
+      <c r="AC3">
+        <v>950</v>
+      </c>
+      <c r="AD3">
+        <v>950</v>
+      </c>
+      <c r="AE3">
+        <v>500</v>
+      </c>
+      <c r="AF3">
+        <v>500</v>
+      </c>
+      <c r="AG3">
+        <v>950</v>
+      </c>
+      <c r="AH3">
+        <v>950</v>
+      </c>
+      <c r="AI3">
+        <v>500</v>
+      </c>
+      <c r="AJ3">
+        <v>900</v>
+      </c>
+      <c r="AK3">
+        <v>500</v>
+      </c>
+      <c r="AL3">
+        <v>500</v>
+      </c>
+      <c r="AM3">
+        <v>500</v>
+      </c>
+      <c r="AN3">
+        <v>500</v>
+      </c>
+      <c r="AO3">
+        <v>500</v>
+      </c>
+      <c r="AP3">
+        <v>1.05</v>
+      </c>
+      <c r="AQ3">
+        <v>1.12</v>
+      </c>
+      <c r="AR3">
+        <v>1.12</v>
+      </c>
+      <c r="AS3">
+        <v>1.12</v>
+      </c>
+      <c r="AT3">
+        <v>1.12</v>
+      </c>
+      <c r="AU3">
         <v>1.09</v>
       </c>
-      <c r="N3">
-        <v>2.96</v>
-      </c>
-      <c r="O3">
-        <v>1.39</v>
-      </c>
-      <c r="P3">
-        <v>1.68</v>
-      </c>
-      <c r="Q3">
-        <v>2.14</v>
-      </c>
-      <c r="R3">
-        <v>1.25</v>
-      </c>
-      <c r="S3">
-        <v>3.8</v>
-      </c>
-      <c r="T3">
-        <v>1.94</v>
-      </c>
-      <c r="U3">
-        <v>1.93</v>
-      </c>
-      <c r="V3">
-        <v>1.39</v>
-      </c>
-      <c r="W3">
-        <v>1.6</v>
-      </c>
-      <c r="X3">
-        <v>12</v>
-      </c>
-      <c r="Y3">
-        <v>11.5</v>
-      </c>
-      <c r="Z3">
-        <v>23</v>
-      </c>
-      <c r="AA3">
-        <v>65</v>
-      </c>
-      <c r="AB3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC3">
-        <v>7.8</v>
-      </c>
-      <c r="AD3">
-        <v>15</v>
-      </c>
-      <c r="AE3">
-        <v>46</v>
-      </c>
-      <c r="AF3">
-        <v>17</v>
-      </c>
-      <c r="AG3">
-        <v>13</v>
-      </c>
-      <c r="AH3">
-        <v>20</v>
-      </c>
-      <c r="AI3">
-        <v>100</v>
-      </c>
-      <c r="AJ3">
-        <v>42</v>
-      </c>
-      <c r="AK3">
-        <v>34</v>
-      </c>
-      <c r="AL3">
-        <v>55</v>
-      </c>
-      <c r="AM3">
-        <v>580</v>
-      </c>
-      <c r="AN3">
-        <v>32</v>
-      </c>
-      <c r="AO3">
-        <v>48</v>
-      </c>
-      <c r="AP3">
-        <v>7.4</v>
-      </c>
-      <c r="AQ3">
-        <v>8.4</v>
-      </c>
-      <c r="AR3">
-        <v>15</v>
-      </c>
-      <c r="AS3">
-        <v>26</v>
-      </c>
-      <c r="AT3">
-        <v>6.8</v>
-      </c>
-      <c r="AU3">
-        <v>5.7</v>
-      </c>
       <c r="AV3">
-        <v>10.5</v>
+        <v>1.12</v>
       </c>
       <c r="AW3">
-        <v>16.5</v>
+        <v>1.12</v>
       </c>
       <c r="AX3">
-        <v>11.5</v>
+        <v>1.12</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="AZ3">
-        <v>14.5</v>
+        <v>1.12</v>
       </c>
       <c r="BA3">
-        <v>24</v>
+        <v>1.12</v>
       </c>
       <c r="BB3">
-        <v>17</v>
+        <v>1.12</v>
       </c>
       <c r="BC3">
-        <v>13</v>
+        <v>1.12</v>
       </c>
       <c r="BD3">
-        <v>20</v>
+        <v>1.12</v>
       </c>
       <c r="BE3">
-        <v>50</v>
+        <v>1.12</v>
       </c>
       <c r="BF3">
-        <v>12</v>
+        <v>1.55</v>
       </c>
       <c r="BG3">
-        <v>16.5</v>
+        <v>1.55</v>
       </c>
       <c r="BH3">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.48</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW3">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1442,241 +1430,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>108</v>
+      </c>
+      <c r="F4">
+        <v>4.2</v>
+      </c>
+      <c r="G4">
+        <v>4.4</v>
+      </c>
+      <c r="H4">
+        <v>1.75</v>
+      </c>
+      <c r="I4">
+        <v>1.81</v>
+      </c>
+      <c r="J4">
+        <v>4.7</v>
+      </c>
+      <c r="K4">
+        <v>5.1</v>
+      </c>
+      <c r="L4">
+        <v>1.21</v>
+      </c>
+      <c r="M4">
+        <v>1.02</v>
+      </c>
+      <c r="N4">
+        <v>8.4</v>
+      </c>
+      <c r="O4">
+        <v>1.11</v>
+      </c>
+      <c r="P4">
+        <v>3.5</v>
+      </c>
+      <c r="Q4">
+        <v>1.37</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4">
+        <v>1.92</v>
+      </c>
+      <c r="T4">
+        <v>1.43</v>
+      </c>
+      <c r="U4">
+        <v>3</v>
+      </c>
+      <c r="V4">
+        <v>2.22</v>
+      </c>
+      <c r="W4">
+        <v>1.29</v>
+      </c>
+      <c r="X4">
+        <v>120</v>
+      </c>
+      <c r="Y4">
+        <v>20</v>
+      </c>
+      <c r="Z4">
+        <v>18.5</v>
+      </c>
+      <c r="AA4">
+        <v>23</v>
+      </c>
+      <c r="AB4">
+        <v>34</v>
+      </c>
+      <c r="AC4">
+        <v>14</v>
+      </c>
+      <c r="AD4">
+        <v>12.5</v>
+      </c>
+      <c r="AE4">
+        <v>17</v>
+      </c>
+      <c r="AF4">
         <v>100</v>
       </c>
-      <c r="E4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F4">
-        <v>2.24</v>
-      </c>
-      <c r="G4">
-        <v>2.74</v>
-      </c>
-      <c r="H4">
-        <v>3.15</v>
-      </c>
-      <c r="I4">
-        <v>5.7</v>
-      </c>
-      <c r="J4">
-        <v>2.78</v>
-      </c>
-      <c r="K4">
-        <v>3.75</v>
-      </c>
-      <c r="L4">
-        <v>1.01</v>
-      </c>
-      <c r="M4">
-        <v>1.01</v>
-      </c>
-      <c r="N4">
-        <v>1.5</v>
-      </c>
-      <c r="O4">
-        <v>1.59</v>
-      </c>
-      <c r="P4">
-        <v>1.4</v>
-      </c>
-      <c r="Q4">
-        <v>1.59</v>
-      </c>
-      <c r="R4">
-        <v>1.13</v>
-      </c>
-      <c r="S4">
-        <v>1.05</v>
-      </c>
-      <c r="T4">
-        <v>1.11</v>
-      </c>
-      <c r="U4">
-        <v>1.11</v>
-      </c>
-      <c r="V4">
-        <v>1.29</v>
-      </c>
-      <c r="W4">
-        <v>1.58</v>
-      </c>
-      <c r="X4">
-        <v>970</v>
-      </c>
-      <c r="Y4">
-        <v>950</v>
-      </c>
-      <c r="Z4">
+      <c r="AG4">
+        <v>19.5</v>
+      </c>
+      <c r="AH4">
+        <v>16</v>
+      </c>
+      <c r="AI4">
+        <v>22</v>
+      </c>
+      <c r="AJ4">
         <v>500</v>
       </c>
-      <c r="AA4">
-        <v>900</v>
-      </c>
-      <c r="AB4">
-        <v>950</v>
-      </c>
-      <c r="AC4">
-        <v>950</v>
-      </c>
-      <c r="AD4">
-        <v>950</v>
-      </c>
-      <c r="AE4">
-        <v>500</v>
-      </c>
-      <c r="AF4">
-        <v>500</v>
-      </c>
-      <c r="AG4">
-        <v>950</v>
-      </c>
-      <c r="AH4">
-        <v>950</v>
-      </c>
-      <c r="AI4">
-        <v>500</v>
-      </c>
-      <c r="AJ4">
-        <v>900</v>
-      </c>
       <c r="AK4">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AL4">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM4">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AN4">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AO4">
-        <v>500</v>
+        <v>6.8</v>
       </c>
       <c r="AP4">
-        <v>1.05</v>
+        <v>30</v>
       </c>
       <c r="AQ4">
-        <v>1.12</v>
+        <v>16.5</v>
       </c>
       <c r="AR4">
-        <v>1.12</v>
+        <v>15</v>
       </c>
       <c r="AS4">
-        <v>1.12</v>
+        <v>18.5</v>
       </c>
       <c r="AT4">
-        <v>1.12</v>
+        <v>26</v>
       </c>
       <c r="AU4">
-        <v>1.09</v>
+        <v>11</v>
       </c>
       <c r="AV4">
-        <v>1.12</v>
+        <v>10</v>
       </c>
       <c r="AW4">
-        <v>1.12</v>
+        <v>13.5</v>
       </c>
       <c r="AX4">
-        <v>1.12</v>
+        <v>34</v>
       </c>
       <c r="AY4">
-        <v>1.12</v>
+        <v>16</v>
       </c>
       <c r="AZ4">
-        <v>1.12</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>1.12</v>
+        <v>18</v>
       </c>
       <c r="BB4">
-        <v>1.12</v>
+        <v>65</v>
       </c>
       <c r="BC4">
-        <v>1.12</v>
+        <v>32</v>
       </c>
       <c r="BD4">
-        <v>1.12</v>
+        <v>28</v>
       </c>
       <c r="BE4">
-        <v>1.12</v>
+        <v>34</v>
       </c>
       <c r="BF4">
-        <v>1.55</v>
+        <v>17.5</v>
       </c>
       <c r="BG4">
-        <v>1.55</v>
+        <v>4.9</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="CB4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1684,241 +1672,241 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F5">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="G5">
+        <v>1.95</v>
+      </c>
+      <c r="H5">
+        <v>3.5</v>
+      </c>
+      <c r="I5">
+        <v>4.1</v>
+      </c>
+      <c r="J5">
         <v>4.4</v>
       </c>
-      <c r="H5">
-        <v>1.73</v>
-      </c>
-      <c r="I5">
-        <v>1.85</v>
-      </c>
-      <c r="J5">
-        <v>4.7</v>
-      </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L5">
+        <v>1.21</v>
+      </c>
+      <c r="M5">
         <v>1.01</v>
       </c>
-      <c r="M5">
-        <v>1.02</v>
-      </c>
       <c r="N5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="O5">
         <v>1.11</v>
       </c>
       <c r="P5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q5">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R5">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="S5">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="T5">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U5">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="V5">
-        <v>2.16</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.29</v>
+        <v>2.04</v>
       </c>
       <c r="X5">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="Y5">
+        <v>34</v>
+      </c>
+      <c r="Z5">
+        <v>100</v>
+      </c>
+      <c r="AA5">
+        <v>500</v>
+      </c>
+      <c r="AB5">
         <v>21</v>
       </c>
-      <c r="Z5">
-        <v>18.5</v>
-      </c>
-      <c r="AA5">
-        <v>27</v>
-      </c>
-      <c r="AB5">
+      <c r="AC5">
+        <v>14.5</v>
+      </c>
+      <c r="AD5">
+        <v>19.5</v>
+      </c>
+      <c r="AE5">
         <v>85</v>
       </c>
-      <c r="AC5">
-        <v>16.5</v>
-      </c>
-      <c r="AD5">
-        <v>12.5</v>
-      </c>
-      <c r="AE5">
-        <v>17</v>
-      </c>
       <c r="AF5">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="AG5">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="AH5">
         <v>16.5</v>
       </c>
       <c r="AI5">
+        <v>80</v>
+      </c>
+      <c r="AJ5">
+        <v>26</v>
+      </c>
+      <c r="AK5">
+        <v>18</v>
+      </c>
+      <c r="AL5">
         <v>23</v>
       </c>
-      <c r="AJ5">
+      <c r="AM5">
         <v>500</v>
       </c>
-      <c r="AK5">
-        <v>48</v>
-      </c>
-      <c r="AL5">
-        <v>42</v>
-      </c>
-      <c r="AM5">
-        <v>55</v>
-      </c>
       <c r="AN5">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="AO5">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="AP5">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ5">
-        <v>16.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR5">
+        <v>6.4</v>
+      </c>
+      <c r="AS5">
+        <v>7</v>
+      </c>
+      <c r="AT5">
+        <v>5.6</v>
+      </c>
+      <c r="AU5">
+        <v>5</v>
+      </c>
+      <c r="AV5">
+        <v>5.5</v>
+      </c>
+      <c r="AW5">
+        <v>6.4</v>
+      </c>
+      <c r="AX5">
+        <v>5.6</v>
+      </c>
+      <c r="AY5">
+        <v>4.8</v>
+      </c>
+      <c r="AZ5">
+        <v>5.2</v>
+      </c>
+      <c r="BA5">
+        <v>6.2</v>
+      </c>
+      <c r="BB5">
+        <v>5.9</v>
+      </c>
+      <c r="BC5">
+        <v>5.3</v>
+      </c>
+      <c r="BD5">
+        <v>5.7</v>
+      </c>
+      <c r="BE5">
+        <v>6.4</v>
+      </c>
+      <c r="BF5">
+        <v>3.4</v>
+      </c>
+      <c r="BG5">
         <v>15</v>
       </c>
-      <c r="AS5">
+      <c r="BH5">
+        <v>6.2</v>
+      </c>
+      <c r="BI5">
+        <v>4.5</v>
+      </c>
+      <c r="BJ5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK5">
+        <v>4.2</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>7</v>
+      </c>
+      <c r="BN5">
+        <v>6</v>
+      </c>
+      <c r="BO5">
+        <v>4.5</v>
+      </c>
+      <c r="BP5">
+        <v>12.5</v>
+      </c>
+      <c r="BQ5">
+        <v>4.9</v>
+      </c>
+      <c r="BR5">
         <v>18.5</v>
       </c>
-      <c r="AT5">
-        <v>23</v>
-      </c>
-      <c r="AU5">
-        <v>11</v>
-      </c>
-      <c r="AV5">
-        <v>10</v>
-      </c>
-      <c r="AW5">
-        <v>13.5</v>
-      </c>
-      <c r="AX5">
-        <v>34</v>
-      </c>
-      <c r="AY5">
-        <v>16</v>
-      </c>
-      <c r="AZ5">
-        <v>13</v>
-      </c>
-      <c r="BA5">
-        <v>18</v>
-      </c>
-      <c r="BB5">
+      <c r="BS5">
         <v>5.6</v>
       </c>
-      <c r="BC5">
-        <v>28</v>
-      </c>
-      <c r="BD5">
-        <v>24</v>
-      </c>
-      <c r="BE5">
-        <v>32</v>
-      </c>
-      <c r="BF5">
-        <v>15</v>
-      </c>
-      <c r="BG5">
-        <v>4.8</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.04</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.04</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.04</v>
-      </c>
-      <c r="BN5">
-        <v>1000</v>
-      </c>
-      <c r="BO5">
-        <v>1.04</v>
-      </c>
-      <c r="BP5">
-        <v>1000</v>
-      </c>
-      <c r="BQ5">
-        <v>1.04</v>
-      </c>
-      <c r="BR5">
-        <v>1000</v>
-      </c>
-      <c r="BS5">
-        <v>1.04</v>
-      </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1926,130 +1914,130 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F6">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="G6">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="H6">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
-        <v>4.4</v>
+        <v>11</v>
       </c>
       <c r="J6">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="P6">
-        <v>3.3</v>
+        <v>1.89</v>
       </c>
       <c r="Q6">
+        <v>1.99</v>
+      </c>
+      <c r="R6">
         <v>1.33</v>
       </c>
-      <c r="R6">
-        <v>1.94</v>
-      </c>
       <c r="S6">
-        <v>1.81</v>
+        <v>3.55</v>
       </c>
       <c r="T6">
-        <v>1.39</v>
+        <v>2.12</v>
       </c>
       <c r="U6">
-        <v>2.96</v>
+        <v>1.68</v>
       </c>
       <c r="V6">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="W6">
-        <v>2.06</v>
+        <v>2.74</v>
       </c>
       <c r="X6">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="Y6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z6">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AA6">
         <v>500</v>
       </c>
       <c r="AB6">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="AC6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD6">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AF6">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH6">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AI6">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="AJ6">
-        <v>26</v>
+        <v>13.5</v>
       </c>
       <c r="AK6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL6">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AM6">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AN6">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AO6">
-        <v>19.5</v>
+        <v>390</v>
       </c>
       <c r="AP6">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="AQ6">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR6">
         <v>6.6</v>
@@ -2058,109 +2046,109 @@
         <v>7</v>
       </c>
       <c r="AT6">
-        <v>15.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="AW6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX6">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB6">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="BC6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD6">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BE6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF6">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BG6">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="BI6">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="BJ6">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="BN6">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="BO6">
-        <v>4.5</v>
+        <v>1.84</v>
       </c>
       <c r="BP6">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ6">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BR6">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>13</v>
+        <v>3.45</v>
       </c>
       <c r="BT6">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>6.4</v>
+        <v>3.45</v>
       </c>
       <c r="BV6">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="BX6">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>6.2</v>
+        <v>3.35</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="CB6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2168,483 +2156,483 @@
         <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F7">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="G7">
-        <v>1.58</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="I7">
+        <v>4.3</v>
+      </c>
+      <c r="J7">
+        <v>3.15</v>
+      </c>
+      <c r="K7">
+        <v>3.2</v>
+      </c>
+      <c r="L7">
+        <v>1.53</v>
+      </c>
+      <c r="M7">
+        <v>1.12</v>
+      </c>
+      <c r="N7">
+        <v>2.92</v>
+      </c>
+      <c r="O7">
+        <v>1.49</v>
+      </c>
+      <c r="P7">
+        <v>1.6</v>
+      </c>
+      <c r="Q7">
+        <v>2.52</v>
+      </c>
+      <c r="R7">
+        <v>1.22</v>
+      </c>
+      <c r="S7">
+        <v>5</v>
+      </c>
+      <c r="T7">
+        <v>2.06</v>
+      </c>
+      <c r="U7">
+        <v>1.8</v>
+      </c>
+      <c r="V7">
+        <v>1.3</v>
+      </c>
+      <c r="W7">
+        <v>1.79</v>
+      </c>
+      <c r="X7">
+        <v>10</v>
+      </c>
+      <c r="Y7">
+        <v>12</v>
+      </c>
+      <c r="Z7">
+        <v>34</v>
+      </c>
+      <c r="AA7">
+        <v>500</v>
+      </c>
+      <c r="AB7">
+        <v>7.8</v>
+      </c>
+      <c r="AC7">
+        <v>7.8</v>
+      </c>
+      <c r="AD7">
+        <v>17.5</v>
+      </c>
+      <c r="AE7">
+        <v>160</v>
+      </c>
+      <c r="AF7">
+        <v>13.5</v>
+      </c>
+      <c r="AG7">
+        <v>12</v>
+      </c>
+      <c r="AH7">
+        <v>24</v>
+      </c>
+      <c r="AI7">
+        <v>380</v>
+      </c>
+      <c r="AJ7">
+        <v>40</v>
+      </c>
+      <c r="AK7">
+        <v>32</v>
+      </c>
+      <c r="AL7">
+        <v>130</v>
+      </c>
+      <c r="AM7">
+        <v>580</v>
+      </c>
+      <c r="AN7">
+        <v>60</v>
+      </c>
+      <c r="AO7">
+        <v>500</v>
+      </c>
+      <c r="AP7">
+        <v>7.4</v>
+      </c>
+      <c r="AQ7">
+        <v>9.4</v>
+      </c>
+      <c r="AR7">
+        <v>16</v>
+      </c>
+      <c r="AS7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT7">
+        <v>6.4</v>
+      </c>
+      <c r="AU7">
+        <v>6.4</v>
+      </c>
+      <c r="AV7">
+        <v>14</v>
+      </c>
+      <c r="AW7">
+        <v>23</v>
+      </c>
+      <c r="AX7">
+        <v>11</v>
+      </c>
+      <c r="AY7">
         <v>9.800000000000001</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
-        <v>4.8</v>
-      </c>
-      <c r="L7">
-        <v>1.27</v>
-      </c>
-      <c r="M7">
-        <v>1.07</v>
-      </c>
-      <c r="N7">
-        <v>3.4</v>
-      </c>
-      <c r="O7">
-        <v>1.33</v>
-      </c>
-      <c r="P7">
-        <v>1.85</v>
-      </c>
-      <c r="Q7">
-        <v>1.96</v>
-      </c>
-      <c r="R7">
-        <v>1.32</v>
-      </c>
-      <c r="S7">
-        <v>3.5</v>
-      </c>
-      <c r="T7">
-        <v>2.08</v>
-      </c>
-      <c r="U7">
-        <v>1.73</v>
-      </c>
-      <c r="V7">
-        <v>1.11</v>
-      </c>
-      <c r="W7">
-        <v>2.74</v>
-      </c>
-      <c r="X7">
-        <v>15</v>
-      </c>
-      <c r="Y7">
-        <v>25</v>
-      </c>
-      <c r="Z7">
-        <v>95</v>
-      </c>
-      <c r="AA7">
-        <v>390</v>
-      </c>
-      <c r="AB7">
-        <v>7.4</v>
-      </c>
-      <c r="AC7">
-        <v>10.5</v>
-      </c>
-      <c r="AD7">
-        <v>34</v>
-      </c>
-      <c r="AE7">
-        <v>190</v>
-      </c>
-      <c r="AF7">
-        <v>8.6</v>
-      </c>
-      <c r="AG7">
-        <v>11</v>
-      </c>
-      <c r="AH7">
-        <v>28</v>
-      </c>
-      <c r="AI7">
-        <v>170</v>
-      </c>
-      <c r="AJ7">
-        <v>14</v>
-      </c>
-      <c r="AK7">
-        <v>18.5</v>
-      </c>
-      <c r="AL7">
-        <v>48</v>
-      </c>
-      <c r="AM7">
-        <v>220</v>
-      </c>
-      <c r="AN7">
-        <v>9.6</v>
-      </c>
-      <c r="AO7">
-        <v>300</v>
-      </c>
-      <c r="AP7">
-        <v>10.5</v>
-      </c>
-      <c r="AQ7">
-        <v>6.6</v>
-      </c>
-      <c r="AR7">
-        <v>8.4</v>
-      </c>
-      <c r="AS7">
-        <v>9</v>
-      </c>
-      <c r="AT7">
-        <v>6</v>
-      </c>
-      <c r="AU7">
-        <v>4.9</v>
-      </c>
-      <c r="AV7">
-        <v>7.2</v>
-      </c>
-      <c r="AW7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX7">
-        <v>7</v>
-      </c>
-      <c r="AY7">
-        <v>5</v>
       </c>
       <c r="AZ7">
         <v>19</v>
       </c>
       <c r="BA7">
+        <v>32</v>
+      </c>
+      <c r="BB7">
+        <v>22</v>
+      </c>
+      <c r="BC7">
+        <v>21</v>
+      </c>
+      <c r="BD7">
+        <v>23</v>
+      </c>
+      <c r="BE7">
+        <v>9</v>
+      </c>
+      <c r="BF7">
+        <v>21</v>
+      </c>
+      <c r="BG7">
+        <v>12.5</v>
+      </c>
+      <c r="BH7">
+        <v>3.15</v>
+      </c>
+      <c r="BI7">
+        <v>2.56</v>
+      </c>
+      <c r="BJ7">
+        <v>11.5</v>
+      </c>
+      <c r="BK7">
+        <v>5</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
         <v>8.6</v>
       </c>
-      <c r="BB7">
-        <v>5.5</v>
-      </c>
-      <c r="BC7">
+      <c r="BN7">
+        <v>4.9</v>
+      </c>
+      <c r="BO7">
+        <v>4.1</v>
+      </c>
+      <c r="BP7">
+        <v>18.5</v>
+      </c>
+      <c r="BQ7">
         <v>6</v>
       </c>
-      <c r="BD7">
-        <v>7.6</v>
-      </c>
-      <c r="BE7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF7">
-        <v>7</v>
-      </c>
-      <c r="BG7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH7">
-        <v>1000</v>
-      </c>
-      <c r="BI7">
-        <v>1.04</v>
-      </c>
-      <c r="BJ7">
-        <v>1000</v>
-      </c>
-      <c r="BK7">
-        <v>1.04</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>1.04</v>
-      </c>
-      <c r="BN7">
-        <v>1000</v>
-      </c>
-      <c r="BO7">
-        <v>1.04</v>
-      </c>
-      <c r="BP7">
-        <v>1000</v>
-      </c>
-      <c r="BQ7">
-        <v>1.04</v>
-      </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
         <v>86</v>
       </c>
-      <c r="B8" t="s">
-        <v>87</v>
-      </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>2.76</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>3.95</v>
+        <v>2.44</v>
       </c>
       <c r="I8">
+        <v>2.64</v>
+      </c>
+      <c r="J8">
+        <v>3.7</v>
+      </c>
+      <c r="K8">
         <v>4.3</v>
       </c>
-      <c r="J8">
-        <v>3.1</v>
-      </c>
-      <c r="K8">
-        <v>3.2</v>
-      </c>
       <c r="L8">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="N8">
-        <v>2.74</v>
+        <v>5.3</v>
       </c>
       <c r="O8">
-        <v>1.48</v>
+        <v>1.19</v>
       </c>
       <c r="P8">
-        <v>1.58</v>
+        <v>2.44</v>
       </c>
       <c r="Q8">
-        <v>2.42</v>
+        <v>1.6</v>
       </c>
       <c r="R8">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="S8">
-        <v>4.9</v>
+        <v>2.54</v>
       </c>
       <c r="T8">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="U8">
-        <v>1.8</v>
+        <v>2.52</v>
       </c>
       <c r="V8">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="W8">
-        <v>1.76</v>
+        <v>1.51</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AA8">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AB8">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="AC8">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AD8">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>160</v>
+        <v>24</v>
       </c>
       <c r="AF8">
+        <v>25</v>
+      </c>
+      <c r="AG8">
+        <v>14.5</v>
+      </c>
+      <c r="AH8">
+        <v>16</v>
+      </c>
+      <c r="AI8">
+        <v>32</v>
+      </c>
+      <c r="AJ8">
+        <v>200</v>
+      </c>
+      <c r="AK8">
+        <v>60</v>
+      </c>
+      <c r="AL8">
+        <v>60</v>
+      </c>
+      <c r="AM8">
+        <v>200</v>
+      </c>
+      <c r="AN8">
+        <v>17.5</v>
+      </c>
+      <c r="AO8">
         <v>13.5</v>
       </c>
-      <c r="AG8">
-        <v>12</v>
-      </c>
-      <c r="AH8">
-        <v>24</v>
-      </c>
-      <c r="AI8">
-        <v>500</v>
-      </c>
-      <c r="AJ8">
-        <v>40</v>
-      </c>
-      <c r="AK8">
-        <v>32</v>
-      </c>
-      <c r="AL8">
-        <v>130</v>
-      </c>
-      <c r="AM8">
-        <v>580</v>
-      </c>
-      <c r="AN8">
-        <v>60</v>
-      </c>
-      <c r="AO8">
-        <v>500</v>
-      </c>
       <c r="AP8">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AR8">
         <v>16</v>
       </c>
       <c r="AS8">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="AT8">
+        <v>5.6</v>
+      </c>
+      <c r="AU8">
+        <v>5.1</v>
+      </c>
+      <c r="AV8">
+        <v>10</v>
+      </c>
+      <c r="AW8">
+        <v>6</v>
+      </c>
+      <c r="AX8">
+        <v>6</v>
+      </c>
+      <c r="AY8">
+        <v>11</v>
+      </c>
+      <c r="AZ8">
+        <v>12</v>
+      </c>
+      <c r="BA8">
+        <v>14.5</v>
+      </c>
+      <c r="BB8">
+        <v>6.8</v>
+      </c>
+      <c r="BC8">
+        <v>13</v>
+      </c>
+      <c r="BD8">
+        <v>6.6</v>
+      </c>
+      <c r="BE8">
+        <v>7.2</v>
+      </c>
+      <c r="BF8">
+        <v>13.5</v>
+      </c>
+      <c r="BG8">
+        <v>5</v>
+      </c>
+      <c r="BH8">
+        <v>4.7</v>
+      </c>
+      <c r="BI8">
+        <v>3.55</v>
+      </c>
+      <c r="BJ8">
+        <v>9</v>
+      </c>
+      <c r="BK8">
+        <v>4.4</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>7.6</v>
+      </c>
+      <c r="BN8">
+        <v>6.8</v>
+      </c>
+      <c r="BO8">
+        <v>5</v>
+      </c>
+      <c r="BP8">
+        <v>21</v>
+      </c>
+      <c r="BQ8">
+        <v>6</v>
+      </c>
+      <c r="BR8">
+        <v>28</v>
+      </c>
+      <c r="BS8">
         <v>6.4</v>
       </c>
-      <c r="AU8">
+      <c r="BT8">
+        <v>6.2</v>
+      </c>
+      <c r="BU8">
+        <v>3.6</v>
+      </c>
+      <c r="BV8">
+        <v>17.5</v>
+      </c>
+      <c r="BW8">
+        <v>5.7</v>
+      </c>
+      <c r="BX8">
+        <v>25</v>
+      </c>
+      <c r="BY8">
         <v>6.4</v>
       </c>
-      <c r="AV8">
-        <v>14</v>
-      </c>
-      <c r="AW8">
-        <v>23</v>
-      </c>
-      <c r="AX8">
-        <v>11</v>
-      </c>
-      <c r="AY8">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ8">
-        <v>19</v>
-      </c>
-      <c r="BA8">
-        <v>32</v>
-      </c>
-      <c r="BB8">
-        <v>22</v>
-      </c>
-      <c r="BC8">
-        <v>21</v>
-      </c>
-      <c r="BD8">
-        <v>23</v>
-      </c>
-      <c r="BE8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF8">
-        <v>21</v>
-      </c>
-      <c r="BG8">
-        <v>12.5</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
-      <c r="BI8">
-        <v>1.04</v>
-      </c>
-      <c r="BJ8">
-        <v>1000</v>
-      </c>
-      <c r="BK8">
-        <v>1.04</v>
-      </c>
-      <c r="BL8">
-        <v>1000</v>
-      </c>
-      <c r="BM8">
-        <v>1.04</v>
-      </c>
-      <c r="BN8">
-        <v>1000</v>
-      </c>
-      <c r="BO8">
-        <v>1.04</v>
-      </c>
-      <c r="BP8">
-        <v>1000</v>
-      </c>
-      <c r="BQ8">
-        <v>1.04</v>
-      </c>
-      <c r="BR8">
-        <v>1000</v>
-      </c>
-      <c r="BS8">
-        <v>1.04</v>
-      </c>
-      <c r="BT8">
-        <v>1000</v>
-      </c>
-      <c r="BU8">
-        <v>1.04</v>
-      </c>
-      <c r="BV8">
-        <v>1000</v>
-      </c>
-      <c r="BW8">
-        <v>1.04</v>
-      </c>
-      <c r="BX8">
-        <v>1000</v>
-      </c>
-      <c r="BY8">
-        <v>1.04</v>
-      </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2652,178 +2640,178 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F9">
-        <v>2.74</v>
+        <v>2.04</v>
       </c>
       <c r="G9">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="H9">
-        <v>2.36</v>
+        <v>3.65</v>
       </c>
       <c r="I9">
-        <v>2.66</v>
+        <v>4.2</v>
       </c>
       <c r="J9">
+        <v>3.55</v>
+      </c>
+      <c r="K9">
         <v>3.7</v>
       </c>
-      <c r="K9">
-        <v>4.6</v>
-      </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M9">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="Q9">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="R9">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="S9">
-        <v>2.26</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="U9">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="V9">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="X9">
-        <v>50</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z9">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AA9">
-        <v>900</v>
+        <v>290</v>
       </c>
       <c r="AB9">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AC9">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AE9">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AF9">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AG9">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AJ9">
-        <v>200</v>
+        <v>27</v>
       </c>
       <c r="AK9">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AL9">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AO9">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AP9">
-        <v>3.45</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9">
-        <v>3.25</v>
+        <v>13</v>
       </c>
       <c r="AR9">
-        <v>3.35</v>
+        <v>18</v>
       </c>
       <c r="AS9">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT9">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AV9">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AW9">
-        <v>3.4</v>
+        <v>28</v>
       </c>
       <c r="AX9">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY9">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="AZ9">
-        <v>3.2</v>
+        <v>14</v>
       </c>
       <c r="BA9">
+        <v>32</v>
+      </c>
+      <c r="BB9">
         <v>21</v>
       </c>
-      <c r="BB9">
-        <v>3.65</v>
-      </c>
       <c r="BC9">
-        <v>3.55</v>
+        <v>16</v>
       </c>
       <c r="BD9">
-        <v>3.7</v>
+        <v>22</v>
       </c>
       <c r="BE9">
-        <v>3.85</v>
+        <v>9.4</v>
       </c>
       <c r="BF9">
-        <v>3.3</v>
+        <v>11.5</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -2880,255 +2868,255 @@
         <v>1.04</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F10">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="G10">
-        <v>2.22</v>
+        <v>1.59</v>
       </c>
       <c r="H10">
-        <v>2.88</v>
+        <v>7.6</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J10">
-        <v>2.96</v>
+        <v>3.85</v>
       </c>
       <c r="K10">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M10">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N10">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="Q10">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
         <v>1.32</v>
       </c>
       <c r="S10">
-        <v>2.58</v>
+        <v>3.6</v>
       </c>
       <c r="T10">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="U10">
-        <v>2.08</v>
+        <v>1.76</v>
       </c>
       <c r="V10">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="W10">
-        <v>1.82</v>
+        <v>2.68</v>
       </c>
       <c r="X10">
         <v>1000</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE10">
         <v>1000</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI10">
         <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM10">
         <v>1000</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO10">
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF10">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="CB10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3136,483 +3124,241 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F11">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="G11">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="H11">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="I11">
-        <v>9.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="L11">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11">
         <v>3.35</v>
       </c>
       <c r="O11">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="Q11">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="R11">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S11">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="T11">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="U11">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="V11">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>2.68</v>
+        <v>1.9</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y11">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB11">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC11">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF11">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AG11">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AH11">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ11">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AK11">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AL11">
         <v>46</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN11">
-        <v>9.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP11">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ11">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="AR11">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS11">
+        <v>4.9</v>
+      </c>
+      <c r="AT11">
+        <v>7</v>
+      </c>
+      <c r="AU11">
+        <v>6.8</v>
+      </c>
+      <c r="AV11">
+        <v>13</v>
+      </c>
+      <c r="AW11">
+        <v>4.7</v>
+      </c>
+      <c r="AX11">
+        <v>10</v>
+      </c>
+      <c r="AY11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11">
+        <v>17</v>
+      </c>
+      <c r="BA11">
+        <v>4.8</v>
+      </c>
+      <c r="BB11">
+        <v>21</v>
+      </c>
+      <c r="BC11">
+        <v>20</v>
+      </c>
+      <c r="BD11">
+        <v>4.6</v>
+      </c>
+      <c r="BE11">
+        <v>4.9</v>
+      </c>
+      <c r="BF11">
+        <v>15.5</v>
+      </c>
+      <c r="BG11">
+        <v>4.8</v>
+      </c>
+      <c r="BH11">
+        <v>3.6</v>
+      </c>
+      <c r="BI11">
+        <v>2.78</v>
+      </c>
+      <c r="BJ11">
+        <v>12.5</v>
+      </c>
+      <c r="BK11">
+        <v>3.5</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>4.8</v>
+      </c>
+      <c r="BN11">
+        <v>5.5</v>
+      </c>
+      <c r="BO11">
+        <v>3.6</v>
+      </c>
+      <c r="BP11">
+        <v>18.5</v>
+      </c>
+      <c r="BQ11">
+        <v>3.85</v>
+      </c>
+      <c r="BR11">
+        <v>40</v>
+      </c>
+      <c r="BS11">
         <v>4.3</v>
       </c>
-      <c r="AT11">
+      <c r="BT11">
+        <v>9</v>
+      </c>
+      <c r="BU11">
         <v>5.6</v>
       </c>
-      <c r="AU11">
-        <v>7.6</v>
-      </c>
-      <c r="AV11">
+      <c r="BV11">
+        <v>48</v>
+      </c>
+      <c r="BW11">
+        <v>4.4</v>
+      </c>
+      <c r="BX11">
+        <v>65</v>
+      </c>
+      <c r="BY11">
+        <v>4.5</v>
+      </c>
+      <c r="BZ11">
+        <v>38</v>
+      </c>
+      <c r="CA11">
         <v>4.3</v>
       </c>
-      <c r="AW11">
-        <v>4.3</v>
-      </c>
-      <c r="AX11">
-        <v>6.4</v>
-      </c>
-      <c r="AY11">
-        <v>7.8</v>
-      </c>
-      <c r="AZ11">
-        <v>20</v>
-      </c>
-      <c r="BA11">
-        <v>4.3</v>
-      </c>
-      <c r="BB11">
-        <v>10.5</v>
-      </c>
-      <c r="BC11">
-        <v>13.5</v>
-      </c>
-      <c r="BD11">
-        <v>3.95</v>
-      </c>
-      <c r="BE11">
-        <v>4.3</v>
-      </c>
-      <c r="BF11">
-        <v>7.4</v>
-      </c>
-      <c r="BG11">
-        <v>4.3</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.04</v>
-      </c>
-      <c r="BJ11">
-        <v>1000</v>
-      </c>
-      <c r="BK11">
-        <v>1.04</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.04</v>
-      </c>
-      <c r="BN11">
-        <v>1000</v>
-      </c>
-      <c r="BO11">
-        <v>1.04</v>
-      </c>
-      <c r="BP11">
-        <v>1000</v>
-      </c>
-      <c r="BQ11">
-        <v>1.04</v>
-      </c>
-      <c r="BR11">
-        <v>1000</v>
-      </c>
-      <c r="BS11">
-        <v>1.04</v>
-      </c>
-      <c r="BT11">
-        <v>1000</v>
-      </c>
-      <c r="BU11">
-        <v>1.04</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>1.04</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>1.04</v>
-      </c>
-      <c r="BZ11">
-        <v>1000</v>
-      </c>
-      <c r="CA11">
-        <v>1.04</v>
-      </c>
       <c r="CB11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:80">
-      <c r="A12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12">
-        <v>1.97</v>
-      </c>
-      <c r="G12">
-        <v>2.12</v>
-      </c>
-      <c r="H12">
-        <v>4</v>
-      </c>
-      <c r="I12">
-        <v>4.7</v>
-      </c>
-      <c r="J12">
-        <v>3.35</v>
-      </c>
-      <c r="K12">
-        <v>3.7</v>
-      </c>
-      <c r="L12">
-        <v>1.38</v>
-      </c>
-      <c r="M12">
-        <v>1.08</v>
-      </c>
-      <c r="N12">
-        <v>3.2</v>
-      </c>
-      <c r="O12">
-        <v>1.38</v>
-      </c>
-      <c r="P12">
-        <v>1.75</v>
-      </c>
-      <c r="Q12">
-        <v>2.12</v>
-      </c>
-      <c r="R12">
-        <v>1.28</v>
-      </c>
-      <c r="S12">
-        <v>3.95</v>
-      </c>
-      <c r="T12">
-        <v>1.9</v>
-      </c>
-      <c r="U12">
-        <v>1.94</v>
-      </c>
-      <c r="V12">
-        <v>1.27</v>
-      </c>
-      <c r="W12">
-        <v>1.89</v>
-      </c>
-      <c r="X12">
-        <v>14.5</v>
-      </c>
-      <c r="Y12">
-        <v>16.5</v>
-      </c>
-      <c r="Z12">
-        <v>38</v>
-      </c>
-      <c r="AA12">
-        <v>120</v>
-      </c>
-      <c r="AB12">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC12">
-        <v>8.4</v>
-      </c>
-      <c r="AD12">
-        <v>22</v>
-      </c>
-      <c r="AE12">
-        <v>65</v>
-      </c>
-      <c r="AF12">
-        <v>14.5</v>
-      </c>
-      <c r="AG12">
-        <v>13</v>
-      </c>
-      <c r="AH12">
-        <v>25</v>
-      </c>
-      <c r="AI12">
-        <v>85</v>
-      </c>
-      <c r="AJ12">
-        <v>30</v>
-      </c>
-      <c r="AK12">
-        <v>29</v>
-      </c>
-      <c r="AL12">
-        <v>46</v>
-      </c>
-      <c r="AM12">
-        <v>160</v>
-      </c>
-      <c r="AN12">
-        <v>22</v>
-      </c>
-      <c r="AO12">
-        <v>80</v>
-      </c>
-      <c r="AP12">
-        <v>10</v>
-      </c>
-      <c r="AQ12">
-        <v>10</v>
-      </c>
-      <c r="AR12">
-        <v>4.3</v>
-      </c>
-      <c r="AS12">
-        <v>4.7</v>
-      </c>
-      <c r="AT12">
-        <v>7</v>
-      </c>
-      <c r="AU12">
-        <v>6.8</v>
-      </c>
-      <c r="AV12">
-        <v>13</v>
-      </c>
-      <c r="AW12">
-        <v>4.5</v>
-      </c>
-      <c r="AX12">
-        <v>10</v>
-      </c>
-      <c r="AY12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ12">
-        <v>17</v>
-      </c>
-      <c r="BA12">
-        <v>4.6</v>
-      </c>
-      <c r="BB12">
-        <v>21</v>
-      </c>
-      <c r="BC12">
-        <v>20</v>
-      </c>
-      <c r="BD12">
-        <v>4.4</v>
-      </c>
-      <c r="BE12">
-        <v>4.7</v>
-      </c>
-      <c r="BF12">
-        <v>15.5</v>
-      </c>
-      <c r="BG12">
-        <v>4.6</v>
-      </c>
-      <c r="BH12">
-        <v>3.65</v>
-      </c>
-      <c r="BI12">
-        <v>2.54</v>
-      </c>
-      <c r="BJ12">
-        <v>12.5</v>
-      </c>
-      <c r="BK12">
-        <v>3.5</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>4.7</v>
-      </c>
-      <c r="BN12">
-        <v>5.5</v>
-      </c>
-      <c r="BO12">
-        <v>3.6</v>
-      </c>
-      <c r="BP12">
-        <v>18.5</v>
-      </c>
-      <c r="BQ12">
-        <v>3.85</v>
-      </c>
-      <c r="BR12">
-        <v>40</v>
-      </c>
-      <c r="BS12">
-        <v>4.3</v>
-      </c>
-      <c r="BT12">
-        <v>9</v>
-      </c>
-      <c r="BU12">
-        <v>5.6</v>
-      </c>
-      <c r="BV12">
-        <v>46</v>
-      </c>
-      <c r="BW12">
-        <v>4.4</v>
-      </c>
-      <c r="BX12">
-        <v>65</v>
-      </c>
-      <c r="BY12">
-        <v>4.5</v>
-      </c>
-      <c r="BZ12">
-        <v>38</v>
-      </c>
-      <c r="CA12">
-        <v>4.3</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -364,7 +364,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-04 02:41:30</t>
+    <t>2026-08-04 04:48:38</t>
   </si>
 </sst>
 </file>
@@ -958,10 +958,10 @@
         <v>106</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H2">
         <v>3.05</v>
@@ -973,19 +973,19 @@
         <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L2">
         <v>1.49</v>
       </c>
       <c r="M2">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
         <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P2">
         <v>1.71</v>
@@ -994,7 +994,7 @@
         <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S2">
         <v>4.2</v>
@@ -1003,7 +1003,7 @@
         <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
         <v>1.42</v>
@@ -1012,166 +1012,166 @@
         <v>1.6</v>
       </c>
       <c r="X2">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="Y2">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>900</v>
+        <v>65</v>
       </c>
       <c r="AB2">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD2">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AE2">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AF2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG2">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI2">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AJ2">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="AK2">
+        <v>34</v>
+      </c>
+      <c r="AL2">
         <v>75</v>
-      </c>
-      <c r="AL2">
-        <v>130</v>
       </c>
       <c r="AM2">
         <v>580</v>
       </c>
       <c r="AN2">
-        <v>600</v>
+        <v>32</v>
       </c>
       <c r="AO2">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AP2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>2.08</v>
+        <v>15.5</v>
       </c>
       <c r="AS2">
-        <v>2.06</v>
+        <v>38</v>
       </c>
       <c r="AT2">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AV2">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>2.08</v>
+        <v>27</v>
       </c>
       <c r="AX2">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
-        <v>4.6</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>2.1</v>
+        <v>38</v>
       </c>
       <c r="BB2">
-        <v>2.08</v>
+        <v>25</v>
       </c>
       <c r="BC2">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="BD2">
-        <v>2.08</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>2.12</v>
+        <v>60</v>
       </c>
       <c r="BF2">
-        <v>2.02</v>
+        <v>13.5</v>
       </c>
       <c r="BG2">
-        <v>2.12</v>
+        <v>19</v>
       </c>
       <c r="BH2">
         <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BN2">
+        <v>5.6</v>
+      </c>
+      <c r="BO2">
+        <v>4.2</v>
+      </c>
+      <c r="BP2">
+        <v>22</v>
+      </c>
+      <c r="BQ2">
+        <v>5.5</v>
+      </c>
+      <c r="BR2">
+        <v>40</v>
+      </c>
+      <c r="BS2">
+        <v>6.2</v>
+      </c>
+      <c r="BT2">
         <v>6.4</v>
       </c>
-      <c r="BO2">
-        <v>4.1</v>
-      </c>
-      <c r="BP2">
-        <v>25</v>
-      </c>
-      <c r="BQ2">
-        <v>4</v>
-      </c>
-      <c r="BR2">
-        <v>46</v>
-      </c>
-      <c r="BS2">
-        <v>4.3</v>
-      </c>
-      <c r="BT2">
-        <v>7.4</v>
-      </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="BV2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BW2">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BX2">
         <v>55</v>
       </c>
       <c r="BY2">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1200,103 +1200,103 @@
         <v>107</v>
       </c>
       <c r="F3">
+        <v>2.36</v>
+      </c>
+      <c r="G3">
+        <v>2.82</v>
+      </c>
+      <c r="H3">
+        <v>3.4</v>
+      </c>
+      <c r="I3">
+        <v>4.3</v>
+      </c>
+      <c r="J3">
+        <v>2.68</v>
+      </c>
+      <c r="K3">
+        <v>3.05</v>
+      </c>
+      <c r="L3">
         <v>1.71</v>
       </c>
-      <c r="G3">
-        <v>4.8</v>
-      </c>
-      <c r="H3">
-        <v>2.54</v>
-      </c>
-      <c r="I3">
-        <v>17</v>
-      </c>
-      <c r="J3">
-        <v>2.48</v>
-      </c>
-      <c r="K3">
-        <v>6.8</v>
-      </c>
-      <c r="L3">
-        <v>1.01</v>
-      </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="O3">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="P3">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="Q3">
-        <v>1.6</v>
+        <v>3.15</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
-        <v>1.6</v>
+        <v>7.2</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.56</v>
       </c>
       <c r="V3">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="Y3">
-        <v>950</v>
+        <v>9.6</v>
       </c>
       <c r="Z3">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="AC3">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AE3">
         <v>500</v>
       </c>
       <c r="AF3">
-        <v>500</v>
+        <v>16</v>
       </c>
       <c r="AG3">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI3">
         <v>500</v>
       </c>
       <c r="AJ3">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK3">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AL3">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AM3">
         <v>500</v>
@@ -1305,121 +1305,121 @@
         <v>500</v>
       </c>
       <c r="AO3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP3">
-        <v>1.05</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3">
-        <v>1.12</v>
+        <v>6.6</v>
       </c>
       <c r="AR3">
-        <v>1.12</v>
+        <v>5.5</v>
       </c>
       <c r="AS3">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="AT3">
-        <v>1.12</v>
+        <v>5</v>
       </c>
       <c r="AU3">
-        <v>1.09</v>
+        <v>5.8</v>
       </c>
       <c r="AV3">
-        <v>1.12</v>
+        <v>5.2</v>
       </c>
       <c r="AW3">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="AX3">
-        <v>1.12</v>
+        <v>4.8</v>
       </c>
       <c r="AY3">
-        <v>1.12</v>
+        <v>4.7</v>
       </c>
       <c r="AZ3">
-        <v>1.12</v>
+        <v>5.7</v>
       </c>
       <c r="BA3">
-        <v>1.12</v>
+        <v>6.6</v>
       </c>
       <c r="BB3">
-        <v>1.12</v>
+        <v>6</v>
       </c>
       <c r="BC3">
-        <v>1.12</v>
+        <v>6</v>
       </c>
       <c r="BD3">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="BE3">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>1.55</v>
+        <v>6.2</v>
       </c>
       <c r="BG3">
-        <v>1.55</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="CB3" t="s">
         <v>116</v>
@@ -1451,13 +1451,13 @@
         <v>1.75</v>
       </c>
       <c r="I4">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J4">
         <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
         <v>1.21</v>
@@ -1466,22 +1466,22 @@
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O4">
         <v>1.11</v>
       </c>
       <c r="P4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S4">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="T4">
         <v>1.43</v>
@@ -1490,13 +1490,13 @@
         <v>3</v>
       </c>
       <c r="V4">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W4">
         <v>1.29</v>
       </c>
       <c r="X4">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="Y4">
         <v>20</v>
@@ -1514,13 +1514,13 @@
         <v>14</v>
       </c>
       <c r="AD4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE4">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF4">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="AG4">
         <v>19.5</v>
@@ -1532,7 +1532,7 @@
         <v>22</v>
       </c>
       <c r="AJ4">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="AK4">
         <v>48</v>
@@ -1544,13 +1544,13 @@
         <v>48</v>
       </c>
       <c r="AN4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO4">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AP4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ4">
         <v>16.5</v>
@@ -1574,7 +1574,7 @@
         <v>13.5</v>
       </c>
       <c r="AX4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AY4">
         <v>16</v>
@@ -1595,19 +1595,19 @@
         <v>28</v>
       </c>
       <c r="BE4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF4">
         <v>17.5</v>
       </c>
       <c r="BG4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH4">
         <v>6.6</v>
       </c>
       <c r="BI4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ4">
         <v>10.5</v>
@@ -1616,7 +1616,7 @@
         <v>3.4</v>
       </c>
       <c r="BL4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BM4">
         <v>4.7</v>
@@ -1625,19 +1625,19 @@
         <v>10.5</v>
       </c>
       <c r="BO4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BP4">
         <v>28</v>
       </c>
       <c r="BQ4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR4">
         <v>28</v>
       </c>
       <c r="BS4">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT4">
         <v>6.4</v>
@@ -1655,13 +1655,13 @@
         <v>21</v>
       </c>
       <c r="BY4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ4">
         <v>12</v>
       </c>
       <c r="CA4">
-        <v>3.55</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="s">
         <v>116</v>
@@ -1684,19 +1684,19 @@
         <v>109</v>
       </c>
       <c r="F5">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="G5">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -1720,184 +1720,184 @@
         <v>1.36</v>
       </c>
       <c r="R5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="T5">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="U5">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="X5">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="Y5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z5">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AA5">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AB5">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AC5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AD5">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH5">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="AJ5">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AK5">
+        <v>20</v>
+      </c>
+      <c r="AL5">
+        <v>22</v>
+      </c>
+      <c r="AM5">
+        <v>44</v>
+      </c>
+      <c r="AN5">
+        <v>7.8</v>
+      </c>
+      <c r="AO5">
+        <v>15</v>
+      </c>
+      <c r="AP5">
+        <v>30</v>
+      </c>
+      <c r="AQ5">
+        <v>23</v>
+      </c>
+      <c r="AR5">
+        <v>28</v>
+      </c>
+      <c r="AS5">
+        <v>38</v>
+      </c>
+      <c r="AT5">
+        <v>18.5</v>
+      </c>
+      <c r="AU5">
+        <v>10</v>
+      </c>
+      <c r="AV5">
+        <v>13.5</v>
+      </c>
+      <c r="AW5">
+        <v>24</v>
+      </c>
+      <c r="AX5">
+        <v>18.5</v>
+      </c>
+      <c r="AY5">
+        <v>10.5</v>
+      </c>
+      <c r="AZ5">
+        <v>11.5</v>
+      </c>
+      <c r="BA5">
+        <v>23</v>
+      </c>
+      <c r="BB5">
+        <v>24</v>
+      </c>
+      <c r="BC5">
+        <v>15.5</v>
+      </c>
+      <c r="BD5">
         <v>18</v>
       </c>
-      <c r="AL5">
-        <v>23</v>
-      </c>
-      <c r="AM5">
-        <v>500</v>
-      </c>
-      <c r="AN5">
-        <v>6.2</v>
-      </c>
-      <c r="AO5">
-        <v>19.5</v>
-      </c>
-      <c r="AP5">
-        <v>6.6</v>
-      </c>
-      <c r="AQ5">
-        <v>6.2</v>
-      </c>
-      <c r="AR5">
-        <v>6.4</v>
-      </c>
-      <c r="AS5">
-        <v>7</v>
-      </c>
-      <c r="AT5">
-        <v>5.6</v>
-      </c>
-      <c r="AU5">
-        <v>5</v>
-      </c>
-      <c r="AV5">
-        <v>5.5</v>
-      </c>
-      <c r="AW5">
-        <v>6.4</v>
-      </c>
-      <c r="AX5">
-        <v>5.6</v>
-      </c>
-      <c r="AY5">
-        <v>4.8</v>
-      </c>
-      <c r="AZ5">
-        <v>5.2</v>
-      </c>
-      <c r="BA5">
-        <v>6.2</v>
-      </c>
-      <c r="BB5">
+      <c r="BE5">
+        <v>30</v>
+      </c>
+      <c r="BF5">
+        <v>6</v>
+      </c>
+      <c r="BG5">
+        <v>12</v>
+      </c>
+      <c r="BH5">
         <v>5.9</v>
       </c>
-      <c r="BC5">
-        <v>5.3</v>
-      </c>
-      <c r="BD5">
-        <v>5.7</v>
-      </c>
-      <c r="BE5">
-        <v>6.4</v>
-      </c>
-      <c r="BF5">
-        <v>3.4</v>
-      </c>
-      <c r="BG5">
-        <v>15</v>
-      </c>
-      <c r="BH5">
-        <v>6.2</v>
-      </c>
       <c r="BI5">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BN5">
+        <v>6.4</v>
+      </c>
+      <c r="BO5">
+        <v>5</v>
+      </c>
+      <c r="BP5">
+        <v>13.5</v>
+      </c>
+      <c r="BQ5">
+        <v>9.6</v>
+      </c>
+      <c r="BR5">
+        <v>19.5</v>
+      </c>
+      <c r="BS5">
         <v>6</v>
       </c>
-      <c r="BO5">
-        <v>4.5</v>
-      </c>
-      <c r="BP5">
-        <v>12.5</v>
-      </c>
-      <c r="BQ5">
-        <v>4.9</v>
-      </c>
-      <c r="BR5">
-        <v>18.5</v>
-      </c>
-      <c r="BS5">
-        <v>5.6</v>
-      </c>
       <c r="BT5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5">
         <v>4.2</v>
       </c>
       <c r="BV5">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BW5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BY5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1926,139 +1926,139 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="G6">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="I6">
+        <v>15.5</v>
+      </c>
+      <c r="J6">
+        <v>4.5</v>
+      </c>
+      <c r="K6">
+        <v>5.4</v>
+      </c>
+      <c r="L6">
+        <v>1.4</v>
+      </c>
+      <c r="M6">
+        <v>1.06</v>
+      </c>
+      <c r="N6">
+        <v>3.8</v>
+      </c>
+      <c r="O6">
+        <v>1.3</v>
+      </c>
+      <c r="P6">
+        <v>1.98</v>
+      </c>
+      <c r="Q6">
+        <v>1.93</v>
+      </c>
+      <c r="R6">
+        <v>1.4</v>
+      </c>
+      <c r="S6">
+        <v>3.3</v>
+      </c>
+      <c r="T6">
+        <v>2.28</v>
+      </c>
+      <c r="U6">
+        <v>1.62</v>
+      </c>
+      <c r="V6">
+        <v>1.08</v>
+      </c>
+      <c r="W6">
+        <v>3.35</v>
+      </c>
+      <c r="X6">
+        <v>17</v>
+      </c>
+      <c r="Y6">
+        <v>36</v>
+      </c>
+      <c r="Z6">
+        <v>420</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>7.8</v>
+      </c>
+      <c r="AC6">
+        <v>12</v>
+      </c>
+      <c r="AD6">
+        <v>55</v>
+      </c>
+      <c r="AE6">
+        <v>360</v>
+      </c>
+      <c r="AF6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG6">
+        <v>12</v>
+      </c>
+      <c r="AH6">
+        <v>38</v>
+      </c>
+      <c r="AI6">
+        <v>470</v>
+      </c>
+      <c r="AJ6">
         <v>11</v>
       </c>
-      <c r="J6">
-        <v>3.9</v>
-      </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>1.42</v>
-      </c>
-      <c r="M6">
-        <v>1.07</v>
-      </c>
-      <c r="N6">
-        <v>3.6</v>
-      </c>
-      <c r="O6">
-        <v>1.35</v>
-      </c>
-      <c r="P6">
-        <v>1.89</v>
-      </c>
-      <c r="Q6">
-        <v>1.99</v>
-      </c>
-      <c r="R6">
-        <v>1.33</v>
-      </c>
-      <c r="S6">
-        <v>3.55</v>
-      </c>
-      <c r="T6">
-        <v>2.12</v>
-      </c>
-      <c r="U6">
-        <v>1.68</v>
-      </c>
-      <c r="V6">
-        <v>1.1</v>
-      </c>
-      <c r="W6">
-        <v>2.74</v>
-      </c>
-      <c r="X6">
-        <v>16</v>
-      </c>
-      <c r="Y6">
-        <v>32</v>
-      </c>
-      <c r="Z6">
-        <v>120</v>
-      </c>
-      <c r="AA6">
-        <v>500</v>
-      </c>
-      <c r="AB6">
-        <v>7.4</v>
-      </c>
-      <c r="AC6">
-        <v>11</v>
-      </c>
-      <c r="AD6">
-        <v>40</v>
-      </c>
-      <c r="AE6">
-        <v>230</v>
-      </c>
-      <c r="AF6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG6">
-        <v>11</v>
-      </c>
-      <c r="AH6">
-        <v>32</v>
-      </c>
-      <c r="AI6">
-        <v>200</v>
-      </c>
-      <c r="AJ6">
-        <v>13.5</v>
-      </c>
       <c r="AK6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL6">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AM6">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="AN6">
-        <v>9.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO6">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
         <v>11</v>
       </c>
       <c r="AQ6">
-        <v>5.7</v>
+        <v>24</v>
       </c>
       <c r="AR6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS6">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU6">
         <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AW6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX6">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AY6">
         <v>8.6</v>
@@ -2067,34 +2067,34 @@
         <v>19.5</v>
       </c>
       <c r="BA6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB6">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD6">
         <v>32</v>
       </c>
       <c r="BE6">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF6">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG6">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH6">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BI6">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK6">
         <v>9.199999999999999</v>
@@ -2103,49 +2103,49 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>3.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BO6">
-        <v>1.84</v>
+        <v>3.15</v>
       </c>
       <c r="BP6">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ6">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS6">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU6">
-        <v>3.45</v>
+        <v>9.6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="CA6">
-        <v>2.98</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="s">
         <v>116</v>
@@ -2168,46 +2168,46 @@
         <v>111</v>
       </c>
       <c r="F7">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G7">
         <v>2.28</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I7">
         <v>4.3</v>
       </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K7">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L7">
         <v>1.53</v>
       </c>
       <c r="M7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="O7">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P7">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q7">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R7">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S7">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T7">
         <v>2.06</v>
@@ -2219,13 +2219,13 @@
         <v>1.3</v>
       </c>
       <c r="W7">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z7">
         <v>34</v>
@@ -2234,7 +2234,7 @@
         <v>500</v>
       </c>
       <c r="AB7">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC7">
         <v>7.8</v>
@@ -2255,7 +2255,7 @@
         <v>24</v>
       </c>
       <c r="AI7">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ7">
         <v>40</v>
@@ -2264,7 +2264,7 @@
         <v>32</v>
       </c>
       <c r="AL7">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="AM7">
         <v>580</v>
@@ -2285,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="AS7">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT7">
         <v>6.4</v>
@@ -2321,7 +2321,7 @@
         <v>23</v>
       </c>
       <c r="BE7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF7">
         <v>21</v>
@@ -2330,7 +2330,7 @@
         <v>12.5</v>
       </c>
       <c r="BH7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI7">
         <v>2.56</v>
@@ -2339,13 +2339,13 @@
         <v>11.5</v>
       </c>
       <c r="BK7">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2357,13 +2357,13 @@
         <v>18.5</v>
       </c>
       <c r="BQ7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR7">
         <v>42</v>
       </c>
       <c r="BS7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT7">
         <v>7.4</v>
@@ -2375,19 +2375,19 @@
         <v>44</v>
       </c>
       <c r="BW7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX7">
         <v>70</v>
       </c>
       <c r="BY7">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7">
         <v>46</v>
       </c>
       <c r="CA7">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="CB7" t="s">
         <v>116</v>
@@ -2410,22 +2410,22 @@
         <v>112</v>
       </c>
       <c r="F8">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H8">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="I8">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="J8">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K8">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L8">
         <v>1.29</v>
@@ -2440,34 +2440,34 @@
         <v>1.19</v>
       </c>
       <c r="P8">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q8">
         <v>1.6</v>
       </c>
       <c r="R8">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S8">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T8">
         <v>1.52</v>
       </c>
       <c r="U8">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V8">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="W8">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="X8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z8">
         <v>21</v>
@@ -2476,7 +2476,7 @@
         <v>95</v>
       </c>
       <c r="AB8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC8">
         <v>10.5</v>
@@ -2491,7 +2491,7 @@
         <v>25</v>
       </c>
       <c r="AG8">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
         <v>16</v>
@@ -2515,7 +2515,7 @@
         <v>17.5</v>
       </c>
       <c r="AO8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP8">
         <v>6.2</v>
@@ -2542,7 +2542,7 @@
         <v>6</v>
       </c>
       <c r="AX8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY8">
         <v>11</v>
@@ -2554,13 +2554,13 @@
         <v>14.5</v>
       </c>
       <c r="BB8">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC8">
         <v>13</v>
       </c>
       <c r="BD8">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BE8">
         <v>7.2</v>
@@ -2569,10 +2569,10 @@
         <v>13.5</v>
       </c>
       <c r="BG8">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI8">
         <v>3.55</v>
@@ -2581,7 +2581,7 @@
         <v>9</v>
       </c>
       <c r="BK8">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
@@ -2608,10 +2608,10 @@
         <v>6.4</v>
       </c>
       <c r="BT8">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV8">
         <v>17.5</v>
@@ -2620,10 +2620,10 @@
         <v>5.7</v>
       </c>
       <c r="BX8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BY8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2652,13 +2652,13 @@
         <v>113</v>
       </c>
       <c r="F9">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="G9">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H9">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I9">
         <v>4.2</v>
@@ -2667,34 +2667,34 @@
         <v>3.55</v>
       </c>
       <c r="K9">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L9">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q9">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="R9">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U9">
         <v>2.22</v>
@@ -2703,31 +2703,31 @@
         <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X9">
+        <v>19.5</v>
+      </c>
+      <c r="Y9">
         <v>17.5</v>
       </c>
-      <c r="Y9">
-        <v>16.5</v>
-      </c>
       <c r="Z9">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AA9">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC9">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE9">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AF9">
         <v>14.5</v>
@@ -2742,136 +2742,136 @@
         <v>120</v>
       </c>
       <c r="AJ9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK9">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AL9">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM9">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AP9">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS9">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AX9">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
         <v>8.4</v>
       </c>
       <c r="AZ9">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA9">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BB9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BC9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD9">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BE9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG9">
+        <v>19</v>
+      </c>
+      <c r="BH9">
+        <v>4.1</v>
+      </c>
+      <c r="BI9">
+        <v>3.15</v>
+      </c>
+      <c r="BJ9">
         <v>9.4</v>
       </c>
-      <c r="BF9">
-        <v>11.5</v>
-      </c>
-      <c r="BG9">
-        <v>25</v>
-      </c>
-      <c r="BH9">
-        <v>1000</v>
-      </c>
-      <c r="BI9">
-        <v>1.04</v>
-      </c>
-      <c r="BJ9">
-        <v>1000</v>
-      </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="s">
         <v>116</v>
@@ -2897,19 +2897,19 @@
         <v>1.51</v>
       </c>
       <c r="G10">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H10">
         <v>7.6</v>
       </c>
       <c r="I10">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L10">
         <v>1.42</v>
@@ -2924,7 +2924,7 @@
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q10">
         <v>2.02</v>
@@ -2945,19 +2945,19 @@
         <v>1.12</v>
       </c>
       <c r="W10">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
         <v>24</v>
       </c>
       <c r="Z10">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AB10">
         <v>7.4</v>
@@ -2969,7 +2969,7 @@
         <v>32</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF10">
         <v>8.6</v>
@@ -2981,7 +2981,7 @@
         <v>28</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ10">
         <v>14</v>
@@ -2993,67 +2993,67 @@
         <v>46</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN10">
         <v>9.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP10">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="AR10">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="AS10">
-        <v>5.3</v>
+        <v>9.4</v>
       </c>
       <c r="AT10">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU10">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="AV10">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW10">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AY10">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="AZ10">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="BA10">
-        <v>5.3</v>
+        <v>9</v>
       </c>
       <c r="BB10">
-        <v>3.85</v>
+        <v>10.5</v>
       </c>
       <c r="BC10">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="BD10">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BE10">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF10">
-        <v>3.45</v>
+        <v>7.4</v>
       </c>
       <c r="BG10">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH10">
         <v>3.45</v>
@@ -3142,16 +3142,16 @@
         <v>2.1</v>
       </c>
       <c r="H11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I11">
         <v>4.5</v>
       </c>
       <c r="J11">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K11">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L11">
         <v>1.47</v>
@@ -3169,13 +3169,13 @@
         <v>1.77</v>
       </c>
       <c r="Q11">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R11">
         <v>1.29</v>
       </c>
       <c r="S11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T11">
         <v>1.92</v>
@@ -3187,7 +3187,7 @@
         <v>1.28</v>
       </c>
       <c r="W11">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X11">
         <v>14.5</v>
@@ -3298,7 +3298,7 @@
         <v>4.8</v>
       </c>
       <c r="BH11">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI11">
         <v>2.78</v>
@@ -3307,16 +3307,16 @@
         <v>12.5</v>
       </c>
       <c r="BK11">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BN11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BO11">
         <v>3.6</v>
@@ -3325,37 +3325,37 @@
         <v>18.5</v>
       </c>
       <c r="BQ11">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BR11">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BS11">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BT11">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU11">
         <v>5.6</v>
       </c>
       <c r="BV11">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BW11">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BX11">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY11">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BZ11">
         <v>38</v>
       </c>
       <c r="CA11">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="CB11" t="s">
         <v>116</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -364,7 +364,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-04 04:48:38</t>
+    <t>2026-08-04 06:55:09</t>
   </si>
 </sst>
 </file>
@@ -958,22 +958,22 @@
         <v>106</v>
       </c>
       <c r="F2">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="G2">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H2">
         <v>3.05</v>
       </c>
       <c r="I2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2">
         <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2">
         <v>1.49</v>
@@ -982,7 +982,7 @@
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O2">
         <v>1.43</v>
@@ -994,19 +994,19 @@
         <v>2.26</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T2">
         <v>1.94</v>
       </c>
       <c r="U2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W2">
         <v>1.6</v>
@@ -1045,10 +1045,10 @@
         <v>20</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK2">
         <v>34</v>
@@ -1057,7 +1057,7 @@
         <v>75</v>
       </c>
       <c r="AM2">
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="AN2">
         <v>32</v>
@@ -1066,67 +1066,67 @@
         <v>48</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR2">
         <v>15.5</v>
       </c>
       <c r="AS2">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AT2">
         <v>6.8</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AV2">
         <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB2">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="BC2">
         <v>21</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BE2">
         <v>60</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="BH2">
         <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>2.72</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
         <v>4.3</v>
@@ -1135,7 +1135,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BN2">
         <v>5.6</v>
@@ -1147,31 +1147,31 @@
         <v>22</v>
       </c>
       <c r="BQ2">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BT2">
         <v>6.4</v>
       </c>
       <c r="BU2">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BV2">
         <v>29</v>
       </c>
       <c r="BW2">
+        <v>5.5</v>
+      </c>
+      <c r="BX2">
+        <v>44</v>
+      </c>
+      <c r="BY2">
         <v>5.9</v>
-      </c>
-      <c r="BX2">
-        <v>55</v>
-      </c>
-      <c r="BY2">
-        <v>6.6</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1200,22 +1200,22 @@
         <v>107</v>
       </c>
       <c r="F3">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="G3">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="I3">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="J3">
         <v>2.68</v>
       </c>
       <c r="K3">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="L3">
         <v>1.71</v>
@@ -1224,202 +1224,202 @@
         <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O3">
         <v>1.71</v>
       </c>
       <c r="P3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Q3">
         <v>3.15</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S3">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Y3">
         <v>9.6</v>
       </c>
       <c r="Z3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA3">
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC3">
         <v>7.8</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE3">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG3">
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI3">
         <v>500</v>
       </c>
       <c r="AJ3">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AK3">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AL3">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR3">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AS3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AT3">
+        <v>5.3</v>
+      </c>
+      <c r="AU3">
+        <v>5.7</v>
+      </c>
+      <c r="AV3">
+        <v>13.5</v>
+      </c>
+      <c r="AW3">
+        <v>5.9</v>
+      </c>
+      <c r="AX3">
+        <v>12</v>
+      </c>
+      <c r="AY3">
+        <v>11</v>
+      </c>
+      <c r="AZ3">
+        <v>20</v>
+      </c>
+      <c r="BA3">
+        <v>6</v>
+      </c>
+      <c r="BB3">
+        <v>5.8</v>
+      </c>
+      <c r="BC3">
+        <v>5.8</v>
+      </c>
+      <c r="BD3">
+        <v>6</v>
+      </c>
+      <c r="BE3">
+        <v>6.2</v>
+      </c>
+      <c r="BF3">
+        <v>5.8</v>
+      </c>
+      <c r="BG3">
+        <v>6</v>
+      </c>
+      <c r="BH3">
+        <v>2.62</v>
+      </c>
+      <c r="BI3">
+        <v>2.04</v>
+      </c>
+      <c r="BJ3">
+        <v>13.5</v>
+      </c>
+      <c r="BK3">
         <v>5</v>
-      </c>
-      <c r="AU3">
-        <v>5.8</v>
-      </c>
-      <c r="AV3">
-        <v>5.2</v>
-      </c>
-      <c r="AW3">
-        <v>6.4</v>
-      </c>
-      <c r="AX3">
-        <v>4.8</v>
-      </c>
-      <c r="AY3">
-        <v>4.7</v>
-      </c>
-      <c r="AZ3">
-        <v>5.7</v>
-      </c>
-      <c r="BA3">
-        <v>6.6</v>
-      </c>
-      <c r="BB3">
-        <v>6</v>
-      </c>
-      <c r="BC3">
-        <v>6</v>
-      </c>
-      <c r="BD3">
-        <v>6.4</v>
-      </c>
-      <c r="BE3">
-        <v>6.8</v>
-      </c>
-      <c r="BF3">
-        <v>6.2</v>
-      </c>
-      <c r="BG3">
-        <v>6.6</v>
-      </c>
-      <c r="BH3">
-        <v>2.52</v>
-      </c>
-      <c r="BI3">
-        <v>1.99</v>
-      </c>
-      <c r="BJ3">
-        <v>14</v>
-      </c>
-      <c r="BK3">
-        <v>5.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BN3">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO3">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BT3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BU3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="CB3" t="s">
         <v>116</v>
@@ -1445,7 +1445,7 @@
         <v>4.2</v>
       </c>
       <c r="G4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H4">
         <v>1.75</v>
@@ -1460,58 +1460,58 @@
         <v>5.2</v>
       </c>
       <c r="L4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M4">
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O4">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R4">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S4">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="T4">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U4">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V4">
         <v>2.24</v>
       </c>
       <c r="W4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X4">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Y4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB4">
         <v>34</v>
       </c>
       <c r="AC4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD4">
         <v>12</v>
@@ -1520,7 +1520,7 @@
         <v>16.5</v>
       </c>
       <c r="AF4">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AG4">
         <v>19.5</v>
@@ -1532,22 +1532,22 @@
         <v>22</v>
       </c>
       <c r="AJ4">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AK4">
+        <v>42</v>
+      </c>
+      <c r="AL4">
         <v>48</v>
-      </c>
-      <c r="AL4">
-        <v>36</v>
       </c>
       <c r="AM4">
         <v>48</v>
       </c>
       <c r="AN4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AP4">
         <v>32</v>
@@ -1556,13 +1556,13 @@
         <v>16.5</v>
       </c>
       <c r="AR4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS4">
         <v>18.5</v>
       </c>
       <c r="AT4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU4">
         <v>11</v>
@@ -1586,7 +1586,7 @@
         <v>18</v>
       </c>
       <c r="BB4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BC4">
         <v>32</v>
@@ -1598,70 +1598,70 @@
         <v>36</v>
       </c>
       <c r="BF4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH4">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI4">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BJ4">
+        <v>8.6</v>
+      </c>
+      <c r="BK4">
+        <v>5</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>10</v>
+      </c>
+      <c r="BN4">
+        <v>8.6</v>
+      </c>
+      <c r="BO4">
+        <v>5</v>
+      </c>
+      <c r="BP4">
+        <v>29</v>
+      </c>
+      <c r="BQ4">
+        <v>8.4</v>
+      </c>
+      <c r="BR4">
+        <v>29</v>
+      </c>
+      <c r="BS4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT4">
+        <v>5.3</v>
+      </c>
+      <c r="BU4">
+        <v>4.8</v>
+      </c>
+      <c r="BV4">
+        <v>13</v>
+      </c>
+      <c r="BW4">
+        <v>6.2</v>
+      </c>
+      <c r="BX4">
+        <v>18</v>
+      </c>
+      <c r="BY4">
+        <v>7</v>
+      </c>
+      <c r="BZ4">
         <v>10.5</v>
       </c>
-      <c r="BK4">
-        <v>3.4</v>
-      </c>
-      <c r="BL4">
-        <v>60</v>
-      </c>
-      <c r="BM4">
-        <v>4.7</v>
-      </c>
-      <c r="BN4">
-        <v>10.5</v>
-      </c>
-      <c r="BO4">
-        <v>6.4</v>
-      </c>
-      <c r="BP4">
-        <v>28</v>
-      </c>
-      <c r="BQ4">
-        <v>4.3</v>
-      </c>
-      <c r="BR4">
-        <v>28</v>
-      </c>
-      <c r="BS4">
-        <v>4.3</v>
-      </c>
-      <c r="BT4">
-        <v>6.4</v>
-      </c>
-      <c r="BU4">
-        <v>4.1</v>
-      </c>
-      <c r="BV4">
-        <v>11.5</v>
-      </c>
-      <c r="BW4">
-        <v>3.5</v>
-      </c>
-      <c r="BX4">
-        <v>21</v>
-      </c>
-      <c r="BY4">
-        <v>4.1</v>
-      </c>
-      <c r="BZ4">
-        <v>12</v>
-      </c>
       <c r="CA4">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="CB4" t="s">
         <v>116</v>
@@ -1684,7 +1684,7 @@
         <v>109</v>
       </c>
       <c r="F5">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G5">
         <v>2.14</v>
@@ -1693,13 +1693,13 @@
         <v>3.15</v>
       </c>
       <c r="I5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5">
         <v>1.21</v>
@@ -1708,7 +1708,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>1.11</v>
@@ -1717,94 +1717,94 @@
         <v>3.5</v>
       </c>
       <c r="Q5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R5">
         <v>2.04</v>
       </c>
       <c r="S5">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="T5">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="U5">
         <v>3.1</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
         <v>1.87</v>
       </c>
       <c r="X5">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="Y5">
         <v>32</v>
       </c>
       <c r="Z5">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AA5">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AB5">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AC5">
         <v>13.5</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AI5">
         <v>32</v>
       </c>
       <c r="AJ5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK5">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL5">
         <v>22</v>
       </c>
       <c r="AM5">
-        <v>44</v>
+        <v>200</v>
       </c>
       <c r="AN5">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP5">
         <v>30</v>
       </c>
       <c r="AQ5">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AR5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AS5">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AT5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU5">
         <v>10</v>
@@ -1816,10 +1816,10 @@
         <v>24</v>
       </c>
       <c r="AX5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ5">
         <v>11.5</v>
@@ -1828,76 +1828,76 @@
         <v>23</v>
       </c>
       <c r="BB5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC5">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BE5">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BF5">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BG5">
         <v>12</v>
       </c>
       <c r="BH5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BI5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5">
         <v>8.6</v>
       </c>
       <c r="BK5">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BN5">
         <v>6.4</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
         <v>13.5</v>
       </c>
       <c r="BQ5">
-        <v>9.6</v>
+        <v>4.9</v>
       </c>
       <c r="BR5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS5">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BT5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU5">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BV5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BW5">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BX5">
         <v>24</v>
       </c>
       <c r="BY5">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1926,10 +1926,10 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G6">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="H6">
         <v>12</v>
@@ -1938,7 +1938,7 @@
         <v>15.5</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K6">
         <v>5.4</v>
@@ -1950,7 +1950,7 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O6">
         <v>1.3</v>
@@ -1959,7 +1959,7 @@
         <v>1.98</v>
       </c>
       <c r="Q6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R6">
         <v>1.4</v>
@@ -1971,19 +1971,19 @@
         <v>2.28</v>
       </c>
       <c r="U6">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V6">
         <v>1.08</v>
       </c>
       <c r="W6">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="X6">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Y6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z6">
         <v>420</v>
@@ -2001,16 +2001,16 @@
         <v>55</v>
       </c>
       <c r="AE6">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="AF6">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AG6">
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI6">
         <v>470</v>
@@ -2022,10 +2022,10 @@
         <v>18</v>
       </c>
       <c r="AL6">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AM6">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AN6">
         <v>7.2</v>
@@ -2034,118 +2034,118 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AQ6">
-        <v>24</v>
+        <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
         <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AW6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
         <v>6.2</v>
       </c>
       <c r="AY6">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BA6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD6">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="BE6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6">
         <v>15</v>
       </c>
       <c r="BK6">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6">
         <v>3.65</v>
       </c>
       <c r="BO6">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="BP6">
         <v>8.199999999999999</v>
       </c>
       <c r="BQ6">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="BR6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BT6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BU6">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ6">
         <v>16</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="CB6" t="s">
         <v>116</v>
@@ -2168,10 +2168,10 @@
         <v>111</v>
       </c>
       <c r="F7">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G7">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H7">
         <v>4.1</v>
@@ -2186,7 +2186,7 @@
         <v>3.25</v>
       </c>
       <c r="L7">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M7">
         <v>1.13</v>
@@ -2195,13 +2195,13 @@
         <v>2.8</v>
       </c>
       <c r="O7">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P7">
         <v>1.57</v>
       </c>
       <c r="Q7">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R7">
         <v>1.21</v>
@@ -2210,10 +2210,10 @@
         <v>5.3</v>
       </c>
       <c r="T7">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V7">
         <v>1.3</v>
@@ -2222,22 +2222,22 @@
         <v>1.78</v>
       </c>
       <c r="X7">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA7">
         <v>500</v>
       </c>
       <c r="AB7">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD7">
         <v>17.5</v>
@@ -2246,148 +2246,148 @@
         <v>160</v>
       </c>
       <c r="AF7">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI7">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="AJ7">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="AK7">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL7">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AM7">
         <v>580</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AO7">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP7">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AQ7">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AS7">
-        <v>9.800000000000001</v>
+        <v>70</v>
       </c>
       <c r="AT7">
         <v>6.4</v>
       </c>
       <c r="AU7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW7">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="AX7">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB7">
         <v>22</v>
       </c>
       <c r="BC7">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD7">
+        <v>42</v>
+      </c>
+      <c r="BE7">
+        <v>36</v>
+      </c>
+      <c r="BF7">
         <v>23</v>
       </c>
-      <c r="BE7">
-        <v>10</v>
-      </c>
-      <c r="BF7">
-        <v>21</v>
-      </c>
       <c r="BG7">
+        <v>65</v>
+      </c>
+      <c r="BH7">
+        <v>2.92</v>
+      </c>
+      <c r="BI7">
+        <v>2.38</v>
+      </c>
+      <c r="BJ7">
         <v>12.5</v>
       </c>
-      <c r="BH7">
-        <v>3.1</v>
-      </c>
-      <c r="BI7">
-        <v>2.56</v>
-      </c>
-      <c r="BJ7">
-        <v>11.5</v>
-      </c>
       <c r="BK7">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
       </c>
       <c r="BO7">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BP7">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BQ7">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BR7">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
+        <v>7</v>
+      </c>
+      <c r="BT7">
+        <v>8</v>
+      </c>
+      <c r="BU7">
+        <v>5.5</v>
+      </c>
+      <c r="BV7">
+        <v>46</v>
+      </c>
+      <c r="BW7">
+        <v>7.2</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
         <v>7.6</v>
       </c>
-      <c r="BT7">
-        <v>7.4</v>
-      </c>
-      <c r="BU7">
-        <v>5.6</v>
-      </c>
-      <c r="BV7">
-        <v>44</v>
-      </c>
-      <c r="BW7">
-        <v>7.6</v>
-      </c>
-      <c r="BX7">
-        <v>70</v>
-      </c>
-      <c r="BY7">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ7">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="CA7">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="CB7" t="s">
         <v>116</v>
@@ -2416,10 +2416,10 @@
         <v>3.1</v>
       </c>
       <c r="H8">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I8">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J8">
         <v>3.65</v>
@@ -2449,34 +2449,34 @@
         <v>1.59</v>
       </c>
       <c r="S8">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T8">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U8">
         <v>2.56</v>
       </c>
       <c r="V8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W8">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA8">
         <v>95</v>
       </c>
       <c r="AB8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC8">
         <v>10.5</v>
@@ -2485,7 +2485,7 @@
         <v>13</v>
       </c>
       <c r="AE8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF8">
         <v>25</v>
@@ -2494,7 +2494,7 @@
         <v>14</v>
       </c>
       <c r="AH8">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI8">
         <v>32</v>
@@ -2512,37 +2512,37 @@
         <v>200</v>
       </c>
       <c r="AN8">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AO8">
         <v>14.5</v>
       </c>
       <c r="AP8">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AQ8">
         <v>13</v>
       </c>
       <c r="AR8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS8">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AT8">
-        <v>5.6</v>
+        <v>14</v>
       </c>
       <c r="AU8">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="AV8">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW8">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AX8">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="AY8">
         <v>11</v>
@@ -2551,25 +2551,25 @@
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BB8">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="BC8">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BE8">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BF8">
         <v>13.5</v>
       </c>
       <c r="BG8">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BH8">
         <v>4.6</v>
@@ -2652,13 +2652,13 @@
         <v>113</v>
       </c>
       <c r="F9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>2.16</v>
       </c>
       <c r="H9">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I9">
         <v>4.2</v>
@@ -2667,7 +2667,7 @@
         <v>3.55</v>
       </c>
       <c r="K9">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L9">
         <v>1.37</v>
@@ -2676,28 +2676,28 @@
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O9">
         <v>1.25</v>
       </c>
       <c r="P9">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R9">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S9">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T9">
         <v>1.66</v>
       </c>
       <c r="U9">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V9">
         <v>1.32</v>
@@ -2706,16 +2706,16 @@
         <v>1.86</v>
       </c>
       <c r="X9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z9">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="AA9">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AB9">
         <v>11.5</v>
@@ -2724,97 +2724,97 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD9">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE9">
-        <v>50</v>
+        <v>290</v>
       </c>
       <c r="AF9">
         <v>14.5</v>
       </c>
       <c r="AG9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI9">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AJ9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK9">
         <v>22</v>
       </c>
       <c r="AL9">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AM9">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN9">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO9">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="AP9">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AQ9">
         <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AS9">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AT9">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9">
         <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW9">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BB9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC9">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BD9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BE9">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BF9">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG9">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BH9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI9">
         <v>3.15</v>
@@ -2823,13 +2823,13 @@
         <v>9.4</v>
       </c>
       <c r="BK9">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
@@ -2841,13 +2841,13 @@
         <v>14.5</v>
       </c>
       <c r="BQ9">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BT9">
         <v>7.6</v>
@@ -2859,19 +2859,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA9">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="CB9" t="s">
         <v>116</v>
@@ -2924,7 +2924,7 @@
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q10">
         <v>2.02</v>
@@ -2954,7 +2954,7 @@
         <v>24</v>
       </c>
       <c r="Z10">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AA10">
         <v>350</v>
@@ -3136,7 +3136,7 @@
         <v>115</v>
       </c>
       <c r="F11">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G11">
         <v>2.1</v>
@@ -3148,7 +3148,7 @@
         <v>4.5</v>
       </c>
       <c r="J11">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K11">
         <v>3.5</v>
@@ -3169,13 +3169,13 @@
         <v>1.77</v>
       </c>
       <c r="Q11">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R11">
         <v>1.29</v>
       </c>
       <c r="S11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T11">
         <v>1.92</v>
@@ -3184,7 +3184,7 @@
         <v>1.96</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W11">
         <v>1.91</v>
@@ -3193,7 +3193,7 @@
         <v>14.5</v>
       </c>
       <c r="Y11">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z11">
         <v>38</v>
@@ -3202,19 +3202,19 @@
         <v>120</v>
       </c>
       <c r="AB11">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD11">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE11">
         <v>65</v>
       </c>
       <c r="AF11">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG11">
         <v>13</v>
@@ -3223,7 +3223,7 @@
         <v>25</v>
       </c>
       <c r="AI11">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ11">
         <v>30</v>
@@ -3250,10 +3250,10 @@
         <v>10</v>
       </c>
       <c r="AR11">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS11">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT11">
         <v>7</v>
@@ -3262,10 +3262,10 @@
         <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW11">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX11">
         <v>10</v>
@@ -3277,7 +3277,7 @@
         <v>17</v>
       </c>
       <c r="BA11">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB11">
         <v>21</v>
@@ -3286,76 +3286,76 @@
         <v>20</v>
       </c>
       <c r="BD11">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE11">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BF11">
         <v>15.5</v>
       </c>
       <c r="BG11">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BH11">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="BI11">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BK11">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>5.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN11">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BO11">
         <v>3.6</v>
       </c>
       <c r="BP11">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BQ11">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BR11">
         <v>34</v>
       </c>
       <c r="BS11">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BT11">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BU11">
         <v>5.6</v>
       </c>
       <c r="BV11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW11">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BX11">
         <v>55</v>
       </c>
       <c r="BY11">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="CA11">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="CB11" t="s">
         <v>116</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -364,7 +364,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-04 06:55:09</t>
+    <t>2026-08-04 09:01:53</t>
   </si>
 </sst>
 </file>
@@ -961,7 +961,7 @@
         <v>2.52</v>
       </c>
       <c r="G2">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H2">
         <v>3.05</v>
@@ -973,7 +973,7 @@
         <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
         <v>1.49</v>
@@ -991,7 +991,7 @@
         <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R2">
         <v>1.26</v>
@@ -1000,7 +1000,7 @@
         <v>4.3</v>
       </c>
       <c r="T2">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
         <v>1.96</v>
@@ -1012,19 +1012,19 @@
         <v>1.6</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y2">
         <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA2">
         <v>65</v>
       </c>
       <c r="AB2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC2">
         <v>7.8</v>
@@ -1039,7 +1039,7 @@
         <v>17</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
         <v>20</v>
@@ -1054,7 +1054,7 @@
         <v>34</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM2">
         <v>450</v>
@@ -1069,55 +1069,55 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS2">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ2">
         <v>15.5</v>
       </c>
       <c r="BA2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB2">
-        <v>16.5</v>
+        <v>26</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD2">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BE2">
         <v>60</v>
       </c>
       <c r="BF2">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="BG2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BH2">
         <v>3.55</v>
@@ -1126,16 +1126,16 @@
         <v>2.48</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BK2">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BN2">
         <v>5.6</v>
@@ -1147,31 +1147,31 @@
         <v>22</v>
       </c>
       <c r="BQ2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BT2">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BV2">
         <v>29</v>
       </c>
       <c r="BW2">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BX2">
         <v>44</v>
       </c>
       <c r="BY2">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1200,82 +1200,82 @@
         <v>107</v>
       </c>
       <c r="F3">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H3">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J3">
         <v>2.68</v>
       </c>
       <c r="K3">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="M3">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="N3">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O3">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="P3">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="T3">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U3">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AB3">
         <v>7.8</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
         <v>19</v>
       </c>
       <c r="AE3">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AF3">
         <v>17</v>
@@ -1284,10 +1284,10 @@
         <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI3">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="AJ3">
         <v>110</v>
@@ -1296,130 +1296,130 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS3">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AT3">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AU3">
         <v>5.7</v>
       </c>
       <c r="AV3">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
+        <v>5.5</v>
+      </c>
+      <c r="AX3">
+        <v>10.5</v>
+      </c>
+      <c r="AY3">
+        <v>10</v>
+      </c>
+      <c r="AZ3">
+        <v>19.5</v>
+      </c>
+      <c r="BA3">
+        <v>5.7</v>
+      </c>
+      <c r="BB3">
+        <v>5.4</v>
+      </c>
+      <c r="BC3">
+        <v>5.4</v>
+      </c>
+      <c r="BD3">
+        <v>5.7</v>
+      </c>
+      <c r="BE3">
         <v>5.9</v>
       </c>
-      <c r="AX3">
-        <v>12</v>
-      </c>
-      <c r="AY3">
-        <v>11</v>
-      </c>
-      <c r="AZ3">
-        <v>20</v>
-      </c>
-      <c r="BA3">
-        <v>6</v>
-      </c>
-      <c r="BB3">
-        <v>5.8</v>
-      </c>
-      <c r="BC3">
-        <v>5.8</v>
-      </c>
-      <c r="BD3">
-        <v>6</v>
-      </c>
-      <c r="BE3">
-        <v>6.2</v>
-      </c>
       <c r="BF3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BH3">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="BI3">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BJ3">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BK3">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BN3">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BQ3">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BR3">
+        <v>75</v>
+      </c>
+      <c r="BS3">
+        <v>5.2</v>
+      </c>
+      <c r="BT3">
+        <v>7.2</v>
+      </c>
+      <c r="BU3">
+        <v>4.8</v>
+      </c>
+      <c r="BV3">
         <v>1000</v>
       </c>
-      <c r="BS3">
-        <v>7</v>
-      </c>
-      <c r="BT3">
-        <v>7</v>
-      </c>
-      <c r="BU3">
-        <v>5.2</v>
-      </c>
-      <c r="BV3">
-        <v>42</v>
-      </c>
       <c r="BW3">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="CA3">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB3" t="s">
         <v>116</v>
@@ -1442,73 +1442,73 @@
         <v>108</v>
       </c>
       <c r="F4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G4">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H4">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="I4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="J4">
         <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M4">
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="O4">
         <v>1.12</v>
       </c>
       <c r="P4">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="Q4">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="S4">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T4">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="U4">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="V4">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="W4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X4">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="Y4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z4">
         <v>18</v>
       </c>
       <c r="AA4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC4">
         <v>13.5</v>
@@ -1520,25 +1520,25 @@
         <v>16.5</v>
       </c>
       <c r="AF4">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI4">
         <v>22</v>
       </c>
       <c r="AJ4">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK4">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AM4">
         <v>48</v>
@@ -1547,19 +1547,19 @@
         <v>23</v>
       </c>
       <c r="AO4">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AP4">
         <v>32</v>
       </c>
       <c r="AQ4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AR4">
         <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AT4">
         <v>27</v>
@@ -1568,7 +1568,7 @@
         <v>11</v>
       </c>
       <c r="AV4">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4">
         <v>13.5</v>
@@ -1577,91 +1577,91 @@
         <v>38</v>
       </c>
       <c r="AY4">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ4">
         <v>13</v>
       </c>
       <c r="BA4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BB4">
         <v>70</v>
       </c>
       <c r="BC4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG4">
+        <v>5.1</v>
+      </c>
+      <c r="BH4">
+        <v>6.4</v>
+      </c>
+      <c r="BI4">
         <v>5</v>
       </c>
-      <c r="BH4">
-        <v>5.5</v>
-      </c>
-      <c r="BI4">
-        <v>4.9</v>
-      </c>
       <c r="BJ4">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BL4">
+        <v>65</v>
+      </c>
+      <c r="BM4">
+        <v>6.6</v>
+      </c>
+      <c r="BN4">
+        <v>10.5</v>
+      </c>
+      <c r="BO4">
+        <v>7.6</v>
+      </c>
+      <c r="BP4">
         <v>1000</v>
       </c>
-      <c r="BM4">
-        <v>10</v>
-      </c>
-      <c r="BN4">
-        <v>8.6</v>
-      </c>
-      <c r="BO4">
-        <v>5</v>
-      </c>
-      <c r="BP4">
-        <v>29</v>
-      </c>
       <c r="BQ4">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR4">
         <v>29</v>
       </c>
       <c r="BS4">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BT4">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BU4">
         <v>4.8</v>
       </c>
       <c r="BV4">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BW4">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BX4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BY4">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BZ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA4">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="CB4" t="s">
         <v>116</v>
@@ -1684,19 +1684,19 @@
         <v>109</v>
       </c>
       <c r="F5">
+        <v>1.97</v>
+      </c>
+      <c r="G5">
         <v>2.04</v>
       </c>
-      <c r="G5">
-        <v>2.14</v>
-      </c>
       <c r="H5">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="I5">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K5">
         <v>4.9</v>
@@ -1705,199 +1705,199 @@
         <v>1.21</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
         <v>8</v>
       </c>
       <c r="O5">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P5">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q5">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="R5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="T5">
+        <v>1.39</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+      <c r="V5">
         <v>1.37</v>
       </c>
-      <c r="U5">
-        <v>3.1</v>
-      </c>
-      <c r="V5">
-        <v>1.4</v>
-      </c>
       <c r="W5">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="X5">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="Y5">
         <v>32</v>
       </c>
       <c r="Z5">
-        <v>500</v>
+        <v>42</v>
       </c>
       <c r="AA5">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AB5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AC5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE5">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI5">
         <v>32</v>
       </c>
       <c r="AJ5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM5">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="AN5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO5">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ5">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AR5">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AS5">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AU5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV5">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AX5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BB5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5">
         <v>14.5</v>
       </c>
       <c r="BD5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BE5">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BF5">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG5">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BH5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BI5">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="BJ5">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BN5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BQ5">
-        <v>4.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR5">
         <v>19</v>
       </c>
       <c r="BS5">
+        <v>13.5</v>
+      </c>
+      <c r="BT5">
+        <v>8.6</v>
+      </c>
+      <c r="BU5">
+        <v>3.85</v>
+      </c>
+      <c r="BV5">
+        <v>24</v>
+      </c>
+      <c r="BW5">
+        <v>5.4</v>
+      </c>
+      <c r="BX5">
+        <v>26</v>
+      </c>
+      <c r="BY5">
         <v>5.5</v>
-      </c>
-      <c r="BT5">
-        <v>8.4</v>
-      </c>
-      <c r="BU5">
-        <v>4</v>
-      </c>
-      <c r="BV5">
-        <v>23</v>
-      </c>
-      <c r="BW5">
-        <v>5.8</v>
-      </c>
-      <c r="BX5">
-        <v>24</v>
-      </c>
-      <c r="BY5">
-        <v>17</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1926,22 +1926,22 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G6">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="J6">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L6">
         <v>1.4</v>
@@ -1956,31 +1956,31 @@
         <v>1.3</v>
       </c>
       <c r="P6">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
         <v>1.92</v>
       </c>
       <c r="R6">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S6">
         <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="U6">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="V6">
         <v>1.08</v>
       </c>
       <c r="W6">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="X6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="Y6">
         <v>34</v>
@@ -1989,34 +1989,34 @@
         <v>420</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>610</v>
       </c>
       <c r="AB6">
         <v>7.8</v>
       </c>
       <c r="AC6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AE6">
-        <v>310</v>
+        <v>270</v>
       </c>
       <c r="AF6">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AG6">
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI6">
         <v>470</v>
       </c>
       <c r="AJ6">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AK6">
         <v>18</v>
@@ -2025,127 +2025,127 @@
         <v>60</v>
       </c>
       <c r="AM6">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="AN6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AP6">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ6">
         <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT6">
+        <v>6.4</v>
+      </c>
+      <c r="AU6">
+        <v>9</v>
+      </c>
+      <c r="AV6">
+        <v>14.5</v>
+      </c>
+      <c r="AW6">
         <v>6.2</v>
       </c>
-      <c r="AU6">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV6">
-        <v>8</v>
-      </c>
-      <c r="AW6">
-        <v>7.4</v>
-      </c>
       <c r="AX6">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AY6">
         <v>9.6</v>
       </c>
       <c r="AZ6">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB6">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC6">
         <v>14</v>
       </c>
       <c r="BD6">
-        <v>8</v>
+        <v>17.5</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG6">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
         <v>3.75</v>
       </c>
       <c r="BI6">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BO6">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BP6">
+        <v>8.4</v>
+      </c>
+      <c r="BQ6">
+        <v>6</v>
+      </c>
+      <c r="BR6">
+        <v>29</v>
+      </c>
+      <c r="BS6">
         <v>8.199999999999999</v>
       </c>
-      <c r="BQ6">
-        <v>4.5</v>
-      </c>
-      <c r="BR6">
-        <v>32</v>
-      </c>
-      <c r="BS6">
-        <v>7.6</v>
-      </c>
       <c r="BT6">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BU6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="CA6">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB6" t="s">
         <v>116</v>
@@ -2168,52 +2168,52 @@
         <v>111</v>
       </c>
       <c r="F7">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G7">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
         <v>4.1</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L7">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M7">
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O7">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P7">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q7">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R7">
         <v>1.21</v>
       </c>
       <c r="S7">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T7">
         <v>2.08</v>
       </c>
       <c r="U7">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V7">
         <v>1.3</v>
@@ -2228,10 +2228,10 @@
         <v>12</v>
       </c>
       <c r="Z7">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA7">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -2240,46 +2240,46 @@
         <v>7</v>
       </c>
       <c r="AD7">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE7">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AF7">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG7">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
         <v>23</v>
       </c>
       <c r="AI7">
-        <v>380</v>
+        <v>190</v>
       </c>
       <c r="AJ7">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="AK7">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AL7">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AM7">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN7">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AO7">
         <v>600</v>
       </c>
       <c r="AP7">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ7">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR7">
         <v>22</v>
@@ -2294,10 +2294,10 @@
         <v>6.2</v>
       </c>
       <c r="AV7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW7">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX7">
         <v>10.5</v>
@@ -2309,19 +2309,19 @@
         <v>19.5</v>
       </c>
       <c r="BA7">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="BB7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7">
         <v>23</v>
       </c>
       <c r="BD7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE7">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="BF7">
         <v>23</v>
@@ -2330,64 +2330,64 @@
         <v>65</v>
       </c>
       <c r="BH7">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="BI7">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BJ7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BK7">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BN7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO7">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="BP7">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ7">
+        <v>5.4</v>
+      </c>
+      <c r="BR7">
+        <v>46</v>
+      </c>
+      <c r="BS7">
+        <v>6.4</v>
+      </c>
+      <c r="BT7">
+        <v>7.4</v>
+      </c>
+      <c r="BU7">
         <v>6</v>
-      </c>
-      <c r="BR7">
-        <v>1000</v>
-      </c>
-      <c r="BS7">
-        <v>7</v>
-      </c>
-      <c r="BT7">
-        <v>8</v>
-      </c>
-      <c r="BU7">
-        <v>5.5</v>
       </c>
       <c r="BV7">
         <v>46</v>
       </c>
       <c r="BW7">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY7">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ7">
         <v>55</v>
       </c>
       <c r="CA7">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="CB7" t="s">
         <v>116</v>
@@ -2410,85 +2410,85 @@
         <v>112</v>
       </c>
       <c r="F8">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="G8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H8">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I8">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="J8">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
         <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
         <v>5.3</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R8">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="S8">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T8">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="U8">
         <v>2.56</v>
       </c>
       <c r="V8">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X8">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA8">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="AB8">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC8">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
         <v>25</v>
       </c>
       <c r="AF8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG8">
         <v>14</v>
@@ -2500,37 +2500,37 @@
         <v>32</v>
       </c>
       <c r="AJ8">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="AK8">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AL8">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AM8">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AN8">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO8">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ8">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR8">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS8">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="AT8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU8">
         <v>8</v>
@@ -2545,85 +2545,85 @@
         <v>19</v>
       </c>
       <c r="AY8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BB8">
+        <v>29</v>
+      </c>
+      <c r="BC8">
+        <v>21</v>
+      </c>
+      <c r="BD8">
         <v>18</v>
       </c>
-      <c r="BC8">
-        <v>13.5</v>
-      </c>
-      <c r="BD8">
-        <v>15</v>
-      </c>
       <c r="BE8">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="BF8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BI8">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BN8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BO8">
         <v>5</v>
       </c>
       <c r="BP8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ8">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BR8">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BS8">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BT8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BV8">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BX8">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="BY8">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>113</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G9">
         <v>2.16</v>
@@ -2664,73 +2664,73 @@
         <v>4.2</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O9">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P9">
         <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="R9">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S9">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="T9">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
         <v>1.86</v>
       </c>
       <c r="X9">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="Y9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z9">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AA9">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC9">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD9">
         <v>17.5</v>
       </c>
       <c r="AE9">
-        <v>290</v>
+        <v>65</v>
       </c>
       <c r="AF9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG9">
         <v>12</v>
@@ -2739,7 +2739,7 @@
         <v>18</v>
       </c>
       <c r="AI9">
-        <v>390</v>
+        <v>75</v>
       </c>
       <c r="AJ9">
         <v>27</v>
@@ -2748,40 +2748,40 @@
         <v>22</v>
       </c>
       <c r="AL9">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM9">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN9">
+        <v>14</v>
+      </c>
+      <c r="AO9">
+        <v>50</v>
+      </c>
+      <c r="AP9">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9">
         <v>13</v>
-      </c>
-      <c r="AO9">
-        <v>230</v>
-      </c>
-      <c r="AP9">
-        <v>14</v>
-      </c>
-      <c r="AQ9">
-        <v>13.5</v>
       </c>
       <c r="AR9">
         <v>22</v>
       </c>
       <c r="AS9">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="AT9">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU9">
         <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW9">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2793,7 +2793,7 @@
         <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB9">
         <v>21</v>
@@ -2802,25 +2802,25 @@
         <v>17.5</v>
       </c>
       <c r="BD9">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BE9">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="BF9">
         <v>10.5</v>
       </c>
       <c r="BG9">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BH9">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BI9">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BK9">
         <v>4.9</v>
@@ -2838,13 +2838,13 @@
         <v>4</v>
       </c>
       <c r="BP9">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BQ9">
         <v>6</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BS9">
         <v>7.4</v>
@@ -2865,10 +2865,10 @@
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CA9">
         <v>7</v>
@@ -2897,16 +2897,16 @@
         <v>1.51</v>
       </c>
       <c r="G10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H10">
         <v>7.6</v>
       </c>
       <c r="I10">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K10">
         <v>4.7</v>
@@ -2918,19 +2918,19 @@
         <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O10">
         <v>1.34</v>
       </c>
       <c r="P10">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q10">
         <v>2.02</v>
       </c>
       <c r="R10">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S10">
         <v>3.6</v>
@@ -2939,25 +2939,25 @@
         <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V10">
         <v>1.12</v>
       </c>
       <c r="W10">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="X10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z10">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AA10">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AB10">
         <v>7.4</v>
@@ -2969,7 +2969,7 @@
         <v>32</v>
       </c>
       <c r="AE10">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="AF10">
         <v>8.6</v>
@@ -2978,142 +2978,142 @@
         <v>10.5</v>
       </c>
       <c r="AH10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI10">
-        <v>160</v>
+        <v>470</v>
       </c>
       <c r="AJ10">
         <v>14</v>
       </c>
       <c r="AK10">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL10">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AM10">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="AN10">
         <v>9.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>260</v>
+        <v>350</v>
       </c>
       <c r="AP10">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10">
         <v>19.5</v>
       </c>
       <c r="AR10">
+        <v>46</v>
+      </c>
+      <c r="AS10">
+        <v>10.5</v>
+      </c>
+      <c r="AT10">
+        <v>6.4</v>
+      </c>
+      <c r="AU10">
         <v>8.6</v>
       </c>
-      <c r="AS10">
-        <v>9.4</v>
-      </c>
-      <c r="AT10">
-        <v>6.2</v>
-      </c>
-      <c r="AU10">
-        <v>7.6</v>
-      </c>
       <c r="AV10">
-        <v>7.4</v>
+        <v>22</v>
       </c>
       <c r="AW10">
-        <v>9.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AX10">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY10">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="BB10">
+        <v>11.5</v>
+      </c>
+      <c r="BC10">
+        <v>15</v>
+      </c>
+      <c r="BD10">
+        <v>25</v>
+      </c>
+      <c r="BE10">
         <v>10.5</v>
       </c>
-      <c r="BC10">
+      <c r="BF10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH10">
+        <v>3.8</v>
+      </c>
+      <c r="BI10">
+        <v>2.82</v>
+      </c>
+      <c r="BJ10">
         <v>13.5</v>
       </c>
-      <c r="BD10">
-        <v>8</v>
-      </c>
-      <c r="BE10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF10">
-        <v>7.4</v>
-      </c>
-      <c r="BG10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH10">
-        <v>3.45</v>
-      </c>
-      <c r="BI10">
-        <v>2.78</v>
-      </c>
-      <c r="BJ10">
-        <v>12</v>
-      </c>
       <c r="BK10">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="BN10">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="BO10">
         <v>3.15</v>
       </c>
       <c r="BP10">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BQ10">
-        <v>5.7</v>
+        <v>3.85</v>
       </c>
       <c r="BR10">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BS10">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BT10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BU10">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BW10">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY10">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BZ10">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="CA10">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="CB10" t="s">
         <v>116</v>
@@ -3139,13 +3139,13 @@
         <v>2.08</v>
       </c>
       <c r="G11">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3166,43 +3166,43 @@
         <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q11">
         <v>2.24</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T11">
         <v>1.92</v>
       </c>
       <c r="U11">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V11">
         <v>1.29</v>
       </c>
       <c r="W11">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="X11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z11">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB11">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC11">
         <v>8</v>
@@ -3214,10 +3214,10 @@
         <v>65</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH11">
         <v>25</v>
@@ -3226,7 +3226,7 @@
         <v>75</v>
       </c>
       <c r="AJ11">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK11">
         <v>29</v>
@@ -3241,121 +3241,121 @@
         <v>22</v>
       </c>
       <c r="AO11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP11">
         <v>10</v>
       </c>
       <c r="AQ11">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR11">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="AS11">
-        <v>5.8</v>
+        <v>70</v>
       </c>
       <c r="AT11">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU11">
         <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW11">
-        <v>5.5</v>
+        <v>42</v>
       </c>
       <c r="AX11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY11">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="BB11">
         <v>21</v>
       </c>
       <c r="BC11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD11">
-        <v>5.4</v>
+        <v>32</v>
       </c>
       <c r="BE11">
-        <v>5.9</v>
+        <v>90</v>
       </c>
       <c r="BF11">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG11">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="BH11">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI11">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11">
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BN11">
         <v>4.9</v>
       </c>
       <c r="BO11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP11">
         <v>16.5</v>
       </c>
       <c r="BQ11">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR11">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS11">
+        <v>8</v>
+      </c>
+      <c r="BT11">
         <v>7.6</v>
       </c>
-      <c r="BT11">
-        <v>7.8</v>
-      </c>
       <c r="BU11">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BV11">
         <v>40</v>
       </c>
       <c r="BW11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX11">
         <v>55</v>
       </c>
       <c r="BY11">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ11">
         <v>34</v>
       </c>
       <c r="CA11">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="CB11" t="s">
         <v>116</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -364,7 +364,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-04 09:01:53</t>
+    <t>2026-08-04 11:09:02</t>
   </si>
 </sst>
 </file>
@@ -961,19 +961,19 @@
         <v>2.52</v>
       </c>
       <c r="G2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I2">
         <v>3.35</v>
       </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L2">
         <v>1.49</v>
@@ -988,7 +988,7 @@
         <v>1.43</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q2">
         <v>2.28</v>
@@ -997,37 +997,37 @@
         <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T2">
         <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V2">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W2">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y2">
         <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB2">
         <v>9.6</v>
       </c>
       <c r="AC2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
         <v>15</v>
@@ -1039,13 +1039,13 @@
         <v>17</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI2">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
         <v>42</v>
@@ -1054,7 +1054,7 @@
         <v>34</v>
       </c>
       <c r="AL2">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM2">
         <v>450</v>
@@ -1066,112 +1066,112 @@
         <v>48</v>
       </c>
       <c r="AP2">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AQ2">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AR2">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS2">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="AT2">
+        <v>7.6</v>
+      </c>
+      <c r="AU2">
+        <v>4.1</v>
+      </c>
+      <c r="AV2">
+        <v>7.6</v>
+      </c>
+      <c r="AW2">
+        <v>7.2</v>
+      </c>
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
         <v>7</v>
       </c>
-      <c r="AU2">
-        <v>5.8</v>
-      </c>
-      <c r="AV2">
-        <v>11</v>
-      </c>
-      <c r="AW2">
-        <v>29</v>
-      </c>
-      <c r="AX2">
-        <v>12</v>
-      </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
       <c r="AZ2">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="BA2">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="BB2">
-        <v>26</v>
+        <v>7.4</v>
       </c>
       <c r="BC2">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>7.4</v>
       </c>
       <c r="BE2">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BG2">
-        <v>29</v>
+        <v>7.2</v>
       </c>
       <c r="BH2">
         <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="BJ2">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BN2">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO2">
         <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BQ2">
+        <v>4.6</v>
+      </c>
+      <c r="BR2">
+        <v>38</v>
+      </c>
+      <c r="BS2">
+        <v>4.9</v>
+      </c>
+      <c r="BT2">
+        <v>6.4</v>
+      </c>
+      <c r="BU2">
+        <v>3</v>
+      </c>
+      <c r="BV2">
+        <v>34</v>
+      </c>
+      <c r="BW2">
+        <v>4.9</v>
+      </c>
+      <c r="BX2">
+        <v>55</v>
+      </c>
+      <c r="BY2">
         <v>5.1</v>
-      </c>
-      <c r="BR2">
-        <v>40</v>
-      </c>
-      <c r="BS2">
-        <v>5.7</v>
-      </c>
-      <c r="BT2">
-        <v>7.4</v>
-      </c>
-      <c r="BU2">
-        <v>3.5</v>
-      </c>
-      <c r="BV2">
-        <v>29</v>
-      </c>
-      <c r="BW2">
-        <v>5.4</v>
-      </c>
-      <c r="BX2">
-        <v>44</v>
-      </c>
-      <c r="BY2">
-        <v>5.7</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1200,34 +1200,34 @@
         <v>107</v>
       </c>
       <c r="F3">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="G3">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="I3">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="J3">
         <v>2.68</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3">
         <v>1.67</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="P3">
         <v>1.4</v>
@@ -1236,91 +1236,91 @@
         <v>3</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S3">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="T3">
         <v>2.26</v>
       </c>
       <c r="U3">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="X3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="Y3">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z3">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA3">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="AB3">
-        <v>7.8</v>
+        <v>970</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE3">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AF3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AG3">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI3">
         <v>310</v>
       </c>
       <c r="AJ3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AK3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL3">
-        <v>240</v>
+        <v>500</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO3">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AP3">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ3">
         <v>6.2</v>
       </c>
       <c r="AR3">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="AT3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AU3">
         <v>5.7</v>
@@ -1329,97 +1329,97 @@
         <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AX3">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ3">
         <v>19.5</v>
       </c>
       <c r="BA3">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BB3">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC3">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="BD3">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE3">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BF3">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG3">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="BH3">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="BI3">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="BJ3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="BN3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BQ3">
+        <v>4.5</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
         <v>4.8</v>
       </c>
-      <c r="BR3">
-        <v>75</v>
-      </c>
-      <c r="BS3">
-        <v>5.2</v>
-      </c>
       <c r="BT3">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BU3">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW3">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="BZ3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="CB3" t="s">
         <v>116</v>
@@ -1442,16 +1442,16 @@
         <v>108</v>
       </c>
       <c r="F4">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="G4">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="H4">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="I4">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="J4">
         <v>4.7</v>
@@ -1460,7 +1460,7 @@
         <v>5</v>
       </c>
       <c r="L4">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M4">
         <v>1.02</v>
@@ -1478,64 +1478,64 @@
         <v>1.38</v>
       </c>
       <c r="R4">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T4">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="U4">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="V4">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="W4">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X4">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Y4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AA4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB4">
         <v>32</v>
       </c>
       <c r="AC4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AF4">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AK4">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AL4">
         <v>38</v>
@@ -1544,124 +1544,124 @@
         <v>48</v>
       </c>
       <c r="AN4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AP4">
         <v>32</v>
       </c>
       <c r="AQ4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS4">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AT4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AU4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW4">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX4">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AY4">
         <v>16.5</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BB4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BC4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ4">
         <v>8.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BL4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM4">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BN4">
         <v>10.5</v>
       </c>
       <c r="BO4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BP4">
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BR4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS4">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BT4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU4">
         <v>4.8</v>
       </c>
       <c r="BV4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BW4">
-        <v>4.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX4">
         <v>18.5</v>
       </c>
       <c r="BY4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BZ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA4">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="s">
         <v>116</v>
@@ -1684,16 +1684,16 @@
         <v>109</v>
       </c>
       <c r="F5">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="G5">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H5">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="I5">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="J5">
         <v>4.4</v>
@@ -1708,61 +1708,61 @@
         <v>1.02</v>
       </c>
       <c r="N5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O5">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P5">
         <v>3.4</v>
       </c>
       <c r="Q5">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S5">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="T5">
         <v>1.39</v>
       </c>
       <c r="U5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V5">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="X5">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="Y5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Z5">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AA5">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AB5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC5">
         <v>12.5</v>
       </c>
       <c r="AD5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE5">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AF5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
@@ -1771,25 +1771,25 @@
         <v>15</v>
       </c>
       <c r="AI5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ5">
         <v>32</v>
       </c>
       <c r="AK5">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AL5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM5">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AN5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AO5">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AP5">
         <v>32</v>
@@ -1798,10 +1798,10 @@
         <v>25</v>
       </c>
       <c r="AR5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AT5">
         <v>18.5</v>
@@ -1810,40 +1810,40 @@
         <v>10.5</v>
       </c>
       <c r="AV5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
         <v>12.5</v>
       </c>
       <c r="BA5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BB5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC5">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BE5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BF5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG5">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BH5">
         <v>6.4</v>
@@ -1852,52 +1852,52 @@
         <v>4.5</v>
       </c>
       <c r="BJ5">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BK5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BN5">
         <v>6.2</v>
       </c>
       <c r="BO5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BQ5">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BR5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BS5">
-        <v>13.5</v>
+        <v>5.6</v>
       </c>
       <c r="BT5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BV5">
+        <v>22</v>
+      </c>
+      <c r="BW5">
+        <v>5.8</v>
+      </c>
+      <c r="BX5">
         <v>24</v>
       </c>
-      <c r="BW5">
-        <v>5.4</v>
-      </c>
-      <c r="BX5">
-        <v>26</v>
-      </c>
       <c r="BY5">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1929,16 +1929,16 @@
         <v>1.39</v>
       </c>
       <c r="G6">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
         <v>5.2</v>
@@ -1950,16 +1950,16 @@
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q6">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R6">
         <v>1.38</v>
@@ -1968,19 +1968,19 @@
         <v>3.3</v>
       </c>
       <c r="T6">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U6">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="V6">
         <v>1.08</v>
       </c>
       <c r="W6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X6">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y6">
         <v>34</v>
@@ -1989,49 +1989,49 @@
         <v>420</v>
       </c>
       <c r="AA6">
-        <v>610</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AE6">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AF6">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AG6">
         <v>12</v>
       </c>
       <c r="AH6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI6">
         <v>470</v>
       </c>
       <c r="AJ6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK6">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL6">
         <v>60</v>
       </c>
       <c r="AM6">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AN6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO6">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="AP6">
         <v>13</v>
@@ -2040,34 +2040,34 @@
         <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AS6">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6">
         <v>6.4</v>
       </c>
       <c r="AU6">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6">
         <v>14.5</v>
       </c>
       <c r="AW6">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX6">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AY6">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="BA6">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB6">
         <v>9.199999999999999</v>
@@ -2079,73 +2079,73 @@
         <v>17.5</v>
       </c>
       <c r="BE6">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF6">
         <v>6</v>
       </c>
       <c r="BG6">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH6">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BI6">
         <v>2.88</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>3.85</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="BN6">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BO6">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BP6">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ6">
         <v>6</v>
       </c>
       <c r="BR6">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BS6">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BT6">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BU6">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="BW6">
-        <v>10.5</v>
+        <v>4.9</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BZ6">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="CA6">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="CB6" t="s">
         <v>116</v>
@@ -2171,7 +2171,7 @@
         <v>2.22</v>
       </c>
       <c r="G7">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H7">
         <v>4.1</v>
@@ -2183,46 +2183,46 @@
         <v>3.05</v>
       </c>
       <c r="K7">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="M7">
         <v>1.13</v>
       </c>
       <c r="N7">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O7">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q7">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="R7">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S7">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T7">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V7">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W7">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>12</v>
@@ -2243,46 +2243,46 @@
         <v>18</v>
       </c>
       <c r="AE7">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG7">
         <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI7">
-        <v>190</v>
+        <v>100</v>
       </c>
       <c r="AJ7">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK7">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL7">
         <v>65</v>
       </c>
       <c r="AM7">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AN7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO7">
         <v>600</v>
       </c>
       <c r="AP7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7">
         <v>10</v>
       </c>
       <c r="AR7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS7">
         <v>70</v>
@@ -2294,7 +2294,7 @@
         <v>6.2</v>
       </c>
       <c r="AV7">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW7">
         <v>48</v>
@@ -2306,10 +2306,10 @@
         <v>10</v>
       </c>
       <c r="AZ7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BB7">
         <v>23</v>
@@ -2318,76 +2318,76 @@
         <v>23</v>
       </c>
       <c r="BD7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE7">
         <v>100</v>
       </c>
       <c r="BF7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG7">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BH7">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI7">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BK7">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO7">
         <v>4.1</v>
       </c>
       <c r="BP7">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BQ7">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BR7">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BS7">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BT7">
+        <v>7.6</v>
+      </c>
+      <c r="BU7">
+        <v>6.2</v>
+      </c>
+      <c r="BV7">
+        <v>42</v>
+      </c>
+      <c r="BW7">
+        <v>7.2</v>
+      </c>
+      <c r="BX7">
+        <v>65</v>
+      </c>
+      <c r="BY7">
+        <v>7.8</v>
+      </c>
+      <c r="BZ7">
+        <v>48</v>
+      </c>
+      <c r="CA7">
         <v>7.4</v>
-      </c>
-      <c r="BU7">
-        <v>6</v>
-      </c>
-      <c r="BV7">
-        <v>46</v>
-      </c>
-      <c r="BW7">
-        <v>6.4</v>
-      </c>
-      <c r="BX7">
-        <v>70</v>
-      </c>
-      <c r="BY7">
-        <v>6.6</v>
-      </c>
-      <c r="BZ7">
-        <v>55</v>
-      </c>
-      <c r="CA7">
-        <v>6.6</v>
       </c>
       <c r="CB7" t="s">
         <v>116</v>
@@ -2410,7 +2410,7 @@
         <v>112</v>
       </c>
       <c r="F8">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G8">
         <v>3.05</v>
@@ -2440,22 +2440,22 @@
         <v>1.2</v>
       </c>
       <c r="P8">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q8">
         <v>1.63</v>
       </c>
       <c r="R8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S8">
         <v>2.56</v>
       </c>
       <c r="T8">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U8">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V8">
         <v>1.6</v>
@@ -2470,7 +2470,7 @@
         <v>16.5</v>
       </c>
       <c r="Z8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA8">
         <v>42</v>
@@ -2479,7 +2479,7 @@
         <v>18</v>
       </c>
       <c r="AC8">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
@@ -2503,10 +2503,10 @@
         <v>46</v>
       </c>
       <c r="AK8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL8">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM8">
         <v>75</v>
@@ -2515,7 +2515,7 @@
         <v>19</v>
       </c>
       <c r="AO8">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP8">
         <v>19.5</v>
@@ -2530,10 +2530,10 @@
         <v>28</v>
       </c>
       <c r="AT8">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV8">
         <v>9.800000000000001</v>
@@ -2560,7 +2560,7 @@
         <v>21</v>
       </c>
       <c r="BD8">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BE8">
         <v>46</v>
@@ -2569,10 +2569,10 @@
         <v>14.5</v>
       </c>
       <c r="BG8">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH8">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BI8">
         <v>3.45</v>
@@ -2602,10 +2602,10 @@
         <v>4.4</v>
       </c>
       <c r="BR8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BS8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BT8">
         <v>6.8</v>
@@ -2620,7 +2620,7 @@
         <v>4.3</v>
       </c>
       <c r="BX8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY8">
         <v>4.6</v>
@@ -2652,7 +2652,7 @@
         <v>113</v>
       </c>
       <c r="F9">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G9">
         <v>2.16</v>
@@ -2664,61 +2664,61 @@
         <v>4.2</v>
       </c>
       <c r="J9">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
         <v>2.12</v>
       </c>
       <c r="Q9">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S9">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="U9">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V9">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W9">
         <v>1.86</v>
       </c>
       <c r="X9">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y9">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z9">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA9">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AB9">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AC9">
         <v>8.800000000000001</v>
@@ -2727,7 +2727,7 @@
         <v>17.5</v>
       </c>
       <c r="AE9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF9">
         <v>14</v>
@@ -2748,22 +2748,22 @@
         <v>22</v>
       </c>
       <c r="AL9">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM9">
         <v>200</v>
       </c>
       <c r="AN9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AP9">
+        <v>15.5</v>
+      </c>
+      <c r="AQ9">
         <v>13.5</v>
-      </c>
-      <c r="AQ9">
-        <v>13</v>
       </c>
       <c r="AR9">
         <v>22</v>
@@ -2772,7 +2772,7 @@
         <v>50</v>
       </c>
       <c r="AT9">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU9">
         <v>7.4</v>
@@ -2784,52 +2784,52 @@
         <v>27</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY9">
         <v>9.4</v>
       </c>
       <c r="AZ9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA9">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BB9">
         <v>21</v>
       </c>
       <c r="BC9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD9">
         <v>23</v>
       </c>
       <c r="BE9">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF9">
         <v>10.5</v>
       </c>
       <c r="BG9">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="BH9">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BI9">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ9">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK9">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
@@ -2838,16 +2838,16 @@
         <v>4</v>
       </c>
       <c r="BP9">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BQ9">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR9">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT9">
         <v>7.6</v>
@@ -2859,16 +2859,16 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ9">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="CA9">
         <v>7</v>
@@ -2906,10 +2906,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
         <v>1.42</v>
@@ -2939,16 +2939,16 @@
         <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V10">
         <v>1.12</v>
       </c>
       <c r="W10">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="X10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y10">
         <v>23</v>
@@ -2969,7 +2969,7 @@
         <v>32</v>
       </c>
       <c r="AE10">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AF10">
         <v>8.6</v>
@@ -2990,7 +2990,7 @@
         <v>18</v>
       </c>
       <c r="AL10">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AM10">
         <v>390</v>
@@ -2999,19 +2999,19 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO10">
-        <v>350</v>
+        <v>240</v>
       </c>
       <c r="AP10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ10">
         <v>19.5</v>
       </c>
       <c r="AR10">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="AS10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT10">
         <v>6.4</v>
@@ -3020,13 +3020,13 @@
         <v>8.6</v>
       </c>
       <c r="AV10">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AW10">
-        <v>34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY10">
         <v>8.800000000000001</v>
@@ -3035,10 +3035,10 @@
         <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>29</v>
+        <v>9.6</v>
       </c>
       <c r="BB10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC10">
         <v>15</v>
@@ -3047,34 +3047,34 @@
         <v>25</v>
       </c>
       <c r="BE10">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI10">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10">
         <v>13.5</v>
       </c>
       <c r="BK10">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BN10">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO10">
         <v>3.15</v>
@@ -3083,37 +3083,37 @@
         <v>11.5</v>
       </c>
       <c r="BQ10">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BR10">
         <v>34</v>
       </c>
       <c r="BS10">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BT10">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BU10">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BV10">
         <v>90</v>
       </c>
       <c r="BW10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BX10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BY10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ10">
         <v>24</v>
       </c>
       <c r="CA10">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB10" t="s">
         <v>116</v>
@@ -3136,16 +3136,16 @@
         <v>115</v>
       </c>
       <c r="F11">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G11">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
         <v>4.2</v>
-      </c>
-      <c r="I11">
-        <v>4.4</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3169,28 +3169,28 @@
         <v>1.75</v>
       </c>
       <c r="Q11">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R11">
         <v>1.28</v>
       </c>
       <c r="S11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T11">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U11">
         <v>1.97</v>
       </c>
       <c r="V11">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="X11">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y11">
         <v>14</v>
@@ -3208,19 +3208,19 @@
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE11">
         <v>65</v>
       </c>
       <c r="AF11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG11">
         <v>11.5</v>
       </c>
       <c r="AH11">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI11">
         <v>75</v>
@@ -3229,19 +3229,19 @@
         <v>27</v>
       </c>
       <c r="AK11">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL11">
         <v>46</v>
       </c>
       <c r="AM11">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO11">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP11">
         <v>10</v>
@@ -3253,7 +3253,7 @@
         <v>23</v>
       </c>
       <c r="AS11">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AT11">
         <v>7.4</v>
@@ -3262,10 +3262,10 @@
         <v>6.8</v>
       </c>
       <c r="AV11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3277,7 +3277,7 @@
         <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BB11">
         <v>21</v>
@@ -3289,13 +3289,13 @@
         <v>32</v>
       </c>
       <c r="BE11">
-        <v>90</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11">
         <v>17.5</v>
       </c>
       <c r="BG11">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BH11">
         <v>3.2</v>
@@ -3307,10 +3307,10 @@
         <v>11</v>
       </c>
       <c r="BK11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM11">
         <v>10</v>
@@ -3331,31 +3331,31 @@
         <v>36</v>
       </c>
       <c r="BS11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT11">
         <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="BV11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BW11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX11">
         <v>55</v>
       </c>
       <c r="BY11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ11">
         <v>34</v>
       </c>
       <c r="CA11">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB11" t="s">
         <v>116</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-04.xlsx
@@ -364,7 +364,7 @@
     <t>Ind Medellin</t>
   </si>
   <si>
-    <t>2026-08-04 11:09:02</t>
+    <t>2026-08-04 13:15:54</t>
   </si>
 </sst>
 </file>
@@ -958,220 +958,220 @@
         <v>106</v>
       </c>
       <c r="F2">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="G2">
-        <v>2.68</v>
+        <v>1.27</v>
       </c>
       <c r="H2">
-        <v>3.1</v>
+        <v>21</v>
       </c>
       <c r="I2">
-        <v>3.35</v>
+        <v>25</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>6.4</v>
       </c>
       <c r="L2">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="P2">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
-        <v>2.28</v>
+        <v>2.72</v>
       </c>
       <c r="R2">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="S2">
-        <v>4.4</v>
+        <v>7.8</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="U2">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="V2">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
-        <v>1.59</v>
+        <v>4.6</v>
       </c>
       <c r="X2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>3.65</v>
       </c>
       <c r="AC2">
         <v>7.6</v>
       </c>
       <c r="AD2">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="AE2">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="AF2">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AH2">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="AI2">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="AJ2">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="AK2">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AM2">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
         <v>32</v>
       </c>
       <c r="AO2">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>5.6</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="AR2">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="AS2">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT2">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="AU2">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="AW2">
-        <v>7.2</v>
+        <v>150</v>
       </c>
       <c r="AX2">
+        <v>4.3</v>
+      </c>
+      <c r="AY2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ2">
+        <v>36</v>
+      </c>
+      <c r="BA2">
+        <v>170</v>
+      </c>
+      <c r="BB2">
         <v>11.5</v>
       </c>
-      <c r="AY2">
-        <v>7</v>
-      </c>
-      <c r="AZ2">
-        <v>8.4</v>
-      </c>
-      <c r="BA2">
-        <v>7.6</v>
-      </c>
-      <c r="BB2">
-        <v>7.4</v>
-      </c>
       <c r="BC2">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BD2">
-        <v>7.4</v>
+        <v>75</v>
       </c>
       <c r="BE2">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="BF2">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BG2">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BH2">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1200,88 +1200,88 @@
         <v>107</v>
       </c>
       <c r="F3">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="G3">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="H3">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="I3">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J3">
         <v>2.68</v>
       </c>
       <c r="K3">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L3">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M3">
         <v>1.16</v>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O3">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="P3">
         <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="R3">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S3">
         <v>6</v>
       </c>
       <c r="T3">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="U3">
         <v>1.62</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W3">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X3">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Y3">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>22</v>
       </c>
       <c r="AA3">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AE3">
-        <v>65</v>
+        <v>200</v>
       </c>
       <c r="AF3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH3">
         <v>32</v>
@@ -1293,7 +1293,7 @@
         <v>150</v>
       </c>
       <c r="AK3">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AL3">
         <v>500</v>
@@ -1302,124 +1302,124 @@
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AO3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP3">
         <v>5.9</v>
       </c>
       <c r="AQ3">
+        <v>6.8</v>
+      </c>
+      <c r="AR3">
+        <v>15.5</v>
+      </c>
+      <c r="AS3">
+        <v>5.4</v>
+      </c>
+      <c r="AT3">
         <v>6.2</v>
-      </c>
-      <c r="AR3">
-        <v>14.5</v>
-      </c>
-      <c r="AS3">
-        <v>4.2</v>
-      </c>
-      <c r="AT3">
-        <v>6.4</v>
       </c>
       <c r="AU3">
         <v>5.7</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW3">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX3">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY3">
         <v>11.5</v>
       </c>
       <c r="AZ3">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB3">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC3">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BD3">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE3">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BF3">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG3">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH3">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BI3">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="BJ3">
         <v>14.5</v>
       </c>
       <c r="BK3">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BN3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BP3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BQ3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BT3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BV3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BW3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB3" t="s">
         <v>116</v>
@@ -1442,19 +1442,19 @@
         <v>108</v>
       </c>
       <c r="F4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I4">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -1466,49 +1466,49 @@
         <v>1.02</v>
       </c>
       <c r="N4">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q4">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="T4">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U4">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="V4">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W4">
         <v>1.27</v>
       </c>
       <c r="X4">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Z4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA4">
         <v>22</v>
       </c>
       <c r="AB4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AC4">
         <v>13</v>
@@ -1517,7 +1517,7 @@
         <v>10.5</v>
       </c>
       <c r="AE4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AF4">
         <v>46</v>
@@ -1526,16 +1526,16 @@
         <v>21</v>
       </c>
       <c r="AH4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI4">
         <v>21</v>
       </c>
       <c r="AJ4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AK4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL4">
         <v>38</v>
@@ -1544,25 +1544,25 @@
         <v>48</v>
       </c>
       <c r="AN4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO4">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AP4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AQ4">
         <v>17</v>
       </c>
       <c r="AR4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AS4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU4">
         <v>11.5</v>
@@ -1577,16 +1577,16 @@
         <v>42</v>
       </c>
       <c r="AY4">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AZ4">
         <v>13.5</v>
       </c>
       <c r="BA4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BB4">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BC4">
         <v>38</v>
@@ -1595,19 +1595,19 @@
         <v>32</v>
       </c>
       <c r="BE4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG4">
         <v>5</v>
       </c>
       <c r="BH4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BI4">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BJ4">
         <v>8.800000000000001</v>
@@ -1619,49 +1619,49 @@
         <v>60</v>
       </c>
       <c r="BM4">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BN4">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO4">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ4">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BR4">
         <v>28</v>
       </c>
       <c r="BS4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BT4">
         <v>5.4</v>
       </c>
       <c r="BU4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
         <v>11</v>
       </c>
       <c r="BW4">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX4">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BY4">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BZ4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB4" t="s">
         <v>116</v>
@@ -1684,19 +1684,19 @@
         <v>109</v>
       </c>
       <c r="F5">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="G5">
-        <v>2.12</v>
+        <v>1.9</v>
       </c>
       <c r="H5">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
         <v>4.9</v>
@@ -1708,196 +1708,196 @@
         <v>1.02</v>
       </c>
       <c r="N5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O5">
         <v>1.11</v>
       </c>
       <c r="P5">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q5">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R5">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S5">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="T5">
         <v>1.39</v>
       </c>
       <c r="U5">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="V5">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="X5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Z5">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AB5">
         <v>23</v>
       </c>
       <c r="AC5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD5">
+        <v>18</v>
+      </c>
+      <c r="AE5">
+        <v>40</v>
+      </c>
+      <c r="AF5">
+        <v>21</v>
+      </c>
+      <c r="AG5">
+        <v>11.5</v>
+      </c>
+      <c r="AH5">
         <v>16.5</v>
       </c>
-      <c r="AE5">
-        <v>32</v>
-      </c>
-      <c r="AF5">
-        <v>22</v>
-      </c>
-      <c r="AG5">
-        <v>12.5</v>
-      </c>
-      <c r="AH5">
-        <v>15</v>
-      </c>
       <c r="AI5">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AJ5">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AK5">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AL5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AN5">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO5">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AP5">
         <v>32</v>
       </c>
       <c r="AQ5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR5">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AS5">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AT5">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AU5">
         <v>10.5</v>
       </c>
       <c r="AV5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AX5">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AY5">
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB5">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BC5">
+        <v>13.5</v>
+      </c>
+      <c r="BD5">
+        <v>18</v>
+      </c>
+      <c r="BE5">
+        <v>34</v>
+      </c>
+      <c r="BF5">
+        <v>5.4</v>
+      </c>
+      <c r="BG5">
         <v>15.5</v>
-      </c>
-      <c r="BD5">
-        <v>19</v>
-      </c>
-      <c r="BE5">
-        <v>32</v>
-      </c>
-      <c r="BF5">
-        <v>6.6</v>
-      </c>
-      <c r="BG5">
-        <v>12</v>
       </c>
       <c r="BH5">
         <v>6.4</v>
       </c>
       <c r="BI5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BK5">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM5">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN5">
         <v>6.2</v>
       </c>
       <c r="BO5">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BP5">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="BR5">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS5">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BT5">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BV5">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BW5">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BX5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BY5">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BZ5">
         <v>0</v>
@@ -1926,64 +1926,64 @@
         <v>110</v>
       </c>
       <c r="F6">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="G6">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="H6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="K6">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M6">
         <v>1.06</v>
       </c>
       <c r="N6">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O6">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q6">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="R6">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S6">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="T6">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U6">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="V6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W6">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="X6">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="Y6">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="Z6">
         <v>420</v>
@@ -1995,82 +1995,82 @@
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AD6">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AE6">
-        <v>290</v>
+        <v>400</v>
       </c>
       <c r="AF6">
         <v>8</v>
       </c>
       <c r="AG6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AI6">
         <v>470</v>
       </c>
       <c r="AJ6">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AM6">
-        <v>230</v>
+        <v>320</v>
       </c>
       <c r="AN6">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO6">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="AR6">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS6">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT6">
         <v>6.4</v>
       </c>
       <c r="AU6">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AV6">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW6">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AX6">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AY6">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
         <v>14</v>
       </c>
       <c r="BA6">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB6">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC6">
         <v>14</v>
@@ -2079,73 +2079,73 @@
         <v>17.5</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF6">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="BG6">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI6">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="BJ6">
         <v>16</v>
       </c>
       <c r="BK6">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BN6">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BO6">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BP6">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ6">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="BR6">
         <v>34</v>
       </c>
       <c r="BS6">
+        <v>4.9</v>
+      </c>
+      <c r="BT6">
+        <v>19.5</v>
+      </c>
+      <c r="BU6">
         <v>4.4</v>
       </c>
-      <c r="BT6">
-        <v>17</v>
-      </c>
-      <c r="BU6">
-        <v>3.9</v>
-      </c>
       <c r="BV6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BZ6">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="CA6">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="CB6" t="s">
         <v>116</v>
@@ -2168,115 +2168,115 @@
         <v>111</v>
       </c>
       <c r="F7">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
         <v>4.1</v>
       </c>
-      <c r="I7">
-        <v>4.4</v>
-      </c>
       <c r="J7">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L7">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="M7">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N7">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="O7">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="P7">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q7">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S7">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U7">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="V7">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W7">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="Y7">
         <v>12</v>
       </c>
       <c r="Z7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA7">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD7">
         <v>18</v>
       </c>
       <c r="AE7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI7">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK7">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AL7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM7">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AN7">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO7">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="AP7">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ7">
         <v>10</v>
@@ -2285,52 +2285,52 @@
         <v>24</v>
       </c>
       <c r="AS7">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AT7">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU7">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW7">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX7">
+        <v>11</v>
+      </c>
+      <c r="AY7">
         <v>10.5</v>
       </c>
-      <c r="AY7">
-        <v>10</v>
-      </c>
       <c r="AZ7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BB7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BC7">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD7">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BE7">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BG7">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BH7">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="BI7">
         <v>2.32</v>
@@ -2342,10 +2342,10 @@
         <v>9.6</v>
       </c>
       <c r="BL7">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM7">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN7">
         <v>4.9</v>
@@ -2354,16 +2354,16 @@
         <v>4.1</v>
       </c>
       <c r="BP7">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BQ7">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BR7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BS7">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BT7">
         <v>7.6</v>
@@ -2372,22 +2372,22 @@
         <v>6.2</v>
       </c>
       <c r="BV7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW7">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BX7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY7">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BZ7">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="CA7">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB7" t="s">
         <v>116</v>
@@ -2410,7 +2410,7 @@
         <v>112</v>
       </c>
       <c r="F8">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="G8">
         <v>3.05</v>
@@ -2419,7 +2419,7 @@
         <v>2.5</v>
       </c>
       <c r="I8">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="J8">
         <v>3.6</v>
@@ -2428,58 +2428,58 @@
         <v>3.9</v>
       </c>
       <c r="L8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M8">
         <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P8">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q8">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R8">
         <v>1.57</v>
       </c>
       <c r="S8">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="T8">
         <v>1.56</v>
       </c>
       <c r="U8">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W8">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="X8">
         <v>25</v>
       </c>
       <c r="Y8">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA8">
         <v>42</v>
       </c>
       <c r="AB8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC8">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD8">
         <v>12.5</v>
@@ -2488,10 +2488,10 @@
         <v>25</v>
       </c>
       <c r="AF8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH8">
         <v>15.5</v>
@@ -2500,7 +2500,7 @@
         <v>32</v>
       </c>
       <c r="AJ8">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AK8">
         <v>36</v>
@@ -2512,10 +2512,10 @@
         <v>75</v>
       </c>
       <c r="AN8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP8">
         <v>19.5</v>
@@ -2524,25 +2524,25 @@
         <v>12.5</v>
       </c>
       <c r="AR8">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS8">
         <v>28</v>
       </c>
       <c r="AT8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW8">
         <v>19</v>
       </c>
       <c r="AX8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY8">
         <v>10.5</v>
@@ -2557,37 +2557,37 @@
         <v>29</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD8">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE8">
         <v>46</v>
       </c>
       <c r="BF8">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG8">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH8">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BI8">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8">
         <v>9.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BN8">
         <v>7.2</v>
@@ -2599,16 +2599,16 @@
         <v>23</v>
       </c>
       <c r="BQ8">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BR8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BT8">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU8">
         <v>4.6</v>
@@ -2617,13 +2617,13 @@
         <v>19.5</v>
       </c>
       <c r="BW8">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BX8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY8">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BZ8">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>113</v>
       </c>
       <c r="F9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>2.16</v>
@@ -2661,7 +2661,7 @@
         <v>3.65</v>
       </c>
       <c r="I9">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J9">
         <v>3.55</v>
@@ -2670,40 +2670,40 @@
         <v>4.1</v>
       </c>
       <c r="L9">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M9">
         <v>1.05</v>
       </c>
       <c r="N9">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q9">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R9">
         <v>1.45</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U9">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X9">
         <v>19</v>
@@ -2715,13 +2715,13 @@
         <v>36</v>
       </c>
       <c r="AA9">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AB9">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC9">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9">
         <v>17.5</v>
@@ -2736,19 +2736,19 @@
         <v>12</v>
       </c>
       <c r="AH9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ9">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK9">
         <v>22</v>
       </c>
       <c r="AL9">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AM9">
         <v>200</v>
@@ -2757,22 +2757,22 @@
         <v>13</v>
       </c>
       <c r="AO9">
-        <v>40</v>
+        <v>600</v>
       </c>
       <c r="AP9">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ9">
         <v>13.5</v>
       </c>
       <c r="AR9">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS9">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT9">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU9">
         <v>7.4</v>
@@ -2793,25 +2793,25 @@
         <v>14</v>
       </c>
       <c r="BA9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB9">
         <v>21</v>
       </c>
       <c r="BC9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE9">
         <v>55</v>
       </c>
       <c r="BF9">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG9">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BH9">
         <v>4</v>
@@ -2829,7 +2829,7 @@
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN9">
         <v>5.2</v>
@@ -2841,7 +2841,7 @@
         <v>14.5</v>
       </c>
       <c r="BQ9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR9">
         <v>1000</v>
@@ -2859,19 +2859,19 @@
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="CA9">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="CB9" t="s">
         <v>116</v>
@@ -2909,7 +2909,7 @@
         <v>4.1</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L10">
         <v>1.42</v>
@@ -2948,13 +2948,13 @@
         <v>2.7</v>
       </c>
       <c r="X10">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y10">
         <v>23</v>
       </c>
       <c r="Z10">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA10">
         <v>330</v>
@@ -2963,7 +2963,7 @@
         <v>7.4</v>
       </c>
       <c r="AC10">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD10">
         <v>32</v>
@@ -2990,7 +2990,7 @@
         <v>18</v>
       </c>
       <c r="AL10">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AM10">
         <v>390</v>
@@ -3008,22 +3008,22 @@
         <v>19.5</v>
       </c>
       <c r="AR10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT10">
         <v>6.4</v>
       </c>
       <c r="AU10">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV10">
         <v>15</v>
       </c>
       <c r="AW10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AX10">
         <v>7.4</v>
@@ -3035,7 +3035,7 @@
         <v>19.5</v>
       </c>
       <c r="BA10">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB10">
         <v>12</v>
@@ -3047,13 +3047,13 @@
         <v>25</v>
       </c>
       <c r="BE10">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF10">
         <v>8.4</v>
       </c>
       <c r="BG10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH10">
         <v>3.75</v>
@@ -3136,7 +3136,7 @@
         <v>115</v>
       </c>
       <c r="F11">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G11">
         <v>2.16</v>
@@ -3145,7 +3145,7 @@
         <v>4</v>
       </c>
       <c r="I11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
         <v>3.35</v>
@@ -3160,16 +3160,16 @@
         <v>1.09</v>
       </c>
       <c r="N11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O11">
         <v>1.4</v>
       </c>
       <c r="P11">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q11">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R11">
         <v>1.28</v>
@@ -3178,10 +3178,10 @@
         <v>4.2</v>
       </c>
       <c r="T11">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U11">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V11">
         <v>1.31</v>
@@ -3190,34 +3190,34 @@
         <v>1.86</v>
       </c>
       <c r="X11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z11">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA11">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB11">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD11">
         <v>18</v>
       </c>
       <c r="AE11">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG11">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH11">
         <v>21</v>
@@ -3226,7 +3226,7 @@
         <v>75</v>
       </c>
       <c r="AJ11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK11">
         <v>26</v>
@@ -3235,19 +3235,19 @@
         <v>46</v>
       </c>
       <c r="AM11">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN11">
         <v>21</v>
       </c>
       <c r="AO11">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP11">
         <v>10</v>
       </c>
       <c r="AQ11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR11">
         <v>23</v>
@@ -3256,46 +3256,46 @@
         <v>60</v>
       </c>
       <c r="AT11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU11">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV11">
         <v>15</v>
       </c>
       <c r="AW11">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AX11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY11">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD11">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BE11">
-        <v>9.199999999999999</v>
+        <v>90</v>
       </c>
       <c r="BF11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH11">
         <v>3.2</v>
@@ -3319,7 +3319,7 @@
         <v>4.9</v>
       </c>
       <c r="BO11">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP11">
         <v>16.5</v>
